--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134CE567-829D-4B71-9384-71E644EFE5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41600E24-F793-4DF8-962D-D38EBF946B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="1380" windowWidth="14430" windowHeight="18900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4230" yWindow="0" windowWidth="14100" windowHeight="20985" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -401,10 +401,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -742,11 +742,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-2.7619047619047601</v>
+        <v>-2.4761904761904701</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.63109523809523771</v>
+        <v>-0.56580952380952243</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -757,11 +757,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>-3.7878787878787801</v>
+        <v>5.0505050505050502</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>-0.54166666666666563</v>
+        <v>0.7222222222222221</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -772,11 +772,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>6.6889632107023395E-2</v>
+        <v>0.334448160535117</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>5.1705685618729088E-3</v>
+        <v>2.5852842809364548E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -787,11 +787,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.790330079033007</v>
+        <v>0.185960018596001</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>5.6429567642956702E-2</v>
+        <v>1.3277545327754471E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -802,11 +802,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>0.80745341614906796</v>
+        <v>2.1118012422360199</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>5.3534161490683206E-2</v>
+        <v>0.14001242236024811</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -817,11 +817,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>-2.1064301552106399</v>
+        <v>0</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.1181707317073169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -832,11 +832,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>1.1244979919678699</v>
+        <v>4.41767068273092</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>2.2377510040160611E-2</v>
+        <v>8.7911646586345302E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,11 +847,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>2.1401594628619298</v>
+        <v>-1.09106168694922</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>2.2257658413764071E-2</v>
+        <v>-1.1347041544271887E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -862,11 +862,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>0.18703241895261799</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>1.0099750623441372E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -877,11 +877,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>3.4090909090908998</v>
+        <v>2.3484848484848402</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.7727272727272682E-2</v>
+        <v>1.2212121212121169E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -892,11 +892,11 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>-1.8907563025209999</v>
+        <v>-2.1008403361344499</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-5.1050420168066999E-3</v>
+        <v>-5.6722689075630155E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,11 +907,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>0.98231827111984205</v>
+        <v>0.261951538965291</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>1.375245579567779E-3</v>
+        <v>3.6673215455140746E-4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -922,11 +922,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-0.70921985815602795</v>
+        <v>-3.5460992907801399</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-4.9645390070921956E-4</v>
+        <v>-2.4822695035460981E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>-1.1134771728681141</v>
+        <v>0.4197194289077037</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1055,14 +1055,14 @@
       <c r="A32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27" t="s">
+      <c r="C32" s="26"/>
+      <c r="D32" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="27"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="5" t="s">
         <v>68</v>
       </c>
@@ -1075,10 +1075,10 @@
         <v>98970</v>
       </c>
       <c r="C33" s="25"/>
-      <c r="D33" s="26">
+      <c r="D33" s="27">
         <v>232874657613</v>
       </c>
-      <c r="E33" s="26"/>
+      <c r="E33" s="27"/>
       <c r="F33" s="21">
         <v>1310146537</v>
       </c>
@@ -1091,10 +1091,10 @@
         <v>99051</v>
       </c>
       <c r="C34" s="25"/>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <v>227320292084</v>
       </c>
-      <c r="E34" s="26"/>
+      <c r="E34" s="27"/>
       <c r="F34" s="22">
         <v>-6072488957</v>
       </c>
@@ -1148,11 +1148,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>-4.0828402366863896</v>
+        <v>-8.2840236686390494</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.36418934911242595</v>
+        <v>-0.73893491124260324</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1163,11 +1163,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>0.29914529914529903</v>
+        <v>5.55555555555555</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>2.6354700854700847E-2</v>
+        <v>0.48944444444444402</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1178,11 +1178,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>2.1177467174925799</v>
+        <v>6.3108852181279103</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.17534942820838559</v>
+        <v>0.52254129606099087</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,11 +1193,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>-2.3684210526315699</v>
+        <v>0.61403508771929804</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.14613157894736786</v>
+        <v>3.788596491228069E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1208,11 +1208,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>-1.8907563025209999</v>
+        <v>-2.1008403361344499</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-8.9810924369747497E-2</v>
+        <v>-9.9789915966386367E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,11 +1223,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>7.9936051159072694E-2</v>
+        <v>-0.23980815347721801</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>3.5331734612310127E-3</v>
+        <v>-1.0599520383693035E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,11 +1238,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>0.52199850857568897</v>
+        <v>0.82028337061894097</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1.9679343773303475E-2</v>
+        <v>3.0924683072334074E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,11 +1253,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>0.49455984174084999</v>
+        <v>-2.8288822947576602</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>1.78041543026706E-2</v>
+        <v>-0.10183976261127578</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,11 +1268,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>6.0132291040288603E-2</v>
+        <v>0.300661455201443</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>2.0264582080577261E-3</v>
+        <v>1.013229104028863E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,11 +1283,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-1.79640718562874</v>
+        <v>-3.7125748502993998</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-4.8143712574850242E-2</v>
+        <v>-9.9497005988023926E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,11 +1298,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-2.8571428571428501</v>
+        <v>-2.4761904761904701</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-7.3714285714285538E-2</v>
+        <v>-6.3885714285714129E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,11 +1328,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>1.2048192771084301</v>
+        <v>4.41767068273092</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>2.4698795180722811E-2</v>
+        <v>9.0562248995983849E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,11 +1343,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-0.72568940493468803</v>
+        <v>-4.7895500725689404</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2554426705370103E-2</v>
+        <v>-8.2859216255442666E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1358,11 +1358,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>-1.1102299762093499</v>
+        <v>-1.18953211736716</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.8207771609833338E-2</v>
+        <v>-1.9508326724821425E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,11 +1373,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>-1.08015918135304</v>
+        <v>-0.96645821489482597</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7498578737919251E-2</v>
+        <v>-1.5656623081296183E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1388,11 +1388,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-1.7285531370038401</v>
+        <v>-2.62483994878361</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.5582586427656831E-2</v>
+        <v>-3.884763124199743E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1403,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-2.5714285714285698</v>
+        <v>-1.2380952380952299</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-3.5999999999999976E-2</v>
+        <v>-1.7333333333333218E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1418,11 +1418,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-1.1604439959636701</v>
+        <v>-0.302724520686175</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-1.508577194752771E-2</v>
+        <v>-3.9354187689202751E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,11 +1433,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-3.6837376460017901</v>
+        <v>-2.9649595687331498</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6415094339622556E-2</v>
+        <v>-3.735849056603769E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,11 +1448,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>4.7999999999999996E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,11 +1463,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>6.6889632107023395E-2</v>
+        <v>0.334448160535117</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>4.8829431438127081E-4</v>
+        <v>2.4414715719063541E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,11 +1478,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>0.37406483790523598</v>
+        <v>0.74812967581047296</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>2.6558603491271754E-3</v>
+        <v>5.3117206982543578E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,11 +1493,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>0.24937655860349101</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>1.4713216957605967E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,11 +1508,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-0.60790273556231</v>
+        <v>-3.5460992907801399</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-3.4042553191489361E-3</v>
+        <v>-1.9858156028368785E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1523,11 +1523,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>0.80717488789237601</v>
+        <v>2.3318385650224198</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>3.2286995515695043E-3</v>
+        <v>9.3273542600896802E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,11 +1538,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>-1.14942528735632</v>
+        <v>1.3409961685823699</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-4.482758620689648E-3</v>
+        <v>5.2298850574712431E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,11 +1553,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.4452473596442399</v>
+        <v>-1.2784880489160599</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-5.2028904947192638E-3</v>
+        <v>-4.6025569760978161E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1568,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>3.0254777070063601</v>
+        <v>2.0700636942675099</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>1.0286624203821626E-2</v>
+        <v>7.0382165605095337E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,11 +1583,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>0.19940179461615101</v>
+        <v>-0.299102691924227</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>6.7796610169491346E-4</v>
+        <v>-1.0169491525423718E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,11 +1598,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>0</v>
+        <v>9.64320154291224E-2</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.1822565091610395E-4</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1613,11 +1613,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>0.80745341614906796</v>
+        <v>2.1118012422360199</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>2.0993788819875766E-3</v>
+        <v>5.4906832298136522E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1628,11 +1628,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>0.40322580645161199</v>
+        <v>-0.40322580645161199</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>7.2580645161290165E-4</v>
+        <v>-7.2580645161290165E-4</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1643,11 +1643,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>-2.1064301552106399</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-2.5277161862527681E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1658,11 +1658,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>1.8820577164366299</v>
+        <v>0.37641154328732701</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>1.317440401505641E-3</v>
+        <v>2.634880803011289E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1673,11 +1673,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-0.67873303167420795</v>
+        <v>-2.0814479638008998</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-3.3936651583710395E-4</v>
+        <v>-1.04072398190045E-3</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1688,11 +1688,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>4.5983379501385002</v>
+        <v>1.93905817174515</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>1.8393351800553999E-3</v>
+        <v>7.7562326869806003E-4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1703,11 +1703,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>2.0911127707244201</v>
+        <v>1.64301717699775</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>8.3644510828976811E-4</v>
+        <v>6.5720687079909995E-4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1718,11 +1718,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>0.23529411764705799</v>
+        <v>-0.52941176470588203</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>7.0588235294117392E-4</v>
+        <v>-1.5882352941176462E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>-1.0914758821183579</v>
+        <v>-0.61369741763602703</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1808,10 +1808,10 @@
       <c r="A55" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="27"/>
+      <c r="C55" s="26"/>
       <c r="D55" s="20" t="s">
         <v>54</v>
       </c>
@@ -1927,11 +1927,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>0.29914529914529903</v>
+        <v>5.55555555555555</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>2.8867521367521357E-2</v>
+        <v>0.53611111111111054</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1942,11 +1942,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>-4.0828402366863896</v>
+        <v>-8.2840236686390494</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>-0.37929585798816556</v>
+        <v>-0.76958579881656763</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1957,11 +1957,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>2.03303684879288</v>
+        <v>6.3108852181279103</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.18785260482846211</v>
+        <v>0.58312579415501897</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1972,11 +1972,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-1.91616766467065</v>
+        <v>-3.7125748502993998</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.11669461077844259</v>
+        <v>-0.22609580838323345</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1987,11 +1987,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>-1.8907563025209999</v>
+        <v>-2.1008403361344499</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-8.9432773109243302E-2</v>
+        <v>-9.9369747899159491E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2002,11 +2002,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>-2.3684210526315699</v>
+        <v>0.61403508771929804</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10705263157894696</v>
+        <v>2.7754385964912268E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,11 +2017,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>0.59347181008901995</v>
+        <v>-2.8288822947576602</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>2.017804154302668E-2</v>
+        <v>-9.6181998021760431E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2032,11 +2032,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>7.9936051159072694E-2</v>
+        <v>-0.23980815347721801</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>2.1822541966426846E-3</v>
+        <v>-6.5467625899280511E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,11 +2047,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>1.2048192771084301</v>
+        <v>4.41767068273092</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>2.7710843373493891E-2</v>
+        <v>0.10160642570281116</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,11 +2062,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-2.4761904761904701</v>
+        <v>-1.2380952380952299</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-4.1352380952380849E-2</v>
+        <v>-2.0676190476190338E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2077,11 +2077,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-0.72568940493468803</v>
+        <v>-4.7895500725689404</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1465892597968071E-2</v>
+        <v>-7.5674891146589263E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,11 +2092,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-2.7619047619047601</v>
+        <v>-2.4761904761904701</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-4.336190476190474E-2</v>
+        <v>-3.8876190476190377E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,11 +2107,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>0.52199850857568897</v>
+        <v>0.82028337061894097</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>5.8985831469052855E-3</v>
+        <v>9.2692020879940312E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,11 +2122,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>6.0132291040288603E-2</v>
+        <v>0.300661455201443</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>6.1936259771497261E-4</v>
+        <v>3.096812988574863E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2137,11 +2137,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>-1.1102299762093499</v>
+        <v>-1.18953211736716</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0880253766851629E-2</v>
+        <v>-1.1657414750198167E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,11 +2167,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-0.70921985815602795</v>
+        <v>-3.5460992907801399</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-4.1843971631205642E-3</v>
+        <v>-2.0921985815602825E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,11 +2182,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-0.58823529411764697</v>
+        <v>-2.0814479638008998</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9411764705882348E-3</v>
+        <v>-1.0407239819004498E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2197,11 +2197,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>0.80717488789237601</v>
+        <v>2.3318385650224198</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>3.8744394618834051E-3</v>
+        <v>1.1192825112107613E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2212,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-3.7735849056603699</v>
+        <v>-2.9649595687331498</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5849056603773552E-2</v>
+        <v>-1.245283018867923E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,11 +2227,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-0.97560975609756095</v>
+        <v>-1.8902439024390201</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-3.9024390243902439E-3</v>
+        <v>-7.5609756097560809E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>0.37406483790523598</v>
+        <v>0.74812967581047296</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>1.4214463840398967E-3</v>
+        <v>2.8428927680797973E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,11 +2257,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>0.74534161490683204</v>
+        <v>2.1118012422360199</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>1.8633540372670801E-3</v>
+        <v>5.2795031055900502E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,11 +2272,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-3.3613445378151199</v>
+        <v>-3.4453781512605</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-8.4033613445377991E-3</v>
+        <v>-8.6134453781512507E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,11 +2287,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>2.94585987261146</v>
+        <v>2.0700636942675099</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>7.0700636942675034E-3</v>
+        <v>4.9681528662420234E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,11 +2302,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0</v>
+        <v>0.334448160535117</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.6923076923076912E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,11 +2317,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.95799557848194505</v>
+        <v>-1.10537951363301</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9159911569638902E-3</v>
+        <v>-2.2107590272660202E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,11 +2332,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>4.7645429362880796</v>
+        <v>1.93905817174515</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>3.8116343490304638E-3</v>
+        <v>1.5512465373961201E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,11 +2347,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>1.81932245922208</v>
+        <v>0.37641154328732701</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>1.8193224592220802E-4</v>
+        <v>3.7641154328732703E-5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-1.069355952349814</v>
+        <v>-0.64338212035359388</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,10 +2482,10 @@
       <c r="A53" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="27"/>
+      <c r="C53" s="26"/>
       <c r="D53" s="20" t="s">
         <v>54</v>
       </c>
@@ -2602,11 +2602,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>1.3707165109034201</v>
+        <v>2.3052959501557599</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.72305295950155413</v>
+        <v>1.2160436137071633</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,11 +2617,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-1.3</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.14455999999999999</v>
+        <v>-0.24464</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2632,11 +2632,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-6.3926940639269398</v>
+        <v>-6.7579908675798999</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-3.3881278538812787E-2</v>
+        <v>-3.5817351598173473E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2665,7 +2665,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>0.72651368096274127</v>
+        <v>1.1174882621089899</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,10 +2702,10 @@
       <c r="A31" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="27"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="20" t="s">
         <v>54</v>
       </c>
@@ -2838,11 +2838,11 @@
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.64670658682634</v>
+        <v>-1.19760479041916</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.70050898203592493</v>
+        <v>-0.50946107784431061</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,11 +2853,11 @@
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>-0.63734862970044603</v>
+        <v>-1.1472275334608</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>-0.20611854684512426</v>
+        <v>-0.37101338432122277</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2868,11 +2868,11 @@
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>-1.51791135397692</v>
+        <v>-0.91074681238615596</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-0.18533697632058196</v>
+        <v>-0.11120218579234965</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2883,11 +2883,11 @@
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>-8.0873433077234103E-2</v>
+        <v>-0.121310149615851</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>-8.8313788920339649E-3</v>
+        <v>-1.3247068338050928E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,11 +2898,11 @@
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.52056220718375801</v>
+        <v>-0.57261842790213402</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-3.0661114003123345E-2</v>
+        <v>-3.3727225403435687E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,11 +2913,11 @@
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>-4.3154761904761898</v>
+        <v>-2.6785714285714199</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.24511904761904757</v>
+        <v>-0.15214285714285664</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2931,7 +2931,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-1.376576045715836</v>
+        <v>-1.1907937988422264</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2986,10 +2986,10 @@
       <c r="A37" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="20" t="s">
         <v>54</v>
       </c>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41600E24-F793-4DF8-962D-D38EBF946B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A45E0B0-5CD9-4889-BEFD-9EBBE348B0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="0" windowWidth="14100" windowHeight="20985" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19410" yWindow="4905" windowWidth="14100" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -937,11 +937,11 @@
         <v>11.91</v>
       </c>
       <c r="C15" s="3">
-        <v>0</v>
+        <v>-4.17</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.49664699999999995</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>0.4197194289077037</v>
+        <v>-7.692757109229624E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A45E0B0-5CD9-4889-BEFD-9EBBE348B0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEFA076-854B-42EA-9EBB-D35350B48A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19410" yWindow="4905" windowWidth="14100" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3060" yWindow="375" windowWidth="13785" windowHeight="20655" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -401,10 +401,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -742,11 +742,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-2.4761904761904701</v>
+        <v>-2.734375</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.56580952380952243</v>
+        <v>-0.62480468750000007</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -757,11 +757,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>5.0505050505050502</v>
+        <v>9.8557692307692299</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.7222222222222221</v>
+        <v>1.409375</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -772,11 +772,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>0.334448160535117</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>2.5852842809364548E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -787,11 +787,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.185960018596001</v>
+        <v>0.23201856148491801</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>1.3277545327754471E-2</v>
+        <v>1.6566125290023145E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -802,11 +802,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>2.1118012422360199</v>
+        <v>0.36496350364963498</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.14001242236024811</v>
+        <v>2.4197080291970798E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -817,11 +817,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>0</v>
+        <v>-5.5986696230598598</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.31408536585365815</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -832,11 +832,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>4.41767068273092</v>
+        <v>-10</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>8.7911646586345302E-2</v>
+        <v>-0.19899999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,11 +847,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-1.09106168694922</v>
+        <v>2.46075519728468</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1347041544271887E-2</v>
+        <v>2.5591854051760673E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -862,11 +862,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>0</v>
+        <v>6.23441396508728E-2</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.3665835411471313E-4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -877,11 +877,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>2.3484848484848402</v>
+        <v>-3.1828275351591402</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.2212121212121169E-2</v>
+        <v>-1.6550703182827527E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -892,11 +892,11 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>-2.1008403361344499</v>
+        <v>3.0042918454935599</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-5.6722689075630155E-3</v>
+        <v>8.1115879828326121E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,11 +907,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>0.261951538965291</v>
+        <v>-1.89418680600914</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>3.6673215455140746E-4</v>
+        <v>-2.6518615284127963E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -922,11 +922,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-3.5460992907801399</v>
+        <v>1.26050420168067</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-2.4822695035460981E-3</v>
+        <v>8.823529411764691E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -937,11 +937,11 @@
         <v>11.91</v>
       </c>
       <c r="C15" s="3">
-        <v>-4.17</v>
+        <v>-2.9</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-0.49664699999999995</v>
+        <v>-0.34539000000000003</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -952,11 +952,11 @@
         <v>1.27</v>
       </c>
       <c r="C16" s="3">
-        <v>0.25</v>
+        <v>-1.57</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>3.1749999999999999E-3</v>
+        <v>-1.9938999999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>-7.692757109229624E-2</v>
+        <v>-3.7360959153020193E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1055,14 +1055,14 @@
       <c r="A32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26" t="s">
+      <c r="C32" s="27"/>
+      <c r="D32" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="26"/>
+      <c r="E32" s="27"/>
       <c r="F32" s="5" t="s">
         <v>68</v>
       </c>
@@ -1075,10 +1075,10 @@
         <v>98970</v>
       </c>
       <c r="C33" s="25"/>
-      <c r="D33" s="27">
+      <c r="D33" s="26">
         <v>232874657613</v>
       </c>
-      <c r="E33" s="27"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="21">
         <v>1310146537</v>
       </c>
@@ -1091,16 +1091,34 @@
         <v>99051</v>
       </c>
       <c r="C34" s="25"/>
-      <c r="D34" s="27">
+      <c r="D34" s="26">
         <v>227320292084</v>
       </c>
-      <c r="E34" s="27"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="22">
         <v>-6072488957</v>
       </c>
     </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
+        <v>46230</v>
+      </c>
+      <c r="B35" s="25">
+        <v>98455</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="26">
+        <v>229116006481</v>
+      </c>
+      <c r="E35" s="26"/>
+      <c r="F35" s="22">
+        <v>291803673</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="A30:B30"/>
@@ -1148,11 +1166,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>-8.2840236686390494</v>
+        <v>0.58064516129032195</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.73893491124260324</v>
+        <v>5.1793548387096718E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1163,11 +1181,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>5.55555555555555</v>
+        <v>5.56680161943319</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.48944444444444402</v>
+        <v>0.49043522267206408</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1178,11 +1196,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>6.3108852181279103</v>
+        <v>4.7808764940239001</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.52254129606099087</v>
+        <v>0.3958565737051789</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,11 +1211,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>0.61403508771929804</v>
+        <v>4.6207497820401002</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>3.788596491228069E-2</v>
+        <v>0.28510026155187418</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1208,11 +1226,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>-2.1008403361344499</v>
+        <v>3.0042918454935599</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-9.9789915966386367E-2</v>
+        <v>0.14270386266094409</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,11 +1241,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-0.23980815347721801</v>
+        <v>1.92307692307692</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0599520383693035E-2</v>
+        <v>8.4999999999999853E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,11 +1256,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>0.82028337061894097</v>
+        <v>-1.70118343195266</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>3.0924683072334074E-2</v>
+        <v>-6.413461538461529E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,11 +1271,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>-2.8288822947576602</v>
+        <v>-1.75081433224755</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10183976261127578</v>
+        <v>-6.3029315960911797E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,11 +1286,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>0.300661455201443</v>
+        <v>-1.378896882494</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>1.013229104028863E-2</v>
+        <v>-4.6468824940047802E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,11 +1301,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-3.7125748502993998</v>
+        <v>-4.1044776119402897</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-9.9497005988023926E-2</v>
+        <v>-0.10999999999999976</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,11 +1316,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-2.4761904761904701</v>
+        <v>-2.734375</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3885714285714129E-2</v>
+        <v>-7.0546874999999995E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1313,11 +1331,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-0.61538461538461497</v>
+        <v>-0.23219814241486</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5076923076923068E-2</v>
+        <v>-5.6888544891640705E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,11 +1346,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>4.41767068273092</v>
+        <v>-10</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>9.0562248995983849E-2</v>
+        <v>-0.20499999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,11 +1361,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-4.7895500725689404</v>
+        <v>-4.1920731707316996</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-8.2859216255442666E-2</v>
+        <v>-7.25228658536584E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1358,11 +1376,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>-1.18953211736716</v>
+        <v>0.32102728731942198</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9508326724821425E-2</v>
+        <v>5.2648475120385205E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,11 +1391,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>-0.96645821489482597</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5656623081296183E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1388,11 +1406,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-2.62483994878361</v>
+        <v>0.78895463510848096</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-3.884763124199743E-2</v>
+        <v>1.1676528599605518E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1421,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-1.2380952380952299</v>
+        <v>-1.3500482160077101</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7333333333333218E-2</v>
+        <v>-1.890067502410794E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1418,11 +1436,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-0.302724520686175</v>
+        <v>-0.45546558704453399</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-3.9354187689202751E-3</v>
+        <v>-5.9210526315789424E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,11 +1451,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-2.9649595687331498</v>
+        <v>-2.31481481481481</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-3.735849056603769E-2</v>
+        <v>-2.9166666666666608E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,11 +1466,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>0.8</v>
+        <v>0.87301587301587302</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>9.5999999999999992E-3</v>
+        <v>1.0476190476190477E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,11 +1481,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>0.334448160535117</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>2.4414715719063541E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,11 +1496,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>0.74812967581047296</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>5.3117206982543578E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,11 +1511,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>0</v>
+        <v>6.23441396508728E-2</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.6783042394014946E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,11 +1526,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-3.5460992907801399</v>
+        <v>1.26050420168067</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9858156028368785E-2</v>
+        <v>7.0588235294117528E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1523,11 +1541,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>2.3318385650224198</v>
+        <v>-1.5775635407537201</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>9.3273542600896802E-3</v>
+        <v>-6.3102541630148815E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,11 +1556,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>1.3409961685823699</v>
+        <v>0.56710775047258899</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>5.2298850574712431E-3</v>
+        <v>2.2117202268430972E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,11 +1571,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.2784880489160599</v>
+        <v>-0.168918918918918</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6025569760978161E-3</v>
+        <v>-6.0810810810810472E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1586,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>2.0700636942675099</v>
+        <v>1.6380655226209</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>7.0382165605095337E-3</v>
+        <v>5.5694227769110607E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,11 +1601,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>-0.299102691924227</v>
+        <v>-1.9</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0169491525423718E-3</v>
+        <v>-6.4600000000000005E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,11 +1616,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>9.64320154291224E-2</v>
+        <v>1.0597302504816899</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>3.1822565091610395E-4</v>
+        <v>3.4971098265895767E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1613,11 +1631,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>2.1118012422360199</v>
+        <v>0.36496350364963498</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>5.4906832298136522E-3</v>
+        <v>9.4890510948905107E-4</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1628,11 +1646,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-0.40322580645161199</v>
+        <v>-2.0242914979757001</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-7.2580645161290165E-4</v>
+        <v>-3.6437246963562596E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1643,11 +1661,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>0</v>
+        <v>-5.5986696230598598</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6.7184035476718319E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1658,11 +1676,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>0.37641154328732701</v>
+        <v>-4.6875</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>2.634880803011289E-4</v>
+        <v>-3.2812500000000007E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1673,11 +1691,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-2.0814479638008998</v>
+        <v>-4.6210720887245801E-2</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-1.04072398190045E-3</v>
+        <v>-2.3105360443622899E-5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1688,11 +1706,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>1.93905817174515</v>
+        <v>-4.0217391304347796</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>7.7562326869806003E-4</v>
+        <v>-1.6086956521739117E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1703,11 +1721,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>1.64301717699775</v>
+        <v>-1.6899338721528201</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>6.5720687079909995E-4</v>
+        <v>-6.7597354886112806E-4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1718,11 +1736,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>-0.52941176470588203</v>
+        <v>0.29568302779420402</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5882352941176462E-3</v>
+        <v>8.8704908338261212E-4</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,11 +1751,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>-3.51</v>
+        <v>-8.61</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>-0.292383</v>
+        <v>-0.71721299999999999</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1748,11 +1766,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-2.16</v>
+        <v>-6.98</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-0.17863199999999999</v>
+        <v>-0.57724600000000004</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1763,11 +1781,11 @@
         <v>2.56</v>
       </c>
       <c r="C43" s="4">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" si="0"/>
-        <v>3.3280000000000002E-3</v>
+        <v>9.7280000000000005E-3</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1780,7 +1798,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>-0.61369741763602703</v>
+        <v>-0.5065923644858209</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1808,10 +1826,10 @@
       <c r="A55" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="26"/>
+      <c r="C55" s="27"/>
       <c r="D55" s="20" t="s">
         <v>54</v>
       </c>
@@ -1850,8 +1868,19 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
+      <c r="A58" s="18">
+        <v>46230</v>
+      </c>
+      <c r="B58" s="25">
+        <v>159672</v>
+      </c>
+      <c r="C58" s="25"/>
+      <c r="D58" s="21">
+        <v>74765554505</v>
+      </c>
+      <c r="E58" s="21">
+        <v>831945602</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D59" s="24"/>
@@ -1882,7 +1911,8 @@
       <c r="E65" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B58:C58"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A50:B50"/>
@@ -1927,11 +1957,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>5.55555555555555</v>
+        <v>5.56680161943319</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.53611111111111054</v>
+        <v>0.53719635627530282</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1942,11 +1972,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>-8.2840236686390494</v>
+        <v>0.58064516129032195</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>-0.76958579881656763</v>
+        <v>5.3941935483870912E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1957,11 +1987,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>6.3108852181279103</v>
+        <v>4.7808764940239001</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.58312579415501897</v>
+        <v>0.44175298804780838</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1972,11 +2002,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-3.7125748502993998</v>
+        <v>-4.1044776119402897</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.22609580838323345</v>
+        <v>-0.24996268656716364</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1987,11 +2017,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>-2.1008403361344499</v>
+        <v>3.0042918454935599</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-9.9369747899159491E-2</v>
+        <v>0.14210300429184539</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2002,11 +2032,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>0.61403508771929804</v>
+        <v>4.6207497820401002</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>2.7754385964912268E-2</v>
+        <v>0.20885789014821252</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,11 +2047,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>-2.8288822947576602</v>
+        <v>-1.75081433224755</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-9.6181998021760431E-2</v>
+        <v>-5.9527687296416693E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2032,11 +2062,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-0.23980815347721801</v>
+        <v>1.92307692307692</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-6.5467625899280511E-3</v>
+        <v>5.2499999999999922E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,11 +2077,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>4.41767068273092</v>
+        <v>-10</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.10160642570281116</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,11 +2092,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-1.2380952380952299</v>
+        <v>-1.3500482160077101</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0676190476190338E-2</v>
+        <v>-2.2545805207328757E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2077,11 +2107,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-4.7895500725689404</v>
+        <v>-4.1920731707316996</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5674891146589263E-2</v>
+        <v>-6.6234756097560854E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,11 +2122,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-2.4761904761904701</v>
+        <v>-2.734375</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8876190476190377E-2</v>
+        <v>-4.2929687500000001E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,11 +2137,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>0.82028337061894097</v>
+        <v>-1.70118343195266</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>9.2692020879940312E-3</v>
+        <v>-1.9223372781065055E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,11 +2152,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>0.300661455201443</v>
+        <v>-1.378896882494</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>3.096812988574863E-3</v>
+        <v>-1.42026378896882E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2137,11 +2167,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>-1.18953211736716</v>
+        <v>0.32102728731942198</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1657414750198167E-2</v>
+        <v>3.1460674157303354E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,11 +2182,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.9540581929555891</v>
+        <v>-9.9489795918367303</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6600306278713624E-2</v>
+        <v>-8.6556122448979561E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,11 +2197,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-3.5460992907801399</v>
+        <v>1.26050420168067</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0921985815602825E-2</v>
+        <v>7.4369747899159519E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,11 +2212,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-2.0814479638008998</v>
+        <v>-4.6210720887245801E-2</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0407239819004498E-2</v>
+        <v>-2.3105360443622901E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2197,11 +2227,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>2.3318385650224198</v>
+        <v>-1.5775635407537201</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>1.1192825112107613E-2</v>
+        <v>-7.5723049956178557E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2242,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-2.9649595687331498</v>
+        <v>-2.31481481481481</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.245283018867923E-2</v>
+        <v>-9.7222222222222016E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,11 +2257,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-1.8902439024390201</v>
+        <v>-1.1808576755748901</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5609756097560809E-3</v>
+        <v>-4.7234307022995603E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2242,11 +2272,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>0.74812967581047296</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>2.8428927680797973E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,11 +2287,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>2.1118012422360199</v>
+        <v>0.36496350364963498</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>5.2795031055900502E-3</v>
+        <v>9.1240875912408745E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,11 +2302,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-3.4453781512605</v>
+        <v>0.69625761531766694</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6134453781512507E-3</v>
+        <v>1.7406440382941673E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,11 +2317,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>2.0700636942675099</v>
+        <v>1.6380655226209</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>4.9681528662420234E-3</v>
+        <v>3.93135725429016E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,11 +2332,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0.334448160535117</v>
+        <v>0</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>7.6923076923076912E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,11 +2347,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>-1.10537951363301</v>
+        <v>1.71385991058122</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-2.2107590272660202E-3</v>
+        <v>3.4277198211624406E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,11 +2362,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>1.93905817174515</v>
+        <v>-4.0217391304347796</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>1.5512465373961201E-3</v>
+        <v>-3.2173913043478234E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,11 +2377,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>0.37641154328732701</v>
+        <v>-4.6875</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>3.7641154328732703E-5</v>
+        <v>-4.6874999999999998E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,11 +2392,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>-3.51</v>
+        <v>-8.61</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-0.280449</v>
+        <v>-0.68793899999999997</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2377,11 +2407,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-2.16</v>
+        <v>-6.98</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-0.16632000000000002</v>
+        <v>-0.53746000000000005</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2392,11 +2422,11 @@
         <v>2.5</v>
       </c>
       <c r="C33" s="4">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>3.2500000000000003E-3</v>
+        <v>9.4999999999999998E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2407,11 +2437,11 @@
         <v>0.78</v>
       </c>
       <c r="C34" s="4">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>1.0140000000000001E-3</v>
+        <v>2.9640000000000001E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2422,11 +2452,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>0.9</v>
+        <v>-2.0099999999999998</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>5.2199999999999998E-3</v>
+        <v>-1.1657999999999996E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2437,11 +2467,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>-0.45</v>
+        <v>-0.48</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-2.7E-4</v>
+        <v>-2.8800000000000001E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2454,7 +2484,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-0.64338212035359388</v>
+        <v>-0.58505156229156896</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,10 +2512,10 @@
       <c r="A53" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="B53" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="26"/>
+      <c r="C53" s="27"/>
       <c r="D53" s="20" t="s">
         <v>54</v>
       </c>
@@ -2524,8 +2554,19 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
+      <c r="A56" s="18">
+        <v>46230</v>
+      </c>
+      <c r="B56" s="25">
+        <v>78840</v>
+      </c>
+      <c r="C56" s="25"/>
+      <c r="D56" s="21">
+        <v>39148877217</v>
+      </c>
+      <c r="E56" s="22">
+        <v>706423581</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D57" s="24"/>
@@ -2556,7 +2597,8 @@
       <c r="E63" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A45:B45"/>
@@ -2602,11 +2644,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>2.3052959501557599</v>
+        <v>-0.48721071863581</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>1.2160436137071633</v>
+        <v>-0.25700365408038978</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2617,11 +2659,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-2.2000000000000002</v>
+        <v>-3.4764826175869099</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.24464</v>
+        <v>-0.38658486707566431</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2632,11 +2674,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-6.7579908675798999</v>
+        <v>-4.7012732615083204</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-3.5817351598173473E-2</v>
+        <v>-2.4916748285994102E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2647,11 +2689,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>0.61</v>
+        <v>2.09</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.18190200000000001</v>
+        <v>0.62323799999999996</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2665,7 +2707,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>1.1174882621089899</v>
+        <v>-4.5267269442048286E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,10 +2744,10 @@
       <c r="A31" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="26"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="20" t="s">
         <v>54</v>
       </c>
@@ -2744,8 +2786,19 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
+      <c r="A34" s="23">
+        <v>46230</v>
+      </c>
+      <c r="B34" s="25">
+        <v>49403</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="21">
+        <v>30359209400</v>
+      </c>
+      <c r="E34" s="21">
+        <v>781254453</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D35" s="24"/>
@@ -2792,7 +2845,8 @@
       <c r="E46" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
@@ -2838,11 +2892,11 @@
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.19760479041916</v>
+        <v>-1.8181818181818099</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.50946107784431061</v>
+        <v>-0.77345454545454184</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,11 +2907,11 @@
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>-1.1472275334608</v>
+        <v>0.12894906511927701</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>-0.37101338432122277</v>
+        <v>4.1702127659574185E-2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2868,11 +2922,11 @@
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.91074681238615596</v>
+        <v>0.12254901960784299</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-0.11120218579234965</v>
+        <v>1.496323529411763E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2883,11 +2937,11 @@
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>-0.121310149615851</v>
+        <v>-4.2105263157894699</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>-1.3247068338050928E-2</v>
+        <v>-0.45978947368421008</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,11 +2952,11 @@
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.57261842790213402</v>
+        <v>-0.89005235602094201</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-3.3727225403435687E-2</v>
+        <v>-5.2424083769633478E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,11 +2967,11 @@
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>-2.6785714285714199</v>
+        <v>9.9898063200815397</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.15214285714285664</v>
+        <v>0.56742099898063147</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2931,7 +2985,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-1.1907937988422264</v>
+        <v>-0.66158174097406219</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2986,10 +3040,10 @@
       <c r="A37" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="26"/>
+      <c r="C37" s="27"/>
       <c r="D37" s="20" t="s">
         <v>54</v>
       </c>
@@ -3028,7 +3082,19 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="24"/>
+      <c r="A40" s="23">
+        <v>46230</v>
+      </c>
+      <c r="B40" s="25">
+        <v>6906</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="21">
+        <v>1167160796</v>
+      </c>
+      <c r="E40" s="21">
+        <v>99781628</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E41" s="24"/>
@@ -3076,7 +3142,8 @@
       <c r="E55" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="B37:C37"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEFA076-854B-42EA-9EBB-D35350B48A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B451332-BA59-4A21-A863-2A8C02FD2D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="375" windowWidth="13785" windowHeight="20655" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
   <si>
     <t>DSTKF</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Tarih</t>
+  </si>
+  <si>
+    <t>MARJ</t>
   </si>
 </sst>
 </file>
@@ -334,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,11 +404,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -709,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -959,7 +965,7 @@
         <v>-1.9938999999999998E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>64</v>
       </c>
@@ -973,70 +979,70 @@
         <v>-3.7360959153020193E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="6"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C28" s="5"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="25"/>
       <c r="C30" s="4"/>
@@ -1044,30 +1050,33 @@
       <c r="E30" s="4"/>
       <c r="F30" s="17"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
       <c r="B31" s="25"/>
       <c r="C31" s="9"/>
       <c r="D31" s="19"/>
       <c r="E31" s="17"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27" t="s">
+      <c r="C32" s="26"/>
+      <c r="D32" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="27"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
         <v>46226</v>
       </c>
@@ -1075,15 +1084,18 @@
         <v>98970</v>
       </c>
       <c r="C33" s="25"/>
-      <c r="D33" s="26">
+      <c r="D33" s="27">
         <v>232874657613</v>
       </c>
-      <c r="E33" s="26"/>
+      <c r="E33" s="27"/>
       <c r="F33" s="21">
         <v>1310146537</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" s="28">
+        <v>2.1100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
         <v>46227</v>
       </c>
@@ -1091,15 +1103,18 @@
         <v>99051</v>
       </c>
       <c r="C34" s="25"/>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <v>227320292084</v>
       </c>
-      <c r="E34" s="26"/>
+      <c r="E34" s="27"/>
       <c r="F34" s="22">
         <v>-6072488957</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="28">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
         <v>46230</v>
       </c>
@@ -1107,12 +1122,15 @@
         <v>98455</v>
       </c>
       <c r="C35" s="25"/>
-      <c r="D35" s="26">
+      <c r="D35" s="27">
         <v>229116006481</v>
       </c>
-      <c r="E35" s="26"/>
+      <c r="E35" s="27"/>
       <c r="F35" s="22">
         <v>291803673</v>
+      </c>
+      <c r="G35" s="28">
+        <v>6.6E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3EFDCB2-2AE4-47FF-8CDC-B26B49C81EBA}">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1809,35 +1827,38 @@
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="25"/>
       <c r="B49" s="25"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="17"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
       <c r="B50" s="25"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="27"/>
+      <c r="C55" s="26"/>
       <c r="D55" s="20" t="s">
         <v>54</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
         <v>46226</v>
       </c>
@@ -1851,8 +1872,11 @@
       <c r="E56" s="21">
         <v>-1765745461</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="28">
+        <v>1.15E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="18">
         <v>46227</v>
       </c>
@@ -1866,8 +1890,11 @@
       <c r="E57" s="21">
         <v>-535063133</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="28">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="18">
         <v>46230</v>
       </c>
@@ -1881,28 +1908,31 @@
       <c r="E58" s="21">
         <v>831945602</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="28">
+        <v>-1.4E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D59" s="24"/>
       <c r="E59" s="24"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D60" s="24"/>
       <c r="E60" s="24"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D61" s="24"/>
       <c r="E61" s="24"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D63" s="24"/>
       <c r="E63" s="24"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D64" s="24"/>
       <c r="E64" s="24"/>
     </row>
@@ -1925,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8ADE70-F8B5-43C2-B046-025D01A118D2}">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2508,22 +2538,25 @@
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="27"/>
+      <c r="C53" s="26"/>
       <c r="D53" s="20" t="s">
         <v>54</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="18">
         <v>46226</v>
       </c>
@@ -2537,8 +2570,11 @@
       <c r="E54" s="22">
         <v>-656504519</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="28">
+        <v>8.0999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
         <v>46227</v>
       </c>
@@ -2552,8 +2588,11 @@
       <c r="E55" s="22">
         <v>45631782</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="28">
+        <v>4.1000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
         <v>46230</v>
       </c>
@@ -2567,32 +2606,35 @@
       <c r="E56" s="22">
         <v>706423581</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="28">
+        <v>-2.7000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D57" s="24"/>
       <c r="E57" s="24"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D58" s="24"/>
       <c r="E58" s="24"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D59" s="24"/>
       <c r="E59" s="24"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D60" s="24"/>
       <c r="E60" s="24"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D61" s="24"/>
       <c r="E61" s="24"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D63" s="24"/>
       <c r="E63" s="24"/>
     </row>
@@ -2612,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545E6D6F-F0E5-4763-8F78-0375F1A09A45}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -2740,22 +2782,25 @@
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="27"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="20" t="s">
         <v>54</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
         <v>46226</v>
       </c>
@@ -2769,8 +2814,11 @@
       <c r="E32" s="21">
         <v>578476685</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="28">
+        <v>3.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
         <v>46227</v>
       </c>
@@ -2784,8 +2832,11 @@
       <c r="E33" s="21">
         <v>630289948</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="28">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
         <v>46230</v>
       </c>
@@ -2799,49 +2850,52 @@
       <c r="E34" s="21">
         <v>781254453</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="28">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D36" s="24"/>
       <c r="E36" s="24"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D37" s="24"/>
       <c r="E37" s="24"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D38" s="24"/>
       <c r="E38" s="24"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D41" s="24"/>
       <c r="E41" s="24"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="24"/>
       <c r="E42" s="24"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E44" s="24"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E46" s="24"/>
     </row>
   </sheetData>
@@ -3036,22 +3090,25 @@
       <c r="C16" s="3"/>
       <c r="D16" s="7"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="20" t="s">
         <v>54</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="23">
         <v>46226</v>
       </c>
@@ -3065,8 +3122,11 @@
       <c r="E38" s="21">
         <v>95865997</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="28">
+        <v>5.4000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23">
         <v>46227</v>
       </c>
@@ -3080,8 +3140,11 @@
       <c r="E39" s="21">
         <v>42490384</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="28">
+        <v>-8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="23">
         <v>46230</v>
       </c>
@@ -3095,29 +3158,32 @@
       <c r="E40" s="21">
         <v>99781628</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="28">
+        <v>-8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E41" s="24"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E42" s="24"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E44" s="24"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E46" s="24"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E47" s="24"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E48" s="24"/>
     </row>
     <row r="49" spans="5:5" x14ac:dyDescent="0.25">

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B451332-BA59-4A21-A863-2A8C02FD2D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEDE6F5-80D0-423A-8A8F-6CE34AAC14C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37620" yWindow="780" windowWidth="17010" windowHeight="18450" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="76">
   <si>
     <t>DSTKF</t>
   </si>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>IEYHO</t>
-  </si>
-  <si>
-    <t>TPKGY</t>
   </si>
   <si>
     <t>SELEC</t>
@@ -398,21 +395,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,11 +743,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-2.734375</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.62480468750000007</v>
+        <v>-2.2827058232931732</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -763,11 +758,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>9.8557692307692299</v>
+        <v>9.9927060539751995</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>1.409375</v>
+        <v>1.4289569657184535</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -778,11 +773,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>0</v>
+        <v>-1.3333333333333299</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>0</v>
+        <f t="shared" ref="D4:D15" si="0">B4*C4/100</f>
+        <v>-0.10306666666666642</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -793,11 +788,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.23201856148491801</v>
+        <v>1.2037037037036999</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>1.6566125290023145E-2</v>
+        <v>8.5944444444444171E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -808,11 +803,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>0.36496350364963498</v>
+        <v>-0.48484848484848397</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>2.4197080291970798E-2</v>
+        <v>-3.2145454545454484E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -823,11 +818,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>-5.5986696230598598</v>
+        <v>2.8185554903112102</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.31408536585365815</v>
+        <v>0.15812096300645892</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -838,26 +833,26 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-0.19899999999999998</v>
+        <v>0.19899999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>2.46075519728468</v>
+        <v>-9.97929606625258</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>2.5591854051760673E-2</v>
+        <v>-0.10378467908902683</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -868,11 +863,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>6.23441396508728E-2</v>
+        <v>-0.80996884735202401</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>3.3665835411471313E-4</v>
+        <v>-4.3738317757009296E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -883,11 +878,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>-3.1828275351591402</v>
+        <v>-3.3639143730886798</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6550703182827527E-2</v>
+        <v>-1.7492354740061136E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -898,26 +893,26 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>3.0042918454935599</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>8.1115879828326121E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="4">
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>-1.89418680600914</v>
+        <v>-7.12383488681757</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6518615284127963E-3</v>
+        <v>-9.9733688415445994E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -928,56 +923,47 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>1.26050420168067</v>
+        <v>-3.63070539419087</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>8.823529411764691E-4</v>
+        <v>-2.5414937759336092E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="4">
-        <v>11.91</v>
+        <v>1.27</v>
       </c>
       <c r="C15" s="3">
-        <v>-2.9</v>
+        <v>-1.41</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-0.34539000000000003</v>
+        <v>-1.7906999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="4">
-        <v>1.27</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-1.57</v>
-      </c>
-      <c r="D16" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.9938999999999998E-2</v>
+      <c r="A16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="5">
+        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15</f>
+        <v>70.100000000000009</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15</f>
+        <v>-0.70196829955820472</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="5">
-        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16</f>
-        <v>82.01</v>
-      </c>
+      <c r="A17" s="16"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="6">
-        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>-3.7360959153020193E-2</v>
-      </c>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
@@ -1027,124 +1013,139 @@
       <c r="C25" s="5"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6"/>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="25"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="17"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="27"/>
+      <c r="F31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26" t="s">
-        <v>54</v>
+      <c r="A32" s="18">
+        <v>46226</v>
+      </c>
+      <c r="B32" s="25">
+        <v>98970</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="26">
+        <v>232874657613</v>
       </c>
       <c r="E32" s="26"/>
-      <c r="F32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>76</v>
+      <c r="F32" s="21">
+        <v>1310146537</v>
+      </c>
+      <c r="G32" s="24">
+        <v>2.1100000000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B33" s="25">
-        <v>98970</v>
+        <v>99051</v>
       </c>
       <c r="C33" s="25"/>
-      <c r="D33" s="27">
-        <v>232874657613</v>
-      </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="21">
-        <v>1310146537</v>
-      </c>
-      <c r="G33" s="28">
-        <v>2.1100000000000001E-2</v>
+      <c r="D33" s="26">
+        <v>227320292084</v>
+      </c>
+      <c r="E33" s="26"/>
+      <c r="F33" s="22">
+        <v>-6072488957</v>
+      </c>
+      <c r="G33" s="24">
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B34" s="25">
-        <v>99051</v>
+        <v>98455</v>
       </c>
       <c r="C34" s="25"/>
-      <c r="D34" s="27">
-        <v>227320292084</v>
-      </c>
-      <c r="E34" s="27"/>
+      <c r="D34" s="26">
+        <v>229116006481</v>
+      </c>
+      <c r="E34" s="26"/>
       <c r="F34" s="22">
-        <v>-6072488957</v>
-      </c>
-      <c r="G34" s="28">
-        <v>2.2000000000000001E-3</v>
+        <v>291803673</v>
+      </c>
+      <c r="G34" s="24">
+        <v>6.6E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B35" s="25">
-        <v>98455</v>
+        <v>98583</v>
       </c>
       <c r="C35" s="25"/>
-      <c r="D35" s="27">
-        <v>229116006481</v>
-      </c>
-      <c r="E35" s="27"/>
+      <c r="D35" s="26">
+        <v>232227975662</v>
+      </c>
+      <c r="E35" s="26"/>
       <c r="F35" s="22">
-        <v>291803673</v>
-      </c>
-      <c r="G35" s="28">
-        <v>6.6E-3</v>
+        <v>-464304680</v>
+      </c>
+      <c r="G35" s="24">
+        <v>1.5600000000000001E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -1152,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3EFDCB2-2AE4-47FF-8CDC-B26B49C81EBA}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1160,6 +1161,7 @@
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1167,7 +1169,7 @@
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -1184,11 +1186,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>0.58064516129032195</v>
+        <v>0.89801154586273202</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>5.1793548387096718E-2</v>
+        <v>8.0102629890955693E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1199,11 +1201,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>5.56680161943319</v>
+        <v>-0.28763183125599201</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.49043522267206408</v>
+        <v>-2.5340364333652898E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,11 +1216,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>4.7808764940239001</v>
+        <v>-10</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.3958565737051789</v>
+        <v>-0.82799999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1229,11 +1231,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>4.6207497820401002</v>
+        <v>5.8333333333333304</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.28510026155187418</v>
+        <v>0.35991666666666644</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,11 +1246,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>3.0042918454935599</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.14270386266094409</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1259,11 +1261,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>1.92307692307692</v>
+        <v>0.31446540880503099</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>8.4999999999999853E-2</v>
+        <v>1.3899371069182369E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1274,11 +1276,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-1.70118343195266</v>
+        <v>-0.97817908201655301</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-6.413461538461529E-2</v>
+        <v>-3.6877351392024048E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1289,11 +1291,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>-1.75081433224755</v>
+        <v>-3.7297969332780698</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3029315960911797E-2</v>
+        <v>-0.1342726895980105</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1304,26 +1306,26 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-1.378896882494</v>
+        <v>-0.48632218844984798</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6468824940047802E-2</v>
+        <v>-1.6389057750759876E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4">
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-4.1044776119402897</v>
+        <v>-2.65888456549935</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10999999999999976</v>
+        <v>-7.1258106355382586E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1334,11 +1336,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-2.734375</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-7.0546874999999995E-2</v>
+        <v>-0.25774096385542172</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1349,11 +1351,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-0.23219814241486</v>
+        <v>-0.54305663304887497</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-5.6888544891640705E-3</v>
+        <v>-1.3304887509697438E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,11 +1366,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-0.20499999999999999</v>
+        <v>0.20499999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,11 +1381,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-4.1920731707316996</v>
+        <v>3.0230708035003899</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-7.25228658536584E-2</v>
+        <v>5.229912490055675E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,11 +1396,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>0.32102728731942198</v>
+        <v>1.44</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>5.2648475120385205E-3</v>
+        <v>2.3615999999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,11 +1411,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>0</v>
+        <v>0.28702640642939098</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.6498277841561346E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,11 +1426,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>0.78895463510848096</v>
+        <v>1.63078930202217</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>1.1676528599605518E-2</v>
+        <v>2.4135681669928119E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1439,11 +1441,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-1.3500482160077101</v>
+        <v>-0.58651026392961803</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-1.890067502410794E-2</v>
+        <v>-8.2111436950146523E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,11 +1456,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-0.45546558704453399</v>
+        <v>-0.864260294865277</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9210526315789424E-3</v>
+        <v>-1.1235383833248602E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,11 +1471,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-2.31481481481481</v>
+        <v>-1.3270142180094699</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9166666666666608E-2</v>
+        <v>-1.6720379146919321E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,11 +1486,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>0.87301587301587302</v>
+        <v>0.2360346184107</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>1.0476190476190477E-2</v>
+        <v>2.8324154209283998E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,11 +1501,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>0</v>
+        <v>-1.3333333333333299</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-9.7333333333333091E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1514,11 +1516,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>0</v>
+        <v>-1.1757425742574199</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-8.3477722772276816E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,11 +1531,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>6.23441396508728E-2</v>
+        <v>-0.80996884735202401</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>3.6783042394014946E-4</v>
+        <v>-4.7788161993769411E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,11 +1546,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>1.26050420168067</v>
+        <v>-3.63070539419087</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>7.0588235294117528E-3</v>
+        <v>-2.0331950207468873E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1559,11 +1561,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.5775635407537201</v>
+        <v>0.80142475512021305</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3102541630148815E-3</v>
+        <v>3.205699020480852E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,11 +1576,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>0.56710775047258899</v>
+        <v>0.46992481203007502</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>2.2117202268430972E-3</v>
+        <v>1.8327067669172928E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,11 +1591,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-0.168918918918918</v>
+        <v>0.112803158488437</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-6.0810810810810472E-4</v>
+        <v>4.0609137055837318E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,41 +1606,41 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>1.6380655226209</v>
+        <v>9.9769762087490399</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>5.5694227769110607E-3</v>
+        <v>3.3921719109746735E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="4">
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>-1.9</v>
+        <v>-5.81039755351682</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-6.4600000000000005E-3</v>
+        <v>-1.9755351681957189E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" s="4">
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>1.0597302504816899</v>
+        <v>2.1925643469971399</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>3.4971098265895767E-3</v>
+        <v>7.2354623450905618E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1649,11 +1651,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>0.36496350364963498</v>
+        <v>-0.48484848484848397</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>9.4890510948905107E-4</v>
+        <v>-1.2606060606060584E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1664,11 +1666,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.0242914979757001</v>
+        <v>-2.0661157024793302</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6437246963562596E-3</v>
+        <v>-3.7190082644627943E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1679,71 +1681,71 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>-5.5986696230598598</v>
+        <v>2.8185554903112102</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-6.7184035476718319E-3</v>
+        <v>3.382266588373452E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-4.6875</v>
+        <v>-1.44262295081967</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-3.2812500000000007E-3</v>
+        <v>-1.0098360655737691E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" s="4">
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-4.6210720887245801E-2</v>
+        <v>1.38696255201109</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3105360443622899E-5</v>
+        <v>6.9348127600554505E-4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B38" s="4">
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>-4.0217391304347796</v>
+        <v>-8.8901472253680591</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>-1.6086956521739117E-3</v>
+        <v>-3.5560588901472241E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" s="4">
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>-1.6899338721528201</v>
+        <v>-1.5695067264573901</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>-6.7597354886112806E-4</v>
+        <v>-6.2780269058295606E-4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1754,11 +1756,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>0.29568302779420402</v>
+        <v>-2.1226415094339601</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>8.8704908338261212E-4</v>
+        <v>-6.3679245283018802E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1769,11 +1771,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>-8.61</v>
+        <v>0.59</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>-0.71721299999999999</v>
+        <v>4.9146999999999996E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1784,31 +1786,31 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-6.98</v>
+        <v>1.95</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-0.57724600000000004</v>
+        <v>0.16126499999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" s="4">
         <v>2.56</v>
       </c>
       <c r="C43" s="4">
-        <v>0.38</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" si="0"/>
-        <v>9.7280000000000005E-3</v>
+        <v>3.5840000000000004E-3</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="5">
         <f>SUM(B2:B43)</f>
@@ -1816,7 +1818,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>-0.5065923644858209</v>
+        <v>-0.46771364378962371</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1842,20 +1844,20 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" s="27"/>
+      <c r="D55" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F55" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B55" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="26"/>
-      <c r="D55" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1872,7 +1874,7 @@
       <c r="E56" s="21">
         <v>-1765745461</v>
       </c>
-      <c r="F56" s="28">
+      <c r="F56" s="24">
         <v>1.15E-2</v>
       </c>
     </row>
@@ -1890,7 +1892,7 @@
       <c r="E57" s="21">
         <v>-535063133</v>
       </c>
-      <c r="F57" s="28">
+      <c r="F57" s="24">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -1908,40 +1910,229 @@
       <c r="E58" s="21">
         <v>831945602</v>
       </c>
-      <c r="F58" s="28">
+      <c r="F58" s="24">
         <v>-1.4E-3</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
+      <c r="A59" s="18">
+        <v>46231</v>
+      </c>
+      <c r="B59" s="25">
+        <v>160788</v>
+      </c>
+      <c r="C59" s="25"/>
+      <c r="D59" s="21">
+        <v>74770957010</v>
+      </c>
+      <c r="E59" s="21">
+        <v>-37325878</v>
+      </c>
+      <c r="F59" s="24">
+        <v>5.9999999999999995E-4</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-    </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="24"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="18"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="24"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="18"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="24"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="18"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="24"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="18"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="18"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="18"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="24"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="18"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="24"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="18"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="18"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="24"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="18"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="24"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="18"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="18"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="18"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="24"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="18"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="18"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="18"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="24"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="18"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="29">
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="A49:B49"/>
@@ -1955,7 +2146,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8ADE70-F8B5-43C2-B046-025D01A118D2}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1970,7 +2161,7 @@
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -1987,11 +2178,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>5.56680161943319</v>
+        <v>-0.28763183125599201</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.53719635627530282</v>
+        <v>-2.775647171620323E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2002,11 +2193,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>0.58064516129032195</v>
+        <v>0.89801154586273202</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>5.3941935483870912E-2</v>
+        <v>8.3425272610647791E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,26 +2208,26 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>4.7808764940239001</v>
+        <v>-10</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.44175298804780838</v>
+        <v>-0.92400000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-4.1044776119402897</v>
+        <v>-2.65888456549935</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.24996268656716364</v>
+        <v>-0.16192607003891041</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2047,11 +2238,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>3.0042918454935599</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.14210300429184539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2062,11 +2253,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>4.6207497820401002</v>
+        <v>5.8333333333333304</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.20885789014821252</v>
+        <v>0.26366666666666649</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2077,11 +2268,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>-1.75081433224755</v>
+        <v>-3.7297969332780698</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9527687296416693E-2</v>
+        <v>-0.12681309573145438</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2092,11 +2283,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>1.92307692307692</v>
+        <v>0.31446540880503099</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>5.2499999999999922E-2</v>
+        <v>8.5849056603773451E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,11 +2298,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-0.23</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,11 +2313,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-1.3500482160077101</v>
+        <v>-0.58651026392961803</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-2.2545805207328757E-2</v>
+        <v>-9.7947214076246208E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2137,11 +2328,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-4.1920731707316996</v>
+        <v>3.0230708035003899</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-6.6234756097560854E-2</v>
+        <v>4.7764518695306159E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,11 +2343,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-2.734375</v>
+        <v>-9.9899598393574305</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-4.2929687500000001E-2</v>
+        <v>-0.15684236947791166</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,11 +2358,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-1.70118343195266</v>
+        <v>-0.97817908201655301</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9223372781065055E-2</v>
+        <v>-1.1053423626787049E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,11 +2373,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-1.378896882494</v>
+        <v>-0.48632218844984798</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-1.42026378896882E-2</v>
+        <v>-5.0091185410334341E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2197,11 +2388,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>0.32102728731942198</v>
+        <v>1.44</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>3.1460674157303354E-3</v>
+        <v>1.4112E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2403,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.9489795918367303</v>
+        <v>-9.9150141643059406</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6556122448979561E-2</v>
+        <v>-8.626062322946168E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,26 +2418,26 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>1.26050420168067</v>
+        <v>-3.63070539419087</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>7.4369747899159519E-3</v>
+        <v>-2.1421161825726131E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="4">
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-4.6210720887245801E-2</v>
+        <v>1.38696255201109</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3105360443622901E-4</v>
+        <v>6.9348127600554503E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,11 +2448,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>-1.5775635407537201</v>
+        <v>0.80142475512021305</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5723049956178557E-3</v>
+        <v>3.8468388245770225E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,11 +2463,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-2.31481481481481</v>
+        <v>-1.3270142180094699</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-9.7222222222222016E-3</v>
+        <v>-5.5734597156397734E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,11 +2478,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-1.1808576755748901</v>
+        <v>1.1320754716981101</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-4.7234307022995603E-3</v>
+        <v>4.5283018867924409E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,11 +2493,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>0</v>
+        <v>-1.1757425742574199</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4.4678217821781958E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,11 +2508,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>0.36496350364963498</v>
+        <v>-0.48484848484848397</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>9.1240875912408745E-4</v>
+        <v>-1.21212121212121E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,11 +2523,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>0.69625761531766694</v>
+        <v>-0.60501296456352605</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>1.7406440382941673E-3</v>
+        <v>-1.512532411408815E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,11 +2538,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>1.6380655226209</v>
+        <v>9.9769762087490399</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>3.93135725429016E-3</v>
+        <v>2.3944742900997695E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,11 +2553,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0</v>
+        <v>-1.3333333333333299</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3.0666666666666594E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2377,41 +2568,41 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>1.71385991058122</v>
+        <v>-0.439560439560439</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>3.4277198211624406E-3</v>
+        <v>-8.7912087912087804E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" s="13">
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>-4.0217391304347796</v>
+        <v>-8.8901472253680591</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-3.2173913043478234E-3</v>
+        <v>-7.1121177802944482E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="4">
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-4.6875</v>
+        <v>-1.44262295081967</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6874999999999998E-4</v>
+        <v>-1.4426229508196701E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,11 +2613,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>-8.61</v>
+        <v>0.59</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-0.68793899999999997</v>
+        <v>4.7141000000000002E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2437,76 +2628,76 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-6.98</v>
+        <v>1.95</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-0.53746000000000005</v>
+        <v>0.15015000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33" s="4">
         <v>2.5</v>
       </c>
       <c r="C33" s="4">
-        <v>0.38</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>9.4999999999999998E-3</v>
+        <v>3.5000000000000005E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="4">
         <v>0.78</v>
       </c>
       <c r="C34" s="4">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>2.9640000000000001E-3</v>
+        <v>1.0140000000000001E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="4">
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>-2.0099999999999998</v>
+        <v>2.96</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1657999999999996E-2</v>
+        <v>1.7167999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36" s="4">
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>-0.48</v>
+        <v>0.63</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8800000000000001E-4</v>
+        <v>3.7800000000000003E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" s="5">
         <f>SUM(B2:B36)</f>
@@ -2514,7 +2705,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-0.58505156229156896</v>
+        <v>-0.64868609833220436</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2540,20 +2731,20 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="27"/>
+      <c r="D53" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="26"/>
-      <c r="D53" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2570,7 +2761,7 @@
       <c r="E54" s="22">
         <v>-656504519</v>
       </c>
-      <c r="F54" s="28">
+      <c r="F54" s="24">
         <v>8.0999999999999996E-3</v>
       </c>
     </row>
@@ -2588,7 +2779,7 @@
       <c r="E55" s="22">
         <v>45631782</v>
       </c>
-      <c r="F55" s="28">
+      <c r="F55" s="24">
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
@@ -2606,40 +2797,904 @@
       <c r="E56" s="22">
         <v>706423581</v>
       </c>
-      <c r="F56" s="28">
+      <c r="F56" s="24">
         <v>-2.7000000000000001E-3</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
+      <c r="A57" s="18">
+        <v>46231</v>
+      </c>
+      <c r="B57" s="25">
+        <v>78840</v>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="21">
+        <v>39148877217</v>
+      </c>
+      <c r="E57" s="22">
+        <v>706423581</v>
+      </c>
+      <c r="F57" s="24">
+        <v>5.9999999999999995E-4</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="24"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="18"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="24"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="18"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="24"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="18"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="24"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="18"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="24"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="18"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="18"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="18"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="24"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="18"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="24"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="18"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="18"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="24"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="18"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="24"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="18"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="18"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="18"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="24"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="18"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="18"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="18"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="24"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="18"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="24"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="18"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="24"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="18"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="24"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="18"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="24"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="18"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="24"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="18"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="24"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="18"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="24"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="18"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="24"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="18"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="24"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="18"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="24"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="18"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="24"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="18"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="24"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="18"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="24"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="18"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="24"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="18"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="24"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="18"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="18"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="18"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="18"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="18"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="18"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="18"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="18"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="25"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="18"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="24"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="18"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="24"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="18"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="24"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="18"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="24"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="18"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="25"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="24"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="18"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="25"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="24"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="18"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="24"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="18"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="24"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="18"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="24"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="18"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="25"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="24"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="18"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="24"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="18"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="21"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="24"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="18"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+      <c r="D116" s="21"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="24"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="18"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="25"/>
+      <c r="D117" s="21"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="24"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="18"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="25"/>
+      <c r="D118" s="21"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="24"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="18"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="25"/>
+      <c r="D119" s="21"/>
+      <c r="E119" s="22"/>
+      <c r="F119" s="24"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="18"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="25"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="22"/>
+      <c r="F120" s="24"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="18"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="25"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="24"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="18"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="24"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="18"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="25"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="24"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="18"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="25"/>
+      <c r="D124" s="21"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="24"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="18"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="25"/>
+      <c r="D125" s="21"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="24"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="18"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="25"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="24"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="18"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="25"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="24"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="18"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+      <c r="D128" s="21"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="24"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="18"/>
+      <c r="B129" s="25"/>
+      <c r="C129" s="25"/>
+      <c r="D129" s="21"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="24"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="18"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="25"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="24"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="18"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="25"/>
+      <c r="D131" s="21"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="24"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="18"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="25"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="24"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="18"/>
+      <c r="B133" s="25"/>
+      <c r="C133" s="25"/>
+      <c r="D133" s="21"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="24"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="18"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="22"/>
+      <c r="F134" s="24"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="18"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="25"/>
+      <c r="D135" s="21"/>
+      <c r="E135" s="22"/>
+      <c r="F135" s="24"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="18"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="25"/>
+      <c r="D136" s="21"/>
+      <c r="E136" s="22"/>
+      <c r="F136" s="24"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="18"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="25"/>
+      <c r="D137" s="21"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="24"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="18"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="25"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="24"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="18"/>
+      <c r="B139" s="25"/>
+      <c r="C139" s="25"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="22"/>
+      <c r="F139" s="24"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="18"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="22"/>
+      <c r="F140" s="24"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="18"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="25"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="22"/>
+      <c r="F141" s="24"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="18"/>
+      <c r="B142" s="25"/>
+      <c r="C142" s="25"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="22"/>
+      <c r="F142" s="24"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="18"/>
+      <c r="B143" s="25"/>
+      <c r="C143" s="25"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="22"/>
+      <c r="F143" s="24"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="18"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="25"/>
+      <c r="D144" s="21"/>
+      <c r="E144" s="22"/>
+      <c r="F144" s="24"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="18"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="25"/>
+      <c r="D145" s="21"/>
+      <c r="E145" s="22"/>
+      <c r="F145" s="24"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="18"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+      <c r="D146" s="21"/>
+      <c r="E146" s="22"/>
+      <c r="F146" s="24"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="18"/>
+      <c r="B147" s="25"/>
+      <c r="C147" s="25"/>
+      <c r="D147" s="21"/>
+      <c r="E147" s="22"/>
+      <c r="F147" s="24"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="18"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="25"/>
+      <c r="D148" s="21"/>
+      <c r="E148" s="22"/>
+      <c r="F148" s="24"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="18"/>
+      <c r="B149" s="25"/>
+      <c r="C149" s="25"/>
+      <c r="D149" s="21"/>
+      <c r="E149" s="22"/>
+      <c r="F149" s="24"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="18"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="25"/>
+      <c r="D150" s="21"/>
+      <c r="E150" s="22"/>
+      <c r="F150" s="24"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="18"/>
+      <c r="B151" s="25"/>
+      <c r="C151" s="25"/>
+      <c r="D151" s="21"/>
+      <c r="E151" s="22"/>
+      <c r="F151" s="24"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="18"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+      <c r="D152" s="21"/>
+      <c r="E152" s="22"/>
+      <c r="F152" s="24"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="18"/>
+      <c r="B153" s="25"/>
+      <c r="C153" s="25"/>
+      <c r="D153" s="21"/>
+      <c r="E153" s="22"/>
+      <c r="F153" s="24"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="18"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="25"/>
+      <c r="D154" s="21"/>
+      <c r="E154" s="22"/>
+      <c r="F154" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="104">
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="A44:B44"/>
@@ -2654,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545E6D6F-F0E5-4763-8F78-0375F1A09A45}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -2686,11 +3741,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>-0.48721071863581</v>
+        <v>1.5299877600979099</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.25700365408038978</v>
+        <v>0.80706854345164747</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2701,11 +3756,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-3.4764826175869099</v>
+        <v>-9.9576271186440692</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.38658486707566431</v>
+        <v>-1.1072881355932205</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2716,11 +3771,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-4.7012732615083204</v>
+        <v>-3.28879753340185</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4916748285994102E-2</v>
+        <v>-1.7430626927029805E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2731,16 +3786,16 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.62323799999999996</v>
+        <v>-0.19979400000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="5">
         <f>B2++B3+B4+B5</f>
@@ -2749,7 +3804,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>-4.5267269442048286E-2</v>
+        <v>-0.51744421906860283</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2784,20 +3839,20 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="27"/>
+      <c r="D31" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2814,7 +3869,7 @@
       <c r="E32" s="21">
         <v>578476685</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="24">
         <v>3.3999999999999998E-3</v>
       </c>
     </row>
@@ -2832,7 +3887,7 @@
       <c r="E33" s="21">
         <v>630289948</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="24">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
@@ -2850,56 +3905,985 @@
       <c r="E34" s="21">
         <v>781254453</v>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="24">
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
+      <c r="A35" s="23">
+        <v>46231</v>
+      </c>
+      <c r="B35" s="25">
+        <v>49817</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="21">
+        <v>30985486603</v>
+      </c>
+      <c r="E35" s="21">
+        <v>577239728</v>
+      </c>
+      <c r="F35" s="24">
+        <v>1.6000000000000001E-3</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="24"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E43" s="24"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E44" s="24"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E45" s="24"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E46" s="24"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="24"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="23"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="24"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="23"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="24"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="23"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="24"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="23"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="24"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="23"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="24"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="23"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="24"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="23"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="24"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="23"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="24"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="23"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="23"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="24"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="23"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="24"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="23"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="24"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="23"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="24"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="23"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="24"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="23"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="24"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="23"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="24"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="23"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="24"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="23"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="24"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="23"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="24"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="23"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="24"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="23"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="24"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="23"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="23"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="23"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="24"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="23"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="24"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="23"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="23"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="24"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="23"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="24"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="23"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="23"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="23"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="24"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="23"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="23"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="23"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="24"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="23"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="24"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="23"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="24"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="23"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="24"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="23"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="24"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="23"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="24"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="23"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="24"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="23"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="24"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="23"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="24"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="23"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="24"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="23"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="24"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="23"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="24"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="23"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="24"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="23"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="24"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="23"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="24"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="23"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="24"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="23"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="23"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="23"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="23"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="23"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="23"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="23"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="23"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="25"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="23"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="21"/>
+      <c r="F104" s="24"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="23"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="21"/>
+      <c r="F105" s="24"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="23"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="24"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="23"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="24"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="23"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="25"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="24"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="23"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="25"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="24"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="23"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="24"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="23"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="21"/>
+      <c r="F111" s="24"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="23"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="21"/>
+      <c r="F112" s="24"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="23"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="25"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="24"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="23"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="21"/>
+      <c r="F114" s="24"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="23"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="21"/>
+      <c r="E115" s="21"/>
+      <c r="F115" s="24"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="23"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+      <c r="D116" s="21"/>
+      <c r="E116" s="21"/>
+      <c r="F116" s="24"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="23"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="25"/>
+      <c r="D117" s="21"/>
+      <c r="E117" s="21"/>
+      <c r="F117" s="24"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="23"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="25"/>
+      <c r="D118" s="21"/>
+      <c r="E118" s="21"/>
+      <c r="F118" s="24"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="23"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="25"/>
+      <c r="D119" s="21"/>
+      <c r="E119" s="21"/>
+      <c r="F119" s="24"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="23"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="25"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="24"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="23"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="25"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="24"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="23"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="24"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="23"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="25"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="21"/>
+      <c r="F123" s="24"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="23"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="25"/>
+      <c r="D124" s="21"/>
+      <c r="E124" s="21"/>
+      <c r="F124" s="24"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="23"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="25"/>
+      <c r="D125" s="21"/>
+      <c r="E125" s="21"/>
+      <c r="F125" s="24"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="23"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="25"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="24"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="23"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="25"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="24"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="23"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+      <c r="D128" s="21"/>
+      <c r="E128" s="21"/>
+      <c r="F128" s="24"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="23"/>
+      <c r="B129" s="25"/>
+      <c r="C129" s="25"/>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="24"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="23"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="25"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="21"/>
+      <c r="F130" s="24"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="23"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="25"/>
+      <c r="D131" s="21"/>
+      <c r="E131" s="21"/>
+      <c r="F131" s="24"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="23"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="25"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="21"/>
+      <c r="F132" s="24"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="23"/>
+      <c r="B133" s="25"/>
+      <c r="C133" s="25"/>
+      <c r="D133" s="21"/>
+      <c r="E133" s="21"/>
+      <c r="F133" s="24"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="23"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="21"/>
+      <c r="F134" s="24"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="23"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="25"/>
+      <c r="D135" s="21"/>
+      <c r="E135" s="21"/>
+      <c r="F135" s="24"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="23"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="25"/>
+      <c r="D136" s="21"/>
+      <c r="E136" s="21"/>
+      <c r="F136" s="24"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="23"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="25"/>
+      <c r="D137" s="21"/>
+      <c r="E137" s="21"/>
+      <c r="F137" s="24"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="23"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="25"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="24"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="23"/>
+      <c r="B139" s="25"/>
+      <c r="C139" s="25"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="24"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="23"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="24"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="23"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="25"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="113">
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="A10:B10"/>
@@ -2913,7 +4897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F549F2-A66C-43F1-8B7E-B9FC6B9E004D}">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2940,97 +4924,97 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="4">
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.8181818181818099</v>
+        <v>-1.0802469135802399</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.77345454545454184</v>
+        <v>-0.45953703703703402</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="4">
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>0.12894906511927701</v>
+        <v>0</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>4.1702127659574185E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" s="4">
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>0.12254901960784299</v>
+        <v>-0.55079559363525099</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>1.496323529411763E-2</v>
+        <v>-6.7252141982864153E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="4">
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>-4.2105263157894699</v>
+        <v>4.7337278106508798</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>-0.45978947368421008</v>
+        <v>0.51692307692307604</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="4">
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.89005235602094201</v>
+        <v>-1.9545694664553599</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-5.2424083769633478E-2</v>
+        <v>-0.1151241415742207</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4">
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>9.9898063200815397</v>
+        <v>-9.3605189990732107</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.56742099898063147</v>
+        <v>-0.5316774791473583</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" s="5">
         <f>B2+B3+B4+B5+B6+B7</f>
@@ -3039,7 +5023,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-0.66158174097406219</v>
+        <v>-0.65666772281840113</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3092,20 +5076,20 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="27"/>
+      <c r="D37" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3122,7 +5106,7 @@
       <c r="E38" s="21">
         <v>95865997</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="24">
         <v>5.4000000000000003E-3</v>
       </c>
     </row>
@@ -3140,7 +5124,7 @@
       <c r="E39" s="21">
         <v>42490384</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="24">
         <v>-8.9999999999999998E-4</v>
       </c>
     </row>
@@ -3158,57 +5142,1210 @@
       <c r="E40" s="21">
         <v>99781628</v>
       </c>
-      <c r="F40" s="28">
+      <c r="F40" s="24">
         <v>-8.5000000000000006E-3</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E41" s="24"/>
+      <c r="A41" s="23">
+        <v>46231</v>
+      </c>
+      <c r="B41" s="25">
+        <v>7221</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="21">
+        <v>1220111851</v>
+      </c>
+      <c r="E41" s="21">
+        <v>60385808</v>
+      </c>
+      <c r="F41" s="24">
+        <v>-6.4000000000000003E-3</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E42" s="24"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E43" s="24"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E44" s="24"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E45" s="24"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E46" s="24"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E47" s="24"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E48" s="24"/>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="24"/>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="24"/>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="24"/>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="24"/>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="24"/>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="24"/>
-    </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="24"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="24"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="23"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="24"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="23"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="24"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="23"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="24"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="23"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="24"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="23"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="24"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="23"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="24"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="23"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="23"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="24"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="23"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="24"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="23"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="24"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="23"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="24"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="23"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="24"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="23"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="24"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="23"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="24"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="23"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="24"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="23"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="24"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="23"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="24"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="23"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="24"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="23"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="24"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="23"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="23"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="23"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="24"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="23"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="24"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="23"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="23"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="24"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="23"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="24"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="23"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="23"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="23"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="24"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="23"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="23"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="23"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="24"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="23"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="24"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="23"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="24"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="23"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="24"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="23"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="24"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="23"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="24"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="23"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="24"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="23"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="24"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="23"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="24"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="23"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="24"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="23"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="24"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="23"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="24"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="23"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="24"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="23"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="24"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="23"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="24"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="23"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="24"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="23"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="23"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="23"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="23"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="23"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="23"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="23"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="23"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="25"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="23"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="21"/>
+      <c r="F104" s="24"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="23"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="21"/>
+      <c r="E105" s="21"/>
+      <c r="F105" s="24"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="23"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="24"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="23"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="24"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="23"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="25"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="24"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="23"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="25"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="24"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="23"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="24"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="23"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="21"/>
+      <c r="F111" s="24"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="23"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="21"/>
+      <c r="F112" s="24"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="23"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="25"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="24"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="23"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="21"/>
+      <c r="F114" s="24"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="23"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="21"/>
+      <c r="E115" s="21"/>
+      <c r="F115" s="24"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="23"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+      <c r="D116" s="21"/>
+      <c r="E116" s="21"/>
+      <c r="F116" s="24"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="23"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="25"/>
+      <c r="D117" s="21"/>
+      <c r="E117" s="21"/>
+      <c r="F117" s="24"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="23"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="25"/>
+      <c r="D118" s="21"/>
+      <c r="E118" s="21"/>
+      <c r="F118" s="24"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="23"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="25"/>
+      <c r="D119" s="21"/>
+      <c r="E119" s="21"/>
+      <c r="F119" s="24"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="23"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="25"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="24"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="23"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="25"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="24"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="23"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="25"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="24"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="23"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="25"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="21"/>
+      <c r="F123" s="24"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="23"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="25"/>
+      <c r="D124" s="21"/>
+      <c r="E124" s="21"/>
+      <c r="F124" s="24"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="23"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="25"/>
+      <c r="D125" s="21"/>
+      <c r="E125" s="21"/>
+      <c r="F125" s="24"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="23"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="25"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="24"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="23"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="25"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="24"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="23"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="25"/>
+      <c r="D128" s="21"/>
+      <c r="E128" s="21"/>
+      <c r="F128" s="24"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="23"/>
+      <c r="B129" s="25"/>
+      <c r="C129" s="25"/>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="24"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="23"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="25"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="21"/>
+      <c r="F130" s="24"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="23"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="25"/>
+      <c r="D131" s="21"/>
+      <c r="E131" s="21"/>
+      <c r="F131" s="24"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="23"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="25"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="21"/>
+      <c r="F132" s="24"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="23"/>
+      <c r="B133" s="25"/>
+      <c r="C133" s="25"/>
+      <c r="D133" s="21"/>
+      <c r="E133" s="21"/>
+      <c r="F133" s="24"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="23"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="25"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="21"/>
+      <c r="F134" s="24"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="23"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="25"/>
+      <c r="D135" s="21"/>
+      <c r="E135" s="21"/>
+      <c r="F135" s="24"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="23"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="25"/>
+      <c r="D136" s="21"/>
+      <c r="E136" s="21"/>
+      <c r="F136" s="24"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="23"/>
+      <c r="B137" s="25"/>
+      <c r="C137" s="25"/>
+      <c r="D137" s="21"/>
+      <c r="E137" s="21"/>
+      <c r="F137" s="24"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="23"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="25"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="24"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="23"/>
+      <c r="B139" s="25"/>
+      <c r="C139" s="25"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="24"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="23"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="25"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="24"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="23"/>
+      <c r="B141" s="25"/>
+      <c r="C141" s="25"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="24"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="23"/>
+      <c r="B142" s="25"/>
+      <c r="C142" s="25"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="24"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="23"/>
+      <c r="B143" s="25"/>
+      <c r="C143" s="25"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="24"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="23"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="25"/>
+      <c r="D144" s="21"/>
+      <c r="E144" s="21"/>
+      <c r="F144" s="24"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="23"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="25"/>
+      <c r="D145" s="21"/>
+      <c r="E145" s="21"/>
+      <c r="F145" s="24"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="23"/>
+      <c r="B146" s="25"/>
+      <c r="C146" s="25"/>
+      <c r="D146" s="21"/>
+      <c r="E146" s="21"/>
+      <c r="F146" s="24"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="23"/>
+      <c r="B147" s="25"/>
+      <c r="C147" s="25"/>
+      <c r="D147" s="21"/>
+      <c r="E147" s="21"/>
+      <c r="F147" s="24"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="23"/>
+      <c r="B148" s="25"/>
+      <c r="C148" s="25"/>
+      <c r="D148" s="21"/>
+      <c r="E148" s="21"/>
+      <c r="F148" s="24"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="23"/>
+      <c r="B149" s="25"/>
+      <c r="C149" s="25"/>
+      <c r="D149" s="21"/>
+      <c r="E149" s="21"/>
+      <c r="F149" s="24"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="23"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="25"/>
+      <c r="D150" s="21"/>
+      <c r="E150" s="21"/>
+      <c r="F150" s="24"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="23"/>
+      <c r="B151" s="25"/>
+      <c r="C151" s="25"/>
+      <c r="D151" s="21"/>
+      <c r="E151" s="21"/>
+      <c r="F151" s="24"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="23"/>
+      <c r="B152" s="25"/>
+      <c r="C152" s="25"/>
+      <c r="D152" s="21"/>
+      <c r="E152" s="21"/>
+      <c r="F152" s="24"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="23"/>
+      <c r="B153" s="25"/>
+      <c r="C153" s="25"/>
+      <c r="D153" s="21"/>
+      <c r="E153" s="21"/>
+      <c r="F153" s="24"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="23"/>
+      <c r="B154" s="25"/>
+      <c r="C154" s="25"/>
+      <c r="D154" s="21"/>
+      <c r="E154" s="21"/>
+      <c r="F154" s="24"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="23"/>
+      <c r="B155" s="25"/>
+      <c r="C155" s="25"/>
+      <c r="D155" s="21"/>
+      <c r="E155" s="21"/>
+      <c r="F155" s="24"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="23"/>
+      <c r="B156" s="25"/>
+      <c r="C156" s="25"/>
+      <c r="D156" s="21"/>
+      <c r="E156" s="21"/>
+      <c r="F156" s="24"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="23"/>
+      <c r="B157" s="25"/>
+      <c r="C157" s="25"/>
+      <c r="D157" s="21"/>
+      <c r="E157" s="21"/>
+      <c r="F157" s="24"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="23"/>
+      <c r="B158" s="25"/>
+      <c r="C158" s="25"/>
+      <c r="D158" s="21"/>
+      <c r="E158" s="21"/>
+      <c r="F158" s="24"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="23"/>
+      <c r="B159" s="25"/>
+      <c r="C159" s="25"/>
+      <c r="D159" s="21"/>
+      <c r="E159" s="21"/>
+      <c r="F159" s="24"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="23"/>
+      <c r="B160" s="25"/>
+      <c r="C160" s="25"/>
+      <c r="D160" s="21"/>
+      <c r="E160" s="21"/>
+      <c r="F160" s="24"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="23"/>
+      <c r="B161" s="25"/>
+      <c r="C161" s="25"/>
+      <c r="D161" s="21"/>
+      <c r="E161" s="21"/>
+      <c r="F161" s="24"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="23"/>
+      <c r="B162" s="25"/>
+      <c r="C162" s="25"/>
+      <c r="D162" s="21"/>
+      <c r="E162" s="21"/>
+      <c r="F162" s="24"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="23"/>
+      <c r="B163" s="25"/>
+      <c r="C163" s="25"/>
+      <c r="D163" s="21"/>
+      <c r="E163" s="21"/>
+      <c r="F163" s="24"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="23"/>
+      <c r="B164" s="25"/>
+      <c r="C164" s="25"/>
+      <c r="D164" s="21"/>
+      <c r="E164" s="21"/>
+      <c r="F164" s="24"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="23"/>
+      <c r="B165" s="25"/>
+      <c r="C165" s="25"/>
+      <c r="D165" s="21"/>
+      <c r="E165" s="21"/>
+      <c r="F165" s="24"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="23"/>
+      <c r="B166" s="25"/>
+      <c r="C166" s="25"/>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="24"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="23"/>
+      <c r="B167" s="25"/>
+      <c r="C167" s="25"/>
+      <c r="D167" s="21"/>
+      <c r="E167" s="21"/>
+      <c r="F167" s="24"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="23"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="25"/>
+      <c r="D168" s="21"/>
+      <c r="E168" s="21"/>
+      <c r="F168" s="24"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="23"/>
+      <c r="B169" s="25"/>
+      <c r="C169" s="25"/>
+      <c r="D169" s="21"/>
+      <c r="E169" s="21"/>
+      <c r="F169" s="24"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="23"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="25"/>
+      <c r="D170" s="21"/>
+      <c r="E170" s="21"/>
+      <c r="F170" s="24"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="23"/>
+      <c r="B171" s="25"/>
+      <c r="C171" s="25"/>
+      <c r="D171" s="21"/>
+      <c r="E171" s="21"/>
+      <c r="F171" s="24"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="23"/>
+      <c r="B172" s="25"/>
+      <c r="C172" s="25"/>
+      <c r="D172" s="21"/>
+      <c r="E172" s="21"/>
+      <c r="F172" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="138">
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="B166:C166"/>
+    <mergeCell ref="B167:C167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEDE6F5-80D0-423A-8A8F-6CE34AAC14C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03F911C-73C3-421E-89CC-A80B88370687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="780" windowWidth="17010" windowHeight="18450" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35550" yWindow="1920" windowWidth="17010" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -398,16 +398,15 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,15 +709,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="4.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -959,85 +957,82 @@
         <v>-0.70196829955820472</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="6"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="17"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
+      <c r="E29" s="17"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="9"/>
       <c r="D30" s="19"/>
-      <c r="E30" s="17"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
@@ -1045,107 +1040,116 @@
         <v>52</v>
       </c>
       <c r="C31" s="27"/>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="27"/>
+      <c r="E31" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="F31" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="18">
         <v>46226</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <v>98970</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26">
+      <c r="C32" s="26"/>
+      <c r="D32" s="25">
         <v>232874657613</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="21">
+      <c r="E32" s="21">
         <v>1310146537</v>
       </c>
-      <c r="G32" s="24">
+      <c r="F32" s="24">
         <v>2.1100000000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
         <v>46227</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="26">
         <v>99051</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26">
+      <c r="C33" s="26"/>
+      <c r="D33" s="25">
         <v>227320292084</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="22">
+      <c r="E33" s="22">
         <v>-6072488957</v>
       </c>
-      <c r="G33" s="24">
+      <c r="F33" s="24">
         <v>2.2000000000000001E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
         <v>46230</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <v>98455</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="26">
+      <c r="C34" s="26"/>
+      <c r="D34" s="25">
         <v>229116006481</v>
       </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="22">
+      <c r="E34" s="22">
         <v>291803673</v>
       </c>
-      <c r="G34" s="24">
+      <c r="F34" s="24">
         <v>6.6E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
         <v>46231</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <v>98583</v>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="26">
+      <c r="C35" s="26"/>
+      <c r="D35" s="25">
         <v>232227975662</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="22">
+      <c r="E35" s="22">
         <v>-464304680</v>
       </c>
-      <c r="G35" s="24">
+      <c r="F35" s="24">
         <v>1.5600000000000001E-2</v>
       </c>
     </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="18">
+        <v>46232</v>
+      </c>
+      <c r="B36" s="26">
+        <v>98915</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="25">
+        <v>226192717226</v>
+      </c>
+      <c r="E36" s="22">
+        <v>-7041302653</v>
+      </c>
+      <c r="F36" s="24">
+        <v>4.3E-3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
+  <mergeCells count="8">
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -1830,15 +1834,15 @@
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
@@ -1864,10 +1868,10 @@
       <c r="A56" s="18">
         <v>46226</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="26">
         <v>160454</v>
       </c>
-      <c r="C56" s="25"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="21">
         <v>74464707242</v>
       </c>
@@ -1882,10 +1886,10 @@
       <c r="A57" s="18">
         <v>46227</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B57" s="26">
         <v>159246</v>
       </c>
-      <c r="C57" s="25"/>
+      <c r="C57" s="26"/>
       <c r="D57" s="21">
         <v>74038207243</v>
       </c>
@@ -1900,10 +1904,10 @@
       <c r="A58" s="18">
         <v>46230</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B58" s="26">
         <v>159672</v>
       </c>
-      <c r="C58" s="25"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="21">
         <v>74765554505</v>
       </c>
@@ -1918,10 +1922,10 @@
       <c r="A59" s="18">
         <v>46231</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B59" s="26">
         <v>160788</v>
       </c>
-      <c r="C59" s="25"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="21">
         <v>74770957010</v>
       </c>
@@ -1933,183 +1937,213 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="24"/>
+      <c r="A60" s="18">
+        <v>46232</v>
+      </c>
+      <c r="B60" s="26">
+        <v>162385</v>
+      </c>
+      <c r="C60" s="26"/>
+      <c r="D60" s="21">
+        <v>72261693709</v>
+      </c>
+      <c r="E60" s="21">
+        <v>-2205788922</v>
+      </c>
+      <c r="F60" s="24">
+        <v>-4.1000000000000003E-3</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="28"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="19"/>
       <c r="E61" s="22"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="28"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="19"/>
       <c r="E62" s="22"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="28"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="19"/>
       <c r="E63" s="22"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="28"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="19"/>
       <c r="E64" s="22"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="28"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="19"/>
       <c r="E65" s="22"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="28"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="19"/>
       <c r="E66" s="22"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="28"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="19"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="28"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="19"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="28"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="19"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="28"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="19"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="28"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="19"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="28"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="19"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="28"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="19"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="28"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="19"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="28"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="19"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="28"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="19"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="28"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="19"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="28"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="19"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="28"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="19"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="28"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="19"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="28"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="19"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2119,26 +2153,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2717,15 +2731,15 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="17"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="26"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
     </row>
@@ -2751,10 +2765,10 @@
       <c r="A54" s="18">
         <v>46226</v>
       </c>
-      <c r="B54" s="25">
+      <c r="B54" s="26">
         <v>78223</v>
       </c>
-      <c r="C54" s="25"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="21">
         <v>38343912280</v>
       </c>
@@ -2769,10 +2783,10 @@
       <c r="A55" s="18">
         <v>46227</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B55" s="26">
         <v>78055</v>
       </c>
-      <c r="C55" s="25"/>
+      <c r="C55" s="26"/>
       <c r="D55" s="21">
         <v>38547597437</v>
       </c>
@@ -2787,10 +2801,10 @@
       <c r="A56" s="18">
         <v>46230</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="26">
         <v>78840</v>
       </c>
-      <c r="C56" s="25"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="21">
         <v>39148877217</v>
       </c>
@@ -2805,10 +2819,10 @@
       <c r="A57" s="18">
         <v>46231</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B57" s="26">
         <v>78840</v>
       </c>
-      <c r="C57" s="25"/>
+      <c r="C57" s="26"/>
       <c r="D57" s="21">
         <v>39148877217</v>
       </c>
@@ -2820,783 +2834,884 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="24"/>
+      <c r="A58" s="23">
+        <v>46232</v>
+      </c>
+      <c r="B58" s="26">
+        <v>80830</v>
+      </c>
+      <c r="C58" s="26"/>
+      <c r="D58" s="21">
+        <v>38188651284</v>
+      </c>
+      <c r="E58" s="21">
+        <v>-933851594</v>
+      </c>
+      <c r="F58" s="24">
+        <v>-4.3E-3</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="21"/>
       <c r="E59" s="22"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
       <c r="D60" s="21"/>
       <c r="E60" s="22"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
       <c r="D61" s="21"/>
       <c r="E61" s="22"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
       <c r="D62" s="21"/>
       <c r="E62" s="22"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="21"/>
       <c r="E63" s="22"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="21"/>
       <c r="E64" s="22"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="21"/>
       <c r="E65" s="22"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="21"/>
       <c r="E66" s="22"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
       <c r="D67" s="21"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
       <c r="D68" s="21"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
       <c r="D69" s="21"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="21"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="21"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="21"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
       <c r="D73" s="21"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
       <c r="D74" s="21"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
       <c r="D76" s="21"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="21"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="21"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="21"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
       <c r="D80" s="21"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
       <c r="D81" s="21"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
       <c r="D82" s="21"/>
       <c r="E82" s="22"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
       <c r="D83" s="21"/>
       <c r="E83" s="22"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
       <c r="D84" s="21"/>
       <c r="E84" s="22"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
       <c r="D85" s="21"/>
       <c r="E85" s="22"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
       <c r="D86" s="21"/>
       <c r="E86" s="22"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="18"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
       <c r="D87" s="21"/>
       <c r="E87" s="22"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
       <c r="D88" s="21"/>
       <c r="E88" s="22"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="18"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
       <c r="D89" s="21"/>
       <c r="E89" s="22"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="18"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
       <c r="D90" s="21"/>
       <c r="E90" s="22"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="18"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
       <c r="D91" s="21"/>
       <c r="E91" s="22"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
       <c r="D92" s="21"/>
       <c r="E92" s="22"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
       <c r="D93" s="21"/>
       <c r="E93" s="22"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
       <c r="D94" s="21"/>
       <c r="E94" s="22"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
       <c r="D95" s="21"/>
       <c r="E95" s="22"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
       <c r="D96" s="21"/>
       <c r="E96" s="22"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
       <c r="D97" s="21"/>
       <c r="E97" s="22"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
       <c r="D98" s="21"/>
       <c r="E98" s="22"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
       <c r="D99" s="21"/>
       <c r="E99" s="22"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="25"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
       <c r="D100" s="21"/>
       <c r="E100" s="22"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="25"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
       <c r="D101" s="21"/>
       <c r="E101" s="22"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
       <c r="D102" s="21"/>
       <c r="E102" s="22"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="25"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
       <c r="D103" s="21"/>
       <c r="E103" s="22"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
       <c r="D104" s="21"/>
       <c r="E104" s="22"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
       <c r="D105" s="21"/>
       <c r="E105" s="22"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="18"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
       <c r="D106" s="21"/>
       <c r="E106" s="22"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="18"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
       <c r="D107" s="21"/>
       <c r="E107" s="22"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="18"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="25"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
       <c r="D108" s="21"/>
       <c r="E108" s="22"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="18"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
       <c r="D109" s="21"/>
       <c r="E109" s="22"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="25"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
       <c r="D110" s="21"/>
       <c r="E110" s="22"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="18"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
       <c r="D111" s="21"/>
       <c r="E111" s="22"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="18"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="25"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="18"/>
-      <c r="B113" s="25"/>
-      <c r="C113" s="25"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
       <c r="D113" s="21"/>
       <c r="E113" s="22"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="18"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
       <c r="D114" s="21"/>
       <c r="E114" s="22"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="18"/>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
       <c r="D115" s="21"/>
       <c r="E115" s="22"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="18"/>
-      <c r="B116" s="25"/>
-      <c r="C116" s="25"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
       <c r="D116" s="21"/>
       <c r="E116" s="22"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="18"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="25"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
       <c r="D117" s="21"/>
       <c r="E117" s="22"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="18"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="25"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
       <c r="D118" s="21"/>
       <c r="E118" s="22"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="18"/>
-      <c r="B119" s="25"/>
-      <c r="C119" s="25"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
       <c r="D119" s="21"/>
       <c r="E119" s="22"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="18"/>
-      <c r="B120" s="25"/>
-      <c r="C120" s="25"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
       <c r="D120" s="21"/>
       <c r="E120" s="22"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="18"/>
-      <c r="B121" s="25"/>
-      <c r="C121" s="25"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
       <c r="D121" s="21"/>
       <c r="E121" s="22"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
-      <c r="B122" s="25"/>
-      <c r="C122" s="25"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
       <c r="D122" s="21"/>
       <c r="E122" s="22"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="18"/>
-      <c r="B123" s="25"/>
-      <c r="C123" s="25"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
       <c r="D123" s="21"/>
       <c r="E123" s="22"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="18"/>
-      <c r="B124" s="25"/>
-      <c r="C124" s="25"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="26"/>
       <c r="D124" s="21"/>
       <c r="E124" s="22"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="18"/>
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
       <c r="D125" s="21"/>
       <c r="E125" s="22"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="18"/>
-      <c r="B126" s="25"/>
-      <c r="C126" s="25"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
       <c r="D126" s="21"/>
       <c r="E126" s="22"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="18"/>
-      <c r="B127" s="25"/>
-      <c r="C127" s="25"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
       <c r="D127" s="21"/>
       <c r="E127" s="22"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="18"/>
-      <c r="B128" s="25"/>
-      <c r="C128" s="25"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
       <c r="D128" s="21"/>
       <c r="E128" s="22"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="18"/>
-      <c r="B129" s="25"/>
-      <c r="C129" s="25"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
       <c r="D129" s="21"/>
       <c r="E129" s="22"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="18"/>
-      <c r="B130" s="25"/>
-      <c r="C130" s="25"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
       <c r="D130" s="21"/>
       <c r="E130" s="22"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="18"/>
-      <c r="B131" s="25"/>
-      <c r="C131" s="25"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
       <c r="D131" s="21"/>
       <c r="E131" s="22"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="18"/>
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
       <c r="D132" s="21"/>
       <c r="E132" s="22"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="18"/>
-      <c r="B133" s="25"/>
-      <c r="C133" s="25"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="26"/>
       <c r="D133" s="21"/>
       <c r="E133" s="22"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="25"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
       <c r="D134" s="21"/>
       <c r="E134" s="22"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="18"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="25"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="26"/>
       <c r="D135" s="21"/>
       <c r="E135" s="22"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="18"/>
-      <c r="B136" s="25"/>
-      <c r="C136" s="25"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
       <c r="D136" s="21"/>
       <c r="E136" s="22"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="18"/>
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="26"/>
       <c r="D137" s="21"/>
       <c r="E137" s="22"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="18"/>
-      <c r="B138" s="25"/>
-      <c r="C138" s="25"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
       <c r="D138" s="21"/>
       <c r="E138" s="22"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="18"/>
-      <c r="B139" s="25"/>
-      <c r="C139" s="25"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
       <c r="D139" s="21"/>
       <c r="E139" s="22"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="18"/>
-      <c r="B140" s="25"/>
-      <c r="C140" s="25"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
       <c r="D140" s="21"/>
       <c r="E140" s="22"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="18"/>
-      <c r="B141" s="25"/>
-      <c r="C141" s="25"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="26"/>
       <c r="D141" s="21"/>
       <c r="E141" s="22"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="18"/>
-      <c r="B142" s="25"/>
-      <c r="C142" s="25"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="26"/>
       <c r="D142" s="21"/>
       <c r="E142" s="22"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="18"/>
-      <c r="B143" s="25"/>
-      <c r="C143" s="25"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="26"/>
       <c r="D143" s="21"/>
       <c r="E143" s="22"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="18"/>
-      <c r="B144" s="25"/>
-      <c r="C144" s="25"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="26"/>
       <c r="D144" s="21"/>
       <c r="E144" s="22"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="18"/>
-      <c r="B145" s="25"/>
-      <c r="C145" s="25"/>
+      <c r="B145" s="26"/>
+      <c r="C145" s="26"/>
       <c r="D145" s="21"/>
       <c r="E145" s="22"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="18"/>
-      <c r="B146" s="25"/>
-      <c r="C146" s="25"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="26"/>
       <c r="D146" s="21"/>
       <c r="E146" s="22"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="18"/>
-      <c r="B147" s="25"/>
-      <c r="C147" s="25"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="26"/>
       <c r="D147" s="21"/>
       <c r="E147" s="22"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="18"/>
-      <c r="B148" s="25"/>
-      <c r="C148" s="25"/>
+      <c r="B148" s="26"/>
+      <c r="C148" s="26"/>
       <c r="D148" s="21"/>
       <c r="E148" s="22"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="18"/>
-      <c r="B149" s="25"/>
-      <c r="C149" s="25"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
       <c r="D149" s="21"/>
       <c r="E149" s="22"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="18"/>
-      <c r="B150" s="25"/>
-      <c r="C150" s="25"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="26"/>
       <c r="D150" s="21"/>
       <c r="E150" s="22"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="18"/>
-      <c r="B151" s="25"/>
-      <c r="C151" s="25"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="26"/>
       <c r="D151" s="21"/>
       <c r="E151" s="22"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
-      <c r="B152" s="25"/>
-      <c r="C152" s="25"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="26"/>
       <c r="D152" s="21"/>
       <c r="E152" s="22"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="18"/>
-      <c r="B153" s="25"/>
-      <c r="C153" s="25"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="26"/>
       <c r="D153" s="21"/>
       <c r="E153" s="22"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="18"/>
-      <c r="B154" s="25"/>
-      <c r="C154" s="25"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="26"/>
       <c r="D154" s="21"/>
       <c r="E154" s="22"/>
       <c r="F154" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3610,97 +3725,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3825,15 +3849,15 @@
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
@@ -3859,10 +3883,10 @@
       <c r="A32" s="23">
         <v>46226</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <v>48221</v>
       </c>
-      <c r="C32" s="25"/>
+      <c r="C32" s="26"/>
       <c r="D32" s="21">
         <v>28591206600</v>
       </c>
@@ -3877,10 +3901,10 @@
       <c r="A33" s="23">
         <v>46227</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="26">
         <v>48802</v>
       </c>
-      <c r="C33" s="25"/>
+      <c r="C33" s="26"/>
       <c r="D33" s="21">
         <v>29255953804</v>
       </c>
@@ -3895,10 +3919,10 @@
       <c r="A34" s="23">
         <v>46230</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <v>49403</v>
       </c>
-      <c r="C34" s="25"/>
+      <c r="C34" s="26"/>
       <c r="D34" s="21">
         <v>30359209400</v>
       </c>
@@ -3913,10 +3937,10 @@
       <c r="A35" s="23">
         <v>46231</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <v>49817</v>
       </c>
-      <c r="C35" s="25"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="21">
         <v>30985486603</v>
       </c>
@@ -3928,855 +3952,966 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="23"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="24"/>
+      <c r="A36" s="23">
+        <v>46232</v>
+      </c>
+      <c r="B36" s="26">
+        <v>50631</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="21">
+        <v>32047144824</v>
+      </c>
+      <c r="E36" s="21">
+        <v>1031302629</v>
+      </c>
+      <c r="F36" s="24">
+        <v>1E-3</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="24"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
       <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="25"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="25"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="25"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="25"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="25"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="25"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="25"/>
-      <c r="C113" s="25"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="25"/>
-      <c r="C116" s="25"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="25"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="25"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="25"/>
-      <c r="C119" s="25"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="25"/>
-      <c r="C120" s="25"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="25"/>
-      <c r="C121" s="25"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="25"/>
-      <c r="C122" s="25"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="25"/>
-      <c r="C123" s="25"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="25"/>
-      <c r="C124" s="25"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="26"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="25"/>
-      <c r="C126" s="25"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="25"/>
-      <c r="C127" s="25"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="25"/>
-      <c r="C128" s="25"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="25"/>
-      <c r="C129" s="25"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="25"/>
-      <c r="C130" s="25"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="25"/>
-      <c r="C131" s="25"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="25"/>
-      <c r="C133" s="25"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="26"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="25"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="25"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="26"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="25"/>
-      <c r="C136" s="25"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="26"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="25"/>
-      <c r="C138" s="25"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="25"/>
-      <c r="C139" s="25"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="25"/>
-      <c r="C140" s="25"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="25"/>
-      <c r="C141" s="25"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="26"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4789,107 +4924,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5048,16 +5082,16 @@
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="17"/>
@@ -5096,10 +5130,10 @@
       <c r="A38" s="23">
         <v>46226</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="26">
         <v>6356</v>
       </c>
-      <c r="C38" s="25"/>
+      <c r="C38" s="26"/>
       <c r="D38" s="21">
         <v>1033181017</v>
       </c>
@@ -5114,10 +5148,10 @@
       <c r="A39" s="23">
         <v>46227</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="26">
         <v>6609</v>
       </c>
-      <c r="C39" s="25"/>
+      <c r="C39" s="26"/>
       <c r="D39" s="21">
         <v>1076556627</v>
       </c>
@@ -5132,10 +5166,10 @@
       <c r="A40" s="23">
         <v>46230</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="26">
         <v>6906</v>
       </c>
-      <c r="C40" s="25"/>
+      <c r="C40" s="26"/>
       <c r="D40" s="21">
         <v>1167160796</v>
       </c>
@@ -5150,10 +5184,10 @@
       <c r="A41" s="23">
         <v>46231</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="26">
         <v>7221</v>
       </c>
-      <c r="C41" s="25"/>
+      <c r="C41" s="26"/>
       <c r="D41" s="21">
         <v>1220111851</v>
       </c>
@@ -5165,1055 +5199,1191 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="24"/>
+      <c r="A42" s="23">
+        <v>46232</v>
+      </c>
+      <c r="B42" s="26">
+        <v>7429</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21">
+        <v>1191517169</v>
+      </c>
+      <c r="E42" s="21">
+        <v>-26002641</v>
+      </c>
+      <c r="F42" s="24">
+        <v>-2.0999999999999999E-3</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="25"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="25"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="25"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="25"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="25"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="25"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="25"/>
-      <c r="C113" s="25"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="25"/>
-      <c r="C116" s="25"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="25"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="25"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="25"/>
-      <c r="C119" s="25"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="25"/>
-      <c r="C120" s="25"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="25"/>
-      <c r="C121" s="25"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="25"/>
-      <c r="C122" s="25"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="25"/>
-      <c r="C123" s="25"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="25"/>
-      <c r="C124" s="25"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="26"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="25"/>
-      <c r="C126" s="25"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="25"/>
-      <c r="C127" s="25"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="25"/>
-      <c r="C128" s="25"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="25"/>
-      <c r="C129" s="25"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="25"/>
-      <c r="C130" s="25"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="25"/>
-      <c r="C131" s="25"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="25"/>
-      <c r="C132" s="25"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="25"/>
-      <c r="C133" s="25"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="26"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="25"/>
-      <c r="C134" s="25"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="25"/>
-      <c r="C135" s="25"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="26"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="25"/>
-      <c r="C136" s="25"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="26"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="25"/>
-      <c r="C138" s="25"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="25"/>
-      <c r="C139" s="25"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="25"/>
-      <c r="C140" s="25"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="25"/>
-      <c r="C141" s="25"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="26"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="23"/>
-      <c r="B142" s="25"/>
-      <c r="C142" s="25"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="26"/>
       <c r="D142" s="21"/>
       <c r="E142" s="21"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="23"/>
-      <c r="B143" s="25"/>
-      <c r="C143" s="25"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="26"/>
       <c r="D143" s="21"/>
       <c r="E143" s="21"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="23"/>
-      <c r="B144" s="25"/>
-      <c r="C144" s="25"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="26"/>
       <c r="D144" s="21"/>
       <c r="E144" s="21"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="23"/>
-      <c r="B145" s="25"/>
-      <c r="C145" s="25"/>
+      <c r="B145" s="26"/>
+      <c r="C145" s="26"/>
       <c r="D145" s="21"/>
       <c r="E145" s="21"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="23"/>
-      <c r="B146" s="25"/>
-      <c r="C146" s="25"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="26"/>
       <c r="D146" s="21"/>
       <c r="E146" s="21"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="23"/>
-      <c r="B147" s="25"/>
-      <c r="C147" s="25"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="26"/>
       <c r="D147" s="21"/>
       <c r="E147" s="21"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="23"/>
-      <c r="B148" s="25"/>
-      <c r="C148" s="25"/>
+      <c r="B148" s="26"/>
+      <c r="C148" s="26"/>
       <c r="D148" s="21"/>
       <c r="E148" s="21"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="23"/>
-      <c r="B149" s="25"/>
-      <c r="C149" s="25"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
       <c r="D149" s="21"/>
       <c r="E149" s="21"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="23"/>
-      <c r="B150" s="25"/>
-      <c r="C150" s="25"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="26"/>
       <c r="D150" s="21"/>
       <c r="E150" s="21"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="23"/>
-      <c r="B151" s="25"/>
-      <c r="C151" s="25"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="26"/>
       <c r="D151" s="21"/>
       <c r="E151" s="21"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="23"/>
-      <c r="B152" s="25"/>
-      <c r="C152" s="25"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="26"/>
       <c r="D152" s="21"/>
       <c r="E152" s="21"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="23"/>
-      <c r="B153" s="25"/>
-      <c r="C153" s="25"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="26"/>
       <c r="D153" s="21"/>
       <c r="E153" s="21"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="23"/>
-      <c r="B154" s="25"/>
-      <c r="C154" s="25"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="26"/>
       <c r="D154" s="21"/>
       <c r="E154" s="21"/>
       <c r="F154" s="24"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="23"/>
-      <c r="B155" s="25"/>
-      <c r="C155" s="25"/>
+      <c r="B155" s="26"/>
+      <c r="C155" s="26"/>
       <c r="D155" s="21"/>
       <c r="E155" s="21"/>
       <c r="F155" s="24"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="23"/>
-      <c r="B156" s="25"/>
-      <c r="C156" s="25"/>
+      <c r="B156" s="26"/>
+      <c r="C156" s="26"/>
       <c r="D156" s="21"/>
       <c r="E156" s="21"/>
       <c r="F156" s="24"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="23"/>
-      <c r="B157" s="25"/>
-      <c r="C157" s="25"/>
+      <c r="B157" s="26"/>
+      <c r="C157" s="26"/>
       <c r="D157" s="21"/>
       <c r="E157" s="21"/>
       <c r="F157" s="24"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="23"/>
-      <c r="B158" s="25"/>
-      <c r="C158" s="25"/>
+      <c r="B158" s="26"/>
+      <c r="C158" s="26"/>
       <c r="D158" s="21"/>
       <c r="E158" s="21"/>
       <c r="F158" s="24"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="23"/>
-      <c r="B159" s="25"/>
-      <c r="C159" s="25"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="26"/>
       <c r="D159" s="21"/>
       <c r="E159" s="21"/>
       <c r="F159" s="24"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="23"/>
-      <c r="B160" s="25"/>
-      <c r="C160" s="25"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="26"/>
       <c r="D160" s="21"/>
       <c r="E160" s="21"/>
       <c r="F160" s="24"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="23"/>
-      <c r="B161" s="25"/>
-      <c r="C161" s="25"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="26"/>
       <c r="D161" s="21"/>
       <c r="E161" s="21"/>
       <c r="F161" s="24"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="23"/>
-      <c r="B162" s="25"/>
-      <c r="C162" s="25"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="26"/>
       <c r="D162" s="21"/>
       <c r="E162" s="21"/>
       <c r="F162" s="24"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="23"/>
-      <c r="B163" s="25"/>
-      <c r="C163" s="25"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="26"/>
       <c r="D163" s="21"/>
       <c r="E163" s="21"/>
       <c r="F163" s="24"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="23"/>
-      <c r="B164" s="25"/>
-      <c r="C164" s="25"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="26"/>
       <c r="D164" s="21"/>
       <c r="E164" s="21"/>
       <c r="F164" s="24"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="23"/>
-      <c r="B165" s="25"/>
-      <c r="C165" s="25"/>
+      <c r="B165" s="26"/>
+      <c r="C165" s="26"/>
       <c r="D165" s="21"/>
       <c r="E165" s="21"/>
       <c r="F165" s="24"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="23"/>
-      <c r="B166" s="25"/>
-      <c r="C166" s="25"/>
+      <c r="B166" s="26"/>
+      <c r="C166" s="26"/>
       <c r="D166" s="21"/>
       <c r="E166" s="21"/>
       <c r="F166" s="24"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="23"/>
-      <c r="B167" s="25"/>
-      <c r="C167" s="25"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
       <c r="D167" s="21"/>
       <c r="E167" s="21"/>
       <c r="F167" s="24"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="23"/>
-      <c r="B168" s="25"/>
-      <c r="C168" s="25"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="26"/>
       <c r="D168" s="21"/>
       <c r="E168" s="21"/>
       <c r="F168" s="24"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="23"/>
-      <c r="B169" s="25"/>
-      <c r="C169" s="25"/>
+      <c r="B169" s="26"/>
+      <c r="C169" s="26"/>
       <c r="D169" s="21"/>
       <c r="E169" s="21"/>
       <c r="F169" s="24"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="23"/>
-      <c r="B170" s="25"/>
-      <c r="C170" s="25"/>
+      <c r="B170" s="26"/>
+      <c r="C170" s="26"/>
       <c r="D170" s="21"/>
       <c r="E170" s="21"/>
       <c r="F170" s="24"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="23"/>
-      <c r="B171" s="25"/>
-      <c r="C171" s="25"/>
+      <c r="B171" s="26"/>
+      <c r="C171" s="26"/>
       <c r="D171" s="21"/>
       <c r="E171" s="21"/>
       <c r="F171" s="24"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="23"/>
-      <c r="B172" s="25"/>
-      <c r="C172" s="25"/>
+      <c r="B172" s="26"/>
+      <c r="C172" s="26"/>
       <c r="D172" s="21"/>
       <c r="E172" s="21"/>
       <c r="F172" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="138">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6226,132 +6396,6 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03F911C-73C3-421E-89CC-A80B88370687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FBEDC3-4AB7-4174-8F30-AD19F2AB6C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35550" yWindow="1920" windowWidth="17010" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17040" yWindow="1140" windowWidth="13275" windowHeight="18585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -741,11 +741,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-9.9899598393574305</v>
+        <v>1.22699386503067</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-2.2827058232931732</v>
+        <v>0.28036809815950808</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,11 +756,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>9.9927060539751995</v>
+        <v>-2.45358090185676</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>1.4289569657184535</v>
+        <v>-0.35086206896551675</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,11 +771,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>-1.3333333333333299</v>
+        <v>-0.81081081081080997</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D15" si="0">B4*C4/100</f>
-        <v>-0.10306666666666642</v>
+        <v>-6.2675675675675613E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,11 +786,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>1.2037037037036999</v>
+        <v>2.7904849039341202</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>8.5944444444444171E-2</v>
+        <v>0.19924062214089616</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -801,11 +801,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.48484848484848397</v>
+        <v>1.4007308160779499</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-3.2145454545454484E-2</v>
+        <v>9.2868453105968085E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -816,11 +816,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>2.8185554903112102</v>
+        <v>9.6516276413477993</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.15812096300645892</v>
+        <v>0.54145631067961153</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -831,11 +831,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>10</v>
+        <v>-6.1383061383061301</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.19899999999999998</v>
+        <v>-0.12215229215229199</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -846,11 +846,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-9.97929606625258</v>
+        <v>1.4719411223551</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10378467908902683</v>
+        <v>1.5308187672493041E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,11 +861,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.80996884735202401</v>
+        <v>-1.0050251256281399</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-4.3738317757009296E-3</v>
+        <v>-5.4271356783919559E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -876,11 +876,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>-3.3639143730886798</v>
+        <v>0.316455696202531</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7492354740061136E-2</v>
+        <v>1.6455696202531615E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -891,11 +891,11 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.7000000000000003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -906,11 +906,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>-7.12383488681757</v>
+        <v>-3.0107526881720399</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-9.9733688415445994E-3</v>
+        <v>-4.2150537634408564E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -921,11 +921,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-3.63070539419087</v>
+        <v>-1.61463939720129</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5414937759336092E-3</v>
+        <v>-1.1302475780409031E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,11 +936,11 @@
         <v>1.27</v>
       </c>
       <c r="C15" s="3">
-        <v>-1.41</v>
+        <v>-5.88</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7906999999999999E-2</v>
+        <v>-7.4676000000000006E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -954,7 +954,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15</f>
-        <v>-0.70196829955820472</v>
+        <v>0.53674876756537215</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1190,11 +1190,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>0.89801154586273202</v>
+        <v>-0.82644628099173501</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>8.0102629890955693E-2</v>
+        <v>-7.371900826446276E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1205,11 +1205,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>-0.28763183125599201</v>
+        <v>-3.4615384615384599</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>-2.5340364333652898E-2</v>
+        <v>-0.30496153846153834</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1220,11 +1220,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>-10</v>
+        <v>-9.9704267004647207</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82799999999999996</v>
+        <v>-0.82555133079847876</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1235,11 +1235,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>5.8333333333333304</v>
+        <v>9.4488188976377891</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.35991666666666644</v>
+        <v>0.58299212598425154</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1250,11 +1250,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1265,11 +1265,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>0.31446540880503099</v>
+        <v>-1.80250783699059</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>1.3899371069182369E-2</v>
+        <v>-7.9670846394984077E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1280,11 +1280,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-0.97817908201655301</v>
+        <v>-3.7993920972644299</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6877351392024048E-2</v>
+        <v>-0.143237082066869</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,11 +1295,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>-3.7297969332780698</v>
+        <v>-4.9074472664657698</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-0.1342726895980105</v>
+        <v>-0.17666810159276772</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1310,11 +1310,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-0.48632218844984798</v>
+        <v>-2.74893097128894</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-1.6389057750759876E-2</v>
+        <v>-9.2638973732437277E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,11 +1325,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-2.65888456549935</v>
+        <v>-5.0632911392404996</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-7.1258106355382586E-2</v>
+        <v>-0.13569620253164541</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,11 +1340,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-9.9899598393574305</v>
+        <v>1.22699386503067</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-0.25774096385542172</v>
+        <v>3.1656441717791285E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1355,11 +1355,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-0.54305663304887497</v>
+        <v>-4.0561622464898601</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3304887509697438E-2</v>
+        <v>-9.9375975039001571E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1370,11 +1370,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>10</v>
+        <v>-6.1383061383061301</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>0.20499999999999999</v>
+        <v>-0.12583527583527565</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1385,11 +1385,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>3.0230708035003899</v>
+        <v>-3.4749034749034702</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>5.229912490055675E-2</v>
+        <v>-6.0115830115830035E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1400,11 +1400,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>1.44</v>
+        <v>-0.86750788643533105</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>2.3615999999999998E-2</v>
+        <v>-1.4227129337539429E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,11 +1415,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>0.28702640642939098</v>
+        <v>-2.9192902117916399</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>4.6498277841561346E-3</v>
+        <v>-4.7292501431024571E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1430,11 +1430,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>1.63078930202217</v>
+        <v>-0.77021822849807398</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>2.4135681669928119E-2</v>
+        <v>-1.1399229781771493E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1445,11 +1445,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-0.58651026392961803</v>
+        <v>-0.29498525073746301</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-8.2111436950146523E-3</v>
+        <v>-4.129793510324482E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,11 +1460,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-0.864260294865277</v>
+        <v>-0.71794871794871795</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1235383833248602E-2</v>
+        <v>-9.3333333333333341E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1475,11 +1475,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-1.3270142180094699</v>
+        <v>-1.53698366954851</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.6720379146919321E-2</v>
+        <v>-1.9365994236311225E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1490,11 +1490,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>0.2360346184107</v>
+        <v>-0.86342229199372</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>2.8324154209283998E-3</v>
+        <v>-1.036106750392464E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,11 +1505,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>-1.3333333333333299</v>
+        <v>-0.81081081081080997</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-9.7333333333333091E-3</v>
+        <v>-5.9189189189189128E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,11 +1520,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-1.1757425742574199</v>
+        <v>-3.8196618659987398</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-8.3477722772276816E-3</v>
+        <v>-2.7119599248591052E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1535,11 +1535,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.80996884735202401</v>
+        <v>-1.0050251256281399</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-4.7788161993769411E-3</v>
+        <v>-5.9296482412060257E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,11 +1550,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-3.63070539419087</v>
+        <v>-1.61463939720129</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0331950207468873E-2</v>
+        <v>-9.0419806243272251E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1565,11 +1565,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>0.80142475512021305</v>
+        <v>-5.3003533568904597</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>3.205699020480852E-3</v>
+        <v>-2.1201413427561842E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1580,11 +1580,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>0.46992481203007502</v>
+        <v>-9.4013096351730496</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>1.8327067669172928E-3</v>
+        <v>-3.6665107577174894E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1595,11 +1595,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>0.112803158488437</v>
+        <v>-1.35211267605633</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>4.0609137055837318E-4</v>
+        <v>-4.8676056338027877E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1610,11 +1610,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>9.9769762087490399</v>
+        <v>-9.9790648988136699</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>3.3921719109746735E-2</v>
+        <v>-3.3928820655966481E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1625,11 +1625,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>-5.81039755351682</v>
+        <v>-5.0865800865800797</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9755351681957189E-2</v>
+        <v>-1.7294372294372272E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,11 +1640,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>2.1925643469971399</v>
+        <v>1.39925373134328</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>7.2354623450905618E-3</v>
+        <v>4.6175373134328236E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1655,11 +1655,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>-0.48484848484848397</v>
+        <v>1.4007308160779499</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2606060606060584E-3</v>
+        <v>3.6419001218026699E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1670,11 +1670,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.0661157024793302</v>
+        <v>0</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-3.7190082644627943E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1685,11 +1685,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>2.8185554903112102</v>
+        <v>9.6516276413477993</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>3.382266588373452E-3</v>
+        <v>1.1581953169617359E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1700,11 +1700,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-1.44262295081967</v>
+        <v>-2.39520958083832</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0098360655737691E-3</v>
+        <v>-1.6766467065868244E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1715,11 +1715,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>1.38696255201109</v>
+        <v>-1.59598723210214</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>6.9348127600554505E-4</v>
+        <v>-7.9799361605107006E-4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1730,11 +1730,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>-8.8901472253680591</v>
+        <v>-2.98321939092604</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>-3.5560588901472241E-3</v>
+        <v>-1.1932877563704161E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1745,11 +1745,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>-1.5695067264573901</v>
+        <v>-5.0873196659073603</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>-6.2780269058295606E-4</v>
+        <v>-2.0349278663629442E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1760,11 +1760,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>-2.1226415094339601</v>
+        <v>-3.8554216867469799</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3679245283018802E-3</v>
+        <v>-1.1566265060240938E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,11 +1775,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>0.59</v>
+        <v>0.93</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>4.9146999999999996E-2</v>
+        <v>7.7468999999999996E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1790,11 +1790,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>1.95</v>
+        <v>-1.28</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>0.16126499999999999</v>
+        <v>-0.10585599999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1805,11 +1805,11 @@
         <v>2.56</v>
       </c>
       <c r="C43" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" si="0"/>
-        <v>3.5840000000000004E-3</v>
+        <v>3.3280000000000002E-3</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>-0.46771364378962371</v>
+        <v>-1.3283848432881578</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,11 +2192,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>-0.28763183125599201</v>
+        <v>-3.4615384615384599</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-2.775647171620323E-2</v>
+        <v>-0.3340384615384614</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2207,11 +2207,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>0.89801154586273202</v>
+        <v>-0.82644628099173501</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>8.3425272610647791E-2</v>
+        <v>-7.6776859504132183E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2222,11 +2222,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>-10</v>
+        <v>-9.9704267004647207</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.92400000000000004</v>
+        <v>-0.92126742712294019</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2237,11 +2237,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-2.65888456549935</v>
+        <v>-5.0632911392404996</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.16192607003891041</v>
+        <v>-0.30835443037974641</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,11 +2252,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.47300000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2267,11 +2267,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>5.8333333333333304</v>
+        <v>9.4488188976377891</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.26366666666666649</v>
+        <v>0.42708661417322802</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2282,11 +2282,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>-3.7297969332780698</v>
+        <v>-4.9099998474120996</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12681309573145438</v>
+        <v>-0.16693999481201138</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2297,11 +2297,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>0.31446540880503099</v>
+        <v>-1.80250783699059</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>8.5849056603773451E-3</v>
+        <v>-4.9208463949843108E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2312,11 +2312,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>10</v>
+        <v>-6.1399998664855904</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.23</v>
+        <v>-0.14121999692916856</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2327,11 +2327,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-0.58651026392961803</v>
+        <v>-0.29498525073746301</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-9.7947214076246208E-3</v>
+        <v>-4.9262536873156317E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2342,11 +2342,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>3.0230708035003899</v>
+        <v>-3.4749034749034702</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>4.7764518695306159E-2</v>
+        <v>-5.490347490347483E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2357,11 +2357,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-9.9899598393574305</v>
+        <v>1.22699386503067</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-0.15684236947791166</v>
+        <v>1.9263803680981521E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2372,11 +2372,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-0.97817908201655301</v>
+        <v>-3.7993920972644299</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1053423626787049E-2</v>
+        <v>-4.2933130699088051E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2387,11 +2387,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-0.48632218844984798</v>
+        <v>-2.74893097128894</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-5.0091185410334341E-3</v>
+        <v>-2.8313989004276081E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2402,11 +2402,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>1.44</v>
+        <v>-0.86750788643533105</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>1.4112E-2</v>
+        <v>-8.5015772870662438E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2417,11 +2417,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.9150141643059406</v>
+        <v>-9.9580712788259902</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.626062322946168E-2</v>
+        <v>-8.6635220125786103E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2432,11 +2432,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-3.63070539419087</v>
+        <v>-1.61463939720129</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1421161825726131E-2</v>
+        <v>-9.5263724434876112E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2447,11 +2447,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>1.38696255201109</v>
+        <v>-1.59598723210214</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>6.9348127600554503E-3</v>
+        <v>-7.9799361605107002E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2462,11 +2462,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>0.80142475512021305</v>
+        <v>-5.3003533568904597</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>3.8468388245770225E-3</v>
+        <v>-2.5441696113074203E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2477,11 +2477,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-1.3270142180094699</v>
+        <v>-1.53999996185302</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-5.5734597156397734E-3</v>
+        <v>-6.4679998397826847E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2492,11 +2492,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>1.1320754716981101</v>
+        <v>0.44</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>4.5283018867924409E-3</v>
+        <v>1.7600000000000003E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2507,11 +2507,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-1.1757425742574199</v>
+        <v>-3.82</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-4.4678217821781958E-3</v>
+        <v>-1.4515999999999999E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2522,11 +2522,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>-0.48484848484848397</v>
+        <v>1.4007308160779499</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-1.21212121212121E-3</v>
+        <v>3.5018270401948747E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2537,11 +2537,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.60501296456352605</v>
+        <v>-0.95652173913043403</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-1.512532411408815E-3</v>
+        <v>-2.3913043478260851E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2552,11 +2552,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>9.9769762087490399</v>
+        <v>-9.98</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>2.3944742900997695E-2</v>
+        <v>-2.3952000000000001E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2567,11 +2567,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.3333333333333299</v>
+        <v>-0.81</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-3.0666666666666594E-3</v>
+        <v>-1.8630000000000003E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2582,11 +2582,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.439560439560439</v>
+        <v>-0.66225165562913901</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-8.7912087912087804E-4</v>
+        <v>-1.3245033112582779E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2597,11 +2597,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>-8.8901472253680591</v>
+        <v>-2.98321939092604</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-7.1121177802944482E-3</v>
+        <v>-2.3865755127408322E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2612,11 +2612,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-1.44262295081967</v>
+        <v>-2.39520958083832</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4426229508196701E-4</v>
+        <v>-2.3952095808383201E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2627,11 +2627,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>0.59</v>
+        <v>0.93</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>4.7141000000000002E-2</v>
+        <v>7.4307000000000012E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2642,11 +2642,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>1.95</v>
+        <v>-1.28</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>0.15015000000000001</v>
+        <v>-9.8559999999999995E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2657,11 +2657,11 @@
         <v>2.5</v>
       </c>
       <c r="C33" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>3.5000000000000005E-3</v>
+        <v>3.2500000000000003E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2687,11 +2687,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>1.7167999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,11 +2702,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>0.63</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>3.7800000000000003E-4</v>
+        <v>-3.48E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-0.64868609833220436</v>
+        <v>-1.4158329437356698</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3765,11 +3765,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>1.5299877600979099</v>
+        <v>-0.24110910186859499</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.80706854345164747</v>
+        <v>-0.12718505123568385</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3780,11 +3780,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-9.9576271186440692</v>
+        <v>-4.1176470588235201</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-1.1072881355932205</v>
+        <v>-0.45788235294117541</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3795,11 +3795,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-3.28879753340185</v>
+        <v>0.26567481402762999</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7430626927029805E-2</v>
+        <v>1.408076514346439E-3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3810,11 +3810,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.67</v>
+        <v>1.76</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.19979400000000003</v>
+        <v>0.52483200000000008</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3828,7 +3828,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>-0.51744421906860283</v>
+        <v>-5.8827327662512752E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4964,11 +4964,11 @@
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.0802469135802399</v>
+        <v>-2.34009360374414</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.45953703703703402</v>
+        <v>-0.99547581903275717</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4979,11 +4979,11 @@
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>0</v>
+        <v>-1.2878300064391499</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>0</v>
+        <v>-0.41648422408242114</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4994,11 +4994,11 @@
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.55079559363525099</v>
+        <v>-3.6923076923076898</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-6.7252141982864153E-2</v>
+        <v>-0.45083076923076892</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5009,11 +5009,11 @@
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>4.7337278106508798</v>
+        <v>1.8966908797417199</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.51692307692307604</v>
+        <v>0.20711864406779582</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5024,11 +5024,11 @@
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-1.9545694664553599</v>
+        <v>-0.26939655172413701</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.1151241415742207</v>
+        <v>-1.5867456896551668E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,11 +5039,11 @@
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>-9.3605189990732107</v>
+        <v>-2.45398773006134</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.5316774791473583</v>
+        <v>-0.1393865030674841</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,7 +5057,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-0.65666772281840113</v>
+        <v>-1.8109261282421869</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FBEDC3-4AB7-4174-8F30-AD19F2AB6C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7911F8-0832-4917-8CF1-558D56DCA9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17040" yWindow="1140" windowWidth="13275" windowHeight="18585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37695" yWindow="2685" windowWidth="11625" windowHeight="18075" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1140,8 +1140,48 @@
         <v>4.3E-3</v>
       </c>
     </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="18">
+        <v>46233</v>
+      </c>
+      <c r="B37" s="26">
+        <v>97411</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="25">
+        <v>223802010766</v>
+      </c>
+      <c r="E37" s="22">
+        <v>-1443647505</v>
+      </c>
+      <c r="F37" s="24">
+        <v>-4.1999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F40" s="24"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="24"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F43" s="24"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
@@ -1955,12 +1995,22 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
-      <c r="B61" s="26"/>
+      <c r="A61" s="18">
+        <v>46233</v>
+      </c>
+      <c r="B61" s="26">
+        <v>160805</v>
+      </c>
       <c r="C61" s="26"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="24"/>
+      <c r="D61" s="21">
+        <v>69072635445</v>
+      </c>
+      <c r="E61" s="21">
+        <v>-1972729322</v>
+      </c>
+      <c r="F61" s="24">
+        <v>-1.6799999999999999E-2</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
@@ -2124,26 +2174,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2153,6 +2183,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2852,12 +2902,22 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="26"/>
+      <c r="A59" s="18">
+        <v>46233</v>
+      </c>
+      <c r="B59" s="26">
+        <v>160805</v>
+      </c>
       <c r="C59" s="26"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="24"/>
+      <c r="D59" s="21">
+        <v>69072635445</v>
+      </c>
+      <c r="E59" s="21">
+        <v>-1972729322</v>
+      </c>
+      <c r="F59" s="24">
+        <v>-1.4E-2</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
@@ -3621,97 +3681,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3725,6 +3694,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3970,12 +4030,22 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="23"/>
-      <c r="B37" s="26"/>
+      <c r="A37" s="23">
+        <v>46233</v>
+      </c>
+      <c r="B37" s="26">
+        <v>50968</v>
+      </c>
       <c r="C37" s="26"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="24"/>
+      <c r="D37" s="21">
+        <v>32438714789</v>
+      </c>
+      <c r="E37" s="21">
+        <v>329409310</v>
+      </c>
+      <c r="F37" s="24">
+        <v>1.9E-3</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
@@ -4811,107 +4881,6 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4924,6 +4893,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5217,12 +5287,22 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-      <c r="B43" s="26"/>
+      <c r="A43" s="23">
+        <v>46233</v>
+      </c>
+      <c r="B43" s="26">
+        <v>7272</v>
+      </c>
       <c r="C43" s="26"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="24"/>
+      <c r="D43" s="21">
+        <v>1145188929</v>
+      </c>
+      <c r="E43" s="21">
+        <v>-36158316</v>
+      </c>
+      <c r="F43" s="24">
+        <v>-8.5000000000000006E-3</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
@@ -6258,132 +6338,6 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6396,6 +6350,132 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7911F8-0832-4917-8CF1-558D56DCA9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE5CDA0-4E44-4CE1-A74F-92A5D847DD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37695" yWindow="2685" windowWidth="11625" windowHeight="18075" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37350" yWindow="390" windowWidth="12315" windowHeight="20445" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -741,11 +741,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>1.22699386503067</v>
+        <v>-0.93663911845729997</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.28036809815950808</v>
+        <v>-0.21402203856749305</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,11 +756,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>-2.45358090185676</v>
+        <v>3.3310673011556702</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>-0.35086206896551675</v>
+        <v>0.47634262406526084</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,11 +771,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.81081081081080997</v>
+        <v>0.13623978201634801</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D15" si="0">B4*C4/100</f>
-        <v>-6.2675675675675613E-2</v>
+        <v>1.0531335149863701E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,11 +786,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7904849039341202</v>
+        <v>2.8482421005785401</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.19924062214089616</v>
+        <v>0.20336448598130777</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -801,11 +801,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>1.4007308160779499</v>
+        <v>2.3423423423423402</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>9.2868453105968085E-2</v>
+        <v>0.15529729729729713</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -816,11 +816,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>9.6516276413477993</v>
+        <v>-1.09375</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.54145631067961153</v>
+        <v>-6.1359375000000008E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -831,11 +831,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>-6.1383061383061301</v>
+        <v>-2.40066225165562</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-0.12215229215229199</v>
+        <v>-4.7773178807946834E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -846,11 +846,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>1.4719411223551</v>
+        <v>-2.5385312783318201</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>1.5308187672493041E-2</v>
+        <v>-2.6400725294650932E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,11 +861,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>-1.0050251256281399</v>
+        <v>0.50761421319796896</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-5.4271356783919559E-3</v>
+        <v>2.7411167512690327E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -876,11 +876,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>0.316455696202531</v>
+        <v>2.9179810725551998</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.6455696202531615E-3</v>
+        <v>1.5173501577287038E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -891,11 +891,11 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>10</v>
+        <v>7.9545454545454497</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>2.7000000000000003E-2</v>
+        <v>2.1477272727272716E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -906,11 +906,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>-3.0107526881720399</v>
+        <v>-0.295639320029563</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-4.2150537634408564E-3</v>
+        <v>-4.1389504804138826E-4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -921,11 +921,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-1.61463939720129</v>
+        <v>-4.2669584245076502</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1302475780409031E-3</v>
+        <v>-2.9868708971553552E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,11 +936,11 @@
         <v>1.27</v>
       </c>
       <c r="C15" s="3">
-        <v>-5.88</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-7.4676000000000006E-2</v>
+        <v>2.8701999999999995E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -954,7 +954,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15</f>
-        <v>0.53674876756537215</v>
+        <v>0.56067354993427077</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1230,11 +1230,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.82644628099173501</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-7.371900826446276E-2</v>
+        <v>5.1461538461538468E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1245,11 +1245,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>-3.4615384615384599</v>
+        <v>-7.7290836653386403</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>-0.30496153846153834</v>
+        <v>-0.68093227091633424</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1260,11 +1260,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>-9.9704267004647207</v>
+        <v>-9.9953073674331296</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82555133079847876</v>
+        <v>-0.82761145002346315</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1275,11 +1275,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>9.4488188976377891</v>
+        <v>7.9136690647482002</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.58299212598425154</v>
+        <v>0.48827338129496395</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1290,11 +1290,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>10</v>
+        <v>7.9545454545454497</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.47499999999999998</v>
+        <v>0.37784090909090884</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1305,11 +1305,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-1.80250783699059</v>
+        <v>-1.5961691939345499</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-7.9670846394984077E-2</v>
+        <v>-7.0550678371907108E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1320,11 +1320,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-3.7993920972644299</v>
+        <v>-2.6856240126382298</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-0.143237082066869</v>
+        <v>-0.10124802527646126</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1335,11 +1335,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>-4.9074472664657698</v>
+        <v>4.5269352648257097</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-0.17666810159276772</v>
+        <v>0.16296966953372558</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1350,11 +1350,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-2.74893097128894</v>
+        <v>-2.6381909547738598</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-9.2638973732437277E-2</v>
+        <v>-8.8907035175879071E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1365,11 +1365,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-5.0632911392404996</v>
+        <v>7.0175438596491198</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13569620253164541</v>
+        <v>0.18807017543859644</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1380,11 +1380,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>1.22699386503067</v>
+        <v>-0.93663911845729997</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>3.1656441717791285E-2</v>
+        <v>-2.416528925619834E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1395,11 +1395,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-4.0561622464898601</v>
+        <v>-2.1951219512195101</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-9.9375975039001571E-2</v>
+        <v>-5.3780487804878006E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,11 +1410,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>-6.1383061383061301</v>
+        <v>-2.40066225165562</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12583527583527565</v>
+        <v>-4.9213576158940203E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1425,11 +1425,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-3.4749034749034702</v>
+        <v>-0.88</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-6.0115830115830035E-2</v>
+        <v>-1.5224E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1440,11 +1440,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>-0.86750788643533105</v>
+        <v>-0.87509944311853605</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4227129337539429E-2</v>
+        <v>-1.4351630867143989E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1455,11 +1455,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>-2.9192902117916399</v>
+        <v>-2.9481132075471699</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-4.7292501431024571E-2</v>
+        <v>-4.7759433962264161E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1470,11 +1470,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-0.77021822849807398</v>
+        <v>-0.90556274256144897</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1399229781771493E-2</v>
+        <v>-1.3402328589909444E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,11 +1485,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-0.29498525073746301</v>
+        <v>9.8619329388560106E-2</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-4.129793510324482E-3</v>
+        <v>1.3806706114398415E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,11 +1500,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-0.71794871794871795</v>
+        <v>-1.0847107438016499</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-9.3333333333333341E-3</v>
+        <v>-1.4101239669421449E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1515,11 +1515,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-1.53698366954851</v>
+        <v>-1.07317073170731</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9365994236311225E-2</v>
+        <v>-1.3521951219512107E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1530,11 +1530,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>-0.86342229199372</v>
+        <v>-2.5336500395882799</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-1.036106750392464E-2</v>
+        <v>-3.0403800475059358E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1545,11 +1545,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>-0.81081081081080997</v>
+        <v>0.13623978201634801</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9189189189189128E-3</v>
+        <v>9.9455040871934057E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1560,11 +1560,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-3.8196618659987398</v>
+        <v>-3.1901041666666599</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-2.7119599248591052E-2</v>
+        <v>-2.2649739583333287E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1575,11 +1575,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>-1.0050251256281399</v>
+        <v>0.50761421319796896</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9296482412060257E-3</v>
+        <v>2.9949238578680167E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1590,11 +1590,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-1.61463939720129</v>
+        <v>-4.2669584245076502</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-9.0419806243272251E-3</v>
+        <v>-2.3894967177242842E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,11 +1605,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>-5.3003533568904597</v>
+        <v>-1.4925373134328299</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1201413427561842E-2</v>
+        <v>-5.9701492537313191E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,11 +1620,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>-9.4013096351730496</v>
+        <v>0.15487867836861099</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6665107577174894E-2</v>
+        <v>6.0402684563758287E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1635,11 +1635,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.35211267605633</v>
+        <v>-2.6270702455739499</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-4.8676056338027877E-3</v>
+        <v>-9.4574528840662194E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,11 +1650,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>-9.9790648988136699</v>
+        <v>0.62015503875968903</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-3.3928820655966481E-2</v>
+        <v>2.1085271317829429E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1665,11 +1665,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>-5.0865800865800797</v>
+        <v>0.342075256556442</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7294372294372272E-2</v>
+        <v>1.1630558722919029E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,11 +1680,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>1.39925373134328</v>
+        <v>-1.4719411223551</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>4.6175373134328236E-3</v>
+        <v>-4.8574057037718303E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1695,11 +1695,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>1.4007308160779499</v>
+        <v>2.3423423423423402</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>3.6419001218026699E-3</v>
+        <v>6.0900900900900841E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1710,11 +1710,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>0</v>
+        <v>-4.6413502109704599</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-8.3544303797468272E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1725,11 +1725,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>9.6516276413477993</v>
+        <v>-1.09375</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>1.1581953169617359E-2</v>
+        <v>-1.3125000000000001E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1740,11 +1740,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-2.39520958083832</v>
+        <v>-0.340831629175187</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-1.6766467065868244E-3</v>
+        <v>-2.3858214042263092E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1755,11 +1755,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-1.59598723210214</v>
+        <v>-1.7608897126969401</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-7.9799361605107006E-4</v>
+        <v>-8.8044485634847019E-4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1770,11 +1770,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>-2.98321939092604</v>
+        <v>1.2171684817424699</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1932877563704161E-3</v>
+        <v>4.8686739269698798E-4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1785,11 +1785,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>-5.0873196659073603</v>
+        <v>2.56</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0349278663629442E-3</v>
+        <v>1.024E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1800,11 +1800,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>-3.8554216867469799</v>
+        <v>0.50125313283207995</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1566265060240938E-2</v>
+        <v>1.5037593984962396E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1815,11 +1815,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>0.93</v>
+        <v>-0.88</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>7.7468999999999996E-2</v>
+        <v>-7.3303999999999994E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1830,11 +1830,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-1.28</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10585599999999999</v>
+        <v>5.7889999999999999E-3</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>-1.3283848432881578</v>
+        <v>-0.90000972431727866</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2174,6 +2174,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2183,26 +2203,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,11 +2242,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>-3.4615384615384599</v>
+        <v>-7.7290836653386403</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.3340384615384614</v>
+        <v>-0.74585657370517877</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,11 +2257,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>-0.82644628099173501</v>
+        <v>0.57692307692307698</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>-7.6776859504132183E-2</v>
+        <v>5.3596153846153849E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,11 +2272,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9704267004647207</v>
+        <v>-9.9953073674331296</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.92126742712294019</v>
+        <v>-0.9235664007508213</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,11 +2287,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-5.0632911392404996</v>
+        <v>7.0175438596491198</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.30835443037974641</v>
+        <v>0.42736842105263134</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,11 +2302,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>10</v>
+        <v>7.9545454545454497</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.47300000000000003</v>
+        <v>0.37624999999999981</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,11 +2317,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>9.4488188976377891</v>
+        <v>7.9136690647482002</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.42708661417322802</v>
+        <v>0.35769784172661867</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,11 +2332,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>-4.9099998474120996</v>
+        <v>4.5269352648257097</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-0.16693999481201138</v>
+        <v>0.15391579900407412</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,11 +2347,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-1.80250783699059</v>
+        <v>-1.5961691939345499</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9208463949843108E-2</v>
+        <v>-4.3575418994413209E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,11 +2362,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>-6.1399998664855904</v>
+        <v>-2.40066225165562</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-0.14121999692916856</v>
+        <v>-5.5215231788079251E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2377,11 +2377,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-0.29498525073746301</v>
+        <v>9.8619329388560106E-2</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9262536873156317E-3</v>
+        <v>1.6469428007889536E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2392,11 +2392,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-3.4749034749034702</v>
+        <v>-0.88</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-5.490347490347483E-2</v>
+        <v>-1.3904000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2407,11 +2407,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>1.22699386503067</v>
+        <v>-0.93663911845729997</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>1.9263803680981521E-2</v>
+        <v>-1.4705234159779611E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,11 +2422,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-3.7993920972644299</v>
+        <v>-2.6856240126382298</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-4.2933130699088051E-2</v>
+        <v>-3.0347551342811994E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2437,11 +2437,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-2.74893097128894</v>
+        <v>-2.6381909547738598</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8313989004276081E-2</v>
+        <v>-2.7173366834170758E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2452,11 +2452,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>-0.86750788643533105</v>
+        <v>-0.87509944311853605</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-8.5015772870662438E-3</v>
+        <v>-8.5759745425616537E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2467,11 +2467,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.9580712788259902</v>
+        <v>-9.8952270081490106</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6635220125786103E-2</v>
+        <v>-8.6088474970896389E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2482,11 +2482,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.61463939720129</v>
+        <v>-4.2669584245076502</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-9.5263724434876112E-3</v>
+        <v>-2.5175054704595135E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2497,11 +2497,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-1.59598723210214</v>
+        <v>-1.7608897126969401</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-7.9799361605107002E-3</v>
+        <v>-8.804448563484701E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2512,11 +2512,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>-5.3003533568904597</v>
+        <v>-1.4925373134328299</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-2.5441696113074203E-2</v>
+        <v>-7.1641791044775834E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2527,11 +2527,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-1.53999996185302</v>
+        <v>-1.07317073170731</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-6.4679998397826847E-3</v>
+        <v>-4.5073170731707015E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2542,11 +2542,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>0.44</v>
+        <v>-0.86687306501547901</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>1.7600000000000003E-3</v>
+        <v>-3.4674922600619164E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2557,11 +2557,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-3.82</v>
+        <v>-3.1901041666666599</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4515999999999999E-2</v>
+        <v>-1.2122395833333308E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2572,11 +2572,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>1.4007308160779499</v>
+        <v>2.3423423423423402</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>3.5018270401948747E-3</v>
+        <v>5.8558558558558507E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2587,11 +2587,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.95652173913043403</v>
+        <v>-0.96575943810359899</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3913043478260851E-3</v>
+        <v>-2.4143985952589974E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2602,11 +2602,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>-9.98</v>
+        <v>0.62015503875968903</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3952000000000001E-2</v>
+        <v>1.4883720930232536E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2617,11 +2617,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>-0.81</v>
+        <v>0.13623978201634801</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-1.8630000000000003E-3</v>
+        <v>3.1335149863760041E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2632,11 +2632,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.66225165562913901</v>
+        <v>-0.44444444444444398</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3245033112582779E-3</v>
+        <v>-8.8888888888888796E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2647,11 +2647,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>-2.98321939092604</v>
+        <v>1.2171684817424699</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3865755127408322E-3</v>
+        <v>9.7373478539397595E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2662,11 +2662,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-2.39520958083832</v>
+        <v>-0.340831629175187</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3952095808383201E-4</v>
+        <v>-3.4083162917518701E-5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2677,11 +2677,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>0.93</v>
+        <v>-0.88</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>7.4307000000000012E-2</v>
+        <v>-7.0311999999999999E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2692,11 +2692,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-1.28</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-9.8559999999999995E-2</v>
+        <v>5.3900000000000007E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2737,11 +2737,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>0</v>
+        <v>9.49</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.5042000000000001E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2752,11 +2752,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>-0.57999999999999996</v>
+        <v>-0.15</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-3.48E-4</v>
+        <v>-8.9999999999999992E-5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-1.4158329437356698</v>
+        <v>-0.64018601261172448</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3681,6 +3681,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3694,97 +3785,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3825,11 +3825,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>-0.24110910186859499</v>
+        <v>-0.72507552870090597</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.12718505123568385</v>
+        <v>-0.38247734138972789</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3840,11 +3840,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-4.1176470588235201</v>
+        <v>-4.5398773006134903</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.45788235294117541</v>
+        <v>-0.50483435582822012</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3855,11 +3855,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>0.26567481402762999</v>
+        <v>0.105988341282458</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>1.408076514346439E-3</v>
+        <v>5.6173820879702741E-4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3870,11 +3870,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>1.76</v>
+        <v>-0.26</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.52483200000000008</v>
+        <v>-7.7532000000000004E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3888,7 +3888,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>-5.8827327662512752E-2</v>
+        <v>-0.96428195900915104</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4881,6 +4881,107 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4893,107 +4994,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5034,11 +5034,11 @@
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>-2.34009360374414</v>
+        <v>1.6773162939297099</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.99547581903275717</v>
+        <v>0.71353035143769861</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5049,11 +5049,11 @@
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>-1.2878300064391499</v>
+        <v>-4.8923679060665304</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>-0.41648422408242114</v>
+        <v>-1.5821917808219161</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5064,11 +5064,11 @@
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>-3.6923076923076898</v>
+        <v>-3.1948881789137298</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-0.45083076923076892</v>
+        <v>-0.39009584664536645</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,11 +5079,11 @@
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8966908797417199</v>
+        <v>-1.8217821782178201</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.20711864406779582</v>
+        <v>-0.19893861386138595</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5094,11 +5094,11 @@
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.26939655172413701</v>
+        <v>-2.7552674230145802</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-1.5867456896551668E-2</v>
+        <v>-0.16228525121555876</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5109,11 +5109,11 @@
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>-2.45398773006134</v>
+        <v>-2.5157232704402501</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.1393865030674841</v>
+        <v>-0.14289308176100621</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5127,7 +5127,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-1.8109261282421869</v>
+        <v>-1.7628742228675349</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6338,6 +6338,132 @@
     </row>
   </sheetData>
   <mergeCells count="138">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6350,132 +6476,6 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE5CDA0-4E44-4CE1-A74F-92A5D847DD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF41E539-8C54-4D48-9EC7-601A833D5A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37350" yWindow="390" windowWidth="12315" windowHeight="20445" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36090" yWindow="390" windowWidth="15630" windowHeight="20385" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -1159,7 +1159,22 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F38" s="24"/>
+      <c r="A38" s="18">
+        <v>46234</v>
+      </c>
+      <c r="B38" s="26">
+        <v>97269</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="25">
+        <v>223121593370</v>
+      </c>
+      <c r="E38" s="22">
+        <v>-3172256453</v>
+      </c>
+      <c r="F38" s="24">
+        <v>1.11E-2</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F39" s="24"/>
@@ -1180,7 +1195,8 @@
       <c r="F44" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
@@ -2013,12 +2029,22 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
-      <c r="B62" s="26"/>
+      <c r="A62" s="18">
+        <v>46234</v>
+      </c>
+      <c r="B62" s="26">
+        <v>159675</v>
+      </c>
       <c r="C62" s="26"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="24"/>
+      <c r="D62" s="21">
+        <v>63472489182</v>
+      </c>
+      <c r="E62" s="21">
+        <v>-4926393640</v>
+      </c>
+      <c r="F62" s="24">
+        <v>-9.7999999999999997E-3</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
@@ -2174,26 +2200,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2203,6 +2209,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2870,14 +2896,14 @@
         <v>46231</v>
       </c>
       <c r="B57" s="26">
-        <v>78840</v>
+        <v>79795</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="21">
-        <v>39148877217</v>
+        <v>39293398935</v>
       </c>
       <c r="E57" s="22">
-        <v>706423581</v>
+        <v>119712414</v>
       </c>
       <c r="F57" s="24">
         <v>5.9999999999999995E-4</v>
@@ -2906,11 +2932,11 @@
         <v>46233</v>
       </c>
       <c r="B59" s="26">
-        <v>160805</v>
+        <v>80272</v>
       </c>
       <c r="C59" s="26"/>
       <c r="D59" s="21">
-        <v>69072635445</v>
+        <v>36982629736</v>
       </c>
       <c r="E59" s="21">
         <v>-1972729322</v>
@@ -2920,12 +2946,22 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="26"/>
+      <c r="A60" s="18">
+        <v>46234</v>
+      </c>
+      <c r="B60" s="26">
+        <v>79803</v>
+      </c>
       <c r="C60" s="26"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="24"/>
+      <c r="D60" s="21">
+        <v>33560330080</v>
+      </c>
+      <c r="E60" s="21">
+        <v>-3201067093</v>
+      </c>
+      <c r="F60" s="24">
+        <v>-6.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
@@ -3681,97 +3717,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3785,6 +3730,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4048,12 +4084,22 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="26"/>
+      <c r="A38" s="23">
+        <v>46234</v>
+      </c>
+      <c r="B38" s="26">
+        <v>51171</v>
+      </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="24"/>
+      <c r="D38" s="21">
+        <v>31996446996</v>
+      </c>
+      <c r="E38" s="21">
+        <v>-281801311</v>
+      </c>
+      <c r="F38" s="24">
+        <v>-4.8999999999999998E-3</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
@@ -4881,107 +4927,6 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4994,6 +4939,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5305,12 +5351,22 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-      <c r="B44" s="26"/>
+      <c r="A44" s="23">
+        <v>46234</v>
+      </c>
+      <c r="B44" s="26">
+        <v>7038</v>
+      </c>
       <c r="C44" s="26"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="24"/>
+      <c r="D44" s="21">
+        <v>1042575112</v>
+      </c>
+      <c r="E44" s="21">
+        <v>-84952353</v>
+      </c>
+      <c r="F44" s="24">
+        <v>-1.54E-2</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
@@ -6338,132 +6394,6 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6476,6 +6406,132 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF41E539-8C54-4D48-9EC7-601A833D5A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BAF415-617A-49F2-BAAA-5B16F80784EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36090" yWindow="390" windowWidth="15630" windowHeight="20385" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37200" yWindow="120" windowWidth="15300" windowHeight="20730" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -741,11 +741,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-0.93663911845729997</v>
+        <v>-5.2836484983314698</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.21402203856749305</v>
+        <v>-1.2073136818687409</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,11 +756,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>3.3310673011556702</v>
+        <v>2.1052631578947301</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.47634262406526084</v>
+        <v>0.30105263157894641</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,11 +771,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>0.13623978201634801</v>
+        <v>0.20408163265306101</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D15" si="0">B4*C4/100</f>
-        <v>1.0531335149863701E-2</v>
+        <v>1.5775510204081619E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,11 +786,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8482421005785401</v>
+        <v>3.8511466897446902</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.20336448598130777</v>
+        <v>0.27497187364777087</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -801,11 +801,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>2.3423423423423402</v>
+        <v>5.6338028169014001</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.15529729729729713</v>
+        <v>0.37352112676056282</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -816,11 +816,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>-1.09375</v>
+        <v>-2.3696682464454901</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-6.1359375000000008E-2</v>
+        <v>-0.13293838862559201</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -831,11 +831,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>-2.40066225165562</v>
+        <v>2.6293469041560602</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-4.7773178807946834E-2</v>
+        <v>5.2324003392705591E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -846,11 +846,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-2.5385312783318201</v>
+        <v>-0.93023255813953398</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6400725294650932E-2</v>
+        <v>-9.6744186046511544E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,11 +861,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>0.50761421319796896</v>
+        <v>0.12626262626262599</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>2.7411167512690327E-3</v>
+        <v>6.8181818181818035E-4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -876,11 +876,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9179810725551998</v>
+        <v>2.1455938697318002</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.5173501577287038E-2</v>
+        <v>1.1157088122605361E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -891,11 +891,11 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>7.9545454545454497</v>
+        <v>6.7543859649122799</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>2.1477272727272716E-2</v>
+        <v>1.8236842105263159E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -906,11 +906,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>-0.295639320029563</v>
+        <v>6.4492216456634504</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-4.1389504804138826E-4</v>
+        <v>9.0289103039288311E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -921,11 +921,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-4.2669584245076502</v>
+        <v>-0.68571428571428505</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-2.9868708971553552E-3</v>
+        <v>-4.7999999999999958E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,11 +936,11 @@
         <v>1.27</v>
       </c>
       <c r="C15" s="3">
-        <v>2.2599999999999998</v>
+        <v>-1.52</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>2.8701999999999995E-2</v>
+        <v>-1.9304000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -954,7 +954,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15</f>
-        <v>0.56067354993427077</v>
+        <v>-0.31296068480130129</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1246,11 +1246,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>0.57692307692307698</v>
+        <v>-0.82855321861057996</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>5.1461538461538468E-2</v>
+        <v>-7.3906947100063736E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1261,11 +1261,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>-7.7290836653386403</v>
+        <v>7.9447322970638998</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>-0.68093227091633424</v>
+        <v>0.69993091537132957</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1276,11 +1276,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>-9.9953073674331296</v>
+        <v>-9.9582898852971802</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82761145002346315</v>
+        <v>-0.82454640250260658</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,11 +1291,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>7.9136690647482002</v>
+        <v>3.3333333333333299</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.48827338129496395</v>
+        <v>0.20566666666666644</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1306,11 +1306,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>7.9545454545454497</v>
+        <v>6.7543859649122799</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.37784090909090884</v>
+        <v>0.3208333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1321,11 +1321,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-1.5961691939345499</v>
+        <v>1.86536901865369</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-7.0550678371907108E-2</v>
+        <v>8.2449310624493094E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1336,11 +1336,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-2.6856240126382298</v>
+        <v>2.9220779220779201</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10124802527646126</v>
+        <v>0.11016233766233759</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1351,11 +1351,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>4.5269352648257097</v>
+        <v>-4.3741879601559104</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>0.16296966953372558</v>
+        <v>-0.15747076656561279</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1366,11 +1366,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-2.6381909547738598</v>
+        <v>5.67741935483871</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-8.8907035175879071E-2</v>
+        <v>0.19132903225806452</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1381,11 +1381,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>7.0175438596491198</v>
+        <v>-2.2950819672131102</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>0.18807017543859644</v>
+        <v>-6.1508196721311359E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,11 +1396,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-0.93663911845729997</v>
+        <v>-5.2836484983314698</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-2.416528925619834E-2</v>
+        <v>-0.13631813125695191</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1411,11 +1411,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-2.1951219512195101</v>
+        <v>3.6575228595178699</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-5.3780487804878006E-2</v>
+        <v>8.9609310058187827E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1426,11 +1426,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>-2.40066225165562</v>
+        <v>2.6293469041560602</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9213576158940203E-2</v>
+        <v>5.3901611535199227E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1441,11 +1441,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-0.88</v>
+        <v>-7.7481840193704601</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5224E-2</v>
+        <v>-0.13404358353510895</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1456,11 +1456,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>-0.87509944311853605</v>
+        <v>0.40128410914927698</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4351630867143989E-2</v>
+        <v>6.5810593900481416E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,11 +1471,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>-2.9481132075471699</v>
+        <v>2.6731470230862699</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-4.7759433962264161E-2</v>
+        <v>4.3304981773997574E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1486,11 +1486,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-0.90556274256144897</v>
+        <v>1.8929503916449</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3402328589909444E-2</v>
+        <v>2.8015665796344517E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1501,11 +1501,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>9.8619329388560106E-2</v>
+        <v>-1.5270935960591101</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>1.3806706114398415E-3</v>
+        <v>-2.137931034482754E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1516,11 +1516,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-1.0847107438016499</v>
+        <v>2.8198433420365498</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4101239669421449E-2</v>
+        <v>3.665796344647515E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1531,11 +1531,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-1.07317073170731</v>
+        <v>0.59171597633136097</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3521951219512107E-2</v>
+        <v>7.4556213017751482E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1546,11 +1546,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>-2.5336500395882799</v>
+        <v>0.243704305442729</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-3.0403800475059358E-2</v>
+        <v>2.9244516653127478E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,11 +1561,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>0.13623978201634801</v>
+        <v>0.20408163265306101</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>9.9455040871934057E-4</v>
+        <v>1.4897959183673454E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,11 +1576,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-3.1901041666666599</v>
+        <v>2.8917283120376598</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-2.2649739583333287E-2</v>
+        <v>2.0531271015467385E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1591,11 +1591,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>0.50761421319796896</v>
+        <v>0.12626262626262599</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>2.9949238578680167E-3</v>
+        <v>7.4494949494949335E-4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1606,11 +1606,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-4.2669584245076502</v>
+        <v>-0.68571428571428505</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3894967177242842E-2</v>
+        <v>-3.8399999999999966E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1621,11 +1621,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.4925373134328299</v>
+        <v>-1.2310606060606</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9701492537313191E-3</v>
+        <v>-4.9242424242423996E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,11 +1636,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>0.15487867836861099</v>
+        <v>-2.9381443298968999</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>6.0402684563758287E-4</v>
+        <v>-1.145876288659791E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,11 +1651,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-2.6270702455739499</v>
+        <v>2.7565982404692</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-9.4574528840662194E-3</v>
+        <v>9.9237536656891206E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,11 +1666,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>0.62015503875968903</v>
+        <v>0.15408320493066199</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>2.1085271317829429E-3</v>
+        <v>5.2388289676425078E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,11 +1681,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>0.342075256556442</v>
+        <v>-2.2727272727272698</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>1.1630558722919029E-3</v>
+        <v>-7.7272727272727181E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1696,11 +1696,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>-1.4719411223551</v>
+        <v>1.49393090569561</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-4.8574057037718303E-3</v>
+        <v>4.9299719887955134E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1711,11 +1711,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>2.3423423423423402</v>
+        <v>5.6338028169014001</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>6.0900900900900841E-3</v>
+        <v>1.4647887323943641E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1726,11 +1726,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-4.6413502109704599</v>
+        <v>-3.5398230088495501</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-8.3544303797468272E-3</v>
+        <v>-6.3716814159291901E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,11 +1741,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>-1.09375</v>
+        <v>-2.3696682464454901</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3125000000000001E-3</v>
+        <v>-2.8436018957345884E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1756,11 +1756,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-0.340831629175187</v>
+        <v>-0.96685082872928096</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3858214042263092E-4</v>
+        <v>-6.7679558011049675E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1771,11 +1771,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-1.7608897126969401</v>
+        <v>0.330188679245283</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-8.8044485634847019E-4</v>
+        <v>1.6509433962264149E-4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1786,11 +1786,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>1.2171684817424699</v>
+        <v>-1.64556962025316</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>4.8686739269698798E-4</v>
+        <v>-6.5822784810126407E-4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1801,11 +1801,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>2.56</v>
+        <v>-2.8861154446177801</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>1.024E-3</v>
+        <v>-1.1544461778471122E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1816,11 +1816,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>0.50125313283207995</v>
+        <v>-0.62344139650872799</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>1.5037593984962396E-3</v>
+        <v>-1.8703241895261838E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1831,11 +1831,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>-0.88</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>-7.3303999999999994E-2</v>
+        <v>4.7481000000000002E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1846,11 +1846,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>5.7889999999999999E-3</v>
+        <v>2.3156E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>-0.90000972431727866</v>
+        <v>0.55504517435531953</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2200,6 +2200,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2209,26 +2229,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2268,11 +2268,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>-7.7290836653386403</v>
+        <v>7.9447322970638998</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.74585657370517877</v>
+        <v>0.76666666666666639</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2283,11 +2283,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>0.57692307692307698</v>
+        <v>-0.82855321861057996</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>5.3596153846153849E-2</v>
+        <v>-7.6972594008922868E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2298,11 +2298,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9953073674331296</v>
+        <v>-9.9582898852971802</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.9235664007508213</v>
+        <v>-0.92014598540145942</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2313,11 +2313,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>7.0175438596491198</v>
+        <v>-2.2950819672131102</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.42736842105263134</v>
+        <v>-0.13977049180327841</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2328,11 +2328,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>7.9545454545454497</v>
+        <v>6.7543859649122799</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.37624999999999981</v>
+        <v>0.31948245614035087</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2343,11 +2343,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>7.9136690647482002</v>
+        <v>3.3333333333333299</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.35769784172661867</v>
+        <v>0.1506666666666665</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2358,11 +2358,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>4.5269352648257097</v>
+        <v>-4.3741879601559104</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.15391579900407412</v>
+        <v>-0.14872239064530096</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2373,11 +2373,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-1.5961691939345499</v>
+        <v>1.86536901865369</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-4.3575418994413209E-2</v>
+        <v>5.0924574209245739E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,11 +2388,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>-2.40066225165562</v>
+        <v>2.6293469041560602</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-5.5215231788079251E-2</v>
+        <v>6.0474978795589378E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2403,11 +2403,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>9.8619329388560106E-2</v>
+        <v>-1.5270935960591101</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>1.6469428007889536E-3</v>
+        <v>-2.550246305418714E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2418,11 +2418,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-0.88</v>
+        <v>-7.7481840193704601</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3904000000000001E-2</v>
+        <v>-0.12242130750605326</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2433,11 +2433,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-0.93663911845729997</v>
+        <v>-5.2836484983314698</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4705234159779611E-2</v>
+        <v>-8.2953281423804079E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2448,11 +2448,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-2.6856240126382298</v>
+        <v>2.9220779220779201</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-3.0347551342811994E-2</v>
+        <v>3.301948051948049E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2463,11 +2463,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-2.6381909547738598</v>
+        <v>5.67741935483871</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-2.7173366834170758E-2</v>
+        <v>5.8477419354838717E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2478,11 +2478,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>-0.87509944311853605</v>
+        <v>0.40128410914927698</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-8.5759745425616537E-3</v>
+        <v>3.9325842696629146E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2493,11 +2493,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.8952270081490106</v>
+        <v>-9.94832041343669</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6088474970896389E-2</v>
+        <v>-8.6550387596899203E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2508,11 +2508,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-4.2669584245076502</v>
+        <v>-0.68571428571428505</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.5175054704595135E-2</v>
+        <v>-4.045714285714281E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2523,11 +2523,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-1.7608897126969401</v>
+        <v>0.330188679245283</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-8.804448563484701E-3</v>
+        <v>1.6509433962264149E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2538,11 +2538,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>-1.4925373134328299</v>
+        <v>-1.2310606060606</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-7.1641791044775834E-3</v>
+        <v>-5.9090909090908795E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2553,11 +2553,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-1.07317073170731</v>
+        <v>0.59171597633136097</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-4.5073170731707015E-3</v>
+        <v>2.4852071005917161E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2568,11 +2568,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-0.86687306501547901</v>
+        <v>1.18675827607745</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-3.4674922600619164E-3</v>
+        <v>4.7470331043097998E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2583,11 +2583,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-3.1901041666666599</v>
+        <v>2.8917283120376598</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2122395833333308E-2</v>
+        <v>1.0988567585743108E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2598,11 +2598,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>2.3423423423423402</v>
+        <v>5.6338028169014001</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>5.8558558558558507E-3</v>
+        <v>1.4084507042253501E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2613,11 +2613,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.96575943810359899</v>
+        <v>3.45744680851063</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4143985952589974E-3</v>
+        <v>8.6436170212765753E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2628,11 +2628,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>0.62015503875968903</v>
+        <v>0.15408320493066199</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>1.4883720930232536E-3</v>
+        <v>3.6979969183358876E-4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,11 +2643,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0.13623978201634801</v>
+        <v>0.20408163265306101</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>3.1335149863760041E-4</v>
+        <v>4.6938775510204034E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2658,11 +2658,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.44444444444444398</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-8.8888888888888796E-4</v>
+        <v>2.3809523809523803E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2673,11 +2673,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>1.2171684817424699</v>
+        <v>-1.64556962025316</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>9.7373478539397595E-4</v>
+        <v>-1.3164556962025281E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2688,11 +2688,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.340831629175187</v>
+        <v>-0.96685082872928096</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-3.4083162917518701E-5</v>
+        <v>-9.6685082872928097E-5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2703,11 +2703,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>-0.88</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-7.0311999999999999E-2</v>
+        <v>4.5542999999999993E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2718,11 +2718,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>5.3900000000000007E-3</v>
+        <v>2.1560000000000003E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2763,11 +2763,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>9.49</v>
+        <v>7.81</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>5.5042000000000001E-2</v>
+        <v>4.5297999999999998E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2778,11 +2778,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>-0.15</v>
+        <v>0.78</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-8.9999999999999992E-5</v>
+        <v>4.6799999999999999E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-0.64018601261172448</v>
+        <v>-7.8090057129958194E-3</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3717,6 +3717,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3730,97 +3821,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3861,11 +3861,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>-0.72507552870090597</v>
+        <v>1.94765672550213</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.38247734138972789</v>
+        <v>1.0273889227023736</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3876,11 +3876,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-4.5398773006134903</v>
+        <v>2.31362467866323</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.50483435582822012</v>
+        <v>0.25727506426735114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3891,11 +3891,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>0.105988341282458</v>
+        <v>3.0704076230809898</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>5.6173820879702741E-4</v>
+        <v>1.6273160402329248E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3906,11 +3906,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.26</v>
+        <v>-1.41</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-7.7532000000000004E-2</v>
+        <v>-0.420462</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>-0.96428195900915104</v>
+        <v>0.8804751473720539</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4927,6 +4927,107 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4939,107 +5040,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5080,11 +5080,11 @@
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>1.6773162939297099</v>
+        <v>-3.6135113904163298</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.71353035143769861</v>
+        <v>-1.5371877454831067</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5095,11 +5095,11 @@
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>-4.8923679060665304</v>
+        <v>0.48010973936899798</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>-1.5821917808219161</v>
+        <v>0.15526748971193396</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5110,11 +5110,11 @@
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>-3.1948881789137298</v>
+        <v>-4.4884488448844797</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-0.39009584664536645</v>
+        <v>-0.54803960396039497</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5125,11 +5125,11 @@
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>-1.8217821782178201</v>
+        <v>-0.84711577248890602</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>-0.19893861386138595</v>
+        <v>-9.2505042355788533E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5140,11 +5140,11 @@
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-2.7552674230145802</v>
+        <v>-3.3333333333333299</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.16228525121555876</v>
+        <v>-0.19633333333333311</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5155,11 +5155,11 @@
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>-2.5157232704402501</v>
+        <v>-1.9607843137254899</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.14289308176100621</v>
+        <v>-0.11137254901960782</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5173,7 +5173,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-1.7628742228675349</v>
+        <v>-2.330170784440297</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6394,6 +6394,132 @@
     </row>
   </sheetData>
   <mergeCells count="138">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6406,132 +6532,6 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BAF415-617A-49F2-BAAA-5B16F80784EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7D179F-8E85-41A7-833A-189764F2C116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37200" yWindow="120" windowWidth="15300" windowHeight="20730" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24060" yWindow="195" windowWidth="23550" windowHeight="20325" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="PBR" sheetId="3" r:id="rId3"/>
     <sheet name="DFI" sheetId="4" r:id="rId4"/>
     <sheet name="BMU" sheetId="6" r:id="rId5"/>
+    <sheet name="KHA" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="101">
   <si>
     <t>DSTKF</t>
   </si>
@@ -263,6 +264,81 @@
   </si>
   <si>
     <t>MARJ</t>
+  </si>
+  <si>
+    <t>EUPWR</t>
+  </si>
+  <si>
+    <t>KORDS</t>
+  </si>
+  <si>
+    <t>AEFES</t>
+  </si>
+  <si>
+    <t>ARCLK</t>
+  </si>
+  <si>
+    <t>ULKER</t>
+  </si>
+  <si>
+    <t>HALKB</t>
+  </si>
+  <si>
+    <t>ATATR</t>
+  </si>
+  <si>
+    <t>PETKM</t>
+  </si>
+  <si>
+    <t>TOASO</t>
+  </si>
+  <si>
+    <t>ISMEN</t>
+  </si>
+  <si>
+    <t>KRDMD</t>
+  </si>
+  <si>
+    <t>CCOLA</t>
+  </si>
+  <si>
+    <t>CANTE</t>
+  </si>
+  <si>
+    <t>ALARK</t>
+  </si>
+  <si>
+    <t>SISE</t>
+  </si>
+  <si>
+    <t>AGHOL</t>
+  </si>
+  <si>
+    <t>FROTO</t>
+  </si>
+  <si>
+    <t>EGEPO</t>
+  </si>
+  <si>
+    <t>MAVI</t>
+  </si>
+  <si>
+    <t>BRKO</t>
+  </si>
+  <si>
+    <t>ASELS</t>
+  </si>
+  <si>
+    <t>TURSG</t>
+  </si>
+  <si>
+    <t>KGYO</t>
+  </si>
+  <si>
+    <t>TUPRS</t>
+  </si>
+  <si>
+    <t>BIZIM</t>
   </si>
 </sst>
 </file>
@@ -334,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -404,8 +480,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1020,15 +1105,15 @@
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="9"/>
       <c r="D30" s="19"/>
     </row>
@@ -1036,10 +1121,10 @@
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="27"/>
+      <c r="C31" s="28"/>
       <c r="D31" s="20" t="s">
         <v>53</v>
       </c>
@@ -1054,10 +1139,10 @@
       <c r="A32" s="18">
         <v>46226</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>98970</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="25">
         <v>232874657613</v>
       </c>
@@ -1072,10 +1157,10 @@
       <c r="A33" s="18">
         <v>46227</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="27">
         <v>99051</v>
       </c>
-      <c r="C33" s="26"/>
+      <c r="C33" s="27"/>
       <c r="D33" s="25">
         <v>227320292084</v>
       </c>
@@ -1090,10 +1175,10 @@
       <c r="A34" s="18">
         <v>46230</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>98455</v>
       </c>
-      <c r="C34" s="26"/>
+      <c r="C34" s="27"/>
       <c r="D34" s="25">
         <v>229116006481</v>
       </c>
@@ -1108,10 +1193,10 @@
       <c r="A35" s="18">
         <v>46231</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="27">
         <v>98583</v>
       </c>
-      <c r="C35" s="26"/>
+      <c r="C35" s="27"/>
       <c r="D35" s="25">
         <v>232227975662</v>
       </c>
@@ -1126,10 +1211,10 @@
       <c r="A36" s="18">
         <v>46232</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="27">
         <v>98915</v>
       </c>
-      <c r="C36" s="26"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="25">
         <v>226192717226</v>
       </c>
@@ -1144,10 +1229,10 @@
       <c r="A37" s="18">
         <v>46233</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="27">
         <v>97411</v>
       </c>
-      <c r="C37" s="26"/>
+      <c r="C37" s="27"/>
       <c r="D37" s="25">
         <v>223802010766</v>
       </c>
@@ -1162,10 +1247,10 @@
       <c r="A38" s="18">
         <v>46234</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="27">
         <v>97269</v>
       </c>
-      <c r="C38" s="26"/>
+      <c r="C38" s="27"/>
       <c r="D38" s="25">
         <v>223121593370</v>
       </c>
@@ -1890,15 +1975,15 @@
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="27"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="26"/>
-      <c r="B50" s="26"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
@@ -1906,10 +1991,10 @@
       <c r="A55" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="27"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="20" t="s">
         <v>53</v>
       </c>
@@ -1924,10 +2009,10 @@
       <c r="A56" s="18">
         <v>46226</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="27">
         <v>160454</v>
       </c>
-      <c r="C56" s="26"/>
+      <c r="C56" s="27"/>
       <c r="D56" s="21">
         <v>74464707242</v>
       </c>
@@ -1942,10 +2027,10 @@
       <c r="A57" s="18">
         <v>46227</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="27">
         <v>159246</v>
       </c>
-      <c r="C57" s="26"/>
+      <c r="C57" s="27"/>
       <c r="D57" s="21">
         <v>74038207243</v>
       </c>
@@ -1960,10 +2045,10 @@
       <c r="A58" s="18">
         <v>46230</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="27">
         <v>159672</v>
       </c>
-      <c r="C58" s="26"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="21">
         <v>74765554505</v>
       </c>
@@ -1978,10 +2063,10 @@
       <c r="A59" s="18">
         <v>46231</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="27">
         <v>160788</v>
       </c>
-      <c r="C59" s="26"/>
+      <c r="C59" s="27"/>
       <c r="D59" s="21">
         <v>74770957010</v>
       </c>
@@ -1996,10 +2081,10 @@
       <c r="A60" s="18">
         <v>46232</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="27">
         <v>162385</v>
       </c>
-      <c r="C60" s="26"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="21">
         <v>72261693709</v>
       </c>
@@ -2014,10 +2099,10 @@
       <c r="A61" s="18">
         <v>46233</v>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="27">
         <v>160805</v>
       </c>
-      <c r="C61" s="26"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="21">
         <v>69072635445</v>
       </c>
@@ -2032,10 +2117,10 @@
       <c r="A62" s="18">
         <v>46234</v>
       </c>
-      <c r="B62" s="26">
+      <c r="B62" s="27">
         <v>159675</v>
       </c>
-      <c r="C62" s="26"/>
+      <c r="C62" s="27"/>
       <c r="D62" s="21">
         <v>63472489182</v>
       </c>
@@ -2048,178 +2133,158 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
       <c r="D63" s="19"/>
       <c r="E63" s="22"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
       <c r="D64" s="19"/>
       <c r="E64" s="22"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
       <c r="D65" s="19"/>
       <c r="E65" s="22"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
       <c r="D66" s="19"/>
       <c r="E66" s="22"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
       <c r="D67" s="19"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
       <c r="D68" s="19"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
       <c r="D69" s="19"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
       <c r="D70" s="19"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
       <c r="D71" s="19"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
       <c r="D72" s="19"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="27"/>
       <c r="D73" s="19"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="27"/>
       <c r="D74" s="19"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="27"/>
       <c r="D75" s="19"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
       <c r="D76" s="19"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
       <c r="D77" s="19"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
       <c r="D78" s="19"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
       <c r="D79" s="19"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="19"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
       <c r="D81" s="19"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2229,6 +2294,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2807,15 +2892,15 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="26"/>
-      <c r="B44" s="26"/>
+      <c r="A44" s="27"/>
+      <c r="B44" s="27"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="17"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
+      <c r="A45" s="27"/>
+      <c r="B45" s="27"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
     </row>
@@ -2823,10 +2908,10 @@
       <c r="A53" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="27"/>
+      <c r="C53" s="28"/>
       <c r="D53" s="20" t="s">
         <v>53</v>
       </c>
@@ -2841,10 +2926,10 @@
       <c r="A54" s="18">
         <v>46226</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B54" s="27">
         <v>78223</v>
       </c>
-      <c r="C54" s="26"/>
+      <c r="C54" s="27"/>
       <c r="D54" s="21">
         <v>38343912280</v>
       </c>
@@ -2859,10 +2944,10 @@
       <c r="A55" s="18">
         <v>46227</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="27">
         <v>78055</v>
       </c>
-      <c r="C55" s="26"/>
+      <c r="C55" s="27"/>
       <c r="D55" s="21">
         <v>38547597437</v>
       </c>
@@ -2877,10 +2962,10 @@
       <c r="A56" s="18">
         <v>46230</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="27">
         <v>78840</v>
       </c>
-      <c r="C56" s="26"/>
+      <c r="C56" s="27"/>
       <c r="D56" s="21">
         <v>39148877217</v>
       </c>
@@ -2895,10 +2980,10 @@
       <c r="A57" s="18">
         <v>46231</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="27">
         <v>79795</v>
       </c>
-      <c r="C57" s="26"/>
+      <c r="C57" s="27"/>
       <c r="D57" s="21">
         <v>39293398935</v>
       </c>
@@ -2913,10 +2998,10 @@
       <c r="A58" s="23">
         <v>46232</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="27">
         <v>80830</v>
       </c>
-      <c r="C58" s="26"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="21">
         <v>38188651284</v>
       </c>
@@ -2931,10 +3016,10 @@
       <c r="A59" s="18">
         <v>46233</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="27">
         <v>80272</v>
       </c>
-      <c r="C59" s="26"/>
+      <c r="C59" s="27"/>
       <c r="D59" s="21">
         <v>36982629736</v>
       </c>
@@ -2949,10 +3034,10 @@
       <c r="A60" s="18">
         <v>46234</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="27">
         <v>79803</v>
       </c>
-      <c r="C60" s="26"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="21">
         <v>33560330080</v>
       </c>
@@ -2965,849 +3050,758 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="21"/>
       <c r="E61" s="22"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
       <c r="D62" s="21"/>
       <c r="E62" s="22"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
       <c r="D63" s="21"/>
       <c r="E63" s="22"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
       <c r="D64" s="21"/>
       <c r="E64" s="22"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
       <c r="D65" s="21"/>
       <c r="E65" s="22"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
       <c r="D66" s="21"/>
       <c r="E66" s="22"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
       <c r="D67" s="21"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
       <c r="D68" s="21"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
       <c r="D69" s="21"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
       <c r="D70" s="21"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
       <c r="D71" s="21"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
       <c r="D72" s="21"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="27"/>
       <c r="D73" s="21"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="27"/>
       <c r="D74" s="21"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="27"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
       <c r="D76" s="21"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
       <c r="D77" s="21"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
       <c r="D78" s="21"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
       <c r="D79" s="21"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="21"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
       <c r="D81" s="21"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
+      <c r="B82" s="27"/>
+      <c r="C82" s="27"/>
       <c r="D82" s="21"/>
       <c r="E82" s="22"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="26"/>
+      <c r="B83" s="27"/>
+      <c r="C83" s="27"/>
       <c r="D83" s="21"/>
       <c r="E83" s="22"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="27"/>
       <c r="D84" s="21"/>
       <c r="E84" s="22"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
       <c r="D85" s="21"/>
       <c r="E85" s="22"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
       <c r="D86" s="21"/>
       <c r="E86" s="22"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="18"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
+      <c r="B87" s="27"/>
+      <c r="C87" s="27"/>
       <c r="D87" s="21"/>
       <c r="E87" s="22"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="27"/>
       <c r="D88" s="21"/>
       <c r="E88" s="22"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="18"/>
-      <c r="B89" s="26"/>
-      <c r="C89" s="26"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="27"/>
       <c r="D89" s="21"/>
       <c r="E89" s="22"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="18"/>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
       <c r="D90" s="21"/>
       <c r="E90" s="22"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="18"/>
-      <c r="B91" s="26"/>
-      <c r="C91" s="26"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
       <c r="D91" s="21"/>
       <c r="E91" s="22"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
+      <c r="B92" s="27"/>
+      <c r="C92" s="27"/>
       <c r="D92" s="21"/>
       <c r="E92" s="22"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="26"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
       <c r="D93" s="21"/>
       <c r="E93" s="22"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="27"/>
       <c r="D94" s="21"/>
       <c r="E94" s="22"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="27"/>
       <c r="D95" s="21"/>
       <c r="E95" s="22"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26"/>
+      <c r="B96" s="27"/>
+      <c r="C96" s="27"/>
       <c r="D96" s="21"/>
       <c r="E96" s="22"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="27"/>
       <c r="D97" s="21"/>
       <c r="E97" s="22"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
       <c r="D98" s="21"/>
       <c r="E98" s="22"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="27"/>
       <c r="D99" s="21"/>
       <c r="E99" s="22"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
+      <c r="B100" s="27"/>
+      <c r="C100" s="27"/>
       <c r="D100" s="21"/>
       <c r="E100" s="22"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="27"/>
       <c r="D101" s="21"/>
       <c r="E101" s="22"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
+      <c r="B102" s="27"/>
+      <c r="C102" s="27"/>
       <c r="D102" s="21"/>
       <c r="E102" s="22"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="27"/>
       <c r="D103" s="21"/>
       <c r="E103" s="22"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="27"/>
       <c r="D104" s="21"/>
       <c r="E104" s="22"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="27"/>
       <c r="D105" s="21"/>
       <c r="E105" s="22"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="18"/>
-      <c r="B106" s="26"/>
-      <c r="C106" s="26"/>
+      <c r="B106" s="27"/>
+      <c r="C106" s="27"/>
       <c r="D106" s="21"/>
       <c r="E106" s="22"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="18"/>
-      <c r="B107" s="26"/>
-      <c r="C107" s="26"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="27"/>
       <c r="D107" s="21"/>
       <c r="E107" s="22"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="18"/>
-      <c r="B108" s="26"/>
-      <c r="C108" s="26"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="27"/>
       <c r="D108" s="21"/>
       <c r="E108" s="22"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="18"/>
-      <c r="B109" s="26"/>
-      <c r="C109" s="26"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="27"/>
       <c r="D109" s="21"/>
       <c r="E109" s="22"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
+      <c r="B110" s="27"/>
+      <c r="C110" s="27"/>
       <c r="D110" s="21"/>
       <c r="E110" s="22"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="18"/>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="27"/>
       <c r="D111" s="21"/>
       <c r="E111" s="22"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="18"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
+      <c r="B112" s="27"/>
+      <c r="C112" s="27"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="18"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="26"/>
+      <c r="B113" s="27"/>
+      <c r="C113" s="27"/>
       <c r="D113" s="21"/>
       <c r="E113" s="22"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="18"/>
-      <c r="B114" s="26"/>
-      <c r="C114" s="26"/>
+      <c r="B114" s="27"/>
+      <c r="C114" s="27"/>
       <c r="D114" s="21"/>
       <c r="E114" s="22"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="18"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
       <c r="D115" s="21"/>
       <c r="E115" s="22"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="18"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="26"/>
+      <c r="B116" s="27"/>
+      <c r="C116" s="27"/>
       <c r="D116" s="21"/>
       <c r="E116" s="22"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="18"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="26"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="27"/>
       <c r="D117" s="21"/>
       <c r="E117" s="22"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="18"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="26"/>
+      <c r="B118" s="27"/>
+      <c r="C118" s="27"/>
       <c r="D118" s="21"/>
       <c r="E118" s="22"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="18"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="26"/>
+      <c r="B119" s="27"/>
+      <c r="C119" s="27"/>
       <c r="D119" s="21"/>
       <c r="E119" s="22"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="18"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="26"/>
+      <c r="B120" s="27"/>
+      <c r="C120" s="27"/>
       <c r="D120" s="21"/>
       <c r="E120" s="22"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="18"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="26"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="27"/>
       <c r="D121" s="21"/>
       <c r="E121" s="22"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="26"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="27"/>
       <c r="D122" s="21"/>
       <c r="E122" s="22"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="18"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="26"/>
+      <c r="B123" s="27"/>
+      <c r="C123" s="27"/>
       <c r="D123" s="21"/>
       <c r="E123" s="22"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="18"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="26"/>
+      <c r="B124" s="27"/>
+      <c r="C124" s="27"/>
       <c r="D124" s="21"/>
       <c r="E124" s="22"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="18"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="26"/>
+      <c r="B125" s="27"/>
+      <c r="C125" s="27"/>
       <c r="D125" s="21"/>
       <c r="E125" s="22"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="18"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="26"/>
+      <c r="B126" s="27"/>
+      <c r="C126" s="27"/>
       <c r="D126" s="21"/>
       <c r="E126" s="22"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="18"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="26"/>
+      <c r="B127" s="27"/>
+      <c r="C127" s="27"/>
       <c r="D127" s="21"/>
       <c r="E127" s="22"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="18"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="26"/>
+      <c r="B128" s="27"/>
+      <c r="C128" s="27"/>
       <c r="D128" s="21"/>
       <c r="E128" s="22"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="18"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="26"/>
+      <c r="B129" s="27"/>
+      <c r="C129" s="27"/>
       <c r="D129" s="21"/>
       <c r="E129" s="22"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="18"/>
-      <c r="B130" s="26"/>
-      <c r="C130" s="26"/>
+      <c r="B130" s="27"/>
+      <c r="C130" s="27"/>
       <c r="D130" s="21"/>
       <c r="E130" s="22"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="18"/>
-      <c r="B131" s="26"/>
-      <c r="C131" s="26"/>
+      <c r="B131" s="27"/>
+      <c r="C131" s="27"/>
       <c r="D131" s="21"/>
       <c r="E131" s="22"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="18"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
+      <c r="B132" s="27"/>
+      <c r="C132" s="27"/>
       <c r="D132" s="21"/>
       <c r="E132" s="22"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="18"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="26"/>
+      <c r="B133" s="27"/>
+      <c r="C133" s="27"/>
       <c r="D133" s="21"/>
       <c r="E133" s="22"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
-      <c r="B134" s="26"/>
-      <c r="C134" s="26"/>
+      <c r="B134" s="27"/>
+      <c r="C134" s="27"/>
       <c r="D134" s="21"/>
       <c r="E134" s="22"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="18"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="26"/>
+      <c r="B135" s="27"/>
+      <c r="C135" s="27"/>
       <c r="D135" s="21"/>
       <c r="E135" s="22"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="18"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
+      <c r="B136" s="27"/>
+      <c r="C136" s="27"/>
       <c r="D136" s="21"/>
       <c r="E136" s="22"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="18"/>
-      <c r="B137" s="26"/>
-      <c r="C137" s="26"/>
+      <c r="B137" s="27"/>
+      <c r="C137" s="27"/>
       <c r="D137" s="21"/>
       <c r="E137" s="22"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="18"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="26"/>
+      <c r="B138" s="27"/>
+      <c r="C138" s="27"/>
       <c r="D138" s="21"/>
       <c r="E138" s="22"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="18"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
+      <c r="B139" s="27"/>
+      <c r="C139" s="27"/>
       <c r="D139" s="21"/>
       <c r="E139" s="22"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="18"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="26"/>
+      <c r="B140" s="27"/>
+      <c r="C140" s="27"/>
       <c r="D140" s="21"/>
       <c r="E140" s="22"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="18"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="26"/>
+      <c r="B141" s="27"/>
+      <c r="C141" s="27"/>
       <c r="D141" s="21"/>
       <c r="E141" s="22"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="18"/>
-      <c r="B142" s="26"/>
-      <c r="C142" s="26"/>
+      <c r="B142" s="27"/>
+      <c r="C142" s="27"/>
       <c r="D142" s="21"/>
       <c r="E142" s="22"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="18"/>
-      <c r="B143" s="26"/>
-      <c r="C143" s="26"/>
+      <c r="B143" s="27"/>
+      <c r="C143" s="27"/>
       <c r="D143" s="21"/>
       <c r="E143" s="22"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="18"/>
-      <c r="B144" s="26"/>
-      <c r="C144" s="26"/>
+      <c r="B144" s="27"/>
+      <c r="C144" s="27"/>
       <c r="D144" s="21"/>
       <c r="E144" s="22"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="18"/>
-      <c r="B145" s="26"/>
-      <c r="C145" s="26"/>
+      <c r="B145" s="27"/>
+      <c r="C145" s="27"/>
       <c r="D145" s="21"/>
       <c r="E145" s="22"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="18"/>
-      <c r="B146" s="26"/>
-      <c r="C146" s="26"/>
+      <c r="B146" s="27"/>
+      <c r="C146" s="27"/>
       <c r="D146" s="21"/>
       <c r="E146" s="22"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="18"/>
-      <c r="B147" s="26"/>
-      <c r="C147" s="26"/>
+      <c r="B147" s="27"/>
+      <c r="C147" s="27"/>
       <c r="D147" s="21"/>
       <c r="E147" s="22"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="18"/>
-      <c r="B148" s="26"/>
-      <c r="C148" s="26"/>
+      <c r="B148" s="27"/>
+      <c r="C148" s="27"/>
       <c r="D148" s="21"/>
       <c r="E148" s="22"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="18"/>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
+      <c r="B149" s="27"/>
+      <c r="C149" s="27"/>
       <c r="D149" s="21"/>
       <c r="E149" s="22"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="18"/>
-      <c r="B150" s="26"/>
-      <c r="C150" s="26"/>
+      <c r="B150" s="27"/>
+      <c r="C150" s="27"/>
       <c r="D150" s="21"/>
       <c r="E150" s="22"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="18"/>
-      <c r="B151" s="26"/>
-      <c r="C151" s="26"/>
+      <c r="B151" s="27"/>
+      <c r="C151" s="27"/>
       <c r="D151" s="21"/>
       <c r="E151" s="22"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
-      <c r="B152" s="26"/>
-      <c r="C152" s="26"/>
+      <c r="B152" s="27"/>
+      <c r="C152" s="27"/>
       <c r="D152" s="21"/>
       <c r="E152" s="22"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="18"/>
-      <c r="B153" s="26"/>
-      <c r="C153" s="26"/>
+      <c r="B153" s="27"/>
+      <c r="C153" s="27"/>
       <c r="D153" s="21"/>
       <c r="E153" s="22"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="18"/>
-      <c r="B154" s="26"/>
-      <c r="C154" s="26"/>
+      <c r="B154" s="27"/>
+      <c r="C154" s="27"/>
       <c r="D154" s="21"/>
       <c r="E154" s="22"/>
       <c r="F154" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3821,6 +3815,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3945,15 +4030,15 @@
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
@@ -3961,10 +4046,10 @@
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="27"/>
+      <c r="C31" s="28"/>
       <c r="D31" s="20" t="s">
         <v>53</v>
       </c>
@@ -3979,10 +4064,10 @@
       <c r="A32" s="23">
         <v>46226</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>48221</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="21">
         <v>28591206600</v>
       </c>
@@ -3997,10 +4082,10 @@
       <c r="A33" s="23">
         <v>46227</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="27">
         <v>48802</v>
       </c>
-      <c r="C33" s="26"/>
+      <c r="C33" s="27"/>
       <c r="D33" s="21">
         <v>29255953804</v>
       </c>
@@ -4015,10 +4100,10 @@
       <c r="A34" s="23">
         <v>46230</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>49403</v>
       </c>
-      <c r="C34" s="26"/>
+      <c r="C34" s="27"/>
       <c r="D34" s="21">
         <v>30359209400</v>
       </c>
@@ -4033,10 +4118,10 @@
       <c r="A35" s="23">
         <v>46231</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="27">
         <v>49817</v>
       </c>
-      <c r="C35" s="26"/>
+      <c r="C35" s="27"/>
       <c r="D35" s="21">
         <v>30985486603</v>
       </c>
@@ -4051,10 +4136,10 @@
       <c r="A36" s="23">
         <v>46232</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="27">
         <v>50631</v>
       </c>
-      <c r="C36" s="26"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="21">
         <v>32047144824</v>
       </c>
@@ -4069,10 +4154,10 @@
       <c r="A37" s="23">
         <v>46233</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="27">
         <v>50968</v>
       </c>
-      <c r="C37" s="26"/>
+      <c r="C37" s="27"/>
       <c r="D37" s="21">
         <v>32438714789</v>
       </c>
@@ -4087,10 +4172,10 @@
       <c r="A38" s="23">
         <v>46234</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="27">
         <v>51171</v>
       </c>
-      <c r="C38" s="26"/>
+      <c r="C38" s="27"/>
       <c r="D38" s="21">
         <v>31996446996</v>
       </c>
@@ -4103,931 +4188,830 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
       <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="27"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="27"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="27"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
+      <c r="B82" s="27"/>
+      <c r="C82" s="27"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="26"/>
+      <c r="B83" s="27"/>
+      <c r="C83" s="27"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="27"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
+      <c r="B87" s="27"/>
+      <c r="C87" s="27"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="27"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="26"/>
-      <c r="C89" s="26"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="27"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="26"/>
-      <c r="C91" s="26"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
+      <c r="B92" s="27"/>
+      <c r="C92" s="27"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="26"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="27"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="27"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26"/>
+      <c r="B96" s="27"/>
+      <c r="C96" s="27"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="27"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="27"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
+      <c r="B100" s="27"/>
+      <c r="C100" s="27"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="27"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
+      <c r="B102" s="27"/>
+      <c r="C102" s="27"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="27"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="27"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="27"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="26"/>
-      <c r="C106" s="26"/>
+      <c r="B106" s="27"/>
+      <c r="C106" s="27"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="26"/>
-      <c r="C107" s="26"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="27"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="26"/>
-      <c r="C108" s="26"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="27"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="26"/>
-      <c r="C109" s="26"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="27"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
+      <c r="B110" s="27"/>
+      <c r="C110" s="27"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="27"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
+      <c r="B112" s="27"/>
+      <c r="C112" s="27"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="26"/>
+      <c r="B113" s="27"/>
+      <c r="C113" s="27"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="26"/>
-      <c r="C114" s="26"/>
+      <c r="B114" s="27"/>
+      <c r="C114" s="27"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="26"/>
+      <c r="B116" s="27"/>
+      <c r="C116" s="27"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="26"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="27"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="26"/>
+      <c r="B118" s="27"/>
+      <c r="C118" s="27"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="26"/>
+      <c r="B119" s="27"/>
+      <c r="C119" s="27"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="26"/>
+      <c r="B120" s="27"/>
+      <c r="C120" s="27"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="26"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="27"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="26"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="27"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="26"/>
+      <c r="B123" s="27"/>
+      <c r="C123" s="27"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="26"/>
+      <c r="B124" s="27"/>
+      <c r="C124" s="27"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="26"/>
+      <c r="B125" s="27"/>
+      <c r="C125" s="27"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="26"/>
+      <c r="B126" s="27"/>
+      <c r="C126" s="27"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="26"/>
+      <c r="B127" s="27"/>
+      <c r="C127" s="27"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="26"/>
+      <c r="B128" s="27"/>
+      <c r="C128" s="27"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="26"/>
+      <c r="B129" s="27"/>
+      <c r="C129" s="27"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="26"/>
-      <c r="C130" s="26"/>
+      <c r="B130" s="27"/>
+      <c r="C130" s="27"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="26"/>
-      <c r="C131" s="26"/>
+      <c r="B131" s="27"/>
+      <c r="C131" s="27"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
+      <c r="B132" s="27"/>
+      <c r="C132" s="27"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="26"/>
+      <c r="B133" s="27"/>
+      <c r="C133" s="27"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="26"/>
-      <c r="C134" s="26"/>
+      <c r="B134" s="27"/>
+      <c r="C134" s="27"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="26"/>
+      <c r="B135" s="27"/>
+      <c r="C135" s="27"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
+      <c r="B136" s="27"/>
+      <c r="C136" s="27"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="26"/>
-      <c r="C137" s="26"/>
+      <c r="B137" s="27"/>
+      <c r="C137" s="27"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="26"/>
+      <c r="B138" s="27"/>
+      <c r="C138" s="27"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
+      <c r="B139" s="27"/>
+      <c r="C139" s="27"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="26"/>
+      <c r="B140" s="27"/>
+      <c r="C140" s="27"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="26"/>
+      <c r="B141" s="27"/>
+      <c r="C141" s="27"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5040,6 +5024,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5198,16 +5283,16 @@
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="17"/>
@@ -5228,10 +5313,10 @@
       <c r="A37" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="28"/>
       <c r="D37" s="20" t="s">
         <v>53</v>
       </c>
@@ -5246,10 +5331,10 @@
       <c r="A38" s="23">
         <v>46226</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="27">
         <v>6356</v>
       </c>
-      <c r="C38" s="26"/>
+      <c r="C38" s="27"/>
       <c r="D38" s="21">
         <v>1033181017</v>
       </c>
@@ -5264,10 +5349,10 @@
       <c r="A39" s="23">
         <v>46227</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="27">
         <v>6609</v>
       </c>
-      <c r="C39" s="26"/>
+      <c r="C39" s="27"/>
       <c r="D39" s="21">
         <v>1076556627</v>
       </c>
@@ -5282,10 +5367,10 @@
       <c r="A40" s="23">
         <v>46230</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="27">
         <v>6906</v>
       </c>
-      <c r="C40" s="26"/>
+      <c r="C40" s="27"/>
       <c r="D40" s="21">
         <v>1167160796</v>
       </c>
@@ -5300,10 +5385,10 @@
       <c r="A41" s="23">
         <v>46231</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="27">
         <v>7221</v>
       </c>
-      <c r="C41" s="26"/>
+      <c r="C41" s="27"/>
       <c r="D41" s="21">
         <v>1220111851</v>
       </c>
@@ -5318,10 +5403,10 @@
       <c r="A42" s="23">
         <v>46232</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="27">
         <v>7429</v>
       </c>
-      <c r="C42" s="26"/>
+      <c r="C42" s="27"/>
       <c r="D42" s="21">
         <v>1191517169</v>
       </c>
@@ -5336,10 +5421,10 @@
       <c r="A43" s="23">
         <v>46233</v>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="27">
         <v>7272</v>
       </c>
-      <c r="C43" s="26"/>
+      <c r="C43" s="27"/>
       <c r="D43" s="21">
         <v>1145188929</v>
       </c>
@@ -5354,10 +5439,10 @@
       <c r="A44" s="23">
         <v>46234</v>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="27">
         <v>7038</v>
       </c>
-      <c r="C44" s="26"/>
+      <c r="C44" s="27"/>
       <c r="D44" s="21">
         <v>1042575112</v>
       </c>
@@ -5370,1156 +5455,1030 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="27"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="27"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="27"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
+      <c r="B82" s="27"/>
+      <c r="C82" s="27"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="26"/>
+      <c r="B83" s="27"/>
+      <c r="C83" s="27"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
+      <c r="B84" s="27"/>
+      <c r="C84" s="27"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
+      <c r="B87" s="27"/>
+      <c r="C87" s="27"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
+      <c r="B88" s="27"/>
+      <c r="C88" s="27"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="26"/>
-      <c r="C89" s="26"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="27"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="26"/>
-      <c r="C91" s="26"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
+      <c r="B92" s="27"/>
+      <c r="C92" s="27"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="26"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="27"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="27"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26"/>
+      <c r="B96" s="27"/>
+      <c r="C96" s="27"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="27"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="27"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
+      <c r="B100" s="27"/>
+      <c r="C100" s="27"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="27"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
+      <c r="B102" s="27"/>
+      <c r="C102" s="27"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="27"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="27"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="27"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="26"/>
-      <c r="C106" s="26"/>
+      <c r="B106" s="27"/>
+      <c r="C106" s="27"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="26"/>
-      <c r="C107" s="26"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="27"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="26"/>
-      <c r="C108" s="26"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="27"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="26"/>
-      <c r="C109" s="26"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="27"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
+      <c r="B110" s="27"/>
+      <c r="C110" s="27"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="27"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
+      <c r="B112" s="27"/>
+      <c r="C112" s="27"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="26"/>
+      <c r="B113" s="27"/>
+      <c r="C113" s="27"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="26"/>
-      <c r="C114" s="26"/>
+      <c r="B114" s="27"/>
+      <c r="C114" s="27"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="26"/>
+      <c r="B116" s="27"/>
+      <c r="C116" s="27"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="26"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="27"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="26"/>
+      <c r="B118" s="27"/>
+      <c r="C118" s="27"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="26"/>
+      <c r="B119" s="27"/>
+      <c r="C119" s="27"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="26"/>
+      <c r="B120" s="27"/>
+      <c r="C120" s="27"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="26"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="27"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="26"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="27"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="26"/>
+      <c r="B123" s="27"/>
+      <c r="C123" s="27"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="26"/>
+      <c r="B124" s="27"/>
+      <c r="C124" s="27"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="26"/>
+      <c r="B125" s="27"/>
+      <c r="C125" s="27"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="26"/>
+      <c r="B126" s="27"/>
+      <c r="C126" s="27"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="26"/>
+      <c r="B127" s="27"/>
+      <c r="C127" s="27"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="26"/>
+      <c r="B128" s="27"/>
+      <c r="C128" s="27"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="26"/>
+      <c r="B129" s="27"/>
+      <c r="C129" s="27"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="26"/>
-      <c r="C130" s="26"/>
+      <c r="B130" s="27"/>
+      <c r="C130" s="27"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="26"/>
-      <c r="C131" s="26"/>
+      <c r="B131" s="27"/>
+      <c r="C131" s="27"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
+      <c r="B132" s="27"/>
+      <c r="C132" s="27"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="26"/>
+      <c r="B133" s="27"/>
+      <c r="C133" s="27"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="26"/>
-      <c r="C134" s="26"/>
+      <c r="B134" s="27"/>
+      <c r="C134" s="27"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="26"/>
+      <c r="B135" s="27"/>
+      <c r="C135" s="27"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
+      <c r="B136" s="27"/>
+      <c r="C136" s="27"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="26"/>
-      <c r="C137" s="26"/>
+      <c r="B137" s="27"/>
+      <c r="C137" s="27"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="26"/>
+      <c r="B138" s="27"/>
+      <c r="C138" s="27"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
+      <c r="B139" s="27"/>
+      <c r="C139" s="27"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="26"/>
+      <c r="B140" s="27"/>
+      <c r="C140" s="27"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="26"/>
+      <c r="B141" s="27"/>
+      <c r="C141" s="27"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="23"/>
-      <c r="B142" s="26"/>
-      <c r="C142" s="26"/>
+      <c r="B142" s="27"/>
+      <c r="C142" s="27"/>
       <c r="D142" s="21"/>
       <c r="E142" s="21"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="23"/>
-      <c r="B143" s="26"/>
-      <c r="C143" s="26"/>
+      <c r="B143" s="27"/>
+      <c r="C143" s="27"/>
       <c r="D143" s="21"/>
       <c r="E143" s="21"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="23"/>
-      <c r="B144" s="26"/>
-      <c r="C144" s="26"/>
+      <c r="B144" s="27"/>
+      <c r="C144" s="27"/>
       <c r="D144" s="21"/>
       <c r="E144" s="21"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="23"/>
-      <c r="B145" s="26"/>
-      <c r="C145" s="26"/>
+      <c r="B145" s="27"/>
+      <c r="C145" s="27"/>
       <c r="D145" s="21"/>
       <c r="E145" s="21"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="23"/>
-      <c r="B146" s="26"/>
-      <c r="C146" s="26"/>
+      <c r="B146" s="27"/>
+      <c r="C146" s="27"/>
       <c r="D146" s="21"/>
       <c r="E146" s="21"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="23"/>
-      <c r="B147" s="26"/>
-      <c r="C147" s="26"/>
+      <c r="B147" s="27"/>
+      <c r="C147" s="27"/>
       <c r="D147" s="21"/>
       <c r="E147" s="21"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="23"/>
-      <c r="B148" s="26"/>
-      <c r="C148" s="26"/>
+      <c r="B148" s="27"/>
+      <c r="C148" s="27"/>
       <c r="D148" s="21"/>
       <c r="E148" s="21"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="23"/>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
+      <c r="B149" s="27"/>
+      <c r="C149" s="27"/>
       <c r="D149" s="21"/>
       <c r="E149" s="21"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="23"/>
-      <c r="B150" s="26"/>
-      <c r="C150" s="26"/>
+      <c r="B150" s="27"/>
+      <c r="C150" s="27"/>
       <c r="D150" s="21"/>
       <c r="E150" s="21"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="23"/>
-      <c r="B151" s="26"/>
-      <c r="C151" s="26"/>
+      <c r="B151" s="27"/>
+      <c r="C151" s="27"/>
       <c r="D151" s="21"/>
       <c r="E151" s="21"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="23"/>
-      <c r="B152" s="26"/>
-      <c r="C152" s="26"/>
+      <c r="B152" s="27"/>
+      <c r="C152" s="27"/>
       <c r="D152" s="21"/>
       <c r="E152" s="21"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="23"/>
-      <c r="B153" s="26"/>
-      <c r="C153" s="26"/>
+      <c r="B153" s="27"/>
+      <c r="C153" s="27"/>
       <c r="D153" s="21"/>
       <c r="E153" s="21"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="23"/>
-      <c r="B154" s="26"/>
-      <c r="C154" s="26"/>
+      <c r="B154" s="27"/>
+      <c r="C154" s="27"/>
       <c r="D154" s="21"/>
       <c r="E154" s="21"/>
       <c r="F154" s="24"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="23"/>
-      <c r="B155" s="26"/>
-      <c r="C155" s="26"/>
+      <c r="B155" s="27"/>
+      <c r="C155" s="27"/>
       <c r="D155" s="21"/>
       <c r="E155" s="21"/>
       <c r="F155" s="24"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="23"/>
-      <c r="B156" s="26"/>
-      <c r="C156" s="26"/>
+      <c r="B156" s="27"/>
+      <c r="C156" s="27"/>
       <c r="D156" s="21"/>
       <c r="E156" s="21"/>
       <c r="F156" s="24"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="23"/>
-      <c r="B157" s="26"/>
-      <c r="C157" s="26"/>
+      <c r="B157" s="27"/>
+      <c r="C157" s="27"/>
       <c r="D157" s="21"/>
       <c r="E157" s="21"/>
       <c r="F157" s="24"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="23"/>
-      <c r="B158" s="26"/>
-      <c r="C158" s="26"/>
+      <c r="B158" s="27"/>
+      <c r="C158" s="27"/>
       <c r="D158" s="21"/>
       <c r="E158" s="21"/>
       <c r="F158" s="24"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="23"/>
-      <c r="B159" s="26"/>
-      <c r="C159" s="26"/>
+      <c r="B159" s="27"/>
+      <c r="C159" s="27"/>
       <c r="D159" s="21"/>
       <c r="E159" s="21"/>
       <c r="F159" s="24"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="23"/>
-      <c r="B160" s="26"/>
-      <c r="C160" s="26"/>
+      <c r="B160" s="27"/>
+      <c r="C160" s="27"/>
       <c r="D160" s="21"/>
       <c r="E160" s="21"/>
       <c r="F160" s="24"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="23"/>
-      <c r="B161" s="26"/>
-      <c r="C161" s="26"/>
+      <c r="B161" s="27"/>
+      <c r="C161" s="27"/>
       <c r="D161" s="21"/>
       <c r="E161" s="21"/>
       <c r="F161" s="24"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="23"/>
-      <c r="B162" s="26"/>
-      <c r="C162" s="26"/>
+      <c r="B162" s="27"/>
+      <c r="C162" s="27"/>
       <c r="D162" s="21"/>
       <c r="E162" s="21"/>
       <c r="F162" s="24"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="23"/>
-      <c r="B163" s="26"/>
-      <c r="C163" s="26"/>
+      <c r="B163" s="27"/>
+      <c r="C163" s="27"/>
       <c r="D163" s="21"/>
       <c r="E163" s="21"/>
       <c r="F163" s="24"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="23"/>
-      <c r="B164" s="26"/>
-      <c r="C164" s="26"/>
+      <c r="B164" s="27"/>
+      <c r="C164" s="27"/>
       <c r="D164" s="21"/>
       <c r="E164" s="21"/>
       <c r="F164" s="24"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="23"/>
-      <c r="B165" s="26"/>
-      <c r="C165" s="26"/>
+      <c r="B165" s="27"/>
+      <c r="C165" s="27"/>
       <c r="D165" s="21"/>
       <c r="E165" s="21"/>
       <c r="F165" s="24"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="23"/>
-      <c r="B166" s="26"/>
-      <c r="C166" s="26"/>
+      <c r="B166" s="27"/>
+      <c r="C166" s="27"/>
       <c r="D166" s="21"/>
       <c r="E166" s="21"/>
       <c r="F166" s="24"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="23"/>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
+      <c r="B167" s="27"/>
+      <c r="C167" s="27"/>
       <c r="D167" s="21"/>
       <c r="E167" s="21"/>
       <c r="F167" s="24"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="23"/>
-      <c r="B168" s="26"/>
-      <c r="C168" s="26"/>
+      <c r="B168" s="27"/>
+      <c r="C168" s="27"/>
       <c r="D168" s="21"/>
       <c r="E168" s="21"/>
       <c r="F168" s="24"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="23"/>
-      <c r="B169" s="26"/>
-      <c r="C169" s="26"/>
+      <c r="B169" s="27"/>
+      <c r="C169" s="27"/>
       <c r="D169" s="21"/>
       <c r="E169" s="21"/>
       <c r="F169" s="24"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="23"/>
-      <c r="B170" s="26"/>
-      <c r="C170" s="26"/>
+      <c r="B170" s="27"/>
+      <c r="C170" s="27"/>
       <c r="D170" s="21"/>
       <c r="E170" s="21"/>
       <c r="F170" s="24"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="23"/>
-      <c r="B171" s="26"/>
-      <c r="C171" s="26"/>
+      <c r="B171" s="27"/>
+      <c r="C171" s="27"/>
       <c r="D171" s="21"/>
       <c r="E171" s="21"/>
       <c r="F171" s="24"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="23"/>
-      <c r="B172" s="26"/>
-      <c r="C172" s="26"/>
+      <c r="B172" s="27"/>
+      <c r="C172" s="27"/>
       <c r="D172" s="21"/>
       <c r="E172" s="21"/>
       <c r="F172" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6532,6 +6491,1066 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11739A8-E721-41A4-B437-5313D01B9D93}">
+  <dimension ref="A1:F69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="4">
+        <v>9.14</v>
+      </c>
+      <c r="C2" s="3">
+        <v>6.4492216456634504</v>
+      </c>
+      <c r="D2" s="7">
+        <f>B2*C2/100</f>
+        <v>0.58945885841363943</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4">
+        <v>8.17</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.8511466897446902</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
+        <v>0.31463868455214117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6239999999999997E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6.99</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.1052631578947301</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.14715789473684163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.99</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15753700000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.88</v>
+      </c>
+      <c r="C7" s="3">
+        <v>-0.87</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>-4.2455999999999994E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="26">
+        <v>4.46</v>
+      </c>
+      <c r="C8" s="29">
+        <v>0.12626262626262599</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="0"/>
+        <v>5.631313131313119E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4.17</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.1455938697318002</v>
+      </c>
+      <c r="D9" s="7">
+        <f t="shared" si="0"/>
+        <v>8.9471264367816078E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3.23</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-2.3696682464454901</v>
+      </c>
+      <c r="D10" s="7">
+        <f t="shared" si="0"/>
+        <v>-7.6540284360189337E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2.84</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.86536901865369</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2976480129764789E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2.54</v>
+      </c>
+      <c r="C12" s="30">
+        <v>2.89</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="0"/>
+        <v>7.3405999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="26">
+        <v>2.37</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-4.37</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.10356900000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="26">
+        <v>2.37</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-2.9</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="0"/>
+        <v>-6.8729999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="26">
+        <v>2.21</v>
+      </c>
+      <c r="C15" s="29">
+        <v>0.330188679245283</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2971698113207537E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1.93</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.6338028169014001</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10873239436619703</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1.77</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.6731470230862699</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="0"/>
+        <v>4.7314702308626978E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1.53</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-0.91</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.3923000000000001E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3.6575228595178699</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="0"/>
+        <v>5.5228595178719836E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="0"/>
+        <v>5.1839999999999994E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="4">
+        <v>1.44</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-1.82</v>
+      </c>
+      <c r="D21" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.6207999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.8198433420365498</v>
+      </c>
+      <c r="D22" s="7">
+        <f t="shared" si="0"/>
+        <v>4.0323759791122661E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="26">
+        <v>1.42</v>
+      </c>
+      <c r="C23" s="29">
+        <v>-0.68571428571428505</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="0"/>
+        <v>-9.737142857142847E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="C24" s="29">
+        <v>2.9220779220779201</v>
+      </c>
+      <c r="D24" s="7">
+        <f t="shared" si="0"/>
+        <v>4.0909090909090881E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="26">
+        <v>1.33</v>
+      </c>
+      <c r="C25" s="29">
+        <v>1.8929503916449</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" si="0"/>
+        <v>2.5176240208877168E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="26">
+        <v>1.25</v>
+      </c>
+      <c r="C26" s="29">
+        <v>4.76</v>
+      </c>
+      <c r="D26" s="7">
+        <f t="shared" si="0"/>
+        <v>5.949999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="26">
+        <v>1.17</v>
+      </c>
+      <c r="C27" s="29">
+        <v>-1.5270935960591101</v>
+      </c>
+      <c r="D27" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.7866995073891587E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="26">
+        <v>1.04</v>
+      </c>
+      <c r="C28" s="29">
+        <v>-1.66</v>
+      </c>
+      <c r="D28" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.7263999999999998E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="26">
+        <v>0.9</v>
+      </c>
+      <c r="C29" s="29">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D29" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="26">
+        <v>0.84</v>
+      </c>
+      <c r="C30" s="29">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" si="0"/>
+        <v>3.8724000000000001E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="26">
+        <v>0.82</v>
+      </c>
+      <c r="C31" s="29">
+        <v>1.49</v>
+      </c>
+      <c r="D31" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2218E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="C32" s="29">
+        <v>0.243704305442729</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" si="0"/>
+        <v>1.9496344435418322E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="26">
+        <v>0.79</v>
+      </c>
+      <c r="C33" s="29">
+        <v>0.76</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" si="0"/>
+        <v>6.0040000000000007E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="26">
+        <v>0.76</v>
+      </c>
+      <c r="C34" s="29">
+        <v>-0.93</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" si="0"/>
+        <v>-7.0680000000000014E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="26">
+        <v>0.73</v>
+      </c>
+      <c r="C35" s="29">
+        <v>0.40128410914927698</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9293739967897218E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="26">
+        <v>0.72</v>
+      </c>
+      <c r="C36" s="29">
+        <v>0.78</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="0"/>
+        <v>5.6159999999999995E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="26">
+        <v>0.71</v>
+      </c>
+      <c r="C37" s="29">
+        <v>0.61</v>
+      </c>
+      <c r="D37" s="7">
+        <f t="shared" si="0"/>
+        <v>4.3309999999999998E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="C38" s="29">
+        <v>0.84</v>
+      </c>
+      <c r="D38" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8799999999999998E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="C39" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="7">
+        <f t="shared" si="0"/>
+        <v>6.9999999999999988E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="26">
+        <v>0.64</v>
+      </c>
+      <c r="C40" s="29">
+        <v>0.97</v>
+      </c>
+      <c r="D40" s="7">
+        <f t="shared" si="0"/>
+        <v>6.208E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="26">
+        <v>0.63</v>
+      </c>
+      <c r="C41" s="29">
+        <v>0.11</v>
+      </c>
+      <c r="D41" s="7">
+        <f t="shared" si="0"/>
+        <v>6.9300000000000004E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="26">
+        <v>0.61</v>
+      </c>
+      <c r="C42" s="29">
+        <v>4.43</v>
+      </c>
+      <c r="D42" s="7">
+        <f t="shared" si="0"/>
+        <v>2.7022999999999998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="26">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C43" s="29">
+        <v>1.82</v>
+      </c>
+      <c r="D43" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0374E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="26">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C44" s="29">
+        <v>-0.05</v>
+      </c>
+      <c r="D44" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.7500000000000002E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="C45" s="29">
+        <v>-1.91</v>
+      </c>
+      <c r="D45" s="7">
+        <f t="shared" si="0"/>
+        <v>-9.5499999999999995E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="29">
+        <v>1.41</v>
+      </c>
+      <c r="D46" s="7">
+        <f t="shared" si="0"/>
+        <v>7.0499999999999998E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="26">
+        <v>0.45</v>
+      </c>
+      <c r="C47" s="29">
+        <v>0.32</v>
+      </c>
+      <c r="D47" s="7">
+        <f t="shared" si="0"/>
+        <v>1.4400000000000001E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="C48" s="29">
+        <v>5.47</v>
+      </c>
+      <c r="D48" s="7">
+        <f t="shared" si="0"/>
+        <v>2.188E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="26">
+        <v>0.33</v>
+      </c>
+      <c r="C49" s="29">
+        <v>2.52</v>
+      </c>
+      <c r="D49" s="7">
+        <f t="shared" si="0"/>
+        <v>8.3160000000000005E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="26">
+        <v>0.16</v>
+      </c>
+      <c r="C50" s="29">
+        <v>-0.17</v>
+      </c>
+      <c r="D50" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.72E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" s="5">
+        <f>SUM(B2:B50)</f>
+        <v>99.950000000000031</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="6">
+        <f>SUM(D2:D50)</f>
+        <v>1.6092800340545794</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62" s="28"/>
+      <c r="D62" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="23">
+        <v>46226</v>
+      </c>
+      <c r="B63" s="27">
+        <v>18186</v>
+      </c>
+      <c r="C63" s="27"/>
+      <c r="D63" s="21">
+        <v>1825486354</v>
+      </c>
+      <c r="E63" s="21">
+        <v>49785912</v>
+      </c>
+      <c r="F63" s="24">
+        <v>4.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="23">
+        <v>46227</v>
+      </c>
+      <c r="B64" s="27">
+        <v>18753</v>
+      </c>
+      <c r="C64" s="27"/>
+      <c r="D64" s="21">
+        <v>1898338108</v>
+      </c>
+      <c r="E64" s="21">
+        <v>79391973</v>
+      </c>
+      <c r="F64" s="24">
+        <v>-3.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="23">
+        <v>46230</v>
+      </c>
+      <c r="B65" s="27">
+        <v>19293</v>
+      </c>
+      <c r="C65" s="27"/>
+      <c r="D65" s="21">
+        <v>2016158831</v>
+      </c>
+      <c r="E65" s="21">
+        <v>115257058</v>
+      </c>
+      <c r="F65" s="24">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="23">
+        <v>46231</v>
+      </c>
+      <c r="B66" s="27">
+        <v>19624</v>
+      </c>
+      <c r="C66" s="27"/>
+      <c r="D66" s="21">
+        <v>2053257616</v>
+      </c>
+      <c r="E66" s="21">
+        <v>37759305</v>
+      </c>
+      <c r="F66" s="24">
+        <v>-2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="23">
+        <v>46232</v>
+      </c>
+      <c r="B67" s="27">
+        <v>20120</v>
+      </c>
+      <c r="C67" s="27"/>
+      <c r="D67" s="21">
+        <v>2073450735</v>
+      </c>
+      <c r="E67" s="21">
+        <v>45076881</v>
+      </c>
+      <c r="F67" s="24">
+        <v>-1.21E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="23">
+        <v>46233</v>
+      </c>
+      <c r="B68" s="27">
+        <v>20320</v>
+      </c>
+      <c r="C68" s="27"/>
+      <c r="D68" s="21">
+        <v>2050352793</v>
+      </c>
+      <c r="E68" s="21">
+        <v>-24388706</v>
+      </c>
+      <c r="F68" s="24">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="23">
+        <v>46234</v>
+      </c>
+      <c r="B69" s="27">
+        <v>20380</v>
+      </c>
+      <c r="C69" s="27"/>
+      <c r="D69" s="21">
+        <v>1988789335</v>
+      </c>
+      <c r="E69" s="21">
+        <v>-68771429</v>
+      </c>
+      <c r="F69" s="24">
+        <v>3.5000000000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7D179F-8E85-41A7-833A-189764F2C116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F3FB09-3681-4E83-9A2B-5C9713E2CC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24060" yWindow="195" windowWidth="23550" windowHeight="20325" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="285" windowWidth="16335" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -480,17 +480,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1105,15 +1105,15 @@
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
       <c r="C30" s="9"/>
       <c r="D30" s="19"/>
     </row>
@@ -1121,10 +1121,10 @@
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="28"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="20" t="s">
         <v>53</v>
       </c>
@@ -1139,10 +1139,10 @@
       <c r="A32" s="18">
         <v>46226</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="29">
         <v>98970</v>
       </c>
-      <c r="C32" s="27"/>
+      <c r="C32" s="29"/>
       <c r="D32" s="25">
         <v>232874657613</v>
       </c>
@@ -1157,10 +1157,10 @@
       <c r="A33" s="18">
         <v>46227</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="29">
         <v>99051</v>
       </c>
-      <c r="C33" s="27"/>
+      <c r="C33" s="29"/>
       <c r="D33" s="25">
         <v>227320292084</v>
       </c>
@@ -1175,10 +1175,10 @@
       <c r="A34" s="18">
         <v>46230</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="29">
         <v>98455</v>
       </c>
-      <c r="C34" s="27"/>
+      <c r="C34" s="29"/>
       <c r="D34" s="25">
         <v>229116006481</v>
       </c>
@@ -1193,10 +1193,10 @@
       <c r="A35" s="18">
         <v>46231</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="29">
         <v>98583</v>
       </c>
-      <c r="C35" s="27"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="25">
         <v>232227975662</v>
       </c>
@@ -1211,10 +1211,10 @@
       <c r="A36" s="18">
         <v>46232</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="29">
         <v>98915</v>
       </c>
-      <c r="C36" s="27"/>
+      <c r="C36" s="29"/>
       <c r="D36" s="25">
         <v>226192717226</v>
       </c>
@@ -1229,10 +1229,10 @@
       <c r="A37" s="18">
         <v>46233</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="29">
         <v>97411</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="29"/>
       <c r="D37" s="25">
         <v>223802010766</v>
       </c>
@@ -1247,10 +1247,10 @@
       <c r="A38" s="18">
         <v>46234</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="29">
         <v>97269</v>
       </c>
-      <c r="C38" s="27"/>
+      <c r="C38" s="29"/>
       <c r="D38" s="25">
         <v>223121593370</v>
       </c>
@@ -1262,7 +1262,22 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F39" s="24"/>
+      <c r="A39" s="18">
+        <v>46237</v>
+      </c>
+      <c r="B39" s="29">
+        <v>96829</v>
+      </c>
+      <c r="C39" s="29"/>
+      <c r="D39" s="25">
+        <v>222116113609</v>
+      </c>
+      <c r="E39" s="22">
+        <v>-2851667712</v>
+      </c>
+      <c r="F39" s="24">
+        <v>8.3000000000000001E-3</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F40" s="24"/>
@@ -1280,7 +1295,8 @@
       <c r="F44" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
@@ -1975,15 +1991,15 @@
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
@@ -1991,10 +2007,10 @@
       <c r="A55" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="28"/>
+      <c r="C55" s="30"/>
       <c r="D55" s="20" t="s">
         <v>53</v>
       </c>
@@ -2009,10 +2025,10 @@
       <c r="A56" s="18">
         <v>46226</v>
       </c>
-      <c r="B56" s="27">
+      <c r="B56" s="29">
         <v>160454</v>
       </c>
-      <c r="C56" s="27"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="21">
         <v>74464707242</v>
       </c>
@@ -2027,10 +2043,10 @@
       <c r="A57" s="18">
         <v>46227</v>
       </c>
-      <c r="B57" s="27">
+      <c r="B57" s="29">
         <v>159246</v>
       </c>
-      <c r="C57" s="27"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="21">
         <v>74038207243</v>
       </c>
@@ -2045,10 +2061,10 @@
       <c r="A58" s="18">
         <v>46230</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="29">
         <v>159672</v>
       </c>
-      <c r="C58" s="27"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="21">
         <v>74765554505</v>
       </c>
@@ -2063,10 +2079,10 @@
       <c r="A59" s="18">
         <v>46231</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="29">
         <v>160788</v>
       </c>
-      <c r="C59" s="27"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="21">
         <v>74770957010</v>
       </c>
@@ -2081,10 +2097,10 @@
       <c r="A60" s="18">
         <v>46232</v>
       </c>
-      <c r="B60" s="27">
+      <c r="B60" s="29">
         <v>162385</v>
       </c>
-      <c r="C60" s="27"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="21">
         <v>72261693709</v>
       </c>
@@ -2099,10 +2115,10 @@
       <c r="A61" s="18">
         <v>46233</v>
       </c>
-      <c r="B61" s="27">
+      <c r="B61" s="29">
         <v>160805</v>
       </c>
-      <c r="C61" s="27"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="21">
         <v>69072635445</v>
       </c>
@@ -2117,10 +2133,10 @@
       <c r="A62" s="18">
         <v>46234</v>
       </c>
-      <c r="B62" s="27">
+      <c r="B62" s="29">
         <v>159675</v>
       </c>
-      <c r="C62" s="27"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="21">
         <v>63472489182</v>
       </c>
@@ -2132,159 +2148,189 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="24"/>
+      <c r="A63" s="18">
+        <v>46237</v>
+      </c>
+      <c r="B63" s="29">
+        <v>154990</v>
+      </c>
+      <c r="C63" s="29"/>
+      <c r="D63" s="21">
+        <v>57303637201</v>
+      </c>
+      <c r="E63" s="21">
+        <v>-6263046591</v>
+      </c>
+      <c r="F63" s="24">
+        <v>1.5E-3</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="19"/>
       <c r="E64" s="22"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="19"/>
       <c r="E65" s="22"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="19"/>
       <c r="E66" s="22"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="19"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
       <c r="D68" s="19"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="19"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="19"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="19"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
       <c r="D72" s="19"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="19"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="19"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="19"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
       <c r="D76" s="19"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="19"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="19"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="19"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="19"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="19"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2294,26 +2340,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2892,15 +2918,15 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="17"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
     </row>
@@ -2908,10 +2934,10 @@
       <c r="A53" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C53" s="28"/>
+      <c r="C53" s="30"/>
       <c r="D53" s="20" t="s">
         <v>53</v>
       </c>
@@ -2926,10 +2952,10 @@
       <c r="A54" s="18">
         <v>46226</v>
       </c>
-      <c r="B54" s="27">
+      <c r="B54" s="29">
         <v>78223</v>
       </c>
-      <c r="C54" s="27"/>
+      <c r="C54" s="29"/>
       <c r="D54" s="21">
         <v>38343912280</v>
       </c>
@@ -2944,10 +2970,10 @@
       <c r="A55" s="18">
         <v>46227</v>
       </c>
-      <c r="B55" s="27">
+      <c r="B55" s="29">
         <v>78055</v>
       </c>
-      <c r="C55" s="27"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="21">
         <v>38547597437</v>
       </c>
@@ -2962,10 +2988,10 @@
       <c r="A56" s="18">
         <v>46230</v>
       </c>
-      <c r="B56" s="27">
+      <c r="B56" s="29">
         <v>78840</v>
       </c>
-      <c r="C56" s="27"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="21">
         <v>39148877217</v>
       </c>
@@ -2980,10 +3006,10 @@
       <c r="A57" s="18">
         <v>46231</v>
       </c>
-      <c r="B57" s="27">
+      <c r="B57" s="29">
         <v>79795</v>
       </c>
-      <c r="C57" s="27"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="21">
         <v>39293398935</v>
       </c>
@@ -2998,10 +3024,10 @@
       <c r="A58" s="23">
         <v>46232</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="29">
         <v>80830</v>
       </c>
-      <c r="C58" s="27"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="21">
         <v>38188651284</v>
       </c>
@@ -3016,10 +3042,10 @@
       <c r="A59" s="18">
         <v>46233</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="29">
         <v>80272</v>
       </c>
-      <c r="C59" s="27"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="21">
         <v>36982629736</v>
       </c>
@@ -3034,10 +3060,10 @@
       <c r="A60" s="18">
         <v>46234</v>
       </c>
-      <c r="B60" s="27">
+      <c r="B60" s="29">
         <v>79803</v>
       </c>
-      <c r="C60" s="27"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="21">
         <v>33560330080</v>
       </c>
@@ -3049,759 +3075,860 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="24"/>
+      <c r="A61" s="18">
+        <v>46237</v>
+      </c>
+      <c r="B61" s="29">
+        <v>77044</v>
+      </c>
+      <c r="C61" s="29"/>
+      <c r="D61" s="21">
+        <v>29529617301</v>
+      </c>
+      <c r="E61" s="21">
+        <v>-4237217388</v>
+      </c>
+      <c r="F61" s="24">
+        <v>6.1999999999999998E-3</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="21"/>
       <c r="E62" s="22"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="21"/>
       <c r="E63" s="22"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="21"/>
       <c r="E64" s="22"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="21"/>
       <c r="E65" s="22"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="21"/>
       <c r="E66" s="22"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="21"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
       <c r="D68" s="21"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="21"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="21"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="21"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
       <c r="D72" s="21"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="21"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="21"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
       <c r="D76" s="21"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="21"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="21"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="21"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="21"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="21"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="21"/>
       <c r="E82" s="22"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="21"/>
       <c r="E83" s="22"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
       <c r="D84" s="21"/>
       <c r="E84" s="22"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
       <c r="D85" s="21"/>
       <c r="E85" s="22"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="21"/>
       <c r="E86" s="22"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="18"/>
-      <c r="B87" s="27"/>
-      <c r="C87" s="27"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="21"/>
       <c r="E87" s="22"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
       <c r="D88" s="21"/>
       <c r="E88" s="22"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="18"/>
-      <c r="B89" s="27"/>
-      <c r="C89" s="27"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="21"/>
       <c r="E89" s="22"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="18"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
       <c r="D90" s="21"/>
       <c r="E90" s="22"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="18"/>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
       <c r="D91" s="21"/>
       <c r="E91" s="22"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
-      <c r="B92" s="27"/>
-      <c r="C92" s="27"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
       <c r="D92" s="21"/>
       <c r="E92" s="22"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="21"/>
       <c r="E93" s="22"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
-      <c r="B94" s="27"/>
-      <c r="C94" s="27"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
       <c r="D94" s="21"/>
       <c r="E94" s="22"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
-      <c r="B95" s="27"/>
-      <c r="C95" s="27"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="21"/>
       <c r="E95" s="22"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
-      <c r="B96" s="27"/>
-      <c r="C96" s="27"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="21"/>
       <c r="E96" s="22"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
-      <c r="B97" s="27"/>
-      <c r="C97" s="27"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="21"/>
       <c r="E97" s="22"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
-      <c r="B98" s="27"/>
-      <c r="C98" s="27"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
       <c r="D98" s="21"/>
       <c r="E98" s="22"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
-      <c r="B99" s="27"/>
-      <c r="C99" s="27"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="21"/>
       <c r="E99" s="22"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
-      <c r="B100" s="27"/>
-      <c r="C100" s="27"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
       <c r="D100" s="21"/>
       <c r="E100" s="22"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
-      <c r="B101" s="27"/>
-      <c r="C101" s="27"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
       <c r="D101" s="21"/>
       <c r="E101" s="22"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="27"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
       <c r="D102" s="21"/>
       <c r="E102" s="22"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
-      <c r="B103" s="27"/>
-      <c r="C103" s="27"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="21"/>
       <c r="E103" s="22"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="27"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
       <c r="D104" s="21"/>
       <c r="E104" s="22"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
-      <c r="B105" s="27"/>
-      <c r="C105" s="27"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="21"/>
       <c r="E105" s="22"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="18"/>
-      <c r="B106" s="27"/>
-      <c r="C106" s="27"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
       <c r="D106" s="21"/>
       <c r="E106" s="22"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="18"/>
-      <c r="B107" s="27"/>
-      <c r="C107" s="27"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="21"/>
       <c r="E107" s="22"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="18"/>
-      <c r="B108" s="27"/>
-      <c r="C108" s="27"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="29"/>
       <c r="D108" s="21"/>
       <c r="E108" s="22"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="18"/>
-      <c r="B109" s="27"/>
-      <c r="C109" s="27"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="29"/>
       <c r="D109" s="21"/>
       <c r="E109" s="22"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
-      <c r="B110" s="27"/>
-      <c r="C110" s="27"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
       <c r="D110" s="21"/>
       <c r="E110" s="22"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="18"/>
-      <c r="B111" s="27"/>
-      <c r="C111" s="27"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
       <c r="D111" s="21"/>
       <c r="E111" s="22"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="18"/>
-      <c r="B112" s="27"/>
-      <c r="C112" s="27"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="18"/>
-      <c r="B113" s="27"/>
-      <c r="C113" s="27"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="29"/>
       <c r="D113" s="21"/>
       <c r="E113" s="22"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="18"/>
-      <c r="B114" s="27"/>
-      <c r="C114" s="27"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="29"/>
       <c r="D114" s="21"/>
       <c r="E114" s="22"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="18"/>
-      <c r="B115" s="27"/>
-      <c r="C115" s="27"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
       <c r="D115" s="21"/>
       <c r="E115" s="22"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="18"/>
-      <c r="B116" s="27"/>
-      <c r="C116" s="27"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="29"/>
       <c r="D116" s="21"/>
       <c r="E116" s="22"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="18"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="27"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="21"/>
       <c r="E117" s="22"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="18"/>
-      <c r="B118" s="27"/>
-      <c r="C118" s="27"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
       <c r="D118" s="21"/>
       <c r="E118" s="22"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="18"/>
-      <c r="B119" s="27"/>
-      <c r="C119" s="27"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="21"/>
       <c r="E119" s="22"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="18"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="27"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="29"/>
       <c r="D120" s="21"/>
       <c r="E120" s="22"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="18"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="27"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="29"/>
       <c r="D121" s="21"/>
       <c r="E121" s="22"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
-      <c r="B122" s="27"/>
-      <c r="C122" s="27"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="29"/>
       <c r="D122" s="21"/>
       <c r="E122" s="22"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="18"/>
-      <c r="B123" s="27"/>
-      <c r="C123" s="27"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
       <c r="D123" s="21"/>
       <c r="E123" s="22"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="18"/>
-      <c r="B124" s="27"/>
-      <c r="C124" s="27"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
       <c r="D124" s="21"/>
       <c r="E124" s="22"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="18"/>
-      <c r="B125" s="27"/>
-      <c r="C125" s="27"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="29"/>
       <c r="D125" s="21"/>
       <c r="E125" s="22"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="18"/>
-      <c r="B126" s="27"/>
-      <c r="C126" s="27"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
       <c r="D126" s="21"/>
       <c r="E126" s="22"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="18"/>
-      <c r="B127" s="27"/>
-      <c r="C127" s="27"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="21"/>
       <c r="E127" s="22"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="18"/>
-      <c r="B128" s="27"/>
-      <c r="C128" s="27"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="29"/>
       <c r="D128" s="21"/>
       <c r="E128" s="22"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="18"/>
-      <c r="B129" s="27"/>
-      <c r="C129" s="27"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="29"/>
       <c r="D129" s="21"/>
       <c r="E129" s="22"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="18"/>
-      <c r="B130" s="27"/>
-      <c r="C130" s="27"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
       <c r="D130" s="21"/>
       <c r="E130" s="22"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="18"/>
-      <c r="B131" s="27"/>
-      <c r="C131" s="27"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="29"/>
       <c r="D131" s="21"/>
       <c r="E131" s="22"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="18"/>
-      <c r="B132" s="27"/>
-      <c r="C132" s="27"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
       <c r="D132" s="21"/>
       <c r="E132" s="22"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="18"/>
-      <c r="B133" s="27"/>
-      <c r="C133" s="27"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="29"/>
       <c r="D133" s="21"/>
       <c r="E133" s="22"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
-      <c r="B134" s="27"/>
-      <c r="C134" s="27"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="29"/>
       <c r="D134" s="21"/>
       <c r="E134" s="22"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="18"/>
-      <c r="B135" s="27"/>
-      <c r="C135" s="27"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="21"/>
       <c r="E135" s="22"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="18"/>
-      <c r="B136" s="27"/>
-      <c r="C136" s="27"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
       <c r="D136" s="21"/>
       <c r="E136" s="22"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="18"/>
-      <c r="B137" s="27"/>
-      <c r="C137" s="27"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="29"/>
       <c r="D137" s="21"/>
       <c r="E137" s="22"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="18"/>
-      <c r="B138" s="27"/>
-      <c r="C138" s="27"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="29"/>
       <c r="D138" s="21"/>
       <c r="E138" s="22"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="18"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="27"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="29"/>
       <c r="D139" s="21"/>
       <c r="E139" s="22"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="18"/>
-      <c r="B140" s="27"/>
-      <c r="C140" s="27"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="29"/>
       <c r="D140" s="21"/>
       <c r="E140" s="22"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="18"/>
-      <c r="B141" s="27"/>
-      <c r="C141" s="27"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="29"/>
       <c r="D141" s="21"/>
       <c r="E141" s="22"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="18"/>
-      <c r="B142" s="27"/>
-      <c r="C142" s="27"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
       <c r="D142" s="21"/>
       <c r="E142" s="22"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="18"/>
-      <c r="B143" s="27"/>
-      <c r="C143" s="27"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="29"/>
       <c r="D143" s="21"/>
       <c r="E143" s="22"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="18"/>
-      <c r="B144" s="27"/>
-      <c r="C144" s="27"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="29"/>
       <c r="D144" s="21"/>
       <c r="E144" s="22"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="18"/>
-      <c r="B145" s="27"/>
-      <c r="C145" s="27"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="29"/>
       <c r="D145" s="21"/>
       <c r="E145" s="22"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="18"/>
-      <c r="B146" s="27"/>
-      <c r="C146" s="27"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="29"/>
       <c r="D146" s="21"/>
       <c r="E146" s="22"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="18"/>
-      <c r="B147" s="27"/>
-      <c r="C147" s="27"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="29"/>
       <c r="D147" s="21"/>
       <c r="E147" s="22"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="18"/>
-      <c r="B148" s="27"/>
-      <c r="C148" s="27"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
       <c r="D148" s="21"/>
       <c r="E148" s="22"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="18"/>
-      <c r="B149" s="27"/>
-      <c r="C149" s="27"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
       <c r="D149" s="21"/>
       <c r="E149" s="22"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="18"/>
-      <c r="B150" s="27"/>
-      <c r="C150" s="27"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="29"/>
       <c r="D150" s="21"/>
       <c r="E150" s="22"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="18"/>
-      <c r="B151" s="27"/>
-      <c r="C151" s="27"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="29"/>
       <c r="D151" s="21"/>
       <c r="E151" s="22"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
-      <c r="B152" s="27"/>
-      <c r="C152" s="27"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="29"/>
       <c r="D152" s="21"/>
       <c r="E152" s="22"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="18"/>
-      <c r="B153" s="27"/>
-      <c r="C153" s="27"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="29"/>
       <c r="D153" s="21"/>
       <c r="E153" s="22"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="18"/>
-      <c r="B154" s="27"/>
-      <c r="C154" s="27"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
       <c r="D154" s="21"/>
       <c r="E154" s="22"/>
       <c r="F154" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3815,97 +3942,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4030,15 +4066,15 @@
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
@@ -4046,10 +4082,10 @@
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="28"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="20" t="s">
         <v>53</v>
       </c>
@@ -4064,10 +4100,10 @@
       <c r="A32" s="23">
         <v>46226</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="29">
         <v>48221</v>
       </c>
-      <c r="C32" s="27"/>
+      <c r="C32" s="29"/>
       <c r="D32" s="21">
         <v>28591206600</v>
       </c>
@@ -4082,10 +4118,10 @@
       <c r="A33" s="23">
         <v>46227</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="29">
         <v>48802</v>
       </c>
-      <c r="C33" s="27"/>
+      <c r="C33" s="29"/>
       <c r="D33" s="21">
         <v>29255953804</v>
       </c>
@@ -4100,10 +4136,10 @@
       <c r="A34" s="23">
         <v>46230</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="29">
         <v>49403</v>
       </c>
-      <c r="C34" s="27"/>
+      <c r="C34" s="29"/>
       <c r="D34" s="21">
         <v>30359209400</v>
       </c>
@@ -4118,10 +4154,10 @@
       <c r="A35" s="23">
         <v>46231</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="29">
         <v>49817</v>
       </c>
-      <c r="C35" s="27"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="21">
         <v>30985486603</v>
       </c>
@@ -4136,10 +4172,10 @@
       <c r="A36" s="23">
         <v>46232</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="29">
         <v>50631</v>
       </c>
-      <c r="C36" s="27"/>
+      <c r="C36" s="29"/>
       <c r="D36" s="21">
         <v>32047144824</v>
       </c>
@@ -4154,10 +4190,10 @@
       <c r="A37" s="23">
         <v>46233</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="29">
         <v>50968</v>
       </c>
-      <c r="C37" s="27"/>
+      <c r="C37" s="29"/>
       <c r="D37" s="21">
         <v>32438714789</v>
       </c>
@@ -4172,10 +4208,10 @@
       <c r="A38" s="23">
         <v>46234</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="29">
         <v>51171</v>
       </c>
-      <c r="C38" s="27"/>
+      <c r="C38" s="29"/>
       <c r="D38" s="21">
         <v>31996446996</v>
       </c>
@@ -4187,831 +4223,942 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="24"/>
+      <c r="A39" s="23">
+        <v>46237</v>
+      </c>
+      <c r="B39" s="29">
+        <v>51266</v>
+      </c>
+      <c r="C39" s="29"/>
+      <c r="D39" s="21">
+        <v>32456533228</v>
+      </c>
+      <c r="E39" s="21">
+        <v>257679653</v>
+      </c>
+      <c r="F39" s="24">
+        <v>6.3E-3</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="27"/>
-      <c r="C87" s="27"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="27"/>
-      <c r="C89" s="27"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="27"/>
-      <c r="C92" s="27"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="27"/>
-      <c r="C94" s="27"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="27"/>
-      <c r="C95" s="27"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="27"/>
-      <c r="C96" s="27"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="27"/>
-      <c r="C97" s="27"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="27"/>
-      <c r="C98" s="27"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="27"/>
-      <c r="C99" s="27"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="27"/>
-      <c r="C100" s="27"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="27"/>
-      <c r="C101" s="27"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="27"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="27"/>
-      <c r="C103" s="27"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="27"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="27"/>
-      <c r="C105" s="27"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="27"/>
-      <c r="C106" s="27"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="27"/>
-      <c r="C107" s="27"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="27"/>
-      <c r="C108" s="27"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="29"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="27"/>
-      <c r="C109" s="27"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="29"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="27"/>
-      <c r="C110" s="27"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="27"/>
-      <c r="C111" s="27"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="27"/>
-      <c r="C112" s="27"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="27"/>
-      <c r="C113" s="27"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="29"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="27"/>
-      <c r="C114" s="27"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="29"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="27"/>
-      <c r="C115" s="27"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="27"/>
-      <c r="C116" s="27"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="29"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="27"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="27"/>
-      <c r="C118" s="27"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="27"/>
-      <c r="C119" s="27"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="27"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="29"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="27"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="29"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="27"/>
-      <c r="C122" s="27"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="29"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="27"/>
-      <c r="C123" s="27"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="27"/>
-      <c r="C124" s="27"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="27"/>
-      <c r="C125" s="27"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="29"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="27"/>
-      <c r="C126" s="27"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="27"/>
-      <c r="C127" s="27"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="27"/>
-      <c r="C128" s="27"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="29"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="27"/>
-      <c r="C129" s="27"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="29"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="27"/>
-      <c r="C130" s="27"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="27"/>
-      <c r="C131" s="27"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="29"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="27"/>
-      <c r="C132" s="27"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="27"/>
-      <c r="C133" s="27"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="29"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="27"/>
-      <c r="C134" s="27"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="29"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="27"/>
-      <c r="C135" s="27"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="27"/>
-      <c r="C136" s="27"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="27"/>
-      <c r="C137" s="27"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="29"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="27"/>
-      <c r="C138" s="27"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="29"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="27"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="29"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="27"/>
-      <c r="C140" s="27"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="29"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="27"/>
-      <c r="C141" s="27"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="29"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5024,107 +5171,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5283,16 +5329,16 @@
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="17"/>
@@ -5313,10 +5359,10 @@
       <c r="A37" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="28"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="20" t="s">
         <v>53</v>
       </c>
@@ -5331,10 +5377,10 @@
       <c r="A38" s="23">
         <v>46226</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="29">
         <v>6356</v>
       </c>
-      <c r="C38" s="27"/>
+      <c r="C38" s="29"/>
       <c r="D38" s="21">
         <v>1033181017</v>
       </c>
@@ -5349,10 +5395,10 @@
       <c r="A39" s="23">
         <v>46227</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="29">
         <v>6609</v>
       </c>
-      <c r="C39" s="27"/>
+      <c r="C39" s="29"/>
       <c r="D39" s="21">
         <v>1076556627</v>
       </c>
@@ -5367,10 +5413,10 @@
       <c r="A40" s="23">
         <v>46230</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="29">
         <v>6906</v>
       </c>
-      <c r="C40" s="27"/>
+      <c r="C40" s="29"/>
       <c r="D40" s="21">
         <v>1167160796</v>
       </c>
@@ -5385,10 +5431,10 @@
       <c r="A41" s="23">
         <v>46231</v>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="29">
         <v>7221</v>
       </c>
-      <c r="C41" s="27"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="21">
         <v>1220111851</v>
       </c>
@@ -5403,10 +5449,10 @@
       <c r="A42" s="23">
         <v>46232</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="29">
         <v>7429</v>
       </c>
-      <c r="C42" s="27"/>
+      <c r="C42" s="29"/>
       <c r="D42" s="21">
         <v>1191517169</v>
       </c>
@@ -5421,10 +5467,10 @@
       <c r="A43" s="23">
         <v>46233</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="29">
         <v>7272</v>
       </c>
-      <c r="C43" s="27"/>
+      <c r="C43" s="29"/>
       <c r="D43" s="21">
         <v>1145188929</v>
       </c>
@@ -5439,10 +5485,10 @@
       <c r="A44" s="23">
         <v>46234</v>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="29">
         <v>7038</v>
       </c>
-      <c r="C44" s="27"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="21">
         <v>1042575112</v>
       </c>
@@ -5454,1031 +5500,1167 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="23"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="24"/>
+      <c r="A45" s="23">
+        <v>46237</v>
+      </c>
+      <c r="B45" s="29">
+        <v>6723</v>
+      </c>
+      <c r="C45" s="29"/>
+      <c r="D45" s="21">
+        <v>975299201</v>
+      </c>
+      <c r="E45" s="21">
+        <v>-62521284</v>
+      </c>
+      <c r="F45" s="24">
+        <v>-4.5999999999999999E-3</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="27"/>
-      <c r="C87" s="27"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="27"/>
-      <c r="C89" s="27"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="27"/>
-      <c r="C92" s="27"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="27"/>
-      <c r="C93" s="27"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="27"/>
-      <c r="C94" s="27"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="27"/>
-      <c r="C95" s="27"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="27"/>
-      <c r="C96" s="27"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="27"/>
-      <c r="C97" s="27"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="27"/>
-      <c r="C98" s="27"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="27"/>
-      <c r="C99" s="27"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="27"/>
-      <c r="C100" s="27"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="27"/>
-      <c r="C101" s="27"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="27"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="27"/>
-      <c r="C103" s="27"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="27"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="27"/>
-      <c r="C105" s="27"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="27"/>
-      <c r="C106" s="27"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="27"/>
-      <c r="C107" s="27"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="27"/>
-      <c r="C108" s="27"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="29"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="27"/>
-      <c r="C109" s="27"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="29"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="27"/>
-      <c r="C110" s="27"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="27"/>
-      <c r="C111" s="27"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="27"/>
-      <c r="C112" s="27"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="27"/>
-      <c r="C113" s="27"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="29"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="27"/>
-      <c r="C114" s="27"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="29"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="27"/>
-      <c r="C115" s="27"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="27"/>
-      <c r="C116" s="27"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="29"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="27"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="27"/>
-      <c r="C118" s="27"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="27"/>
-      <c r="C119" s="27"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="27"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="29"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="27"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="29"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="27"/>
-      <c r="C122" s="27"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="29"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="27"/>
-      <c r="C123" s="27"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="27"/>
-      <c r="C124" s="27"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="27"/>
-      <c r="C125" s="27"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="29"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="27"/>
-      <c r="C126" s="27"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="27"/>
-      <c r="C127" s="27"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="27"/>
-      <c r="C128" s="27"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="29"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="27"/>
-      <c r="C129" s="27"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="29"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="27"/>
-      <c r="C130" s="27"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="27"/>
-      <c r="C131" s="27"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="29"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="27"/>
-      <c r="C132" s="27"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="27"/>
-      <c r="C133" s="27"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="29"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="27"/>
-      <c r="C134" s="27"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="29"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="27"/>
-      <c r="C135" s="27"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="27"/>
-      <c r="C136" s="27"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="27"/>
-      <c r="C137" s="27"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="29"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="27"/>
-      <c r="C138" s="27"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="29"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="27"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="29"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="27"/>
-      <c r="C140" s="27"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="29"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="27"/>
-      <c r="C141" s="27"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="29"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="23"/>
-      <c r="B142" s="27"/>
-      <c r="C142" s="27"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
       <c r="D142" s="21"/>
       <c r="E142" s="21"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="23"/>
-      <c r="B143" s="27"/>
-      <c r="C143" s="27"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="29"/>
       <c r="D143" s="21"/>
       <c r="E143" s="21"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="23"/>
-      <c r="B144" s="27"/>
-      <c r="C144" s="27"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="29"/>
       <c r="D144" s="21"/>
       <c r="E144" s="21"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="23"/>
-      <c r="B145" s="27"/>
-      <c r="C145" s="27"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="29"/>
       <c r="D145" s="21"/>
       <c r="E145" s="21"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="23"/>
-      <c r="B146" s="27"/>
-      <c r="C146" s="27"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="29"/>
       <c r="D146" s="21"/>
       <c r="E146" s="21"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="23"/>
-      <c r="B147" s="27"/>
-      <c r="C147" s="27"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="29"/>
       <c r="D147" s="21"/>
       <c r="E147" s="21"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="23"/>
-      <c r="B148" s="27"/>
-      <c r="C148" s="27"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
       <c r="D148" s="21"/>
       <c r="E148" s="21"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="23"/>
-      <c r="B149" s="27"/>
-      <c r="C149" s="27"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
       <c r="D149" s="21"/>
       <c r="E149" s="21"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="23"/>
-      <c r="B150" s="27"/>
-      <c r="C150" s="27"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="29"/>
       <c r="D150" s="21"/>
       <c r="E150" s="21"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="23"/>
-      <c r="B151" s="27"/>
-      <c r="C151" s="27"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="29"/>
       <c r="D151" s="21"/>
       <c r="E151" s="21"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="23"/>
-      <c r="B152" s="27"/>
-      <c r="C152" s="27"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="29"/>
       <c r="D152" s="21"/>
       <c r="E152" s="21"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="23"/>
-      <c r="B153" s="27"/>
-      <c r="C153" s="27"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="29"/>
       <c r="D153" s="21"/>
       <c r="E153" s="21"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="23"/>
-      <c r="B154" s="27"/>
-      <c r="C154" s="27"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
       <c r="D154" s="21"/>
       <c r="E154" s="21"/>
       <c r="F154" s="24"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="23"/>
-      <c r="B155" s="27"/>
-      <c r="C155" s="27"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="29"/>
       <c r="D155" s="21"/>
       <c r="E155" s="21"/>
       <c r="F155" s="24"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="23"/>
-      <c r="B156" s="27"/>
-      <c r="C156" s="27"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="29"/>
       <c r="D156" s="21"/>
       <c r="E156" s="21"/>
       <c r="F156" s="24"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="23"/>
-      <c r="B157" s="27"/>
-      <c r="C157" s="27"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="29"/>
       <c r="D157" s="21"/>
       <c r="E157" s="21"/>
       <c r="F157" s="24"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="23"/>
-      <c r="B158" s="27"/>
-      <c r="C158" s="27"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="29"/>
       <c r="D158" s="21"/>
       <c r="E158" s="21"/>
       <c r="F158" s="24"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="23"/>
-      <c r="B159" s="27"/>
-      <c r="C159" s="27"/>
+      <c r="B159" s="29"/>
+      <c r="C159" s="29"/>
       <c r="D159" s="21"/>
       <c r="E159" s="21"/>
       <c r="F159" s="24"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="23"/>
-      <c r="B160" s="27"/>
-      <c r="C160" s="27"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
       <c r="D160" s="21"/>
       <c r="E160" s="21"/>
       <c r="F160" s="24"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="23"/>
-      <c r="B161" s="27"/>
-      <c r="C161" s="27"/>
+      <c r="B161" s="29"/>
+      <c r="C161" s="29"/>
       <c r="D161" s="21"/>
       <c r="E161" s="21"/>
       <c r="F161" s="24"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="23"/>
-      <c r="B162" s="27"/>
-      <c r="C162" s="27"/>
+      <c r="B162" s="29"/>
+      <c r="C162" s="29"/>
       <c r="D162" s="21"/>
       <c r="E162" s="21"/>
       <c r="F162" s="24"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="23"/>
-      <c r="B163" s="27"/>
-      <c r="C163" s="27"/>
+      <c r="B163" s="29"/>
+      <c r="C163" s="29"/>
       <c r="D163" s="21"/>
       <c r="E163" s="21"/>
       <c r="F163" s="24"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="23"/>
-      <c r="B164" s="27"/>
-      <c r="C164" s="27"/>
+      <c r="B164" s="29"/>
+      <c r="C164" s="29"/>
       <c r="D164" s="21"/>
       <c r="E164" s="21"/>
       <c r="F164" s="24"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="23"/>
-      <c r="B165" s="27"/>
-      <c r="C165" s="27"/>
+      <c r="B165" s="29"/>
+      <c r="C165" s="29"/>
       <c r="D165" s="21"/>
       <c r="E165" s="21"/>
       <c r="F165" s="24"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="23"/>
-      <c r="B166" s="27"/>
-      <c r="C166" s="27"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
       <c r="D166" s="21"/>
       <c r="E166" s="21"/>
       <c r="F166" s="24"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="23"/>
-      <c r="B167" s="27"/>
-      <c r="C167" s="27"/>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
       <c r="D167" s="21"/>
       <c r="E167" s="21"/>
       <c r="F167" s="24"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="23"/>
-      <c r="B168" s="27"/>
-      <c r="C168" s="27"/>
+      <c r="B168" s="29"/>
+      <c r="C168" s="29"/>
       <c r="D168" s="21"/>
       <c r="E168" s="21"/>
       <c r="F168" s="24"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="23"/>
-      <c r="B169" s="27"/>
-      <c r="C169" s="27"/>
+      <c r="B169" s="29"/>
+      <c r="C169" s="29"/>
       <c r="D169" s="21"/>
       <c r="E169" s="21"/>
       <c r="F169" s="24"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="23"/>
-      <c r="B170" s="27"/>
-      <c r="C170" s="27"/>
+      <c r="B170" s="29"/>
+      <c r="C170" s="29"/>
       <c r="D170" s="21"/>
       <c r="E170" s="21"/>
       <c r="F170" s="24"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="23"/>
-      <c r="B171" s="27"/>
-      <c r="C171" s="27"/>
+      <c r="B171" s="29"/>
+      <c r="C171" s="29"/>
       <c r="D171" s="21"/>
       <c r="E171" s="21"/>
       <c r="F171" s="24"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="23"/>
-      <c r="B172" s="27"/>
-      <c r="C172" s="27"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
       <c r="D172" s="21"/>
       <c r="E172" s="21"/>
       <c r="F172" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="138">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6491,132 +6673,6 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6624,7 +6680,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11739A8-E721-41A4-B437-5313D01B9D93}">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -6745,7 +6801,7 @@
       <c r="B8" s="26">
         <v>4.46</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="27">
         <v>0.12626262626262599</v>
       </c>
       <c r="D8" s="7">
@@ -6805,7 +6861,7 @@
       <c r="B12" s="4">
         <v>2.54</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="28">
         <v>2.89</v>
       </c>
       <c r="D12" s="7">
@@ -6850,7 +6906,7 @@
       <c r="B15" s="26">
         <v>2.21</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="27">
         <v>0.330188679245283</v>
       </c>
       <c r="D15" s="7">
@@ -6970,7 +7026,7 @@
       <c r="B23" s="26">
         <v>1.42</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="27">
         <v>-0.68571428571428505</v>
       </c>
       <c r="D23" s="7">
@@ -6985,7 +7041,7 @@
       <c r="B24" s="26">
         <v>1.4</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="27">
         <v>2.9220779220779201</v>
       </c>
       <c r="D24" s="7">
@@ -7000,7 +7056,7 @@
       <c r="B25" s="26">
         <v>1.33</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="27">
         <v>1.8929503916449</v>
       </c>
       <c r="D25" s="7">
@@ -7015,7 +7071,7 @@
       <c r="B26" s="26">
         <v>1.25</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="27">
         <v>4.76</v>
       </c>
       <c r="D26" s="7">
@@ -7030,7 +7086,7 @@
       <c r="B27" s="26">
         <v>1.17</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <v>-1.5270935960591101</v>
       </c>
       <c r="D27" s="7">
@@ -7045,7 +7101,7 @@
       <c r="B28" s="26">
         <v>1.04</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="27">
         <v>-1.66</v>
       </c>
       <c r="D28" s="7">
@@ -7060,7 +7116,7 @@
       <c r="B29" s="26">
         <v>0.9</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="27">
         <v>0.57999999999999996</v>
       </c>
       <c r="D29" s="7">
@@ -7075,7 +7131,7 @@
       <c r="B30" s="26">
         <v>0.84</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="27">
         <v>4.6100000000000003</v>
       </c>
       <c r="D30" s="7">
@@ -7090,7 +7146,7 @@
       <c r="B31" s="26">
         <v>0.82</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="27">
         <v>1.49</v>
       </c>
       <c r="D31" s="7">
@@ -7105,7 +7161,7 @@
       <c r="B32" s="26">
         <v>0.8</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="27">
         <v>0.243704305442729</v>
       </c>
       <c r="D32" s="7">
@@ -7120,7 +7176,7 @@
       <c r="B33" s="26">
         <v>0.79</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="27">
         <v>0.76</v>
       </c>
       <c r="D33" s="7">
@@ -7135,7 +7191,7 @@
       <c r="B34" s="26">
         <v>0.76</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="27">
         <v>-0.93</v>
       </c>
       <c r="D34" s="7">
@@ -7150,7 +7206,7 @@
       <c r="B35" s="26">
         <v>0.73</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="27">
         <v>0.40128410914927698</v>
       </c>
       <c r="D35" s="7">
@@ -7165,7 +7221,7 @@
       <c r="B36" s="26">
         <v>0.72</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="27">
         <v>0.78</v>
       </c>
       <c r="D36" s="7">
@@ -7180,7 +7236,7 @@
       <c r="B37" s="26">
         <v>0.71</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="27">
         <v>0.61</v>
       </c>
       <c r="D37" s="7">
@@ -7195,7 +7251,7 @@
       <c r="B38" s="26">
         <v>0.7</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="27">
         <v>0.84</v>
       </c>
       <c r="D38" s="7">
@@ -7210,7 +7266,7 @@
       <c r="B39" s="26">
         <v>0.7</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="27">
         <v>0.1</v>
       </c>
       <c r="D39" s="7">
@@ -7225,7 +7281,7 @@
       <c r="B40" s="26">
         <v>0.64</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="27">
         <v>0.97</v>
       </c>
       <c r="D40" s="7">
@@ -7240,7 +7296,7 @@
       <c r="B41" s="26">
         <v>0.63</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="27">
         <v>0.11</v>
       </c>
       <c r="D41" s="7">
@@ -7255,7 +7311,7 @@
       <c r="B42" s="26">
         <v>0.61</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="27">
         <v>4.43</v>
       </c>
       <c r="D42" s="7">
@@ -7270,7 +7326,7 @@
       <c r="B43" s="26">
         <v>0.56999999999999995</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="27">
         <v>1.82</v>
       </c>
       <c r="D43" s="7">
@@ -7285,7 +7341,7 @@
       <c r="B44" s="26">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="27">
         <v>-0.05</v>
       </c>
       <c r="D44" s="7">
@@ -7300,7 +7356,7 @@
       <c r="B45" s="26">
         <v>0.5</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="27">
         <v>-1.91</v>
       </c>
       <c r="D45" s="7">
@@ -7315,7 +7371,7 @@
       <c r="B46" s="26">
         <v>0.5</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="27">
         <v>1.41</v>
       </c>
       <c r="D46" s="7">
@@ -7330,7 +7386,7 @@
       <c r="B47" s="26">
         <v>0.45</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="27">
         <v>0.32</v>
       </c>
       <c r="D47" s="7">
@@ -7345,7 +7401,7 @@
       <c r="B48" s="26">
         <v>0.4</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="27">
         <v>5.47</v>
       </c>
       <c r="D48" s="7">
@@ -7360,7 +7416,7 @@
       <c r="B49" s="26">
         <v>0.33</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="27">
         <v>2.52</v>
       </c>
       <c r="D49" s="7">
@@ -7375,7 +7431,7 @@
       <c r="B50" s="26">
         <v>0.16</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="27">
         <v>-0.17</v>
       </c>
       <c r="D50" s="7">
@@ -7401,10 +7457,10 @@
       <c r="A62" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C62" s="28"/>
+      <c r="C62" s="30"/>
       <c r="D62" s="20" t="s">
         <v>53</v>
       </c>
@@ -7419,10 +7475,10 @@
       <c r="A63" s="23">
         <v>46226</v>
       </c>
-      <c r="B63" s="27">
+      <c r="B63" s="29">
         <v>18186</v>
       </c>
-      <c r="C63" s="27"/>
+      <c r="C63" s="29"/>
       <c r="D63" s="21">
         <v>1825486354</v>
       </c>
@@ -7437,10 +7493,10 @@
       <c r="A64" s="23">
         <v>46227</v>
       </c>
-      <c r="B64" s="27">
+      <c r="B64" s="29">
         <v>18753</v>
       </c>
-      <c r="C64" s="27"/>
+      <c r="C64" s="29"/>
       <c r="D64" s="21">
         <v>1898338108</v>
       </c>
@@ -7455,10 +7511,10 @@
       <c r="A65" s="23">
         <v>46230</v>
       </c>
-      <c r="B65" s="27">
+      <c r="B65" s="29">
         <v>19293</v>
       </c>
-      <c r="C65" s="27"/>
+      <c r="C65" s="29"/>
       <c r="D65" s="21">
         <v>2016158831</v>
       </c>
@@ -7473,10 +7529,10 @@
       <c r="A66" s="23">
         <v>46231</v>
       </c>
-      <c r="B66" s="27">
+      <c r="B66" s="29">
         <v>19624</v>
       </c>
-      <c r="C66" s="27"/>
+      <c r="C66" s="29"/>
       <c r="D66" s="21">
         <v>2053257616</v>
       </c>
@@ -7491,10 +7547,10 @@
       <c r="A67" s="23">
         <v>46232</v>
       </c>
-      <c r="B67" s="27">
+      <c r="B67" s="29">
         <v>20120</v>
       </c>
-      <c r="C67" s="27"/>
+      <c r="C67" s="29"/>
       <c r="D67" s="21">
         <v>2073450735</v>
       </c>
@@ -7509,10 +7565,10 @@
       <c r="A68" s="23">
         <v>46233</v>
       </c>
-      <c r="B68" s="27">
+      <c r="B68" s="29">
         <v>20320</v>
       </c>
-      <c r="C68" s="27"/>
+      <c r="C68" s="29"/>
       <c r="D68" s="21">
         <v>2050352793</v>
       </c>
@@ -7527,10 +7583,10 @@
       <c r="A69" s="23">
         <v>46234</v>
       </c>
-      <c r="B69" s="27">
+      <c r="B69" s="29">
         <v>20380</v>
       </c>
-      <c r="C69" s="27"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="21">
         <v>1988789335</v>
       </c>
@@ -7541,8 +7597,57 @@
         <v>3.5000000000000001E-3</v>
       </c>
     </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="23">
+        <v>46237</v>
+      </c>
+      <c r="B70" s="29">
+        <v>20094</v>
+      </c>
+      <c r="C70" s="29"/>
+      <c r="D70" s="21">
+        <v>1984485111</v>
+      </c>
+      <c r="E70" s="21">
+        <v>-13488765</v>
+      </c>
+      <c r="F70" s="24">
+        <v>4.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F71" s="24"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F73" s="24"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F74" s="24"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F77" s="24"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F80" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="B70:C70"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="B62:C62"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F3FB09-3681-4E83-9A2B-5C9713E2CC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF31B164-5EBD-49EB-9843-E8A5C297D5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="285" windowWidth="16335" windowHeight="20850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="120" windowWidth="16335" windowHeight="20850" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -826,11 +826,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-5.2836484983314698</v>
+        <v>-5.2847915443335296</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-1.2073136818687409</v>
+        <v>-1.2075748678802116</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -841,11 +841,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>2.1052631578947301</v>
+        <v>3.80154639175257</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.30105263157894641</v>
+        <v>0.54362113402061751</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -856,11 +856,11 @@
         <v>7.73</v>
       </c>
       <c r="C4" s="3">
-        <v>0.20408163265306101</v>
+        <v>-0.20366598778004</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D15" si="0">B4*C4/100</f>
-        <v>1.5775510204081619E-2</v>
+        <v>-1.5743380855397095E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -871,11 +871,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>3.8511466897446902</v>
+        <v>0.41666666666666602</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.27497187364777087</v>
+        <v>2.9749999999999954E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -886,11 +886,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>5.6338028169014001</v>
+        <v>1.05555555555555</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.37352112676056282</v>
+        <v>6.9983333333332967E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -901,11 +901,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>-2.3696682464454901</v>
+        <v>-0.269687162891046</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.13293838862559201</v>
+        <v>-1.512944983818768E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -916,11 +916,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>2.6293469041560602</v>
+        <v>4.1322314049586701</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>5.2324003392705591E-2</v>
+        <v>8.2231404958677534E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -931,11 +931,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-0.93023255813953398</v>
+        <v>-0.23474178403755799</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-9.6744186046511544E-3</v>
+        <v>-2.4413145539906029E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -946,11 +946,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>0.12626262626262599</v>
+        <v>1.2610340479192901</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>6.8181818181818035E-4</v>
+        <v>6.8095838587641667E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -961,11 +961,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>2.1455938697318002</v>
+        <v>-1.2753188297074201</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.1157088122605361E-2</v>
+        <v>-6.6316579144785849E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -976,11 +976,11 @@
         <v>0.27</v>
       </c>
       <c r="C12" s="3">
-        <v>6.7543859649122799</v>
+        <v>9.7781429745275208</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>1.8236842105263159E-2</v>
+        <v>2.6400986031224306E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -991,11 +991,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C13" s="3">
-        <v>6.4492216456634504</v>
+        <v>5.4317548746518103</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>9.0289103039288311E-3</v>
+        <v>7.6044568245125354E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1006,11 +1006,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C14" s="3">
-        <v>-0.68571428571428505</v>
+        <v>-2.1864211737629402</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-4.7999999999999958E-4</v>
+        <v>-1.5304948216340584E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1021,11 +1021,11 @@
         <v>1.27</v>
       </c>
       <c r="C15" s="3">
-        <v>-1.52</v>
+        <v>-0.93</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-1.9304000000000002E-2</v>
+        <v>-1.1811E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1039,7 +1039,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15</f>
-        <v>-0.31296068480130129</v>
+        <v>-0.49446126683677055</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1347,11 +1347,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.82855321861057996</v>
+        <v>-9.9956540634506705</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-7.3906947100063736E-2</v>
+        <v>-0.89161234245979981</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1362,11 +1362,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>7.9447322970638998</v>
+        <v>6.8</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.69993091537132957</v>
+        <v>0.59908000000000006</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,11 +1377,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>-9.9582898852971802</v>
+        <v>-9.9594672843080492</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82454640250260658</v>
+        <v>-0.82464389114070646</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,11 +1392,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>3.3333333333333299</v>
+        <v>9.0322580645161299</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.20566666666666644</v>
+        <v>0.55729032258064526</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1407,11 +1407,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>6.7543859649122799</v>
+        <v>9.7781429745275208</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.3208333333333333</v>
+        <v>0.46446179129005721</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1422,11 +1422,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>1.86536901865369</v>
+        <v>0.95541401273885296</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>8.2449310624493094E-2</v>
+        <v>4.2229299363057304E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1437,11 +1437,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>2.9220779220779201</v>
+        <v>4.1009463722397399</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.11016233766233759</v>
+        <v>0.15460567823343818</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,11 +1452,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>-4.3741879601559104</v>
+        <v>2.0380434782608599</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-0.15747076656561279</v>
+        <v>7.336956521739095E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1467,11 +1467,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>5.67741935483871</v>
+        <v>3.7851037851037801</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.19132903225806452</v>
+        <v>0.12755799755799738</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,11 +1482,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-2.2950819672131102</v>
+        <v>-2.8859060402684502</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-6.1508196721311359E-2</v>
+        <v>-7.7342281879194466E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,11 +1497,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-5.2836484983314698</v>
+        <v>-5.2847915443335296</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13631813125695191</v>
+        <v>-0.13634762184380508</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1512,11 +1512,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>3.6575228595178699</v>
+        <v>1.6840417000801899</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>8.9609310058187827E-2</v>
+        <v>4.1259021651964656E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,11 +1527,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>2.6293469041560602</v>
+        <v>4.1322314049586701</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>5.3901611535199227E-2</v>
+        <v>8.4710743801652735E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1542,11 +1542,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-7.7481840193704601</v>
+        <v>-4.2869641294838097</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13404358353510895</v>
+        <v>-7.4164479440069903E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1557,11 +1557,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>0.40128410914927698</v>
+        <v>-2.3980815347721798</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>6.5810593900481416E-3</v>
+        <v>-3.9328537170263744E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1572,11 +1572,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>2.6731470230862699</v>
+        <v>2.4260355029585798</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>4.3304981773997574E-2</v>
+        <v>3.9301775147928993E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1587,11 +1587,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>1.8929503916449</v>
+        <v>-2.8827674567584798</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>2.8015665796344517E-2</v>
+        <v>-4.2664958360025498E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1602,11 +1602,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-1.5270935960591101</v>
+        <v>4.55227613806903</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.137931034482754E-2</v>
+        <v>6.3731865932966411E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1617,11 +1617,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>2.8198433420365498</v>
+        <v>-0.10157440325038</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>3.665796344647515E-2</v>
+        <v>-1.3204672422549401E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1632,11 +1632,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>0.59171597633136097</v>
+        <v>3.4313725490196001</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>7.4556213017751482E-3</v>
+        <v>4.3235294117646955E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1647,11 +1647,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>0.243704305442729</v>
+        <v>3.6466774716369499</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>2.9244516653127478E-3</v>
+        <v>4.3760129659643397E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,11 +1662,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>0.20408163265306101</v>
+        <v>-0.20366598778004</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>1.4897959183673454E-3</v>
+        <v>-1.4867617107942918E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1677,11 +1677,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>2.8917283120376598</v>
+        <v>2.3529411764705799</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>2.0531271015467385E-2</v>
+        <v>1.6705882352941116E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,11 +1692,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>0.12626262626262599</v>
+        <v>1.2610340479192901</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>7.4494949494949335E-4</v>
+        <v>7.4401008827238114E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1707,11 +1707,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-0.68571428571428505</v>
+        <v>-2.1864211737629402</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8399999999999966E-3</v>
+        <v>-1.2243958573072467E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1722,11 +1722,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.2310606060606</v>
+        <v>2.0134228187919399</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9242424242423996E-3</v>
+        <v>8.0536912751677601E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1737,11 +1737,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>-2.9381443298968999</v>
+        <v>-3.34572490706319</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-1.145876288659791E-2</v>
+        <v>-1.3048327137546443E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,11 +1752,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>2.7565982404692</v>
+        <v>-0.62785388127853803</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>9.9237536656891206E-3</v>
+        <v>-2.2602739726027368E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1767,11 +1767,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>0.15408320493066199</v>
+        <v>-1.6153846153846101</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>5.2388289676425078E-4</v>
+        <v>-5.4923076923076748E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1782,11 +1782,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>-2.2727272727272698</v>
+        <v>1.16279069767441</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-7.7272727272727181E-3</v>
+        <v>3.9534883720929942E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1797,11 +1797,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>1.49393090569561</v>
+        <v>2.29990800367985</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>4.9299719887955134E-3</v>
+        <v>7.589696412143505E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1812,11 +1812,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>5.6338028169014001</v>
+        <v>1.05555555555555</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>1.4647887323943641E-2</v>
+        <v>2.74444444444443E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1827,11 +1827,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-3.5398230088495501</v>
+        <v>-1.8348623853210999</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3716814159291901E-3</v>
+        <v>-3.3027522935779796E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1842,11 +1842,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>-2.3696682464454901</v>
+        <v>-0.269687162891046</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8436018957345884E-3</v>
+        <v>-3.2362459546925513E-4</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1857,11 +1857,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-0.96685082872928096</v>
+        <v>1.1157601115760101</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-6.7679558011049675E-4</v>
+        <v>7.8103207810320703E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1872,11 +1872,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>0.330188679245283</v>
+        <v>-4.3253408556652504</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>1.6509433962264149E-4</v>
+        <v>-2.1626704278326254E-3</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1887,11 +1887,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>-1.64556962025316</v>
+        <v>9.9742599742599705</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>-6.5822784810126407E-4</v>
+        <v>3.9897039897039879E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,11 +1902,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>-2.8861154446177801</v>
+        <v>0.48192771084337299</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1544461778471122E-3</v>
+        <v>1.927710843373492E-4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1917,11 +1917,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>-0.62344139650872799</v>
+        <v>1.5056461731493</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>-1.8703241895261838E-3</v>
+        <v>4.5169385194479003E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1932,11 +1932,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>0.56999999999999995</v>
+        <v>-0.89</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>4.7481000000000002E-2</v>
+        <v>-7.4137000000000008E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1947,11 +1947,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.15</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>2.3156E-2</v>
+        <v>1.2404999999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1962,11 +1962,11 @@
         <v>2.56</v>
       </c>
       <c r="C43" s="4">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" si="0"/>
-        <v>3.3280000000000002E-3</v>
+        <v>9.7280000000000005E-3</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>0.55504517435531953</v>
+        <v>0.21081197802617213</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2311,26 +2311,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2340,6 +2320,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2379,11 +2379,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>7.9447322970638998</v>
+        <v>6.8</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.76666666666666639</v>
+        <v>0.65620000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2394,11 +2394,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>-0.82855321861057996</v>
+        <v>-9.9956540634506705</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>-7.6972594008922868E-2</v>
+        <v>-0.92859626249456728</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2409,11 +2409,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9582898852971802</v>
+        <v>-9.9594672843080492</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.92014598540145942</v>
+        <v>-0.92025477707006376</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2424,11 +2424,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-2.2950819672131102</v>
+        <v>-2.8859060402684502</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13977049180327841</v>
+        <v>-0.1757516778523486</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2439,11 +2439,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>6.7543859649122799</v>
+        <v>9.7781429745275208</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.31948245614035087</v>
+        <v>0.46250616269515177</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2454,11 +2454,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>3.3333333333333299</v>
+        <v>9.0322580645161299</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.1506666666666665</v>
+        <v>0.40825806451612906</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2469,11 +2469,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>-4.3741879601559104</v>
+        <v>2.0380434782608599</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-0.14872239064530096</v>
+        <v>6.9293478260869235E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2484,11 +2484,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>1.86536901865369</v>
+        <v>0.95541401273885296</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>5.0924574209245739E-2</v>
+        <v>2.6082802547770685E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2499,11 +2499,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>2.6293469041560602</v>
+        <v>4.1322314049586701</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>6.0474978795589378E-2</v>
+        <v>9.5041322314049395E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2514,11 +2514,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-1.5270935960591101</v>
+        <v>4.55227613806903</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-2.550246305418714E-2</v>
+        <v>7.6023011505752802E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2529,11 +2529,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-7.7481840193704601</v>
+        <v>-4.2869641294838097</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12242130750605326</v>
+        <v>-6.7734033245844205E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2544,11 +2544,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-5.2836484983314698</v>
+        <v>-5.2847915443335296</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-8.2953281423804079E-2</v>
+        <v>-8.2971227246036408E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2559,11 +2559,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>2.9220779220779201</v>
+        <v>4.1009463722397399</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>3.301948051948049E-2</v>
+        <v>4.6340694006309052E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2574,11 +2574,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>5.67741935483871</v>
+        <v>3.7851037851037801</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>5.8477419354838717E-2</v>
+        <v>3.8986568986568937E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2589,11 +2589,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>0.40128410914927698</v>
+        <v>-2.3980815347721798</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>3.9325842696629146E-3</v>
+        <v>-2.3501199040767359E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2604,11 +2604,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.94832041343669</v>
+        <v>-9.8995695839311306</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6550387596899203E-2</v>
+        <v>-8.6126255380200828E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2619,11 +2619,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-0.68571428571428505</v>
+        <v>-2.1864211737629402</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-4.045714285714281E-3</v>
+        <v>-1.2899884925201346E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2634,11 +2634,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>0.330188679245283</v>
+        <v>-4.3253408556652504</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>1.6509433962264149E-3</v>
+        <v>-2.1626704278326251E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2649,11 +2649,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>-1.2310606060606</v>
+        <v>2.0134228187919399</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9090909090908795E-3</v>
+        <v>9.6644295302013104E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2664,11 +2664,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>0.59171597633136097</v>
+        <v>3.4313725490196001</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>2.4852071005917161E-3</v>
+        <v>1.441176470588232E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2679,11 +2679,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>1.18675827607745</v>
+        <v>-0.67901234567901203</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>4.7470331043097998E-3</v>
+        <v>-2.716049382716048E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,11 +2694,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>2.8917283120376598</v>
+        <v>2.3529411764705799</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>1.0988567585743108E-2</v>
+        <v>8.9411764705882042E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2709,11 +2709,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>5.6338028169014001</v>
+        <v>1.05555555555555</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>1.4084507042253501E-2</v>
+        <v>2.6388888888888751E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2724,11 +2724,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>3.45744680851063</v>
+        <v>-2.7420736932305001</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>8.6436170212765753E-3</v>
+        <v>-6.8551842330762504E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2739,11 +2739,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>0.15408320493066199</v>
+        <v>-1.6153846153846101</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>3.6979969183358876E-4</v>
+        <v>-3.8769230769230638E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2754,11 +2754,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0.20408163265306101</v>
+        <v>-0.20366598778004</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>4.6938775510204034E-4</v>
+        <v>-4.6843177189409205E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2769,11 +2769,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>1.19047619047619</v>
+        <v>0.29411764705882298</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>2.3809523809523803E-3</v>
+        <v>5.8823529411764603E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2784,11 +2784,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>-1.64556962025316</v>
+        <v>9.9742599742599705</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3164556962025281E-3</v>
+        <v>7.9794079794079757E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2799,11 +2799,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.96685082872928096</v>
+        <v>1.1157601115760101</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-9.6685082872928097E-5</v>
+        <v>1.1157601115760101E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2814,11 +2814,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>0.56999999999999995</v>
+        <v>-0.89</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>4.5542999999999993E-2</v>
+        <v>-7.1111000000000008E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2829,11 +2829,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.15</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>2.1560000000000003E-2</v>
+        <v>1.155E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2844,11 +2844,11 @@
         <v>2.5</v>
       </c>
       <c r="C33" s="4">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>3.2500000000000003E-3</v>
+        <v>9.4999999999999998E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2859,11 +2859,11 @@
         <v>0.78</v>
       </c>
       <c r="C34" s="4">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>1.0140000000000001E-3</v>
+        <v>3.0420000000000004E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2874,11 +2874,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>7.81</v>
+        <v>6.58</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>4.5297999999999998E-2</v>
+        <v>3.8163999999999997E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2889,11 +2889,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>4.6799999999999999E-4</v>
+        <v>2.3999999999999997E-5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-7.8090057129958194E-3</v>
+        <v>-0.41914202628512065</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3838,97 +3838,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3942,6 +3851,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3982,11 +3982,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>1.94765672550213</v>
+        <v>1.1940298507462599</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>1.0273889227023736</v>
+        <v>0.62985074626865201</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3997,11 +3997,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>2.31362467866323</v>
+        <v>-4.1457286432160796</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>0.25727506426735114</v>
+        <v>-0.46100502512562808</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4012,11 +4012,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>3.0704076230809898</v>
+        <v>-9.9126861838726192</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>1.6273160402329248E-2</v>
+        <v>-5.253723677452489E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4027,11 +4027,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>-1.41</v>
+        <v>1.48</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.420462</v>
+        <v>0.44133600000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>0.8804751473720539</v>
+        <v>0.557644484368499</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5058,107 +5058,6 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5171,6 +5070,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5211,11 +5211,11 @@
         <v>42.54</v>
       </c>
       <c r="C2" s="3">
-        <v>-3.6135113904163298</v>
+        <v>8.1499592502037393E-2</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-1.5371877454831067</v>
+        <v>3.4669926650366702E-2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5226,11 +5226,11 @@
         <v>32.340000000000003</v>
       </c>
       <c r="C3" s="3">
-        <v>0.48010973936899798</v>
+        <v>0</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>0.15526748971193396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5241,11 +5241,11 @@
         <v>12.21</v>
       </c>
       <c r="C4" s="3">
-        <v>-4.4884488448844797</v>
+        <v>-2.5570145127850701</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-0.54803960396039497</v>
+        <v>-0.31221147201105709</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5256,11 +5256,11 @@
         <v>10.92</v>
       </c>
       <c r="C5" s="3">
-        <v>-0.84711577248890602</v>
+        <v>-3.98698128559804</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>-9.2505042355788533E-2</v>
+        <v>-0.43537835638730599</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5271,11 +5271,11 @@
         <v>5.89</v>
       </c>
       <c r="C6" s="3">
-        <v>-3.3333333333333299</v>
+        <v>-1.8965517241379299</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.19633333333333311</v>
+        <v>-0.11170689655172407</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5286,11 +5286,11 @@
         <v>5.68</v>
       </c>
       <c r="C7" s="3">
-        <v>-1.9607843137254899</v>
+        <v>-2.97435897435897</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-0.11137254901960782</v>
+        <v>-0.16894358974358947</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5304,7 +5304,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6">
         <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-2.330170784440297</v>
+        <v>-0.99357038804330988</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,132 +6535,6 @@
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
     <mergeCell ref="B166:C166"/>
@@ -6673,6 +6547,132 @@
     <mergeCell ref="B163:C163"/>
     <mergeCell ref="B164:C164"/>
     <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6712,11 +6712,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>6.4492216456634504</v>
+        <v>5.4317548746518103</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.58945885841363943</v>
+        <v>0.49646239554317545</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6727,11 +6727,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>3.8511466897446902</v>
+        <v>0.41666666666666602</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>0.31463868455214117</v>
+        <v>3.4041666666666616E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6742,11 +6742,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>0.2</v>
+        <v>-0.20366598778004</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>1.6239999999999997E-2</v>
+        <v>-1.6537678207739246E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6757,11 +6757,11 @@
         <v>6.99</v>
       </c>
       <c r="C5" s="3">
-        <v>2.1052631578947301</v>
+        <v>3.80154639175257</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.14715789473684163</v>
+        <v>0.26572809278350468</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6772,11 +6772,11 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>2.63</v>
+        <v>4.1322314049586701</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.15753700000000001</v>
+        <v>0.24752066115702434</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6802,11 +6802,11 @@
         <v>4.46</v>
       </c>
       <c r="C8" s="27">
-        <v>0.12626262626262599</v>
+        <v>1.2610340479192901</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>5.631313131313119E-3</v>
+        <v>5.624211853720034E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6817,11 +6817,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>2.1455938697318002</v>
+        <v>-1.2753188297074201</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>8.9471264367816078E-2</v>
+        <v>-5.3180795198799417E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6832,11 +6832,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>-2.3696682464454901</v>
+        <v>-0.269687162891046</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-7.6540284360189337E-2</v>
+        <v>-8.7108953613807862E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6847,11 +6847,11 @@
         <v>2.84</v>
       </c>
       <c r="C11" s="3">
-        <v>1.86536901865369</v>
+        <v>0.95541401273885296</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>5.2976480129764789E-2</v>
+        <v>2.7133757961783425E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -6862,11 +6862,11 @@
         <v>2.54</v>
       </c>
       <c r="C12" s="28">
-        <v>2.89</v>
+        <v>2.3529411764705799</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>7.3405999999999999E-2</v>
+        <v>5.9764705882352727E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -6877,11 +6877,11 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>-4.37</v>
+        <v>2.0380434782608599</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10356900000000001</v>
+        <v>4.8301630434782375E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6907,11 +6907,11 @@
         <v>2.21</v>
       </c>
       <c r="C15" s="27">
-        <v>0.330188679245283</v>
+        <v>-4.3253408556652504</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>7.2971698113207537E-3</v>
+        <v>-9.5590032910202044E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6922,11 +6922,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>5.6338028169014001</v>
+        <v>1.05555555555555</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>0.10873239436619703</v>
+        <v>2.0372222222222115E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6937,11 +6937,11 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>2.6731470230862699</v>
+        <v>2.4260355029585798</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>4.7314702308626978E-2</v>
+        <v>4.2940828402366862E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -6967,11 +6967,11 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>3.6575228595178699</v>
+        <v>1.6840417000801899</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>5.5228595178719836E-2</v>
+        <v>2.542902967121087E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -7012,11 +7012,11 @@
         <v>1.43</v>
       </c>
       <c r="C22" s="3">
-        <v>2.8198433420365498</v>
+        <v>-0.10157440325038</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>4.0323759791122661E-2</v>
+        <v>-1.452513966480434E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -7027,11 +7027,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>-0.68571428571428505</v>
+        <v>-2.1864211737629402</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-9.737142857142847E-3</v>
+        <v>-3.1047180667433748E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -7042,11 +7042,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>2.9220779220779201</v>
+        <v>4.1009463722397399</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>4.0909090909090881E-2</v>
+        <v>5.7413249211356356E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -7057,11 +7057,11 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>1.8929503916449</v>
+        <v>-2.8827674567584798</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>2.5176240208877168E-2</v>
+        <v>-3.8340807174887782E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -7087,11 +7087,11 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>-1.5270935960591101</v>
+        <v>4.55227613806903</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7866995073891587E-2</v>
+        <v>5.3261630815407648E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -7147,11 +7147,11 @@
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>1.49</v>
+        <v>2.29990800367985</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>1.2218E-2</v>
+        <v>1.885924563017477E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -7162,11 +7162,11 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>0.243704305442729</v>
+        <v>3.6466774716369499</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>1.9496344435418322E-3</v>
+        <v>2.91734197730956E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -7192,11 +7192,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>-0.93</v>
+        <v>-0.23474178403755799</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>-7.0680000000000014E-3</v>
+        <v>-1.7840375586854406E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -7207,11 +7207,11 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>0.40128410914927698</v>
+        <v>-2.3980815347721798</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>2.9293739967897218E-3</v>
+        <v>-1.7505995203836913E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -7450,7 +7450,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>1.6092800340545794</v>
+        <v>1.2539597184428788</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF31B164-5EBD-49EB-9843-E8A5C297D5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758FF442-1C48-4855-BE68-5839F40F379E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="120" windowWidth="16335" windowHeight="20850" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35310" yWindow="150" windowWidth="15510" windowHeight="20760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
     <sheet name="PHE" sheetId="2" r:id="rId2"/>
     <sheet name="PBR" sheetId="3" r:id="rId3"/>
     <sheet name="DFI" sheetId="4" r:id="rId4"/>
-    <sheet name="BMU" sheetId="6" r:id="rId5"/>
-    <sheet name="KHA" sheetId="7" r:id="rId6"/>
+    <sheet name="KHA" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="95">
   <si>
     <t>DSTKF</t>
   </si>
@@ -240,24 +239,6 @@
   </si>
   <si>
     <t>Para Girişi/Çıkışı</t>
-  </si>
-  <si>
-    <t>KBORU</t>
-  </si>
-  <si>
-    <t>ARFYE</t>
-  </si>
-  <si>
-    <t>EGEGY</t>
-  </si>
-  <si>
-    <t>GRTHO</t>
-  </si>
-  <si>
-    <t>ZGYO</t>
-  </si>
-  <si>
-    <t>YEOTK</t>
   </si>
   <si>
     <t>Tarih</t>
@@ -1119,7 +1100,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>52</v>
@@ -1132,7 +1113,7 @@
         <v>67</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1280,7 +1261,22 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F40" s="24"/>
+      <c r="A40" s="18">
+        <v>46238</v>
+      </c>
+      <c r="B40" s="29">
+        <v>95992</v>
+      </c>
+      <c r="C40" s="29"/>
+      <c r="D40" s="25">
+        <v>223759283155</v>
+      </c>
+      <c r="E40" s="22">
+        <v>-2851667712</v>
+      </c>
+      <c r="F40" s="24">
+        <v>7.4000000000000003E-3</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F41" s="24"/>
@@ -1295,7 +1291,8 @@
       <c r="F44" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B37:C37"/>
@@ -2005,7 +2002,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B55" s="30" t="s">
         <v>52</v>
@@ -2018,7 +2015,7 @@
         <v>67</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2166,12 +2163,22 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="18"/>
-      <c r="B64" s="29"/>
+      <c r="A64" s="18">
+        <v>46238</v>
+      </c>
+      <c r="B64" s="29">
+        <v>147034</v>
+      </c>
       <c r="C64" s="29"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="24"/>
+      <c r="D64" s="21">
+        <v>51950990933</v>
+      </c>
+      <c r="E64" s="21">
+        <v>-5284511372</v>
+      </c>
+      <c r="F64" s="24">
+        <v>-1.1999999999999999E-3</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
@@ -2311,6 +2318,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2320,26 +2347,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2932,7 +2939,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B53" s="30" t="s">
         <v>52</v>
@@ -2945,7 +2952,7 @@
         <v>67</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3093,12 +3100,22 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
-      <c r="B62" s="29"/>
+      <c r="A62" s="18">
+        <v>46238</v>
+      </c>
+      <c r="B62" s="29">
+        <v>72101</v>
+      </c>
       <c r="C62" s="29"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="24"/>
+      <c r="D62" s="21">
+        <v>26219512523</v>
+      </c>
+      <c r="E62" s="21">
+        <v>-3580010999</v>
+      </c>
+      <c r="F62" s="24">
+        <v>9.1000000000000004E-3</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
@@ -3838,6 +3855,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3851,97 +3959,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4080,7 +4097,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>52</v>
@@ -4093,7 +4110,7 @@
         <v>67</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4241,12 +4258,22 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="23"/>
-      <c r="B40" s="29"/>
+      <c r="A40" s="23">
+        <v>46238</v>
+      </c>
+      <c r="B40" s="29">
+        <v>51083</v>
+      </c>
       <c r="C40" s="29"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="24"/>
+      <c r="D40" s="21">
+        <v>31890486608</v>
+      </c>
+      <c r="E40" s="21">
+        <v>-821515583</v>
+      </c>
+      <c r="F40" s="24">
+        <v>7.9000000000000008E-3</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
@@ -5058,6 +5085,107 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5070,1615 +5198,12 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F549F2-A66C-43F1-8B7E-B9FC6B9E004D}">
-  <dimension ref="A1:F172"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="4">
-        <v>42.54</v>
-      </c>
-      <c r="C2" s="3">
-        <v>8.1499592502037393E-2</v>
-      </c>
-      <c r="D2" s="7">
-        <f>B2*C2/100</f>
-        <v>3.4669926650366702E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="4">
-        <v>32.340000000000003</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <f t="shared" ref="D3:D7" si="0">B3*C3/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="4">
-        <v>12.21</v>
-      </c>
-      <c r="C4" s="3">
-        <v>-2.5570145127850701</v>
-      </c>
-      <c r="D4" s="7">
-        <f t="shared" si="0"/>
-        <v>-0.31221147201105709</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="4">
-        <v>10.92</v>
-      </c>
-      <c r="C5" s="3">
-        <v>-3.98698128559804</v>
-      </c>
-      <c r="D5" s="7">
-        <f t="shared" si="0"/>
-        <v>-0.43537835638730599</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="4">
-        <v>5.89</v>
-      </c>
-      <c r="C6" s="3">
-        <v>-1.8965517241379299</v>
-      </c>
-      <c r="D6" s="7">
-        <f t="shared" si="0"/>
-        <v>-0.11170689655172407</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="4">
-        <v>5.68</v>
-      </c>
-      <c r="C7" s="3">
-        <v>-2.97435897435897</v>
-      </c>
-      <c r="D7" s="7">
-        <f t="shared" si="0"/>
-        <v>-0.16894358974358947</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="5">
-        <f>B2+B3+B4+B5+B6+B7</f>
-        <v>109.58000000000001</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6">
-        <f>D2+D3+D4+D5+D6+D7</f>
-        <v>-0.99357038804330988</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="23">
-        <v>46226</v>
-      </c>
-      <c r="B38" s="29">
-        <v>6356</v>
-      </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="21">
-        <v>1033181017</v>
-      </c>
-      <c r="E38" s="21">
-        <v>95865997</v>
-      </c>
-      <c r="F38" s="24">
-        <v>5.4000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="23">
-        <v>46227</v>
-      </c>
-      <c r="B39" s="29">
-        <v>6609</v>
-      </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="21">
-        <v>1076556627</v>
-      </c>
-      <c r="E39" s="21">
-        <v>42490384</v>
-      </c>
-      <c r="F39" s="24">
-        <v>-8.9999999999999998E-4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="23">
-        <v>46230</v>
-      </c>
-      <c r="B40" s="29">
-        <v>6906</v>
-      </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="21">
-        <v>1167160796</v>
-      </c>
-      <c r="E40" s="21">
-        <v>99781628</v>
-      </c>
-      <c r="F40" s="24">
-        <v>-8.5000000000000006E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="23">
-        <v>46231</v>
-      </c>
-      <c r="B41" s="29">
-        <v>7221</v>
-      </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="21">
-        <v>1220111851</v>
-      </c>
-      <c r="E41" s="21">
-        <v>60385808</v>
-      </c>
-      <c r="F41" s="24">
-        <v>-6.4000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="23">
-        <v>46232</v>
-      </c>
-      <c r="B42" s="29">
-        <v>7429</v>
-      </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="21">
-        <v>1191517169</v>
-      </c>
-      <c r="E42" s="21">
-        <v>-26002641</v>
-      </c>
-      <c r="F42" s="24">
-        <v>-2.0999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="23">
-        <v>46233</v>
-      </c>
-      <c r="B43" s="29">
-        <v>7272</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="21">
-        <v>1145188929</v>
-      </c>
-      <c r="E43" s="21">
-        <v>-36158316</v>
-      </c>
-      <c r="F43" s="24">
-        <v>-8.5000000000000006E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="23">
-        <v>46234</v>
-      </c>
-      <c r="B44" s="29">
-        <v>7038</v>
-      </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="21">
-        <v>1042575112</v>
-      </c>
-      <c r="E44" s="21">
-        <v>-84952353</v>
-      </c>
-      <c r="F44" s="24">
-        <v>-1.54E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="23">
-        <v>46237</v>
-      </c>
-      <c r="B45" s="29">
-        <v>6723</v>
-      </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="21">
-        <v>975299201</v>
-      </c>
-      <c r="E45" s="21">
-        <v>-62521284</v>
-      </c>
-      <c r="F45" s="24">
-        <v>-4.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="24"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="23"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="24"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="24"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="24"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="24"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="23"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="24"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="23"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="24"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="23"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="24"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="23"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="24"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="24"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="23"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="24"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="23"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="24"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="23"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="24"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="23"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="24"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="23"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="24"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="23"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="24"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="23"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="24"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="23"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="24"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="23"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="24"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="23"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="24"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="23"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="24"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="23"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="24"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="23"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="24"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="23"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="24"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="24"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="24"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="23"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="24"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="23"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="24"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="24"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="24"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="24"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="24"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="24"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="24"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="24"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="23"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="24"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="23"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="24"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="23"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="24"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="23"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="24"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="23"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="24"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="23"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="24"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="23"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="24"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="23"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="29"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="24"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="23"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="24"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="23"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="29"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="24"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="23"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="24"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="23"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="24"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="23"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="24"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="23"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="24"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="23"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="21"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="24"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="23"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="23"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="24"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="23"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="24"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="23"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="21"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="24"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="23"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29"/>
-      <c r="D100" s="21"/>
-      <c r="E100" s="21"/>
-      <c r="F100" s="24"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="23"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="23"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="24"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="23"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="23"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="29"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="23"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="24"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="23"/>
-      <c r="B106" s="29"/>
-      <c r="C106" s="29"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="24"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="23"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="24"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="23"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="29"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="24"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="23"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="29"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="24"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="23"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="29"/>
-      <c r="D110" s="21"/>
-      <c r="E110" s="21"/>
-      <c r="F110" s="24"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="23"/>
-      <c r="B111" s="29"/>
-      <c r="C111" s="29"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="24"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="23"/>
-      <c r="B112" s="29"/>
-      <c r="C112" s="29"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="24"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="23"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="29"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="24"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="23"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="29"/>
-      <c r="D114" s="21"/>
-      <c r="E114" s="21"/>
-      <c r="F114" s="24"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="23"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="29"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="24"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="23"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="29"/>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21"/>
-      <c r="F116" s="24"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="23"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="29"/>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="24"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="23"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="29"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="21"/>
-      <c r="F118" s="24"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="23"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="29"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="24"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="23"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="29"/>
-      <c r="D120" s="21"/>
-      <c r="E120" s="21"/>
-      <c r="F120" s="24"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="23"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="29"/>
-      <c r="D121" s="21"/>
-      <c r="E121" s="21"/>
-      <c r="F121" s="24"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="23"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="29"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="24"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="23"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="29"/>
-      <c r="D123" s="21"/>
-      <c r="E123" s="21"/>
-      <c r="F123" s="24"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="23"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="29"/>
-      <c r="D124" s="21"/>
-      <c r="E124" s="21"/>
-      <c r="F124" s="24"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="23"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="29"/>
-      <c r="D125" s="21"/>
-      <c r="E125" s="21"/>
-      <c r="F125" s="24"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="23"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="29"/>
-      <c r="D126" s="21"/>
-      <c r="E126" s="21"/>
-      <c r="F126" s="24"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="23"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="29"/>
-      <c r="D127" s="21"/>
-      <c r="E127" s="21"/>
-      <c r="F127" s="24"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="23"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="29"/>
-      <c r="D128" s="21"/>
-      <c r="E128" s="21"/>
-      <c r="F128" s="24"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="23"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="29"/>
-      <c r="D129" s="21"/>
-      <c r="E129" s="21"/>
-      <c r="F129" s="24"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="23"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="29"/>
-      <c r="D130" s="21"/>
-      <c r="E130" s="21"/>
-      <c r="F130" s="24"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="23"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="29"/>
-      <c r="D131" s="21"/>
-      <c r="E131" s="21"/>
-      <c r="F131" s="24"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="23"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="29"/>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="24"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="23"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="29"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="24"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="23"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="29"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="24"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="23"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="29"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="24"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="23"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="29"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="24"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="23"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="29"/>
-      <c r="D137" s="21"/>
-      <c r="E137" s="21"/>
-      <c r="F137" s="24"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="23"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="29"/>
-      <c r="D138" s="21"/>
-      <c r="E138" s="21"/>
-      <c r="F138" s="24"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="23"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="29"/>
-      <c r="D139" s="21"/>
-      <c r="E139" s="21"/>
-      <c r="F139" s="24"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="23"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="29"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="24"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="23"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="29"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="21"/>
-      <c r="F141" s="24"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="23"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="29"/>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="24"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="23"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="29"/>
-      <c r="D143" s="21"/>
-      <c r="E143" s="21"/>
-      <c r="F143" s="24"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="23"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="29"/>
-      <c r="D144" s="21"/>
-      <c r="E144" s="21"/>
-      <c r="F144" s="24"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="23"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="29"/>
-      <c r="D145" s="21"/>
-      <c r="E145" s="21"/>
-      <c r="F145" s="24"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="23"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="29"/>
-      <c r="D146" s="21"/>
-      <c r="E146" s="21"/>
-      <c r="F146" s="24"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="23"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="29"/>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21"/>
-      <c r="F147" s="24"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="23"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="29"/>
-      <c r="D148" s="21"/>
-      <c r="E148" s="21"/>
-      <c r="F148" s="24"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="23"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="29"/>
-      <c r="D149" s="21"/>
-      <c r="E149" s="21"/>
-      <c r="F149" s="24"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="23"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="29"/>
-      <c r="D150" s="21"/>
-      <c r="E150" s="21"/>
-      <c r="F150" s="24"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="23"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="29"/>
-      <c r="D151" s="21"/>
-      <c r="E151" s="21"/>
-      <c r="F151" s="24"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="23"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="29"/>
-      <c r="D152" s="21"/>
-      <c r="E152" s="21"/>
-      <c r="F152" s="24"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="23"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="29"/>
-      <c r="D153" s="21"/>
-      <c r="E153" s="21"/>
-      <c r="F153" s="24"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="23"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="29"/>
-      <c r="D154" s="21"/>
-      <c r="E154" s="21"/>
-      <c r="F154" s="24"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="23"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="29"/>
-      <c r="D155" s="21"/>
-      <c r="E155" s="21"/>
-      <c r="F155" s="24"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="23"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="29"/>
-      <c r="D156" s="21"/>
-      <c r="E156" s="21"/>
-      <c r="F156" s="24"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="23"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="29"/>
-      <c r="D157" s="21"/>
-      <c r="E157" s="21"/>
-      <c r="F157" s="24"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="23"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="29"/>
-      <c r="D158" s="21"/>
-      <c r="E158" s="21"/>
-      <c r="F158" s="24"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="23"/>
-      <c r="B159" s="29"/>
-      <c r="C159" s="29"/>
-      <c r="D159" s="21"/>
-      <c r="E159" s="21"/>
-      <c r="F159" s="24"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="23"/>
-      <c r="B160" s="29"/>
-      <c r="C160" s="29"/>
-      <c r="D160" s="21"/>
-      <c r="E160" s="21"/>
-      <c r="F160" s="24"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="23"/>
-      <c r="B161" s="29"/>
-      <c r="C161" s="29"/>
-      <c r="D161" s="21"/>
-      <c r="E161" s="21"/>
-      <c r="F161" s="24"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="23"/>
-      <c r="B162" s="29"/>
-      <c r="C162" s="29"/>
-      <c r="D162" s="21"/>
-      <c r="E162" s="21"/>
-      <c r="F162" s="24"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="23"/>
-      <c r="B163" s="29"/>
-      <c r="C163" s="29"/>
-      <c r="D163" s="21"/>
-      <c r="E163" s="21"/>
-      <c r="F163" s="24"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="23"/>
-      <c r="B164" s="29"/>
-      <c r="C164" s="29"/>
-      <c r="D164" s="21"/>
-      <c r="E164" s="21"/>
-      <c r="F164" s="24"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="23"/>
-      <c r="B165" s="29"/>
-      <c r="C165" s="29"/>
-      <c r="D165" s="21"/>
-      <c r="E165" s="21"/>
-      <c r="F165" s="24"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="23"/>
-      <c r="B166" s="29"/>
-      <c r="C166" s="29"/>
-      <c r="D166" s="21"/>
-      <c r="E166" s="21"/>
-      <c r="F166" s="24"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="23"/>
-      <c r="B167" s="29"/>
-      <c r="C167" s="29"/>
-      <c r="D167" s="21"/>
-      <c r="E167" s="21"/>
-      <c r="F167" s="24"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="23"/>
-      <c r="B168" s="29"/>
-      <c r="C168" s="29"/>
-      <c r="D168" s="21"/>
-      <c r="E168" s="21"/>
-      <c r="F168" s="24"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="23"/>
-      <c r="B169" s="29"/>
-      <c r="C169" s="29"/>
-      <c r="D169" s="21"/>
-      <c r="E169" s="21"/>
-      <c r="F169" s="24"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="23"/>
-      <c r="B170" s="29"/>
-      <c r="C170" s="29"/>
-      <c r="D170" s="21"/>
-      <c r="E170" s="21"/>
-      <c r="F170" s="24"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="23"/>
-      <c r="B171" s="29"/>
-      <c r="C171" s="29"/>
-      <c r="D171" s="21"/>
-      <c r="E171" s="21"/>
-      <c r="F171" s="24"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="23"/>
-      <c r="B172" s="29"/>
-      <c r="C172" s="29"/>
-      <c r="D172" s="21"/>
-      <c r="E172" s="21"/>
-      <c r="F172" s="24"/>
-    </row>
-  </sheetData>
-  <mergeCells count="138">
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="B166:C166"/>
-    <mergeCell ref="B167:C167"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="B161:C161"/>
-    <mergeCell ref="B162:C162"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B156:C156"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B151:C151"/>
-    <mergeCell ref="B152:C152"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="B154:C154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="B148:C148"/>
-    <mergeCell ref="B149:C149"/>
-    <mergeCell ref="B150:C150"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B144:C144"/>
-    <mergeCell ref="B145:C145"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11739A8-E721-41A4-B437-5313D01B9D93}">
   <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6781,7 +5306,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4">
         <v>4.88</v>
@@ -6886,7 +5411,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B14" s="26">
         <v>2.37</v>
@@ -6946,7 +5471,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B18" s="4">
         <v>1.53</v>
@@ -6976,7 +5501,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B20" s="4">
         <v>1.44</v>
@@ -6991,7 +5516,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B21" s="4">
         <v>1.44</v>
@@ -7066,7 +5591,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B26" s="26">
         <v>1.25</v>
@@ -7096,7 +5621,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B28" s="26">
         <v>1.04</v>
@@ -7111,7 +5636,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B29" s="26">
         <v>0.9</v>
@@ -7126,7 +5651,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B30" s="26">
         <v>0.84</v>
@@ -7171,7 +5696,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B33" s="26">
         <v>0.79</v>
@@ -7216,7 +5741,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B36" s="26">
         <v>0.72</v>
@@ -7231,7 +5756,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B37" s="26">
         <v>0.71</v>
@@ -7246,7 +5771,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B38" s="26">
         <v>0.7</v>
@@ -7261,7 +5786,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B39" s="26">
         <v>0.7</v>
@@ -7276,7 +5801,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B40" s="26">
         <v>0.64</v>
@@ -7291,7 +5816,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B41" s="26">
         <v>0.63</v>
@@ -7306,7 +5831,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B42" s="26">
         <v>0.61</v>
@@ -7321,7 +5846,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B43" s="26">
         <v>0.56999999999999995</v>
@@ -7336,7 +5861,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B44" s="26">
         <v>0.55000000000000004</v>
@@ -7351,7 +5876,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B45" s="26">
         <v>0.5</v>
@@ -7366,7 +5891,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B46" s="26">
         <v>0.5</v>
@@ -7381,7 +5906,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B47" s="26">
         <v>0.45</v>
@@ -7396,7 +5921,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B48" s="26">
         <v>0.4</v>
@@ -7411,7 +5936,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B49" s="26">
         <v>0.33</v>
@@ -7426,7 +5951,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B50" s="26">
         <v>0.16</v>
@@ -7455,7 +5980,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B62" s="30" t="s">
         <v>52</v>
@@ -7468,7 +5993,7 @@
         <v>67</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -7616,7 +6141,22 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F71" s="24"/>
+      <c r="A71" s="23">
+        <v>46238</v>
+      </c>
+      <c r="B71" s="29">
+        <v>20026</v>
+      </c>
+      <c r="C71" s="29"/>
+      <c r="D71" s="21">
+        <v>1998771298</v>
+      </c>
+      <c r="E71" s="21">
+        <v>5725163</v>
+      </c>
+      <c r="F71" s="24">
+        <v>4.3E-3</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F72" s="24"/>
@@ -7646,7 +6186,8 @@
       <c r="F80" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="B71:C71"/>
     <mergeCell ref="B70:C70"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="B69:C69"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758FF442-1C48-4855-BE68-5839F40F379E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122BBFAA-00A6-4F0B-93B5-6CBE8D637B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35310" yWindow="150" windowWidth="15510" windowHeight="20760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19665" yWindow="1785" windowWidth="15510" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="96">
   <si>
     <t>DSTKF</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>BIZIM</t>
+  </si>
+  <si>
+    <t>İSVEA</t>
   </si>
 </sst>
 </file>
@@ -807,11 +810,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-5.2847915443335296</v>
+        <v>0.37197768133911902</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-1.2075748678802116</v>
+        <v>8.4996900185988697E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -822,11 +825,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>3.80154639175257</v>
+        <v>2.54500310366232</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.54362113402061751</v>
+        <v>0.36393544382371174</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -834,14 +837,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>7.73</v>
+        <v>8.14</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.20366598778004</v>
+        <v>0.34013605442176797</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" ref="D4:D15" si="0">B4*C4/100</f>
-        <v>-1.5743380855397095E-2</v>
+        <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
+        <v>2.7687074829931917E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,11 +855,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.41666666666666602</v>
+        <v>0.829875518672199</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>2.9749999999999954E-2</v>
+        <v>5.9253112033195006E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -867,11 +870,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>1.05555555555555</v>
+        <v>4.4529961517317203</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>6.9983333333332967E-2</v>
+        <v>0.29523364485981302</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,11 +885,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>-0.269687162891046</v>
+        <v>-0.59491617090319004</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-1.512944983818768E-2</v>
+        <v>-3.3374797187668961E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -897,11 +900,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>4.1322314049586701</v>
+        <v>-4.2063492063492003</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>8.2231404958677534E-2</v>
+        <v>-8.3706349206349076E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -912,11 +915,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-0.23474178403755799</v>
+        <v>-1.97647058823529</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-2.4413145539906029E-3</v>
+        <v>-2.0555294117647019E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -927,11 +930,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>1.2610340479192901</v>
+        <v>-0.37359900373598998</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>6.8095838587641667E-3</v>
+        <v>-2.0174346201743461E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -942,92 +945,101 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>-1.2753188297074201</v>
+        <v>7.5987841945288695E-2</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-6.6316579144785849E-3</v>
+        <v>3.9513677811550121E-4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="B12" s="4">
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C12" s="3">
-        <v>9.7781429745275208</v>
+        <v>-9.9809523809523792</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>2.6400986031224306E-2</v>
+        <v>-2.7946666666666665E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B13" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="C13" s="3">
-        <v>5.4317548746518103</v>
+        <v>9.5808383233532908</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>7.6044568245125354E-3</v>
+        <v>2.5868263473053887E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>-2.1864211737629402</v>
+        <v>-0.132100396301188</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-1.5304948216340584E-3</v>
+        <v>-1.8494055482166322E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.3529411764705799</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6470588235294062E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B16" s="4">
         <v>1.27</v>
       </c>
-      <c r="C15" s="3">
-        <v>-0.93</v>
-      </c>
-      <c r="D15" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.1811E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="C16" s="3">
+        <v>-1.75</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.2225000000000002E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="5">
-        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15</f>
-        <v>70.100000000000009</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6">
-        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15</f>
-        <v>-0.49446126683677055</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="5"/>
+      <c r="B17" s="5">
+        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16</f>
+        <v>70.790000000000006</v>
+      </c>
       <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
+      <c r="D17" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
+        <v>0.6690061524540114</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
@@ -1292,11 +1304,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="B31:C31"/>
@@ -1304,6 +1311,11 @@
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -1344,11 +1356,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>-9.9956540634506705</v>
+        <v>0.24142926122646</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.89161234245979981</v>
+        <v>2.1535490101400229E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,11 +1371,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>6.8</v>
+        <v>8.8014981273408193</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.59908000000000006</v>
+        <v>0.77541198501872632</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1374,11 +1386,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>-9.9594672843080492</v>
+        <v>-9.9678456591639808</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82464389114070646</v>
+        <v>-0.82533762057877746</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,11 +1401,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>9.0322580645161299</v>
+        <v>5.3254437869822402</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.55729032258064526</v>
+        <v>0.32857988165680424</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1404,11 +1416,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>9.7781429745275208</v>
+        <v>9.5808383233532908</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.46446179129005721</v>
+        <v>0.45508982035928125</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,11 +1431,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>0.95541401273885296</v>
+        <v>2.1293375394321701</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>4.2229299363057304E-2</v>
+        <v>9.4116719242901908E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,11 +1446,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>4.1009463722397399</v>
+        <v>3.1818181818181799</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.15460567823343818</v>
+        <v>0.11995454545454538</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,11 +1461,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>2.0380434782608599</v>
+        <v>2.8406569019085599</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>7.336956521739095E-2</v>
+        <v>0.10226364846870815</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1476,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>3.7851037851037801</v>
+        <v>2.52941176470588</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.12755799755799738</v>
+        <v>8.5241176470588154E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,11 +1491,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-2.8859060402684502</v>
+        <v>-1.7277125086385601</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-7.7342281879194466E-2</v>
+        <v>-4.630269523151341E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,11 +1506,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-5.2847915443335296</v>
+        <v>0.37197768133911902</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13634762184380508</v>
+        <v>9.59702417854927E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1509,11 +1521,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>1.6840417000801899</v>
+        <v>-0.70977917981072502</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>4.1259021651964656E-2</v>
+        <v>-1.7389589905362764E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1536,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>4.1322314049586701</v>
+        <v>-4.2063492063492003</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>8.4710743801652735E-2</v>
+        <v>-8.6230158730158588E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,11 +1551,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-4.2869641294838097</v>
+        <v>-1.5539305301645301</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-7.4164479440069903E-2</v>
+        <v>-2.6882998171846372E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,11 +1566,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>-2.3980815347721798</v>
+        <v>3.0303030303030298</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-3.9328537170263744E-2</v>
+        <v>4.9696969696969691E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,11 +1581,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>2.4260355029585798</v>
+        <v>2.7151935297515801</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>3.9301775147928993E-2</v>
+        <v>4.3986135181975604E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1596,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-2.8827674567584798</v>
+        <v>1.78100263852242</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-4.2664958360025498E-2</v>
+        <v>2.6358839050131814E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,11 +1611,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>4.55227613806903</v>
+        <v>2.9665071770334901</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>6.3731865932966411E-2</v>
+        <v>4.1531100478468863E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,11 +1626,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-0.10157440325038</v>
+        <v>1.1184544992374099</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3204672422549401E-3</v>
+        <v>1.4539908490086328E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,11 +1641,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>3.4313725490196001</v>
+        <v>2.1800947867298501</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>4.3235294117646955E-2</v>
+        <v>2.7469194312796111E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,11 +1656,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>3.6466774716369499</v>
+        <v>3.0492572322126601</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>4.3760129659643397E-2</v>
+        <v>3.6591086786551916E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,11 +1671,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>-0.20366598778004</v>
+        <v>0.34013605442176797</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4867617107942918E-3</v>
+        <v>2.4829931972789061E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,11 +1686,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>2.3529411764705799</v>
+        <v>1.46871008939974</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>1.6705882352941116E-2</v>
+        <v>1.0427841634738153E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1689,11 +1701,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>1.2610340479192901</v>
+        <v>-0.37359900373598998</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>7.4401008827238114E-3</v>
+        <v>-2.2042341220423409E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1716,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-2.1864211737629402</v>
+        <v>2.3529411764705799</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2243958573072467E-2</v>
+        <v>1.317647058823525E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1719,11 +1731,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>2.0134228187919399</v>
+        <v>3.85338345864661</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>8.0536912751677601E-3</v>
+        <v>1.5413533834586442E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1734,11 +1746,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>-3.34572490706319</v>
+        <v>4.2307692307692299</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3048327137546443E-2</v>
+        <v>1.6499999999999997E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1749,11 +1761,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-0.62785388127853803</v>
+        <v>-1.3785180930499701</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-2.2602739726027368E-3</v>
+        <v>-4.9626651349798925E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1776,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>-1.6153846153846101</v>
+        <v>1.9546520719311899</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-5.4923076923076748E-3</v>
+        <v>6.6458170445660462E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,11 +1791,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>1.16279069767441</v>
+        <v>0.229885057471264</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>3.9534883720929942E-3</v>
+        <v>7.816091954022977E-4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,11 +1806,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>2.29990800367985</v>
+        <v>2.8776978417266101</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>7.589696412143505E-3</v>
+        <v>9.496402877697813E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1809,11 +1821,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>1.05555555555555</v>
+        <v>4.4529961517317203</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>2.74444444444443E-3</v>
+        <v>1.1577789994502471E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1824,11 +1836,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-1.8348623853210999</v>
+        <v>-2.3364485981308398</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-3.3027522935779796E-3</v>
+        <v>-4.2056074766355115E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1839,11 +1851,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>-0.269687162891046</v>
+        <v>-0.59491617090319004</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-3.2362459546925513E-4</v>
+        <v>-7.1389940508382807E-4</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1854,11 +1866,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>1.1157601115760101</v>
+        <v>-0.20689655172413701</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>7.8103207810320703E-4</v>
+        <v>-1.4482758620689592E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1869,11 +1881,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-4.3253408556652504</v>
+        <v>2.5552825552825502</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1626704278326254E-3</v>
+        <v>1.2776412776412751E-3</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1884,11 +1896,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>9.9742599742599705</v>
+        <v>5.0906963136336998</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>3.9897039897039879E-3</v>
+        <v>2.0362785254534801E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1899,11 +1911,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>0.48192771084337299</v>
+        <v>0.87929656274979995</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>1.927710843373492E-4</v>
+        <v>3.5171862509991996E-4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1914,11 +1926,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>1.5056461731493</v>
+        <v>2.22496909765142</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>4.5169385194479003E-3</v>
+        <v>6.6749072929542597E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1929,11 +1941,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>-0.89</v>
+        <v>-10.41</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>-7.4137000000000008E-2</v>
+        <v>-0.86715299999999995</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1944,11 +1956,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>0.15</v>
+        <v>-4.42</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>1.2404999999999999E-2</v>
+        <v>-0.36553399999999997</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,11 +1971,11 @@
         <v>2.56</v>
       </c>
       <c r="C43" s="4">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="D43" s="4">
         <f t="shared" si="0"/>
-        <v>9.7280000000000005E-3</v>
+        <v>3.3280000000000002E-3</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1976,7 +1988,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>0.21081197802617213</v>
+        <v>8.507323269403505E-2</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2318,26 +2330,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2347,6 +2339,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2386,11 +2398,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>6.8</v>
+        <v>8.8014981273408193</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.65620000000000001</v>
+        <v>0.84934456928838908</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2401,11 +2413,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>-9.9956540634506705</v>
+        <v>0.24142926122646</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>-0.92859626249456728</v>
+        <v>2.2428778367938135E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2416,11 +2428,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9594672843080492</v>
+        <v>-9.9678456591639808</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.92025477707006376</v>
+        <v>-0.92102893890675186</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2431,11 +2443,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-2.8859060402684502</v>
+        <v>-1.7277125086385601</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.1757516778523486</v>
+        <v>-0.10521769177608829</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2446,11 +2458,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>9.7781429745275208</v>
+        <v>9.5808383233532908</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.46250616269515177</v>
+        <v>0.45317365269461068</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2461,11 +2473,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>9.0322580645161299</v>
+        <v>5.3254437869822402</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.40825806451612906</v>
+        <v>0.24071005917159724</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2476,11 +2488,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>2.0380434782608599</v>
+        <v>2.8406569019085599</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>6.9293478260869235E-2</v>
+        <v>9.6582334664891037E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2491,11 +2503,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>0.95541401273885296</v>
+        <v>2.1293375394321701</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>2.6082802547770685E-2</v>
+        <v>5.8130914826498244E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2506,11 +2518,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>4.1322314049586701</v>
+        <v>-4.2063492063492003</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>9.5041322314049395E-2</v>
+        <v>-9.6746031746031594E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2521,11 +2533,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>4.55227613806903</v>
+        <v>2.9665071770334901</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>7.6023011505752802E-2</v>
+        <v>4.9540669856459288E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2536,11 +2548,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-4.2869641294838097</v>
+        <v>-1.5539305301645301</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-6.7734033245844205E-2</v>
+        <v>-2.4552102376599577E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2551,11 +2563,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-5.2847915443335296</v>
+        <v>0.37197768133911902</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-8.2971227246036408E-2</v>
+        <v>5.8400495970241688E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2566,11 +2578,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>4.1009463722397399</v>
+        <v>3.1818181818181799</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>4.6340694006309052E-2</v>
+        <v>3.5954545454545433E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2581,11 +2593,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>3.7851037851037801</v>
+        <v>2.52941176470588</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>3.8986568986568937E-2</v>
+        <v>2.6052941176470563E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2596,11 +2608,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>-2.3980815347721798</v>
+        <v>3.0303030303030298</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3501199040767359E-2</v>
+        <v>2.9696969696969694E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2611,11 +2623,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-9.8995695839311306</v>
+        <v>2.5477707006369399</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6126255380200828E-2</v>
+        <v>2.2165605095541378E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,11 +2638,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-2.1864211737629402</v>
+        <v>2.3529411764705799</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2899884925201346E-2</v>
+        <v>1.3882352941176422E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2641,11 +2653,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-4.3253408556652504</v>
+        <v>2.5552825552825502</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1626704278326251E-2</v>
+        <v>1.2776412776412751E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2656,11 +2668,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>2.0134228187919399</v>
+        <v>3.85338345864661</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>9.6644295302013104E-3</v>
+        <v>1.8496240601503729E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2671,11 +2683,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>3.4313725490196001</v>
+        <v>2.1800947867298501</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>1.441176470588232E-2</v>
+        <v>9.1563981042653703E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,11 +2698,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-0.67901234567901203</v>
+        <v>2.23741454319453</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-2.716049382716048E-3</v>
+        <v>8.9496581727781209E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2701,11 +2713,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>2.3529411764705799</v>
+        <v>1.46871008939974</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>8.9411764705882042E-3</v>
+        <v>5.5810983397190121E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2716,11 +2728,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>1.05555555555555</v>
+        <v>4.4529961517317203</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>2.6388888888888751E-3</v>
+        <v>1.1132490379329301E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2731,11 +2743,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-2.7420736932305001</v>
+        <v>-8.2819383259911792</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-6.8551842330762504E-3</v>
+        <v>-2.0704845814977949E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2746,11 +2758,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>-1.6153846153846101</v>
+        <v>1.9546520719311899</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8769230769230638E-3</v>
+        <v>4.6911649726348557E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2761,11 +2773,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>-0.20366598778004</v>
+        <v>0.34013605442176797</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6843177189409205E-4</v>
+        <v>7.8231292517006638E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2776,11 +2788,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>0.29411764705882298</v>
+        <v>2.6392961876832799</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>5.8823529411764603E-4</v>
+        <v>5.2785923753665594E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2791,11 +2803,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>9.9742599742599705</v>
+        <v>5.0906963136336998</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>7.9794079794079757E-3</v>
+        <v>4.0725570509069602E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2806,11 +2818,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>1.1157601115760101</v>
+        <v>-0.20689655172413701</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>1.1157601115760101E-4</v>
+        <v>-2.0689655172413702E-5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2821,11 +2833,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>-0.89</v>
+        <v>-10.41</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-7.1111000000000008E-2</v>
+        <v>-0.83175900000000003</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2836,11 +2848,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>0.15</v>
+        <v>-4.42</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>1.155E-2</v>
+        <v>-0.34033999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2851,11 +2863,11 @@
         <v>2.5</v>
       </c>
       <c r="C33" s="4">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>9.4999999999999998E-3</v>
+        <v>3.2500000000000003E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2866,11 +2878,11 @@
         <v>0.78</v>
       </c>
       <c r="C34" s="4">
-        <v>0.39</v>
+        <v>0.13</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>3.0420000000000004E-3</v>
+        <v>1.0140000000000001E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2881,11 +2893,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>6.58</v>
+        <v>9.57</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>3.8163999999999997E-2</v>
+        <v>5.5506E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2896,11 +2908,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>2.3999999999999997E-5</v>
+        <v>-7.7999999999999999E-5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2913,7 +2925,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-0.41914202628512065</v>
+        <v>-0.29625693174542367</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3855,97 +3867,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3959,6 +3880,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3999,11 +4011,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>1.1940298507462599</v>
+        <v>-0.64896755162241804</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.62985074626865201</v>
+        <v>-0.34233038348082551</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4014,11 +4026,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-4.1457286432160796</v>
+        <v>-3.6697247706421998</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.46100502512562808</v>
+        <v>-0.40807339449541258</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4029,11 +4041,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9126861838726192</v>
+        <v>-9.9201824401368306</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-5.253723677452489E-2</v>
+        <v>-5.2576966932725205E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4044,11 +4056,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>1.48</v>
+        <v>0.81</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.44133600000000001</v>
+        <v>0.24154200000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4062,7 +4074,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>0.557644484368499</v>
+        <v>-0.56143874490896317</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5085,107 +5097,6 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5198,6 +5109,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5237,11 +5249,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>5.4317548746518103</v>
+        <v>-0.132100396301188</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.49646239554317545</v>
+        <v>-1.2073976221928583E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5252,11 +5264,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>0.41666666666666602</v>
+        <v>0.829875518672199</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>3.4041666666666616E-2</v>
+        <v>6.7800829875518651E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5267,11 +5279,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.20366598778004</v>
+        <v>0.34013605442176797</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6537678207739246E-2</v>
+        <v>2.7619047619047557E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5282,11 +5294,11 @@
         <v>6.99</v>
       </c>
       <c r="C5" s="3">
-        <v>3.80154639175257</v>
+        <v>2.54500310366232</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.26572809278350468</v>
+        <v>0.17789571694599615</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5297,11 +5309,11 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>4.1322314049586701</v>
+        <v>-4.2063492063492003</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.24752066115702434</v>
+        <v>-0.25196031746031711</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5327,11 +5339,11 @@
         <v>4.46</v>
       </c>
       <c r="C8" s="27">
-        <v>1.2610340479192901</v>
+        <v>-0.37359900373598998</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>5.624211853720034E-2</v>
+        <v>-1.6662515566625152E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5342,11 +5354,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>-1.2753188297074201</v>
+        <v>7.5987841945288695E-2</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-5.3180795198799417E-2</v>
+        <v>3.1686930091185382E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5357,11 +5369,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.269687162891046</v>
+        <v>-0.59491617090319004</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-8.7108953613807862E-3</v>
+        <v>-1.9215792320173036E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5372,11 +5384,11 @@
         <v>2.84</v>
       </c>
       <c r="C11" s="3">
-        <v>0.95541401273885296</v>
+        <v>2.1293375394321701</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>2.7133757961783425E-2</v>
+        <v>6.047318611987363E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5387,11 +5399,11 @@
         <v>2.54</v>
       </c>
       <c r="C12" s="28">
-        <v>2.3529411764705799</v>
+        <v>1.46871008939974</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>5.9764705882352727E-2</v>
+        <v>3.7305236270753397E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,11 +5414,11 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>2.0380434782608599</v>
+        <v>2.8406569019085599</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>4.8301630434782375E-2</v>
+        <v>6.7323568575232876E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5432,11 +5444,11 @@
         <v>2.21</v>
       </c>
       <c r="C15" s="27">
-        <v>-4.3253408556652504</v>
+        <v>2.5552825552825502</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-9.5590032910202044E-2</v>
+        <v>5.6471744471744356E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5447,11 +5459,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>1.05555555555555</v>
+        <v>4.4529961517317203</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>2.0372222222222115E-2</v>
+        <v>8.5942825728422198E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5462,11 +5474,11 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>2.4260355029585798</v>
+        <v>2.7151935297515801</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>4.2940828402366862E-2</v>
+        <v>4.8058925476602968E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5492,11 +5504,11 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>1.6840417000801899</v>
+        <v>-0.70977917981072502</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>2.542902967121087E-2</v>
+        <v>-1.0717665615141947E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5537,11 +5549,11 @@
         <v>1.43</v>
       </c>
       <c r="C22" s="3">
-        <v>-0.10157440325038</v>
+        <v>1.1184544992374099</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>-1.452513966480434E-3</v>
+        <v>1.5993899339094963E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5552,11 +5564,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>-2.1864211737629402</v>
+        <v>2.3529411764705799</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-3.1047180667433748E-2</v>
+        <v>3.3411764705882231E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5567,11 +5579,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>4.1009463722397399</v>
+        <v>3.1818181818181799</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>5.7413249211356356E-2</v>
+        <v>4.4545454545454513E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5582,11 +5594,11 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>-2.8827674567584798</v>
+        <v>1.78100263852242</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>-3.8340807174887782E-2</v>
+        <v>2.3687335092348188E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5612,11 +5624,11 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>4.55227613806903</v>
+        <v>2.9665071770334901</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>5.3261630815407648E-2</v>
+        <v>3.4708133971291827E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5672,11 +5684,11 @@
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>2.29990800367985</v>
+        <v>2.8776978417266101</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>1.885924563017477E-2</v>
+        <v>2.3597122302158203E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5687,11 +5699,11 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>3.6466774716369499</v>
+        <v>3.0492572322126601</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>2.91734197730956E-2</v>
+        <v>2.4394057857701282E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5717,11 +5729,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>-0.23474178403755799</v>
+        <v>-1.97647058823529</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7840375586854406E-3</v>
+        <v>-1.5021176470588204E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5732,11 +5744,11 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>-2.3980815347721798</v>
+        <v>3.0303030303030298</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7505995203836913E-2</v>
+        <v>2.2121212121212118E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5975,7 +5987,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>1.2539597184428788</v>
+        <v>0.5643323103726795</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122BBFAA-00A6-4F0B-93B5-6CBE8D637B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A2600-B466-422B-8D48-1D26CA4CDF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19665" yWindow="1785" windowWidth="15510" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36045" yWindow="195" windowWidth="14505" windowHeight="20790" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -810,11 +810,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>0.37197768133911902</v>
+        <v>0.55589870290302601</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>8.4996900185988697E-2</v>
+        <v>0.12702285361334145</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,11 +825,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>2.54500310366232</v>
+        <v>8.4140435835351006</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.36393544382371174</v>
+        <v>1.2032082324455196</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,11 +840,11 @@
         <v>8.14</v>
       </c>
       <c r="C4" s="3">
-        <v>0.34013605442176797</v>
+        <v>-6.7796610169491497E-2</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>2.7687074829931917E-2</v>
+        <v>-5.5186440677966082E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,11 +855,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.829875518672199</v>
+        <v>0.12345679012345601</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>5.9253112033195006E-2</v>
+        <v>8.814814814814758E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,11 +870,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>4.4529961517317203</v>
+        <v>1.73684210526315</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.29523364485981302</v>
+        <v>0.11515263157894685</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,11 +885,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>-0.59491617090319004</v>
+        <v>0.48966267682263298</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-3.3374797187668961E-2</v>
+        <v>2.747007616974971E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -900,11 +900,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>-4.2063492063492003</v>
+        <v>-5.5509527754763797</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-8.3706349206349076E-2</v>
+        <v>-0.11046396023197996</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,11 +915,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-1.97647058823529</v>
+        <v>1.77628420547287</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-2.0555294117647019E-2</v>
+        <v>1.847335573691785E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,11 +930,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.37359900373598998</v>
+        <v>2.25</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-2.0174346201743461E-3</v>
+        <v>1.2150000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,11 +945,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>7.5987841945288695E-2</v>
+        <v>9.9468488990129007</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>3.9513677811550121E-4</v>
+        <v>5.1723614274867089E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -960,11 +960,11 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="C12" s="3">
-        <v>-9.9809523809523792</v>
+        <v>9.92382564536606</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-2.7946666666666665E-2</v>
+        <v>2.778671180702497E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -975,11 +975,11 @@
         <v>0.27</v>
       </c>
       <c r="C13" s="3">
-        <v>9.5808383233532908</v>
+        <v>-9.9726775956284097</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>2.5868263473053887E-2</v>
+        <v>-2.6926229508196706E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,11 +990,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>-0.132100396301188</v>
+        <v>-0.79365079365079305</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-1.8494055482166322E-4</v>
+        <v>-1.1111111111111105E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1005,11 +1005,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C15" s="3">
-        <v>2.3529411764705799</v>
+        <v>-1.14942528735632</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>1.6470588235294062E-3</v>
+        <v>-8.04597701149424E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,11 +1020,11 @@
         <v>1.27</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.75</v>
+        <v>1.81</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-2.2225000000000002E-2</v>
+        <v>2.2987E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>0.6690061524540114</v>
+        <v>1.469964747820949</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1291,7 +1291,22 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F41" s="24"/>
+      <c r="A41" s="18">
+        <v>46239</v>
+      </c>
+      <c r="B41" s="29">
+        <v>97092</v>
+      </c>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25">
+        <v>230332113229</v>
+      </c>
+      <c r="E41" s="22">
+        <v>4240768585</v>
+      </c>
+      <c r="F41" s="24">
+        <v>1.04E-2</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F42" s="24"/>
@@ -1303,7 +1318,13 @@
       <c r="F44" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="B31:C31"/>
@@ -1311,11 +1332,6 @@
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -1356,11 +1372,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>0.24142926122646</v>
+        <v>4.04624277456647</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>2.1535490101400229E-2</v>
+        <v>0.36092485549132908</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,11 +1387,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>8.8014981273408193</v>
+        <v>-5.5077452667814102</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.77541198501872632</v>
+        <v>-0.48523235800344222</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1386,11 +1402,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>-9.9678456591639808</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82533762057877746</v>
+        <v>0.82799999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,11 +1417,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>5.3254437869822402</v>
+        <v>1.6292134831460601</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.32857988165680424</v>
+        <v>0.1005224719101119</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1416,11 +1432,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>9.5808383233532908</v>
+        <v>-9.9726775956284097</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.45508982035928125</v>
+        <v>-0.47370218579234946</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1431,11 +1447,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>2.1293375394321701</v>
+        <v>-3.01158301158301</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>9.4116719242901908E-2</v>
+        <v>-0.13311196911196904</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1446,11 +1462,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>3.1818181818181799</v>
+        <v>-0.807635829662261</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.11995454545454538</v>
+        <v>-3.0447870778267241E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1461,11 +1477,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>2.8406569019085599</v>
+        <v>5.39490720759603</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>0.10226364846870815</v>
+        <v>0.19421665947345709</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,11 +1492,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>2.52941176470588</v>
+        <v>-1.66379804934021</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>8.5241176470588154E-2</v>
+        <v>-5.6069994262765085E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,11 +1507,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-1.7277125086385601</v>
+        <v>0.140646976090014</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-4.630269523151341E-2</v>
+        <v>3.7693389592123754E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,11 +1522,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>0.37197768133911902</v>
+        <v>0.55589870290302601</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>9.59702417854927E-3</v>
+        <v>1.4342186534898072E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1521,11 +1537,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-0.70977917981072502</v>
+        <v>-1.98570293884034</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7389589905362764E-2</v>
+        <v>-4.8649722001588333E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,11 +1552,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>-4.2063492063492003</v>
+        <v>-5.5509527754763797</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-8.6230158730158588E-2</v>
+        <v>-0.11379453189726578</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1551,11 +1567,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-1.5539305301645301</v>
+        <v>-3.0640668523676799</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-2.6882998171846372E-2</v>
+        <v>-5.3008356545960859E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,11 +1582,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>3.0303030303030298</v>
+        <v>0.31796502384737602</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>4.9696969696969691E-2</v>
+        <v>5.2146263910969656E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1581,11 +1597,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>2.7151935297515801</v>
+        <v>0.22497187851518499</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>4.3986135181975604E-2</v>
+        <v>3.6445444319459968E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1596,11 +1612,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>1.78100263852242</v>
+        <v>-0.90732339598185296</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>2.6358839050131814E-2</v>
+        <v>-1.3428386260531423E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,11 +1627,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>2.9665071770334901</v>
+        <v>-2.32342007434944</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>4.1531100478468863E-2</v>
+        <v>-3.2527881040892159E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1626,11 +1642,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>1.1184544992374099</v>
+        <v>3.5696329813976799</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>1.4539908490086328E-2</v>
+        <v>4.6405228758169839E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1641,11 +1657,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>2.1800947867298501</v>
+        <v>-1.0204081632652999</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>2.7469194312796111E-2</v>
+        <v>-1.2857142857142779E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,11 +1672,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>3.0492572322126601</v>
+        <v>-1.5933232169954401</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>3.6591086786551916E-2</v>
+        <v>-1.9119878603945279E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1671,11 +1687,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>0.34013605442176797</v>
+        <v>-6.7796610169491497E-2</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>2.4829931972789061E-3</v>
+        <v>-4.9491525423728787E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1686,11 +1702,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>1.46871008939974</v>
+        <v>-1.51038388923851</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>1.0427841634738153E-2</v>
+        <v>-1.0723725613593421E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1701,11 +1717,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.37359900373598998</v>
+        <v>2.25</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.2042341220423409E-3</v>
+        <v>1.3274999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1716,11 +1732,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>2.3529411764705799</v>
+        <v>-1.14942528735632</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>1.317647058823525E-2</v>
+        <v>-6.436781609195392E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1731,11 +1747,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>3.85338345864661</v>
+        <v>4.1628959276018103</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>1.5413533834586442E-2</v>
+        <v>1.6651583710407244E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,11 +1762,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>4.2307692307692299</v>
+        <v>1.37058513442277</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>1.6499999999999997E-2</v>
+        <v>5.3452820242488033E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1761,11 +1777,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.3785180930499701</v>
+        <v>1.4560279557367499</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9626651349798925E-3</v>
+        <v>5.2417006406522996E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,11 +1792,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>1.9546520719311899</v>
+        <v>1.22699386503067</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>6.6458170445660462E-3</v>
+        <v>4.171779141104278E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1791,11 +1807,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>0.229885057471264</v>
+        <v>0.34403669724770602</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>7.816091954022977E-4</v>
+        <v>1.1697247706422005E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1806,11 +1822,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>2.8776978417266101</v>
+        <v>-0.69930069930069905</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>9.496402877697813E-3</v>
+        <v>-2.307692307692307E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1821,11 +1837,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>4.4529961517317203</v>
+        <v>1.73684210526315</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>1.1577789994502471E-2</v>
+        <v>4.5157894736841901E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1836,11 +1852,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.3364485981308398</v>
+        <v>-4.3062200956937797</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-4.2056074766355115E-3</v>
+        <v>-7.751196172248803E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1851,11 +1867,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>-0.59491617090319004</v>
+        <v>0.48966267682263298</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-7.1389940508382807E-4</v>
+        <v>5.8759521218715955E-4</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1866,11 +1882,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-0.20689655172413701</v>
+        <v>-0.414651002073255</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4482758620689592E-4</v>
+        <v>-2.9025570145127852E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1881,11 +1897,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>2.5552825552825502</v>
+        <v>0.57498802108289404</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>1.2776412776412751E-3</v>
+        <v>2.8749401054144701E-4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1896,11 +1912,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>5.0906963136336998</v>
+        <v>9.96659242761692</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>2.0362785254534801E-3</v>
+        <v>3.9866369710467682E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1911,11 +1927,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>0.87929656274979995</v>
+        <v>7.2107765451664001</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>3.5171862509991996E-4</v>
+        <v>2.8843106180665599E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1926,11 +1942,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>2.22496909765142</v>
+        <v>4.2321644498186197</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>6.6749072929542597E-3</v>
+        <v>1.269649334945586E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1941,11 +1957,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>-10.41</v>
+        <v>0.32</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>-0.86715299999999995</v>
+        <v>2.6655999999999999E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1956,11 +1972,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-4.42</v>
+        <v>5.48</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-0.36553399999999997</v>
+        <v>0.45319599999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,7 +2004,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>8.507323269403505E-2</v>
+        <v>0.61107845805771988</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2193,12 +2209,22 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
-      <c r="B65" s="29"/>
+      <c r="A65" s="18">
+        <v>46239</v>
+      </c>
+      <c r="B65" s="29">
+        <v>14301</v>
+      </c>
       <c r="C65" s="29"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="24"/>
+      <c r="D65" s="21">
+        <v>50985089717</v>
+      </c>
+      <c r="E65" s="21">
+        <v>-1176645528</v>
+      </c>
+      <c r="F65" s="24">
+        <v>4.1000000000000003E-3</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
@@ -2330,6 +2356,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2339,26 +2385,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2398,11 +2424,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>8.8014981273408193</v>
+        <v>-5.5077452667814102</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.84934456928838908</v>
+        <v>-0.53149741824440611</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2413,11 +2439,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>0.24142926122646</v>
+        <v>4.04624277456647</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>2.2428778367938135E-2</v>
+        <v>0.37589595375722501</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2428,11 +2454,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9678456591639808</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.92102893890675186</v>
+        <v>0.92400000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2443,11 +2469,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-1.7277125086385601</v>
+        <v>0.140646976090014</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.10521769177608829</v>
+        <v>8.5654008438818523E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2458,11 +2484,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>9.5808383233532908</v>
+        <v>-9.9726775956284097</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>0.45317365269461068</v>
+        <v>-0.47170765027322381</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2473,11 +2499,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>5.3254437869822402</v>
+        <v>1.6292134831460601</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.24071005917159724</v>
+        <v>7.3640449438201902E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2488,11 +2514,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>2.8406569019085599</v>
+        <v>5.39490720759603</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>9.6582334664891037E-2</v>
+        <v>0.18342684505826501</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2503,11 +2529,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>2.1293375394321701</v>
+        <v>-3.01158301158301</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>5.8130914826498244E-2</v>
+        <v>-8.2216216216216165E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2518,11 +2544,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>-4.2063492063492003</v>
+        <v>-5.5509527754763797</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-9.6746031746031594E-2</v>
+        <v>-0.12767191383595672</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2533,11 +2559,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>2.9665071770334901</v>
+        <v>-2.32342007434944</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>4.9540669856459288E-2</v>
+        <v>-3.8801115241635646E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2548,11 +2574,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-1.5539305301645301</v>
+        <v>-3.0640668523676799</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4552102376599577E-2</v>
+        <v>-4.8412256267409345E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2563,11 +2589,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>0.37197768133911902</v>
+        <v>0.55589870290302601</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>5.8400495970241688E-3</v>
+        <v>8.7276096355775098E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2578,11 +2604,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>3.1818181818181799</v>
+        <v>-0.807635829662261</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>3.5954545454545433E-2</v>
+        <v>-9.1262848751835473E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2593,11 +2619,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>2.52941176470588</v>
+        <v>-1.66379804934021</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>2.6052941176470563E-2</v>
+        <v>-1.7137119908204164E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2608,11 +2634,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>3.0303030303030298</v>
+        <v>0.31796502384737602</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>2.9696969696969694E-2</v>
+        <v>3.1160572337042849E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2623,11 +2649,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>2.5477707006369399</v>
+        <v>-7.2981366459627299</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>2.2165605095541378E-2</v>
+        <v>-6.3493788819875746E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2638,11 +2664,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>2.3529411764705799</v>
+        <v>-1.14942528735632</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>1.3882352941176422E-2</v>
+        <v>-6.7816091954022873E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2653,11 +2679,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>2.5552825552825502</v>
+        <v>0.57498802108289404</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>1.2776412776412751E-2</v>
+        <v>2.87494010541447E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2668,11 +2694,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>3.85338345864661</v>
+        <v>4.1628959276018103</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>1.8496240601503729E-2</v>
+        <v>1.9981900452488689E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2683,11 +2709,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>2.1800947867298501</v>
+        <v>-1.0204081632652999</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>9.1563981042653703E-3</v>
+        <v>-4.285714285714259E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2698,11 +2724,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>2.23741454319453</v>
+        <v>-1.27659574468085</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>8.9496581727781209E-3</v>
+        <v>-5.1063829787234005E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2713,11 +2739,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>1.46871008939974</v>
+        <v>-1.51038388923851</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>5.5810983397190121E-3</v>
+        <v>-5.7394587791063378E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,11 +2754,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>4.4529961517317203</v>
+        <v>1.73684210526315</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>1.1132490379329301E-2</v>
+        <v>4.3421052631578746E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2743,11 +2769,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-8.2819383259911792</v>
+        <v>-9.9903938520653206</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0704845814977949E-2</v>
+        <v>-2.4975984630163303E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2758,11 +2784,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>1.9546520719311899</v>
+        <v>1.22699386503067</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>4.6911649726348557E-3</v>
+        <v>2.9447852760736077E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2773,11 +2799,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0.34013605442176797</v>
+        <v>-6.7796610169491497E-2</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>7.8231292517006638E-4</v>
+        <v>-1.5593220338983043E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2788,11 +2814,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>2.6392961876832799</v>
+        <v>1.1428571428571399</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>5.2785923753665594E-3</v>
+        <v>2.2857142857142798E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2803,11 +2829,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>5.0906963136336998</v>
+        <v>9.96659242761692</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>4.0725570509069602E-3</v>
+        <v>7.9732739420935363E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2818,11 +2844,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.20689655172413701</v>
+        <v>-0.414651002073255</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0689655172413702E-5</v>
+        <v>-4.14651002073255E-5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2833,11 +2859,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>-10.41</v>
+        <v>0.32</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-0.83175900000000003</v>
+        <v>2.5568E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2848,11 +2874,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-4.42</v>
+        <v>5.48</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-0.34033999999999998</v>
+        <v>0.42196000000000006</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2908,11 +2934,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-7.7999999999999999E-5</v>
+        <v>9.5999999999999989E-5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2925,7 +2951,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>-0.29625693174542367</v>
+        <v>0.68801872443697987</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3130,12 +3156,22 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
-      <c r="B63" s="29"/>
+      <c r="A63" s="18">
+        <v>46239</v>
+      </c>
+      <c r="B63" s="29">
+        <v>69071</v>
+      </c>
       <c r="C63" s="29"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="24"/>
+      <c r="D63" s="21">
+        <v>26446162886</v>
+      </c>
+      <c r="E63" s="21">
+        <v>-148518068</v>
+      </c>
+      <c r="F63" s="24">
+        <v>1.43E-2</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
@@ -3867,6 +3903,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3880,97 +4007,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4011,11 +4047,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>-0.64896755162241804</v>
+        <v>1.5439429928741</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.34233038348082551</v>
+        <v>0.81442992874108766</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4026,11 +4062,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-3.6697247706421998</v>
+        <v>-0.952380952380952</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.40807339449541258</v>
+        <v>-0.10590476190476185</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4041,11 +4077,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.9201824401368306</v>
+        <v>-10</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-5.2576966932725205E-2</v>
+        <v>-5.3000000000000005E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4056,11 +4092,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>0.81</v>
+        <v>-0.41</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.24154200000000003</v>
+        <v>-0.12226199999999998</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4074,7 +4110,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>-0.56143874490896317</v>
+        <v>0.5332631668363258</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4288,12 +4324,22 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="23"/>
-      <c r="B41" s="29"/>
+      <c r="A41" s="23">
+        <v>46239</v>
+      </c>
+      <c r="B41" s="29">
+        <v>51200</v>
+      </c>
       <c r="C41" s="29"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="24"/>
+      <c r="D41" s="21">
+        <v>32440313296</v>
+      </c>
+      <c r="E41" s="21">
+        <v>642330037</v>
+      </c>
+      <c r="F41" s="24">
+        <v>-2.8999999999999998E-3</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
@@ -5097,6 +5143,107 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5109,107 +5256,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5249,11 +5295,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>-0.132100396301188</v>
+        <v>-0.79365079365079305</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-1.2073976221928583E-2</v>
+        <v>-7.2539682539682487E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5264,11 +5310,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>0.829875518672199</v>
+        <v>0.12345679012345601</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>6.7800829875518651E-2</v>
+        <v>1.0086419753086355E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5279,11 +5325,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>0.34013605442176797</v>
+        <v>-6.7796610169491497E-2</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>2.7619047619047557E-2</v>
+        <v>-5.5050847457627098E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5294,11 +5340,11 @@
         <v>6.99</v>
       </c>
       <c r="C5" s="3">
-        <v>2.54500310366232</v>
+        <v>8.4140435835351006</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.17789571694599615</v>
+        <v>0.58814164648910361</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5309,11 +5355,11 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>-4.2063492063492003</v>
+        <v>-5.5509527754763797</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.25196031746031711</v>
+        <v>-0.33250207125103515</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5339,11 +5385,11 @@
         <v>4.46</v>
       </c>
       <c r="C8" s="27">
-        <v>-0.37359900373598998</v>
+        <v>2.25</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6662515566625152E-2</v>
+        <v>0.10034999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5354,11 +5400,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>7.5987841945288695E-2</v>
+        <v>9.9468488990129007</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>3.1686930091185382E-3</v>
+        <v>0.41478359908883794</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5369,11 +5415,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.59491617090319004</v>
+        <v>0.48966267682263298</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-1.9215792320173036E-2</v>
+        <v>1.5816104461371047E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5384,11 +5430,11 @@
         <v>2.84</v>
       </c>
       <c r="C11" s="3">
-        <v>2.1293375394321701</v>
+        <v>-3.01158301158301</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>6.047318611987363E-2</v>
+        <v>-8.5528957528957492E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5399,11 +5445,11 @@
         <v>2.54</v>
       </c>
       <c r="C12" s="28">
-        <v>1.46871008939974</v>
+        <v>-1.51038388923851</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>3.7305236270753397E-2</v>
+        <v>-3.8363750786658157E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5414,11 +5460,11 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8406569019085599</v>
+        <v>5.39490720759603</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>6.7323568575232876E-2</v>
+        <v>0.12785930082002592</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5444,11 +5490,11 @@
         <v>2.21</v>
       </c>
       <c r="C15" s="27">
-        <v>2.5552825552825502</v>
+        <v>0.57498802108289404</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>5.6471744471744356E-2</v>
+        <v>1.2707235265931958E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5459,11 +5505,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>4.4529961517317203</v>
+        <v>1.73684210526315</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>8.5942825728422198E-2</v>
+        <v>3.3521052631578792E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5474,11 +5520,11 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>2.7151935297515801</v>
+        <v>0.22497187851518499</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>4.8058925476602968E-2</v>
+        <v>3.9820022497187744E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5504,11 +5550,11 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>-0.70977917981072502</v>
+        <v>-1.98570293884034</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>-1.0717665615141947E-2</v>
+        <v>-2.9984114376489134E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5549,11 +5595,11 @@
         <v>1.43</v>
       </c>
       <c r="C22" s="3">
-        <v>1.1184544992374099</v>
+        <v>3.5696329813976799</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>1.5993899339094963E-2</v>
+        <v>5.1045751633986815E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5564,11 +5610,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>2.3529411764705799</v>
+        <v>-1.14942528735632</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>3.3411764705882231E-2</v>
+        <v>-1.6321839080459744E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5579,11 +5625,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>3.1818181818181799</v>
+        <v>-0.807635829662261</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>4.4545454545454513E-2</v>
+        <v>-1.1306901615271654E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5594,11 +5640,11 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>1.78100263852242</v>
+        <v>-0.90732339598185296</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>2.3687335092348188E-2</v>
+        <v>-1.2067401166558644E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5624,11 +5670,11 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>2.9665071770334901</v>
+        <v>-2.32342007434944</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>3.4708133971291827E-2</v>
+        <v>-2.7184014869888445E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5684,11 +5730,11 @@
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>2.8776978417266101</v>
+        <v>-0.69930069930069905</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>2.3597122302158203E-2</v>
+        <v>-5.7342657342657321E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5699,11 +5745,11 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>3.0492572322126601</v>
+        <v>-1.5933232169954401</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>2.4394057857701282E-2</v>
+        <v>-1.2746585735963522E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5729,11 +5775,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>-1.97647058823529</v>
+        <v>1.77628420547287</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>-1.5021176470588204E-2</v>
+        <v>1.3499759961593812E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5744,11 +5790,11 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>3.0303030303030298</v>
+        <v>0.31796502384737602</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>2.2121212121212118E-2</v>
+        <v>2.3211446740858451E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5987,7 +6033,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>0.5643323103726795</v>
+        <v>0.75979434759832787</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -6171,7 +6217,22 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F72" s="24"/>
+      <c r="A72" s="23">
+        <v>46239</v>
+      </c>
+      <c r="B72" s="29">
+        <v>20393</v>
+      </c>
+      <c r="C72" s="29"/>
+      <c r="D72" s="21">
+        <v>2081639950</v>
+      </c>
+      <c r="E72" s="21">
+        <v>54568901</v>
+      </c>
+      <c r="F72" s="24">
+        <v>1.4200000000000001E-2</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F73" s="24"/>
@@ -6198,7 +6259,8 @@
       <c r="F80" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="B70:C70"/>
     <mergeCell ref="B68:C68"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A2600-B466-422B-8D48-1D26CA4CDF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4EBD8B-4AD8-4938-B7A6-4C8C4B6CC284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36045" yWindow="195" windowWidth="14505" windowHeight="20790" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17430" yWindow="1590" windowWidth="16500" windowHeight="18180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -1309,7 +1309,22 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42" s="24"/>
+      <c r="A42" s="18">
+        <v>46240</v>
+      </c>
+      <c r="B42" s="29">
+        <v>98383</v>
+      </c>
+      <c r="C42" s="29"/>
+      <c r="D42" s="25">
+        <v>243191073731</v>
+      </c>
+      <c r="E42" s="22">
+        <v>5542399816</v>
+      </c>
+      <c r="F42" s="24">
+        <v>3.1800000000000002E-2</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F43" s="24"/>
@@ -1318,12 +1333,8 @@
       <c r="F44" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
+  <mergeCells count="14">
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
@@ -1332,6 +1343,11 @@
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
@@ -2227,12 +2243,22 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
-      <c r="B66" s="29"/>
+      <c r="A66" s="18">
+        <v>46240</v>
+      </c>
+      <c r="B66" s="29">
+        <v>138786</v>
+      </c>
       <c r="C66" s="29"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="24"/>
+      <c r="D66" s="21">
+        <v>46572819665</v>
+      </c>
+      <c r="E66" s="21">
+        <v>-4303178237</v>
+      </c>
+      <c r="F66" s="24">
+        <v>-2.0999999999999999E-3</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
@@ -2356,26 +2382,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2385,6 +2391,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3174,12 +3200,22 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="18"/>
-      <c r="B64" s="29"/>
+      <c r="A64" s="18">
+        <v>46240</v>
+      </c>
+      <c r="B64" s="29">
+        <v>68911</v>
+      </c>
       <c r="C64" s="29"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="24"/>
+      <c r="D64" s="21">
+        <v>26257978960</v>
+      </c>
+      <c r="E64" s="21">
+        <v>-4303178237</v>
+      </c>
+      <c r="F64" s="24">
+        <v>-1.7899999999999999E-2</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
@@ -3903,97 +3939,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -4007,6 +3952,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4342,12 +4378,22 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-      <c r="B42" s="29"/>
+      <c r="A42" s="23">
+        <v>46240</v>
+      </c>
+      <c r="B42" s="29">
+        <v>51726</v>
+      </c>
       <c r="C42" s="29"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="24"/>
+      <c r="D42" s="21">
+        <v>34436195517</v>
+      </c>
+      <c r="E42" s="21">
+        <v>1878923846</v>
+      </c>
+      <c r="F42" s="24">
+        <v>3.5999999999999999E-3</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
@@ -5143,107 +5189,6 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5256,6 +5201,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6235,7 +6281,22 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F73" s="24"/>
+      <c r="A73" s="23">
+        <v>46240</v>
+      </c>
+      <c r="B73" s="29">
+        <v>20807</v>
+      </c>
+      <c r="C73" s="29"/>
+      <c r="D73" s="21">
+        <v>2244184283</v>
+      </c>
+      <c r="E73" s="21">
+        <v>134383884</v>
+      </c>
+      <c r="F73" s="24">
+        <v>1.35E-2</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F74" s="24"/>
@@ -6259,18 +6320,19 @@
       <c r="F80" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
     <mergeCell ref="B72:C72"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="B70:C70"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4EBD8B-4AD8-4938-B7A6-4C8C4B6CC284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E22626A-CD77-409D-9EAF-54ABEC832E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17430" yWindow="1590" windowWidth="16500" windowHeight="18180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35250" yWindow="225" windowWidth="12525" windowHeight="20655" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -810,11 +810,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>0.55589870290302601</v>
+        <v>4.4226044226044197</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.12702285361334145</v>
+        <v>1.0105651105651099</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,11 +825,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>8.4140435835351006</v>
+        <v>5.58347292015633E-2</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>1.2032082324455196</v>
+        <v>7.9843662758235529E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,11 +840,11 @@
         <v>8.14</v>
       </c>
       <c r="C4" s="3">
-        <v>-6.7796610169491497E-2</v>
+        <v>0.135685210312076</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>-5.5186440677966082E-3</v>
+        <v>1.1044776119402988E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,11 +855,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.12345679012345601</v>
+        <v>1.0275380189066901</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>8.814814814814758E-3</v>
+        <v>7.3366214549937664E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,11 +870,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>1.73684210526315</v>
+        <v>-4.2938437661665798</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.11515263157894685</v>
+        <v>-0.28468184169684424</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,11 +885,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>0.48966267682263298</v>
+        <v>2.27395776935571</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>2.747007616974971E-2</v>
+        <v>0.12756903086085536</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -900,11 +900,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>-5.5509527754763797</v>
+        <v>6.9298245614034997</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-0.11046396023197996</v>
+        <v>0.13790350877192964</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,11 +915,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>1.77628420547287</v>
+        <v>1.88679245283018</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>1.847335573691785E-2</v>
+        <v>1.9622641509433873E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,11 +930,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>2.25</v>
+        <v>2.6894865525672298</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>1.2150000000000001E-2</v>
+        <v>1.4523227383863042E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,11 +945,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>9.9468488990129007</v>
+        <v>0.96685082872928096</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>5.1723614274867089E-2</v>
+        <v>5.0276243093922614E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -960,11 +960,11 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="C12" s="3">
-        <v>9.92382564536606</v>
+        <v>-9.9903753609239594</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>2.778671180702497E-2</v>
+        <v>-2.7973051010587092E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -975,11 +975,11 @@
         <v>0.27</v>
       </c>
       <c r="C13" s="3">
-        <v>-9.9726775956284097</v>
+        <v>-9.9393019726858807</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6926229508196706E-2</v>
+        <v>-2.683611532625188E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,11 +990,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>-0.79365079365079305</v>
+        <v>2</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1111111111111105E-3</v>
+        <v>2.8000000000000004E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1005,11 +1005,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C15" s="3">
-        <v>-1.14942528735632</v>
+        <v>0</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-8.04597701149424E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,11 +1020,11 @@
         <v>1.27</v>
       </c>
       <c r="C16" s="3">
-        <v>1.81</v>
+        <v>-0.7</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>2.2987E-2</v>
+        <v>-8.8899999999999986E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>1.469964747820949</v>
+        <v>1.0620254923120651</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1388,11 +1388,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>4.04624277456647</v>
+        <v>3.0092592592592502</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.36092485549132908</v>
+        <v>0.26842592592592512</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1403,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>-5.5077452667814102</v>
+        <v>-2.00364298724954</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>-0.48523235800344222</v>
+        <v>-0.17652094717668448</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,11 +1433,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>1.6292134831460601</v>
+        <v>-1.6030956329463699</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.1005224719101119</v>
+        <v>-9.891100055279102E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,11 +1448,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>-9.9726775956284097</v>
+        <v>-9.9393019726858807</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47370218579234946</v>
+        <v>-0.47211684370257934</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,11 +1463,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-3.01158301158301</v>
+        <v>-0.87579617834394896</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13311196911196904</v>
+        <v>-3.8710191082802548E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,11 +1478,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-0.807635829662261</v>
+        <v>-0.66617320503330801</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-3.0447870778267241E-2</v>
+        <v>-2.5114729829755711E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,11 +1493,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>5.39490720759603</v>
+        <v>1.22850122850122</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>0.19421665947345709</v>
+        <v>4.4226044226043919E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,11 +1508,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-1.66379804934021</v>
+        <v>-0.70011668611435196</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-5.6069994262765085E-2</v>
+        <v>-2.3593932322053663E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1523,11 +1523,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>0.140646976090014</v>
+        <v>-5.1966292134831402</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.7693389592123754E-3</v>
+        <v>-0.13926966292134815</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,11 +1538,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>0.55589870290302601</v>
+        <v>4.4226044226044197</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>1.4342186534898072E-2</v>
+        <v>0.11410319410319403</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,11 +1553,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-1.98570293884034</v>
+        <v>-8.1037277147487805E-2</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-4.8649722001588333E-2</v>
+        <v>-1.9854132901134512E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1568,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>-5.5509527754763797</v>
+        <v>6.9298245614034997</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-0.11379453189726578</v>
+        <v>0.14206140350877175</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,11 +1583,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-3.0640668523676799</v>
+        <v>-2.3946360153256698</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-5.3008356545960859E-2</v>
+        <v>-4.1427203065134088E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,11 +1598,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>0.31796502384737602</v>
+        <v>-0.79239302694136304</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>5.2146263910969656E-3</v>
+        <v>-1.2995245641838354E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,11 +1613,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>0.22497187851518499</v>
+        <v>-1.1223344556677799</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>3.6445444319459968E-3</v>
+        <v>-1.8181818181818035E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1628,11 +1628,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-0.90732339598185296</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-1.3428386260531423E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1643,11 +1643,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-2.32342007434944</v>
+        <v>0.19029495718363401</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-3.2527881040892159E-2</v>
+        <v>2.6641294005708758E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1658,11 +1658,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>3.5696329813976799</v>
+        <v>-4.9029126213592198</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>4.6405228758169839E-2</v>
+        <v>-6.3737864077669862E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,11 +1673,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>-1.0204081632652999</v>
+        <v>0.28116213683223901</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2857142857142779E-2</v>
+        <v>3.5426429240862116E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,11 +1688,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>-1.5933232169954401</v>
+        <v>-1.4649190439475701</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9119878603945279E-2</v>
+        <v>-1.7579028527370841E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1703,11 +1703,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>-6.7796610169491497E-2</v>
+        <v>0.135685210312076</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9491525423728787E-4</v>
+        <v>9.9050203527815484E-4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1718,11 +1718,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-1.51038388923851</v>
+        <v>-1.15015974440894</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0723725613593421E-2</v>
+        <v>-8.1661341853034725E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1733,11 +1733,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>2.25</v>
+        <v>2.6894865525672298</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>1.3274999999999999E-2</v>
+        <v>1.5867970660146655E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,11 +1748,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-1.14942528735632</v>
+        <v>0</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-6.436781609195392E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1763,11 +1763,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>4.1628959276018103</v>
+        <v>1.30321459600347</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>1.6651583710407244E-2</v>
+        <v>5.2128583840138796E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1778,11 +1778,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>1.37058513442277</v>
+        <v>5.2002080083203298E-2</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>5.3452820242488033E-3</v>
+        <v>2.0280811232449287E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,11 +1793,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>1.4560279557367499</v>
+        <v>-1.4351320321469501</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>5.2417006406522996E-3</v>
+        <v>-5.1664753157290196E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,11 +1808,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>1.22699386503067</v>
+        <v>3.0303030303030298</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>4.171779141104278E-3</v>
+        <v>1.0303030303030303E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,11 +1823,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>0.34403669724770602</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>1.1697247706422005E-3</v>
+        <v>1.9428571428571414E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1838,11 +1838,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>-0.69930069930069905</v>
+        <v>-3.6971830985915402</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-2.307692307692307E-3</v>
+        <v>-1.2200704225352084E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1853,11 +1853,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>1.73684210526315</v>
+        <v>-4.2938437661665798</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>4.5157894736841901E-3</v>
+        <v>-1.116399379203311E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1868,11 +1868,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-4.3062200956937797</v>
+        <v>-1</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-7.751196172248803E-3</v>
+        <v>-1.8E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1883,11 +1883,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>0.48966267682263298</v>
+        <v>2.27395776935571</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>5.8759521218715955E-4</v>
+        <v>2.7287493232268519E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1898,11 +1898,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-0.414651002073255</v>
+        <v>0.62456627342123505</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9025570145127852E-4</v>
+        <v>4.3719639139486454E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1913,11 +1913,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>0.57498802108289404</v>
+        <v>-1.0004764173415901</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>2.8749401054144701E-4</v>
+        <v>-5.0023820867079512E-4</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1928,11 +1928,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>9.96659242761692</v>
+        <v>9.9746835443037902</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>3.9866369710467682E-3</v>
+        <v>3.9898734177215159E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1943,11 +1943,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>7.2107765451664001</v>
+        <v>0.44345898004434497</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>2.8843106180665599E-3</v>
+        <v>1.7738359201773798E-4</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1958,11 +1958,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>4.2321644498186197</v>
+        <v>0.40603248259860703</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>1.269649334945586E-2</v>
+        <v>1.2180974477958211E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1973,11 +1973,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>0.32</v>
+        <v>4.3</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>2.6655999999999999E-2</v>
+        <v>0.35818999999999995</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,11 +1988,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>5.48</v>
+        <v>-0.82</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>0.45319599999999999</v>
+        <v>-6.7813999999999999E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>0.61107845805771988</v>
+        <v>0.57065724079935132</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2382,6 +2382,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2391,26 +2411,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2450,11 +2450,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>-5.5077452667814102</v>
+        <v>-2.00364298724954</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.53149741824440611</v>
+        <v>-0.19335154826958059</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2465,11 +2465,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>4.04624277456647</v>
+        <v>3.0092592592592502</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>0.37589595375722501</v>
+        <v>0.27956018518518433</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2495,11 +2495,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>0.140646976090014</v>
+        <v>-5.1966292134831402</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>8.5654008438818523E-3</v>
+        <v>-0.31647471910112324</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2510,11 +2510,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>-9.9726775956284097</v>
+        <v>-9.9393019726858807</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47170765027322381</v>
+        <v>-0.4701289833080422</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2525,11 +2525,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>1.6292134831460601</v>
+        <v>-1.6030956329463699</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>7.3640449438201902E-2</v>
+        <v>-7.2459922609175914E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2540,11 +2540,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>5.39490720759603</v>
+        <v>1.22850122850122</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.18342684505826501</v>
+        <v>4.1769041769041476E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2555,11 +2555,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-3.01158301158301</v>
+        <v>-0.87579617834394896</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-8.2216216216216165E-2</v>
+        <v>-2.3909235668789806E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2570,11 +2570,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>-5.5509527754763797</v>
+        <v>6.9298245614034997</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12767191383595672</v>
+        <v>0.15938596491228049</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2585,11 +2585,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-2.32342007434944</v>
+        <v>0.19029495718363401</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8801115241635646E-2</v>
+        <v>3.1779257849666883E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2600,11 +2600,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-3.0640668523676799</v>
+        <v>-2.3946360153256698</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-4.8412256267409345E-2</v>
+        <v>-3.7835249042145587E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2615,11 +2615,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>0.55589870290302601</v>
+        <v>4.4226044226044197</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>8.7276096355775098E-3</v>
+        <v>6.9434889434889388E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2630,11 +2630,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-0.807635829662261</v>
+        <v>-0.66617320503330801</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-9.1262848751835473E-3</v>
+        <v>-7.5277572168763792E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2645,11 +2645,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-1.66379804934021</v>
+        <v>-0.70011668611435196</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7137119908204164E-2</v>
+        <v>-7.2112018669778259E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2660,11 +2660,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>0.31796502384737602</v>
+        <v>-0.79239302694136304</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>3.1160572337042849E-3</v>
+        <v>-7.7654516640253577E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2675,11 +2675,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-7.2981366459627299</v>
+        <v>4.6901172529313202</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3493788819875746E-2</v>
+        <v>4.0804020100502492E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2690,11 +2690,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.14942528735632</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-6.7816091954022873E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2705,11 +2705,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>0.57498802108289404</v>
+        <v>-1.0004764173415901</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>2.87494010541447E-3</v>
+        <v>-5.0023820867079504E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2720,11 +2720,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>4.1628959276018103</v>
+        <v>1.30321459600347</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>1.9981900452488689E-2</v>
+        <v>6.2554300608166557E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2735,11 +2735,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>-1.0204081632652999</v>
+        <v>0.28116213683223901</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-4.285714285714259E-3</v>
+        <v>1.1808809746954039E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2750,11 +2750,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-1.27659574468085</v>
+        <v>-1.47783251231527</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-5.1063829787234005E-3</v>
+        <v>-5.9113300492610798E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2765,11 +2765,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-1.51038388923851</v>
+        <v>-1.15015974440894</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-5.7394587791063378E-3</v>
+        <v>-4.3706070287539726E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2780,11 +2780,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>1.73684210526315</v>
+        <v>-4.2938437661665798</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>4.3421052631578746E-3</v>
+        <v>-1.073460941541645E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2795,11 +2795,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-9.9903938520653206</v>
+        <v>-9.9252934898612502</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4975984630163303E-2</v>
+        <v>-2.4813233724653126E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2810,11 +2810,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>1.22699386503067</v>
+        <v>3.0303030303030298</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>2.9447852760736077E-3</v>
+        <v>7.2727272727272719E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2825,11 +2825,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>-6.7796610169491497E-2</v>
+        <v>0.135685210312076</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5593220338983043E-4</v>
+        <v>3.1207598371777481E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2840,11 +2840,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>1.1428571428571399</v>
+        <v>-0.35310734463276799</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>2.2857142857142798E-3</v>
+        <v>-7.0621468926553607E-4</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2855,11 +2855,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>9.96659242761692</v>
+        <v>9.9746835443037902</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>7.9732739420935363E-3</v>
+        <v>7.9797468354430318E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2870,11 +2870,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.414651002073255</v>
+        <v>0.62456627342123505</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-4.14651002073255E-5</v>
+        <v>6.2456627342123507E-5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2885,11 +2885,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>0.32</v>
+        <v>4.3</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>2.5568E-2</v>
+        <v>0.34356999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2900,11 +2900,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>5.48</v>
+        <v>-0.82</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>0.42196000000000006</v>
+        <v>-6.3140000000000002E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2945,11 +2945,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>9.57</v>
+        <v>-9.83</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>5.5506E-2</v>
+        <v>-5.7013999999999995E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,11 +2960,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>0.16</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>9.5999999999999989E-5</v>
+        <v>1.4940000000000001E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>0.68801872443697987</v>
+        <v>0.58216689920081222</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3939,6 +3939,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3952,97 +4043,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4083,11 +4083,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>1.5439429928741</v>
+        <v>0.87719298245613997</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.81442992874108766</v>
+        <v>0.46271929824561381</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4098,11 +4098,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-0.952380952380952</v>
+        <v>2.33516483516483</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.10590476190476185</v>
+        <v>0.25967032967032905</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4113,11 +4113,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-10</v>
+        <v>-9.98593530239099</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-5.3000000000000005E-2</v>
+        <v>-5.2925457102672248E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4146,7 +4146,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>0.5332631668363258</v>
+        <v>0.54720217081327061</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5189,6 +5189,107 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5201,107 +5302,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5341,11 +5341,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>-0.79365079365079305</v>
+        <v>1.0275380189066901</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-7.2539682539682487E-2</v>
+        <v>9.3916974928071467E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5356,11 +5356,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>0.12345679012345601</v>
+        <v>0.135685210312076</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>1.0086419753086355E-2</v>
+        <v>1.1085481682496609E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5371,11 +5371,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>-6.7796610169491497E-2</v>
+        <v>5.58347292015633E-2</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-5.5050847457627098E-3</v>
+        <v>4.53378001116694E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5386,11 +5386,11 @@
         <v>6.99</v>
       </c>
       <c r="C5" s="3">
-        <v>8.4140435835351006</v>
+        <v>6.9298245614034997</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.58814164648910361</v>
+        <v>0.4843947368421046</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5401,11 +5401,11 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>-5.5509527754763797</v>
+        <v>-0.87</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.33250207125103515</v>
+        <v>-5.2113000000000007E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5415,12 +5415,12 @@
       <c r="B7" s="4">
         <v>4.88</v>
       </c>
-      <c r="C7" s="3">
-        <v>-0.87</v>
+      <c r="C7" s="27">
+        <v>2.6894865525672298</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-4.2455999999999994E-2</v>
+        <v>0.13124694376528082</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5430,12 +5430,12 @@
       <c r="B8" s="26">
         <v>4.46</v>
       </c>
-      <c r="C8" s="27">
-        <v>2.25</v>
+      <c r="C8" s="3">
+        <v>0.96685082872928096</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.10034999999999999</v>
+        <v>4.3121546961325932E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5446,11 +5446,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>9.9468488990129007</v>
+        <v>2.27395776935571</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>0.41478359908883794</v>
+        <v>9.482403898213311E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5461,11 +5461,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>0.48966267682263298</v>
+        <v>-0.87579617834394896</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>1.5816104461371047E-2</v>
+        <v>-2.828821656050955E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5475,12 +5475,12 @@
       <c r="B11" s="4">
         <v>2.84</v>
       </c>
-      <c r="C11" s="3">
-        <v>-3.01158301158301</v>
+      <c r="C11" s="28">
+        <v>-1.15015974440894</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-8.5528957528957492E-2</v>
+        <v>-3.266453674121389E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5490,12 +5490,12 @@
       <c r="B12" s="4">
         <v>2.54</v>
       </c>
-      <c r="C12" s="28">
-        <v>-1.51038388923851</v>
+      <c r="C12" s="3">
+        <v>1.22850122850122</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-3.8363750786658157E-2</v>
+        <v>3.1203931203930991E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5506,11 +5506,11 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>5.39490720759603</v>
+        <v>-2.9</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>0.12785930082002592</v>
+        <v>-6.8729999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5520,12 +5520,12 @@
       <c r="B14" s="26">
         <v>2.37</v>
       </c>
-      <c r="C14" s="3">
-        <v>-2.9</v>
+      <c r="C14" s="27">
+        <v>-1.0004764173415901</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-6.8729999999999999E-2</v>
+        <v>-2.3711291090995689E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5535,12 +5535,12 @@
       <c r="B15" s="26">
         <v>2.21</v>
       </c>
-      <c r="C15" s="27">
-        <v>0.57498802108289404</v>
+      <c r="C15" s="3">
+        <v>-4.2938437661665798</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>1.2707235265931958E-2</v>
+        <v>-9.4893947232281409E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5551,11 +5551,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>1.73684210526315</v>
+        <v>-1.1223344556677799</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>3.3521052631578792E-2</v>
+        <v>-2.1661054994388151E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5566,11 +5566,11 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>0.22497187851518499</v>
+        <v>-0.91</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>3.9820022497187744E-3</v>
+        <v>-1.6107E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5581,11 +5581,11 @@
         <v>1.53</v>
       </c>
       <c r="C18" s="3">
-        <v>-0.91</v>
+        <v>-8.1037277147487805E-2</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-1.3923000000000001E-2</v>
+        <v>-1.2398703403565636E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5596,11 +5596,11 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>-1.98570293884034</v>
+        <v>0.36</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>-2.9984114376489134E-2</v>
+        <v>5.4359999999999999E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5611,11 +5611,11 @@
         <v>1.44</v>
       </c>
       <c r="C20" s="3">
-        <v>0.36</v>
+        <v>-1.82</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>5.1839999999999994E-3</v>
+        <v>-2.6207999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5626,11 +5626,11 @@
         <v>1.44</v>
       </c>
       <c r="C21" s="3">
-        <v>-1.82</v>
+        <v>-4.9029126213592198</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6207999999999999E-2</v>
+        <v>-7.0601941747572769E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5640,12 +5640,12 @@
       <c r="B22" s="4">
         <v>1.43</v>
       </c>
-      <c r="C22" s="3">
-        <v>3.5696329813976799</v>
+      <c r="C22" s="27">
+        <v>0</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>5.1045751633986815E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5656,11 +5656,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>-1.14942528735632</v>
+        <v>-0.66617320503330801</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6321839080459744E-2</v>
+        <v>-9.4596595114729738E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5671,11 +5671,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>-0.807635829662261</v>
+        <v>0</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1306901615271654E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5686,11 +5686,11 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>-0.90732339598185296</v>
+        <v>4.76</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>-1.2067401166558644E-2</v>
+        <v>6.3308000000000003E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5701,11 +5701,11 @@
         <v>1.25</v>
       </c>
       <c r="C26" s="27">
-        <v>4.76</v>
+        <v>0.19029495718363401</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>5.949999999999999E-2</v>
+        <v>2.3786869647954251E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5716,11 +5716,11 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>-2.32342007434944</v>
+        <v>-1.66</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>-2.7184014869888445E-2</v>
+        <v>-1.9421999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5731,11 +5731,11 @@
         <v>1.04</v>
       </c>
       <c r="C28" s="27">
-        <v>-1.66</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7263999999999998E-2</v>
+        <v>6.0319999999999992E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5746,11 +5746,11 @@
         <v>0.9</v>
       </c>
       <c r="C29" s="27">
-        <v>0.57999999999999996</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>5.2199999999999998E-3</v>
+        <v>4.1489999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5761,11 +5761,11 @@
         <v>0.84</v>
       </c>
       <c r="C30" s="27">
-        <v>4.6100000000000003</v>
+        <v>-3.6971830985915402</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>3.8724000000000001E-2</v>
+        <v>-3.1056338028168935E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5776,11 +5776,11 @@
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>-0.69930069930069905</v>
+        <v>-1.4649190439475701</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>-5.7342657342657321E-3</v>
+        <v>-1.2012336160370073E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5791,11 +5791,11 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>-1.5933232169954401</v>
+        <v>0.76</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>-1.2746585735963522E-2</v>
+        <v>6.0800000000000012E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5806,11 +5806,11 @@
         <v>0.79</v>
       </c>
       <c r="C33" s="27">
-        <v>0.76</v>
+        <v>1.88679245283018</v>
       </c>
       <c r="D33" s="7">
         <f t="shared" si="0"/>
-        <v>6.0040000000000007E-3</v>
+        <v>1.4905660377358423E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5821,11 +5821,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>1.77628420547287</v>
+        <v>-0.79239302694136304</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>1.3499759961593812E-2</v>
+        <v>-6.0221870047543593E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5836,11 +5836,11 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>0.31796502384737602</v>
+        <v>0.78</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>2.3211446740858451E-3</v>
+        <v>5.6940000000000003E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5851,11 +5851,11 @@
         <v>0.72</v>
       </c>
       <c r="C36" s="27">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="0"/>
-        <v>5.6159999999999995E-3</v>
+        <v>4.3920000000000001E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5866,11 +5866,11 @@
         <v>0.71</v>
       </c>
       <c r="C37" s="27">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="0"/>
-        <v>4.3309999999999998E-3</v>
+        <v>5.9639999999999997E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5881,11 +5881,11 @@
         <v>0.7</v>
       </c>
       <c r="C38" s="27">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="0"/>
-        <v>5.8799999999999998E-3</v>
+        <v>6.9999999999999988E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5896,11 +5896,11 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="27">
-        <v>0.1</v>
+        <v>0.97</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="0"/>
-        <v>6.9999999999999988E-4</v>
+        <v>6.7899999999999992E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5911,11 +5911,11 @@
         <v>0.64</v>
       </c>
       <c r="C40" s="27">
-        <v>0.97</v>
+        <v>0.11</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="0"/>
-        <v>6.208E-3</v>
+        <v>7.0400000000000009E-4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5926,11 +5926,11 @@
         <v>0.63</v>
       </c>
       <c r="C41" s="27">
-        <v>0.11</v>
+        <v>4.43</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="0"/>
-        <v>6.9300000000000004E-4</v>
+        <v>2.7908999999999996E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5941,11 +5941,11 @@
         <v>0.61</v>
       </c>
       <c r="C42" s="27">
-        <v>4.43</v>
+        <v>1.82</v>
       </c>
       <c r="D42" s="7">
         <f t="shared" si="0"/>
-        <v>2.7022999999999998E-2</v>
+        <v>1.1102000000000001E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -5956,11 +5956,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C43" s="27">
-        <v>1.82</v>
+        <v>-0.05</v>
       </c>
       <c r="D43" s="7">
         <f t="shared" si="0"/>
-        <v>1.0374E-2</v>
+        <v>-2.8499999999999999E-4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -5971,11 +5971,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C44" s="27">
-        <v>-0.05</v>
+        <v>-1.91</v>
       </c>
       <c r="D44" s="7">
         <f t="shared" si="0"/>
-        <v>-2.7500000000000002E-4</v>
+        <v>-1.0505E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -5986,11 +5986,11 @@
         <v>0.5</v>
       </c>
       <c r="C45" s="27">
-        <v>-1.91</v>
+        <v>1.41</v>
       </c>
       <c r="D45" s="7">
         <f t="shared" si="0"/>
-        <v>-9.5499999999999995E-3</v>
+        <v>7.0499999999999998E-3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -6001,11 +6001,11 @@
         <v>0.5</v>
       </c>
       <c r="C46" s="27">
-        <v>1.41</v>
+        <v>0.32</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>7.0499999999999998E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -6016,11 +6016,11 @@
         <v>0.45</v>
       </c>
       <c r="C47" s="27">
-        <v>0.32</v>
+        <v>5.47</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>1.4400000000000001E-3</v>
+        <v>2.4615000000000001E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -6031,11 +6031,11 @@
         <v>0.4</v>
       </c>
       <c r="C48" s="27">
-        <v>5.47</v>
+        <v>2.52</v>
       </c>
       <c r="D48" s="7">
         <f t="shared" si="0"/>
-        <v>2.188E-2</v>
+        <v>1.008E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -6046,11 +6046,11 @@
         <v>0.33</v>
       </c>
       <c r="C49" s="27">
-        <v>2.52</v>
+        <v>-0.17</v>
       </c>
       <c r="D49" s="7">
         <f t="shared" si="0"/>
-        <v>8.3160000000000005E-3</v>
+        <v>-5.6100000000000008E-4</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -6079,7 +6079,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>0.75979434759832787</v>
+        <v>0.61474340230657964</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E22626A-CD77-409D-9EAF-54ABEC832E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AA58AE-B52C-4A6A-9BA2-A1E22E374A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35250" yWindow="225" windowWidth="12525" windowHeight="20655" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33015" yWindow="0" windowWidth="12015" windowHeight="20625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -810,11 +810,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>4.4226044226044197</v>
+        <v>4.2941176470588198</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>1.0105651105651099</v>
+        <v>0.98120588235294037</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,11 +825,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>5.58347292015633E-2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>7.9843662758235529E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,11 +840,11 @@
         <v>8.14</v>
       </c>
       <c r="C4" s="3">
-        <v>0.135685210312076</v>
+        <v>-0.40650406504065001</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>1.1044776119402988E-2</v>
+        <v>-3.3089430894308915E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,11 +855,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>1.0275380189066901</v>
+        <v>1.0984540276647601</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>7.3366214549937664E-2</v>
+        <v>7.8429617575263857E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,11 +870,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>-4.2938437661665798</v>
+        <v>0.162162162162162</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.28468184169684424</v>
+        <v>1.0751351351351341E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,11 +885,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>2.27395776935571</v>
+        <v>2.6998411858125899</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.12756903086085536</v>
+        <v>0.15146109052408629</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -900,11 +900,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>6.9298245614034997</v>
+        <v>2.4610336341263301</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.13790350877192964</v>
+        <v>4.8974569319113967E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,11 +915,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>1.88679245283018</v>
+        <v>0.32407407407407401</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>1.9622641509433873E-2</v>
+        <v>3.3703703703703695E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,11 +930,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>2.6894865525672298</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>1.4523227383863042E-2</v>
+        <v>6.4285714285714267E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,11 +945,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>0.96685082872928096</v>
+        <v>-0.68399452804377503</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>5.0276243093922614E-3</v>
+        <v>-3.5567715458276299E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -960,11 +960,11 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="C12" s="3">
-        <v>-9.9903753609239594</v>
+        <v>-5.9024807527801499</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-2.7973051010587092E-2</v>
+        <v>-1.6526946107784421E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -975,11 +975,11 @@
         <v>0.27</v>
       </c>
       <c r="C13" s="3">
-        <v>-9.9393019726858807</v>
+        <v>-9.9410278011794393</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.683611532625188E-2</v>
+        <v>-2.6840775063184486E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,11 +990,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>2</v>
+        <v>0.19607843137254899</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>2.8000000000000004E-3</v>
+        <v>2.7450980392156862E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1005,11 +1005,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C15" s="3">
-        <v>0</v>
+        <v>5.2325581395348797</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.662790697674416E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,11 +1020,11 @@
         <v>1.27</v>
       </c>
       <c r="C16" s="3">
-        <v>-0.7</v>
+        <v>1.29</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-8.8899999999999986E-3</v>
+        <v>1.6383000000000002E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>1.0620254923120651</v>
+        <v>1.2209278298121884</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1327,13 +1327,29 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F43" s="24"/>
+      <c r="A43" s="18">
+        <v>46241</v>
+      </c>
+      <c r="B43" s="29">
+        <v>99770</v>
+      </c>
+      <c r="C43" s="29"/>
+      <c r="D43" s="25">
+        <v>251321783060</v>
+      </c>
+      <c r="E43" s="22">
+        <v>6496955531</v>
+      </c>
+      <c r="F43" s="24">
+        <v>5.4000000000000003E-3</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F44" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="A29:B29"/>
@@ -1388,11 +1404,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>3.0092592592592502</v>
+        <v>-2.0674157303370699</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.26842592592592512</v>
+        <v>-0.18441348314606665</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,11 +1419,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>-2.00364298724954</v>
+        <v>2.32342007434944</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>-0.17652094717668448</v>
+        <v>0.20469330855018569</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1418,11 +1434,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>10</v>
+        <v>7.7922077922077904</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.82799999999999996</v>
+        <v>0.64519480519480499</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,11 +1449,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>-1.6030956329463699</v>
+        <v>-2.1348314606741501</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-9.891100055279102E-2</v>
+        <v>-0.13171910112359506</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1448,11 +1464,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>-9.9393019726858807</v>
+        <v>-9.9410278011794393</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47211684370257934</v>
+        <v>-0.47219882055602336</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1463,11 +1479,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-0.87579617834394896</v>
+        <v>-1.6064257028112401</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8710191082802548E-2</v>
+        <v>-7.1004016064256811E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1478,11 +1494,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-0.66617320503330801</v>
+        <v>0.44709388971684</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-2.5114729829755711E-2</v>
+        <v>1.6855439642324867E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,11 +1509,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>1.22850122850122</v>
+        <v>5.4813915857605098</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>4.4226044226043919E-2</v>
+        <v>0.19733009708737836</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,11 +1524,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-0.70011668611435196</v>
+        <v>-5.8754406580493503E-2</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3593932322053663E-2</v>
+        <v>-1.980023501762631E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1523,11 +1539,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-5.1966292134831402</v>
+        <v>-2.07407407407407</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13926966292134815</v>
+        <v>-5.5585185185185078E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,11 +1554,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>4.4226044226044197</v>
+        <v>4.2941176470588198</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>0.11410319410319403</v>
+        <v>0.11078823529411755</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,11 +1569,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-8.1037277147487805E-2</v>
+        <v>0.24330900243309</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9854132901134512E-3</v>
+        <v>5.9610705596107065E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1568,11 +1584,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>6.9298245614034997</v>
+        <v>2.4610336341263301</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>0.14206140350877175</v>
+        <v>5.0451189499589759E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1583,11 +1599,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-2.3946360153256698</v>
+        <v>1.3738959764474901</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-4.1427203065134088E-2</v>
+        <v>2.3768400392541578E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1598,11 +1614,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>-0.79239302694136304</v>
+        <v>4.5527156549520704</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2995245641838354E-2</v>
+        <v>7.4664536741213941E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,11 +1629,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>-1.1223344556677799</v>
+        <v>-5.67536889897843E-2</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-1.8181818181818035E-2</v>
+        <v>-9.1940976163450562E-4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1628,11 +1644,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>0</v>
+        <v>0.91563113145846897</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.355134074558534E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1643,11 +1659,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>0.19029495718363401</v>
+        <v>-0.189933523266856</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>2.6641294005708758E-3</v>
+        <v>-2.6590693257359838E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1658,11 +1674,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>-4.9029126213592198</v>
+        <v>1.3272077590607401</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3737864077669862E-2</v>
+        <v>1.7253700867789622E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,11 +1689,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>0.28116213683223901</v>
+        <v>1.86915887850467</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>3.5426429240862116E-3</v>
+        <v>2.3551401869158842E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1688,11 +1704,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>-1.4649190439475701</v>
+        <v>-0.62597809076682298</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7579028527370841E-2</v>
+        <v>-7.5117370892018752E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1703,11 +1719,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>0.135685210312076</v>
+        <v>-0.40650406504065001</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>9.9050203527815484E-4</v>
+        <v>-2.9674796747967453E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1718,11 +1734,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-1.15015974440894</v>
+        <v>-0.77569489334195196</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-8.1661341853034725E-3</v>
+        <v>-5.5074337427278583E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1733,11 +1749,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>2.6894865525672298</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>1.5867970660146655E-2</v>
+        <v>7.0238095238095207E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,11 +1764,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>0</v>
+        <v>5.2325581395348797</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.9302325581395328E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1763,11 +1779,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>1.30321459600347</v>
+        <v>-1.88679245283018</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>5.2128583840138796E-3</v>
+        <v>-7.5471698113207209E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1778,11 +1794,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>5.2002080083203298E-2</v>
+        <v>-4.9896049896049899</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>2.0280811232449287E-4</v>
+        <v>-1.9459459459459462E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,11 +1809,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.4351320321469501</v>
+        <v>0.58241118229470001</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-5.1664753157290196E-3</v>
+        <v>2.0966802562609201E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,11 +1824,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>3.0303030303030298</v>
+        <v>1.1029411764705801</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>1.0303030303030303E-2</v>
+        <v>3.749999999999973E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1823,11 +1839,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>0.57142857142857095</v>
+        <v>3.2954545454545401</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>1.9428571428571414E-3</v>
+        <v>1.1204545454545438E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1838,11 +1854,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>-3.6971830985915402</v>
+        <v>0.73126142595978005</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2200704225352084E-2</v>
+        <v>2.4131627056672746E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1853,11 +1869,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>-4.2938437661665798</v>
+        <v>0.162162162162162</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>-1.116399379203311E-2</v>
+        <v>4.2162162162162121E-4</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1868,11 +1884,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-1</v>
+        <v>7.0707070707070701</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-1.8E-3</v>
+        <v>1.2727272727272724E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1883,11 +1899,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>2.27395776935571</v>
+        <v>2.6998411858125899</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>2.7287493232268519E-3</v>
+        <v>3.2398094229751078E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1898,11 +1914,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>0.62456627342123505</v>
+        <v>-2.0689655172413701</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>4.3719639139486454E-4</v>
+        <v>-1.4482758620689594E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1913,11 +1929,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-1.0004764173415901</v>
+        <v>-6.9297401347449403</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-5.0023820867079512E-4</v>
+        <v>-3.4648700673724701E-3</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1928,11 +1944,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>9.9746835443037902</v>
+        <v>2.3941068139963102</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>3.9898734177215159E-3</v>
+        <v>9.5764272559852417E-4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1943,11 +1959,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>0.44345898004434497</v>
+        <v>2.6490066225165498</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>1.7738359201773798E-4</v>
+        <v>1.0596026490066199E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1958,11 +1974,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>0.40603248259860703</v>
+        <v>3.1195840554592702</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>1.2180974477958211E-3</v>
+        <v>9.3587521663778105E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1973,11 +1989,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>4.3</v>
+        <v>3.13</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>0.35818999999999995</v>
+        <v>0.26072899999999999</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,11 +2004,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-0.82</v>
+        <v>-0.09</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-6.7813999999999999E-2</v>
+        <v>-7.443E-3</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2020,7 +2036,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>0.57065724079935132</v>
+        <v>0.7558472169076238</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2261,12 +2277,22 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="18"/>
-      <c r="B67" s="29"/>
+      <c r="A67" s="18">
+        <v>46241</v>
+      </c>
+      <c r="B67" s="29">
+        <v>134555</v>
+      </c>
       <c r="C67" s="29"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="24"/>
+      <c r="D67" s="21">
+        <v>46135293160</v>
+      </c>
+      <c r="E67" s="21">
+        <v>-735791355</v>
+      </c>
+      <c r="F67" s="24">
+        <v>6.4000000000000003E-3</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
@@ -2382,26 +2408,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2411,6 +2417,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2450,11 +2476,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>-2.00364298724954</v>
+        <v>2.32342007434944</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.19335154826958059</v>
+        <v>0.22421003717472096</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2465,11 +2491,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>3.0092592592592502</v>
+        <v>-2.0674157303370699</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>0.27956018518518433</v>
+        <v>-0.19206292134831379</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2480,11 +2506,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>10</v>
+        <v>7.7922077922077904</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.92400000000000004</v>
+        <v>0.71999999999999986</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2495,11 +2521,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-5.1966292134831402</v>
+        <v>-2.07407407407407</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.31647471910112324</v>
+        <v>-0.12631111111111085</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2510,11 +2536,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>-9.9393019726858807</v>
+        <v>-9.9410278011794393</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.4701289833080422</v>
+        <v>-0.47021061499578748</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2525,11 +2551,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>-1.6030956329463699</v>
+        <v>-2.1348314606741501</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-7.2459922609175914E-2</v>
+        <v>-9.649438202247157E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2540,11 +2566,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>1.22850122850122</v>
+        <v>5.4813915857605098</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>4.1769041769041476E-2</v>
+        <v>0.18636731391585734</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2555,11 +2581,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-0.87579617834394896</v>
+        <v>-1.6064257028112401</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3909235668789806E-2</v>
+        <v>-4.3855421686746859E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2570,11 +2596,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>6.9298245614034997</v>
+        <v>2.4610336341263301</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.15938596491228049</v>
+        <v>5.6603773584905585E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2585,11 +2611,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>0.19029495718363401</v>
+        <v>-0.189933523266856</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.1779257849666883E-3</v>
+        <v>-3.1718898385564953E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2600,11 +2626,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-2.3946360153256698</v>
+        <v>1.3738959764474901</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-3.7835249042145587E-2</v>
+        <v>2.1707556427870346E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2615,11 +2641,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>4.4226044226044197</v>
+        <v>4.2941176470588198</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>6.9434889434889388E-2</v>
+        <v>6.7417647058823471E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2630,11 +2656,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-0.66617320503330801</v>
+        <v>0.44709388971684</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5277572168763792E-3</v>
+        <v>5.0521609538002913E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2645,11 +2671,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-0.70011668611435196</v>
+        <v>-5.8754406580493503E-2</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-7.2112018669778259E-3</v>
+        <v>-6.0517038777908308E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2660,11 +2686,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>-0.79239302694136304</v>
+        <v>4.5527156549520704</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-7.7654516640253577E-3</v>
+        <v>4.4616613418530286E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2675,11 +2701,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>4.6901172529313202</v>
+        <v>-2.56</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>4.0804020100502492E-2</v>
+        <v>-2.2272E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2690,11 +2716,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>0</v>
+        <v>5.2325581395348797</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.0872093023255789E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2705,11 +2731,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-1.0004764173415901</v>
+        <v>-6.9297401347449403</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-5.0023820867079504E-3</v>
+        <v>-3.4648700673724699E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2720,11 +2746,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>1.30321459600347</v>
+        <v>-1.88679245283018</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>6.2554300608166557E-3</v>
+        <v>-9.0566037735848644E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2735,11 +2761,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>0.28116213683223901</v>
+        <v>1.86915887850467</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>1.1808809746954039E-3</v>
+        <v>7.8504672897196145E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2750,11 +2776,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>-1.47783251231527</v>
+        <v>6.6875</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9113300492610798E-3</v>
+        <v>2.6750000000000003E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2765,11 +2791,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-1.15015974440894</v>
+        <v>-0.77569489334195196</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-4.3706070287539726E-3</v>
+        <v>-2.9476405946994178E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2780,11 +2806,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>-4.2938437661665798</v>
+        <v>0.162162162162162</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-1.073460941541645E-2</v>
+        <v>4.0540540540540501E-4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2795,11 +2821,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-9.9252934898612502</v>
+        <v>-8.5308056872037898</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4813233724653126E-2</v>
+        <v>-2.1327014218009473E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2810,11 +2836,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>3.0303030303030298</v>
+        <v>1.1029411764705801</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>7.2727272727272719E-3</v>
+        <v>2.6470588235293926E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2825,11 +2851,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>0.135685210312076</v>
+        <v>-0.40650406504065001</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>3.1207598371777481E-4</v>
+        <v>-9.3495934959349507E-4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2840,11 +2866,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.35310734463276799</v>
+        <v>1.34656272147413</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-7.0621468926553607E-4</v>
+        <v>2.6931254429482603E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2855,11 +2881,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>9.9746835443037902</v>
+        <v>2.3941068139963102</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>7.9797468354430318E-3</v>
+        <v>1.9152854511970483E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2870,11 +2896,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>0.62456627342123505</v>
+        <v>-2.0689655172413701</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>6.2456627342123507E-5</v>
+        <v>-2.0689655172413703E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2885,11 +2911,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>4.3</v>
+        <v>3.13</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>0.34356999999999999</v>
+        <v>0.250087</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2900,11 +2926,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-0.82</v>
+        <v>-0.09</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-6.3140000000000002E-2</v>
+        <v>-6.9299999999999995E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2945,11 +2971,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>-9.83</v>
+        <v>-9.82</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-5.7013999999999995E-2</v>
+        <v>-5.6956E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,11 +2986,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>2.4900000000000002</v>
+        <v>1.59</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>1.4940000000000001E-3</v>
+        <v>9.5399999999999999E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2977,7 +3003,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>0.58216689920081222</v>
+        <v>0.5664222114184615</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3218,12 +3244,22 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
-      <c r="B65" s="29"/>
+      <c r="A65" s="18">
+        <v>46241</v>
+      </c>
+      <c r="B65" s="29">
+        <v>70356</v>
+      </c>
       <c r="C65" s="29"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="24"/>
+      <c r="D65" s="21">
+        <v>27495305201</v>
+      </c>
+      <c r="E65" s="21">
+        <v>1190923365</v>
+      </c>
+      <c r="F65" s="24">
+        <v>1.8E-3</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
@@ -3939,97 +3975,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -4043,6 +3988,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4083,11 +4119,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>0.87719298245613997</v>
+        <v>0.98550724637681097</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.46271929824561381</v>
+        <v>0.51985507246376772</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4098,11 +4134,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>2.33516483516483</v>
+        <v>-1.34228187919463</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>0.25967032967032905</v>
+        <v>-0.14926174496644284</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4113,11 +4149,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.98593530239099</v>
+        <v>-10</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-5.2925457102672248E-2</v>
+        <v>-5.3000000000000005E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4128,11 +4164,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.41</v>
+        <v>-0.77</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12226199999999998</v>
+        <v>-0.22961400000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4146,7 +4182,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>0.54720217081327061</v>
+        <v>8.7979327497324872E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4396,12 +4432,22 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-      <c r="B43" s="29"/>
+      <c r="A43" s="23">
+        <v>46241</v>
+      </c>
+      <c r="B43" s="29">
+        <v>52189</v>
+      </c>
       <c r="C43" s="29"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="24"/>
+      <c r="D43" s="21">
+        <v>34489939181</v>
+      </c>
+      <c r="E43" s="21">
+        <v>-25196290</v>
+      </c>
+      <c r="F43" s="24">
+        <v>2.3E-3</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
@@ -5189,107 +5235,6 @@
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5302,6 +5247,107 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5341,11 +5387,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>1.0275380189066901</v>
+        <v>0.19607843137254899</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>9.3916974928071467E-2</v>
+        <v>1.7921568627450979E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5356,11 +5402,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>0.135685210312076</v>
+        <v>1.0984540276647601</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>1.1085481682496609E-2</v>
+        <v>8.9743694060210905E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5371,11 +5417,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>5.58347292015633E-2</v>
+        <v>-0.40650406504065001</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>4.53378001116694E-3</v>
+        <v>-3.3008130081300775E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5386,11 +5432,11 @@
         <v>6.99</v>
       </c>
       <c r="C5" s="3">
-        <v>6.9298245614034997</v>
+        <v>0</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.4843947368421046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5401,11 +5447,11 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.87</v>
+        <v>2.4610336341263301</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-5.2113000000000007E-2</v>
+        <v>0.14741591468416718</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5415,12 +5461,12 @@
       <c r="B7" s="4">
         <v>4.88</v>
       </c>
-      <c r="C7" s="27">
-        <v>2.6894865525672298</v>
+      <c r="C7" s="3">
+        <v>-0.87</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.13124694376528082</v>
+        <v>-4.2455999999999994E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5430,12 +5476,12 @@
       <c r="B8" s="26">
         <v>4.46</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.96685082872928096</v>
+      <c r="C8" s="27">
+        <v>1.19047619047619</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>4.3121546961325932E-2</v>
+        <v>5.3095238095238077E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5446,11 +5492,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>2.27395776935571</v>
+        <v>-0.68399452804377503</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>9.482403898213311E-2</v>
+        <v>-2.8522571819425416E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5461,11 +5507,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.87579617834394896</v>
+        <v>2.6998411858125899</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-2.828821656050955E-2</v>
+        <v>8.7204870301746645E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5475,12 +5521,12 @@
       <c r="B11" s="4">
         <v>2.84</v>
       </c>
-      <c r="C11" s="28">
-        <v>-1.15015974440894</v>
+      <c r="C11" s="3">
+        <v>-1.6064257028112401</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-3.266453674121389E-2</v>
+        <v>-4.5622489959839217E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5490,12 +5536,12 @@
       <c r="B12" s="4">
         <v>2.54</v>
       </c>
-      <c r="C12" s="3">
-        <v>1.22850122850122</v>
+      <c r="C12" s="28">
+        <v>-0.77569489334195196</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>3.1203931203930991E-2</v>
+        <v>-1.9702650290885578E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5506,11 +5552,11 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>-2.9</v>
+        <v>5.4813915857605098</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-6.8729999999999999E-2</v>
+        <v>0.12990898058252409</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5520,12 +5566,12 @@
       <c r="B14" s="26">
         <v>2.37</v>
       </c>
-      <c r="C14" s="27">
-        <v>-1.0004764173415901</v>
+      <c r="C14" s="3">
+        <v>-2.9</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-2.3711291090995689E-2</v>
+        <v>-6.8729999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5535,12 +5581,12 @@
       <c r="B15" s="26">
         <v>2.21</v>
       </c>
-      <c r="C15" s="3">
-        <v>-4.2938437661665798</v>
+      <c r="C15" s="27">
+        <v>-6.9297401347449403</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-9.4893947232281409E-2</v>
+        <v>-0.15314725697786319</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5551,11 +5597,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.1223344556677799</v>
+        <v>0.162162162162162</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-2.1661054994388151E-2</v>
+        <v>3.1297297297297267E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5566,11 +5612,11 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>-0.91</v>
+        <v>-5.67536889897843E-2</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6107E-2</v>
+        <v>-1.0045402951191821E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5581,11 +5627,11 @@
         <v>1.53</v>
       </c>
       <c r="C18" s="3">
-        <v>-8.1037277147487805E-2</v>
+        <v>-0.91</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-1.2398703403565636E-3</v>
+        <v>-1.3923000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5596,11 +5642,11 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>0.36</v>
+        <v>0.24330900243309</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>5.4359999999999999E-3</v>
+        <v>3.6739659367396593E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5611,11 +5657,11 @@
         <v>1.44</v>
       </c>
       <c r="C20" s="3">
-        <v>-1.82</v>
+        <v>0.36</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6207999999999999E-2</v>
+        <v>5.1839999999999994E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5626,11 +5672,11 @@
         <v>1.44</v>
       </c>
       <c r="C21" s="3">
-        <v>-4.9029126213592198</v>
+        <v>-1.82</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-7.0601941747572769E-2</v>
+        <v>-2.6207999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5640,12 +5686,12 @@
       <c r="B22" s="4">
         <v>1.43</v>
       </c>
-      <c r="C22" s="27">
-        <v>0</v>
+      <c r="C22" s="3">
+        <v>1.3272077590607401</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.8979070954568581E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5656,11 +5702,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>-0.66617320503330801</v>
+        <v>5.2325581395348797</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-9.4596595114729738E-3</v>
+        <v>7.4302325581395282E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5671,11 +5717,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>0</v>
+        <v>0.44709388971684</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.2593144560357597E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5686,11 +5732,11 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>4.76</v>
+        <v>0.91563113145846897</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>6.3308000000000003E-2</v>
+        <v>1.2177894048397636E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5701,11 +5747,11 @@
         <v>1.25</v>
       </c>
       <c r="C26" s="27">
-        <v>0.19029495718363401</v>
+        <v>4.76</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>2.3786869647954251E-3</v>
+        <v>5.949999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5716,11 +5762,11 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>-1.66</v>
+        <v>-0.189933523266856</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>-1.9421999999999998E-2</v>
+        <v>-2.2222222222222153E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5731,11 +5777,11 @@
         <v>1.04</v>
       </c>
       <c r="C28" s="27">
-        <v>0.57999999999999996</v>
+        <v>-1.66</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>6.0319999999999992E-3</v>
+        <v>-1.7263999999999998E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5746,11 +5792,11 @@
         <v>0.9</v>
       </c>
       <c r="C29" s="27">
-        <v>4.6100000000000003</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>4.1489999999999999E-2</v>
+        <v>5.2199999999999998E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5761,11 +5807,11 @@
         <v>0.84</v>
       </c>
       <c r="C30" s="27">
-        <v>-3.6971830985915402</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>-3.1056338028168935E-2</v>
+        <v>3.8724000000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5776,11 +5822,11 @@
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>-1.4649190439475701</v>
+        <v>0.73126142595978005</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>-1.2012336160370073E-2</v>
+        <v>5.9963436928701964E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5791,11 +5837,11 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>0.76</v>
+        <v>-0.62597809076682298</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>6.0800000000000012E-3</v>
+        <v>-5.007824726134584E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5806,11 +5852,11 @@
         <v>0.79</v>
       </c>
       <c r="C33" s="27">
-        <v>1.88679245283018</v>
+        <v>0.76</v>
       </c>
       <c r="D33" s="7">
         <f t="shared" si="0"/>
-        <v>1.4905660377358423E-2</v>
+        <v>6.0040000000000007E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5821,11 +5867,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>-0.79239302694136304</v>
+        <v>0.32407407407407401</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>-6.0221870047543593E-3</v>
+        <v>2.4629629629629628E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5836,11 +5882,11 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>0.78</v>
+        <v>4.5527156549520704</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>5.6940000000000003E-3</v>
+        <v>3.3234824281150113E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5851,11 +5897,11 @@
         <v>0.72</v>
       </c>
       <c r="C36" s="27">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="0"/>
-        <v>4.3920000000000001E-3</v>
+        <v>5.6159999999999995E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5866,11 +5912,11 @@
         <v>0.71</v>
       </c>
       <c r="C37" s="27">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="0"/>
-        <v>5.9639999999999997E-3</v>
+        <v>4.3309999999999998E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5881,11 +5927,11 @@
         <v>0.7</v>
       </c>
       <c r="C38" s="27">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="0"/>
-        <v>6.9999999999999988E-4</v>
+        <v>5.8799999999999998E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5896,11 +5942,11 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="27">
-        <v>0.97</v>
+        <v>0.1</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="0"/>
-        <v>6.7899999999999992E-3</v>
+        <v>6.9999999999999988E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5911,11 +5957,11 @@
         <v>0.64</v>
       </c>
       <c r="C40" s="27">
-        <v>0.11</v>
+        <v>0.97</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="0"/>
-        <v>7.0400000000000009E-4</v>
+        <v>6.208E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5926,11 +5972,11 @@
         <v>0.63</v>
       </c>
       <c r="C41" s="27">
-        <v>4.43</v>
+        <v>0.11</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="0"/>
-        <v>2.7908999999999996E-2</v>
+        <v>6.9300000000000004E-4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5941,11 +5987,11 @@
         <v>0.61</v>
       </c>
       <c r="C42" s="27">
-        <v>1.82</v>
+        <v>4.43</v>
       </c>
       <c r="D42" s="7">
         <f t="shared" si="0"/>
-        <v>1.1102000000000001E-2</v>
+        <v>2.7022999999999998E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -5956,11 +6002,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C43" s="27">
-        <v>-0.05</v>
+        <v>1.82</v>
       </c>
       <c r="D43" s="7">
         <f t="shared" si="0"/>
-        <v>-2.8499999999999999E-4</v>
+        <v>1.0374E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -5971,11 +6017,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C44" s="27">
-        <v>-1.91</v>
+        <v>-0.05</v>
       </c>
       <c r="D44" s="7">
         <f t="shared" si="0"/>
-        <v>-1.0505E-2</v>
+        <v>-2.7500000000000002E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -5986,11 +6032,11 @@
         <v>0.5</v>
       </c>
       <c r="C45" s="27">
-        <v>1.41</v>
+        <v>-1.91</v>
       </c>
       <c r="D45" s="7">
         <f t="shared" si="0"/>
-        <v>7.0499999999999998E-3</v>
+        <v>-9.5499999999999995E-3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -6001,11 +6047,11 @@
         <v>0.5</v>
       </c>
       <c r="C46" s="27">
-        <v>0.32</v>
+        <v>1.41</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>1.6000000000000001E-3</v>
+        <v>7.0499999999999998E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -6016,11 +6062,11 @@
         <v>0.45</v>
       </c>
       <c r="C47" s="27">
-        <v>5.47</v>
+        <v>0.32</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>2.4615000000000001E-2</v>
+        <v>1.4400000000000001E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -6031,11 +6077,11 @@
         <v>0.4</v>
       </c>
       <c r="C48" s="27">
-        <v>2.52</v>
+        <v>5.47</v>
       </c>
       <c r="D48" s="7">
         <f t="shared" si="0"/>
-        <v>1.008E-2</v>
+        <v>2.188E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -6046,11 +6092,11 @@
         <v>0.33</v>
       </c>
       <c r="C49" s="27">
-        <v>-0.17</v>
+        <v>2.52</v>
       </c>
       <c r="D49" s="7">
         <f t="shared" si="0"/>
-        <v>-5.6100000000000008E-4</v>
+        <v>8.3160000000000005E-3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -6079,7 +6125,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>0.61474340230657964</v>
+        <v>0.4327340116223975</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -6299,7 +6345,22 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F74" s="24"/>
+      <c r="A74" s="23">
+        <v>46241</v>
+      </c>
+      <c r="B74" s="29">
+        <v>21724</v>
+      </c>
+      <c r="C74" s="29"/>
+      <c r="D74" s="21">
+        <v>2555268873</v>
+      </c>
+      <c r="E74" s="21">
+        <v>295774874</v>
+      </c>
+      <c r="F74" s="24">
+        <v>6.7999999999999996E-3</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F75" s="24"/>
@@ -6320,7 +6381,8 @@
       <c r="F80" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="B74:C74"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B62:C62"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AA58AE-B52C-4A6A-9BA2-A1E22E374A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2279B3-700D-4C95-B97F-1624E0CF8B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33015" yWindow="0" windowWidth="12015" windowHeight="20625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31635" yWindow="60" windowWidth="15015" windowHeight="20805" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -810,11 +810,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>4.2941176470588198</v>
+        <v>-0.67681895093062605</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.98120588235294037</v>
+        <v>-0.15465313028764804</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,11 +825,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0</v>
+        <v>0.22343750000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,11 +840,11 @@
         <v>8.14</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.40650406504065001</v>
+        <v>-2.0408163265306101</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>-3.3089430894308915E-2</v>
+        <v>-0.16612244897959169</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,11 +855,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>1.0984540276647601</v>
+        <v>0.80482897384305796</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>7.8429617575263857E-2</v>
+        <v>5.7464788732394335E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,11 +870,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>0.162162162162162</v>
+        <v>-1.6189962223421399</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>1.0751351351351341E-2</v>
+        <v>-0.10733944954128388</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,11 +885,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>2.6998411858125899</v>
+        <v>1.0309278350515401</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.15146109052408629</v>
+        <v>5.7835051546391403E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -900,11 +900,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>2.4610336341263301</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>4.8974569319113967E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,11 +915,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>0.32407407407407401</v>
+        <v>-1.19981541301338</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>3.3703703703703695E-3</v>
+        <v>-1.2478080295339153E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,11 +930,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>1.19047619047619</v>
+        <v>-0.47058823529411697</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>6.4285714285714267E-3</v>
+        <v>-2.5411764705882316E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,11 +945,11 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>-0.68399452804377503</v>
+        <v>3.30578512396694</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-3.5567715458276299E-3</v>
+        <v>1.7190082644628089E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -960,11 +960,11 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="C12" s="3">
-        <v>-5.9024807527801499</v>
+        <v>-3.63636363636363</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6526946107784421E-2</v>
+        <v>-1.0181818181818165E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -975,11 +975,11 @@
         <v>0.27</v>
       </c>
       <c r="C13" s="3">
-        <v>-9.9410278011794393</v>
+        <v>-9.9719363891487305</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6840775063184486E-2</v>
+        <v>-2.6924228250701576E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,11 +990,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>0.19607843137254899</v>
+        <v>-0.13046314416177399</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>2.7450980392156862E-4</v>
+        <v>-1.8264840182648359E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1005,11 +1005,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C15" s="3">
-        <v>5.2325581395348797</v>
+        <v>-6.0773480662983399</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>3.662790697674416E-3</v>
+        <v>-4.2541436464088381E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,11 +1020,11 @@
         <v>1.27</v>
       </c>
       <c r="C16" s="3">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>1.6383000000000002E-2</v>
+        <v>2.1082E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>1.2209278298121884</v>
+        <v>-0.10766770113179223</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1345,10 +1345,26 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F44" s="24"/>
+      <c r="A44" s="18">
+        <v>46244</v>
+      </c>
+      <c r="B44" s="29">
+        <v>101266</v>
+      </c>
+      <c r="C44" s="29"/>
+      <c r="D44" s="25">
+        <v>257684170583</v>
+      </c>
+      <c r="E44" s="22">
+        <v>4255223231</v>
+      </c>
+      <c r="F44" s="24">
+        <v>5.8999999999999999E-3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B36:C36"/>
@@ -1404,11 +1420,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>-2.0674157303370699</v>
+        <v>2.1110601193207801</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.18441348314606665</v>
+        <v>0.18830656264341358</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1419,11 +1435,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>2.32342007434944</v>
+        <v>6.8119891008174296</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.20469330855018569</v>
+        <v>0.60013623978201558</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1434,11 +1450,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>7.7922077922077904</v>
+        <v>9.9123767798466496</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.64519480519480499</v>
+        <v>0.82074479737130246</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1449,11 +1465,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>-2.1348314606741501</v>
+        <v>0.45924225028702598</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13171910112359506</v>
+        <v>2.8335246842709504E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1464,11 +1480,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>-9.9410278011794393</v>
+        <v>-9.9719363891487305</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47219882055602336</v>
+        <v>-0.47366697848456468</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1479,11 +1495,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-1.6064257028112401</v>
+        <v>-1.06122448979591</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-7.1004016064256811E-2</v>
+        <v>-4.6906122448979223E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,11 +1510,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>0.44709388971684</v>
+        <v>-0.89020771513353103</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>1.6855439642324867E-2</v>
+        <v>-3.3560830860534116E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1509,11 +1525,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>5.4813915857605098</v>
+        <v>3.0680728667305801</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>0.19733009708737836</v>
+        <v>0.1104506232023009</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,11 +1540,11 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-5.8754406580493503E-2</v>
+        <v>-5.8788947677836503E-2</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-1.980023501762631E-3</v>
+        <v>-1.9811875367430902E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1539,11 +1555,11 @@
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-2.07407407407407</v>
+        <v>-9.9848714069591509</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-5.5585185185185078E-2</v>
+        <v>-0.26759455370650526</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,11 +1570,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>4.2941176470588198</v>
+        <v>-0.67681895093062605</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>0.11078823529411755</v>
+        <v>-1.7461928934010152E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,11 +1585,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>0.24330900243309</v>
+        <v>-2.0226537216828402</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>5.9610705596107065E-3</v>
+        <v>-4.9555016181229587E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1584,11 +1600,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>2.4610336341263301</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>5.0451189499589759E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1599,11 +1615,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>1.3738959764474901</v>
+        <v>-9.9709583736689194</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>2.3768400392541578E-2</v>
+        <v>-0.17249757986447228</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1614,11 +1630,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>4.5527156549520704</v>
+        <v>0.53475935828876997</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>7.4664536741213941E-2</v>
+        <v>8.7700534759358271E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1629,11 +1645,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>-5.67536889897843E-2</v>
+        <v>0.51107325383304902</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-9.1940976163450562E-4</v>
+        <v>8.2793867120953945E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1644,11 +1660,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>0.91563113145846897</v>
+        <v>-0.38885288399222201</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>1.355134074558534E-2</v>
+        <v>-5.7550226830848858E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,11 +1675,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>-0.189933523266856</v>
+        <v>0.19029495718363401</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.6590693257359838E-3</v>
+        <v>2.6641294005708758E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1674,11 +1690,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>1.3272077590607401</v>
+        <v>2.7204030226700202</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>1.7253700867789622E-2</v>
+        <v>3.5365239294710263E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1689,11 +1705,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>1.86915887850467</v>
+        <v>2.75229357798165</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>2.3551401869158842E-2</v>
+        <v>3.4678899082568791E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,11 +1720,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>-0.62597809076682298</v>
+        <v>-0.31496062992125901</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5117370892018752E-3</v>
+        <v>-3.7795275590551082E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1719,11 +1735,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>-0.40650406504065001</v>
+        <v>-2.0408163265306101</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9674796747967453E-3</v>
+        <v>-1.4897959183673452E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1734,11 +1750,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-0.77569489334195196</v>
+        <v>-1.4332247557003199</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-5.5074337427278583E-3</v>
+        <v>-1.0175895765472271E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1749,11 +1765,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>1.19047619047619</v>
+        <v>-0.47058823529411697</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>7.0238095238095207E-3</v>
+        <v>-2.7764705882352904E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1764,11 +1780,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>5.2325581395348797</v>
+        <v>-6.0773480662983399</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>2.9302325581395328E-2</v>
+        <v>-3.4033149171270705E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,11 +1795,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.88679245283018</v>
+        <v>9.9650349650349597</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5471698113207209E-3</v>
+        <v>3.9860139860139837E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,11 +1810,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>-4.9896049896049899</v>
+        <v>-9.9562363238512006</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9459459459459462E-2</v>
+        <v>-3.8829321663019688E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1809,11 +1825,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>0.58241118229470001</v>
+        <v>-0.173711638679791</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>2.0966802562609201E-3</v>
+        <v>-6.2536189924724758E-4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1824,11 +1840,11 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>1.1029411764705801</v>
+        <v>-2.47272727272727</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>3.749999999999973E-3</v>
+        <v>-8.4072727272727181E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1839,11 +1855,11 @@
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>3.2954545454545401</v>
+        <v>-5.7205720572057199</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>1.1204545454545438E-2</v>
+        <v>-1.9449944994499448E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1854,11 +1870,11 @@
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>0.73126142595978005</v>
+        <v>-0.81669691470054395</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>2.4131627056672746E-3</v>
+        <v>-2.6950998185117951E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1869,11 +1885,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>0.162162162162162</v>
+        <v>-1.6189962223421399</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>4.2162162162162121E-4</v>
+        <v>-4.2093901780895634E-3</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1884,11 +1900,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>7.0707070707070701</v>
+        <v>-9.9056603773584904</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>1.2727272727272724E-2</v>
+        <v>-1.7830188679245282E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1899,11 +1915,11 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>2.6998411858125899</v>
+        <v>1.0309278350515401</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>3.2398094229751078E-3</v>
+        <v>1.237113402061848E-3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1914,11 +1930,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-2.0689655172413701</v>
+        <v>-2.4647887323943598</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4482758620689594E-3</v>
+        <v>-1.7253521126760522E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1929,11 +1945,11 @@
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-6.9297401347449403</v>
+        <v>-4.6535677352637004</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-3.4648700673724701E-3</v>
+        <v>-2.3267838676318503E-3</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1944,11 +1960,11 @@
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>2.3941068139963102</v>
+        <v>2.0683453237410001</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>9.5764272559852417E-4</v>
+        <v>8.2733812949640009E-4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,11 +1975,11 @@
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>2.6490066225165498</v>
+        <v>0.14336917562724</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>1.0596026490066199E-3</v>
+        <v>5.7347670250895995E-5</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,11 +1990,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>3.1195840554592702</v>
+        <v>-1.00840336134453</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>9.3587521663778105E-3</v>
+        <v>-3.0252100840335899E-3</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1989,11 +2005,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>3.13</v>
+        <v>-2.25</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>0.26072899999999999</v>
+        <v>-0.18742500000000001</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2004,11 +2020,11 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-0.09</v>
+        <v>-3.42</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-7.443E-3</v>
+        <v>-0.28283399999999997</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2036,7 +2052,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>0.7558472169076238</v>
+        <v>0.17901596787751528</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2295,12 +2311,22 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="18"/>
-      <c r="B68" s="29"/>
+      <c r="A68" s="18">
+        <v>46244</v>
+      </c>
+      <c r="B68" s="29">
+        <v>133320</v>
+      </c>
       <c r="C68" s="29"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="24"/>
+      <c r="D68" s="21">
+        <v>42920929089</v>
+      </c>
+      <c r="E68" s="21">
+        <v>-3497980445</v>
+      </c>
+      <c r="F68" s="24">
+        <v>6.1000000000000004E-3</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
@@ -2476,11 +2502,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>2.32342007434944</v>
+        <v>6.8119891008174296</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.22421003717472096</v>
+        <v>0.65735694822888191</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2491,11 +2517,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>-2.0674157303370699</v>
+        <v>2.1110601193207801</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>-0.19206292134831379</v>
+        <v>0.19611748508490046</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2506,11 +2532,11 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>7.7922077922077904</v>
+        <v>9.9123767798466496</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.71999999999999986</v>
+        <v>0.91590361445783042</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2521,11 +2547,11 @@
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-2.07407407407407</v>
+        <v>-9.9848714069591509</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12631111111111085</v>
+        <v>-0.60807866868381222</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2536,11 +2562,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>-9.9410278011794393</v>
+        <v>-9.9719363891487305</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47021061499578748</v>
+        <v>-0.47167259120673499</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2551,11 +2577,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>-2.1348314606741501</v>
+        <v>0.45924225028702598</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-9.649438202247157E-2</v>
+        <v>2.0757749712973571E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2566,11 +2592,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>5.4813915857605098</v>
+        <v>3.0680728667305801</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.18636731391585734</v>
+        <v>0.10431447746883972</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2581,11 +2607,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-1.6064257028112401</v>
+        <v>-1.06122448979591</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-4.3855421686746859E-2</v>
+        <v>-2.8971428571428343E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2596,11 +2622,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>2.4610336341263301</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>5.6603773584905585E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2611,11 +2637,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>-0.189933523266856</v>
+        <v>0.19029495718363401</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-3.1718898385564953E-3</v>
+        <v>3.1779257849666883E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,11 +2652,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>1.3738959764474901</v>
+        <v>-9.9709583736689194</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>2.1707556427870346E-2</v>
+        <v>-0.15754114230396893</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2641,11 +2667,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>4.2941176470588198</v>
+        <v>-0.67681895093062605</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>6.7417647058823471E-2</v>
+        <v>-1.0626057529610829E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2656,11 +2682,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>0.44709388971684</v>
+        <v>-0.89020771513353103</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>5.0521609538002913E-3</v>
+        <v>-1.00593471810089E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2671,11 +2697,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-5.8754406580493503E-2</v>
+        <v>-5.8788947677836503E-2</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-6.0517038777908308E-4</v>
+        <v>-6.05526161081716E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,11 +2712,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>4.5527156549520704</v>
+        <v>0.53475935828876997</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>4.4616613418530286E-2</v>
+        <v>5.2406417112299455E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2701,11 +2727,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-2.56</v>
+        <v>-2.4630541871921099</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-2.2272E-2</v>
+        <v>-2.1428571428571356E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2716,11 +2742,11 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>5.2325581395348797</v>
+        <v>-6.0773480662983399</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>3.0872093023255789E-2</v>
+        <v>-3.5856353591160205E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2731,11 +2757,11 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-6.9297401347449403</v>
+        <v>-4.6535677352637004</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-3.4648700673724699E-2</v>
+        <v>-2.32678386763185E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2746,11 +2772,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>-1.88679245283018</v>
+        <v>9.9650349650349597</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-9.0566037735848644E-3</v>
+        <v>4.7832167832167809E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2761,11 +2787,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>1.86915887850467</v>
+        <v>2.75229357798165</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>7.8504672897196145E-3</v>
+        <v>1.1559633027522928E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2776,11 +2802,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>6.6875</v>
+        <v>0.58582308142940798</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>2.6750000000000003E-2</v>
+        <v>2.343292325717632E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2791,11 +2817,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-0.77569489334195196</v>
+        <v>-1.4332247557003199</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9476405946994178E-3</v>
+        <v>-5.4462540716612162E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2806,11 +2832,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>0.162162162162162</v>
+        <v>-1.6189962223421399</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>4.0540540540540501E-4</v>
+        <v>-4.0474905558553495E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2821,11 +2847,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>-8.5308056872037898</v>
+        <v>0.77720207253885998</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1327014218009473E-2</v>
+        <v>1.94300518134715E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2836,11 +2862,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>1.1029411764705801</v>
+        <v>-2.47272727272727</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>2.6470588235293926E-3</v>
+        <v>-5.9345454545454476E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2851,11 +2877,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>-0.40650406504065001</v>
+        <v>-2.0408163265306101</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-9.3495934959349507E-4</v>
+        <v>-4.6938775510204037E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2866,11 +2892,11 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>1.34656272147413</v>
+        <v>2.72727272727272</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>2.6931254429482603E-3</v>
+        <v>5.4545454545454394E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,11 +2907,11 @@
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>2.3941068139963102</v>
+        <v>2.0683453237410001</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>1.9152854511970483E-3</v>
+        <v>1.6546762589928002E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2896,11 +2922,11 @@
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-2.0689655172413701</v>
+        <v>-2.4647887323943598</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0689655172413703E-4</v>
+        <v>-2.4647887323943596E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2911,11 +2937,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>3.13</v>
+        <v>-2.25</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>0.250087</v>
+        <v>-0.17977499999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2926,11 +2952,11 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-0.09</v>
+        <v>-3.42</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-6.9299999999999995E-3</v>
+        <v>-0.26334000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2971,11 +2997,11 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>-9.82</v>
+        <v>-9.92</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-5.6956E-2</v>
+        <v>-5.7535999999999997E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2986,11 +3012,11 @@
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>9.5399999999999999E-4</v>
+        <v>8.160000000000001E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3003,7 +3029,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>0.5664222114184615</v>
+        <v>8.9608990689898624E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3262,12 +3288,22 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
-      <c r="B66" s="29"/>
+      <c r="A66" s="18">
+        <v>46244</v>
+      </c>
+      <c r="B66" s="29">
+        <v>70743</v>
+      </c>
       <c r="C66" s="29"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="24"/>
+      <c r="D66" s="21">
+        <v>25035325105</v>
+      </c>
+      <c r="E66" s="21">
+        <v>-2430448566</v>
+      </c>
+      <c r="F66" s="24">
+        <v>-1.1000000000000001E-3</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
@@ -4119,11 +4155,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>0.98550724637681097</v>
+        <v>2.3536165327210101</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.51985507246376772</v>
+        <v>1.2415327210103329</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4134,11 +4170,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-1.34228187919463</v>
+        <v>-3.8095238095238</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.14926174496644284</v>
+        <v>-0.42361904761904656</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4149,11 +4185,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-10</v>
+        <v>-9.8958333333333304</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-5.3000000000000005E-2</v>
+        <v>-5.244791666666665E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4164,11 +4200,11 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.77</v>
+        <v>-0.53</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.22961400000000001</v>
+        <v>-0.15804600000000002</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4182,7 +4218,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>8.7979327497324872E-2</v>
+        <v>0.60741975672461967</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4450,12 +4486,22 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-      <c r="B44" s="29"/>
+      <c r="A44" s="23">
+        <v>46244</v>
+      </c>
+      <c r="B44" s="29">
+        <v>52228</v>
+      </c>
       <c r="C44" s="29"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="24"/>
+      <c r="D44" s="21">
+        <v>34191459593</v>
+      </c>
+      <c r="E44" s="21">
+        <v>-347610039</v>
+      </c>
+      <c r="F44" s="24">
+        <v>1.1000000000000001E-3</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
@@ -5387,11 +5433,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>0.19607843137254899</v>
+        <v>0.80482897384305796</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>1.7921568627450979E-2</v>
+        <v>7.3561368209255504E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,11 +5448,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>1.0984540276647601</v>
+        <v>-2.0408163265306101</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>8.9743694060210905E-2</v>
+        <v>-0.16673469387755083</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5417,11 +5463,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>-0.40650406504065001</v>
+        <v>1.5625</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>-3.3008130081300775E-2</v>
+        <v>0.12687499999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5447,11 +5493,11 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>2.4610336341263301</v>
+        <v>-0.87</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.14741591468416718</v>
+        <v>-5.2113000000000007E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5461,12 +5507,12 @@
       <c r="B7" s="4">
         <v>4.88</v>
       </c>
-      <c r="C7" s="3">
-        <v>-0.87</v>
+      <c r="C7" s="27">
+        <v>-0.47058823529411697</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-4.2455999999999994E-2</v>
+        <v>-2.2964705882352908E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5476,12 +5522,12 @@
       <c r="B8" s="26">
         <v>4.46</v>
       </c>
-      <c r="C8" s="27">
-        <v>1.19047619047619</v>
+      <c r="C8" s="3">
+        <v>3.30578512396694</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>5.3095238095238077E-2</v>
+        <v>0.14743801652892552</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5492,11 +5538,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>-0.68399452804377503</v>
+        <v>1.0309278350515401</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-2.8522571819425416E-2</v>
+        <v>4.2989690721649217E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5507,11 +5553,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>2.6998411858125899</v>
+        <v>-1.06122448979591</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>8.7204870301746645E-2</v>
+        <v>-3.4277551020407894E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5521,12 +5567,12 @@
       <c r="B11" s="4">
         <v>2.84</v>
       </c>
-      <c r="C11" s="3">
-        <v>-1.6064257028112401</v>
+      <c r="C11" s="28">
+        <v>-1.4332247557003199</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-4.5622489959839217E-2</v>
+        <v>-4.0703583061889086E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5536,12 +5582,12 @@
       <c r="B12" s="4">
         <v>2.54</v>
       </c>
-      <c r="C12" s="28">
-        <v>-0.77569489334195196</v>
+      <c r="C12" s="3">
+        <v>3.0680728667305801</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-1.9702650290885578E-2</v>
+        <v>7.7929050814956741E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5552,11 +5598,11 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>5.4813915857605098</v>
+        <v>-2.9</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>0.12990898058252409</v>
+        <v>-6.8729999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5566,12 +5612,12 @@
       <c r="B14" s="26">
         <v>2.37</v>
       </c>
-      <c r="C14" s="3">
-        <v>-2.9</v>
+      <c r="C14" s="27">
+        <v>-4.6535677352637004</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-6.8729999999999999E-2</v>
+        <v>-0.1102895553257497</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5581,12 +5627,12 @@
       <c r="B15" s="26">
         <v>2.21</v>
       </c>
-      <c r="C15" s="27">
-        <v>-6.9297401347449403</v>
+      <c r="C15" s="3">
+        <v>-1.6189962223421399</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-0.15314725697786319</v>
+        <v>-3.5779816513761296E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5597,11 +5643,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>0.162162162162162</v>
+        <v>0.51107325383304902</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>3.1297297297297267E-3</v>
+        <v>9.8637137989778453E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5612,11 +5658,11 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>-5.67536889897843E-2</v>
+        <v>-0.91</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>-1.0045402951191821E-3</v>
+        <v>-1.6107E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5627,11 +5673,11 @@
         <v>1.53</v>
       </c>
       <c r="C18" s="3">
-        <v>-0.91</v>
+        <v>-2.0226537216828402</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-1.3923000000000001E-2</v>
+        <v>-3.0946601941747455E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5642,11 +5688,11 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>0.24330900243309</v>
+        <v>0.36</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>3.6739659367396593E-3</v>
+        <v>5.4359999999999999E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5657,11 +5703,11 @@
         <v>1.44</v>
       </c>
       <c r="C20" s="3">
-        <v>0.36</v>
+        <v>-1.82</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>5.1839999999999994E-3</v>
+        <v>-2.6207999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5672,11 +5718,11 @@
         <v>1.44</v>
       </c>
       <c r="C21" s="3">
-        <v>-1.82</v>
+        <v>2.7204030226700202</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6207999999999999E-2</v>
+        <v>3.9173803526448288E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5686,12 +5732,12 @@
       <c r="B22" s="4">
         <v>1.43</v>
       </c>
-      <c r="C22" s="3">
-        <v>1.3272077590607401</v>
+      <c r="C22" s="27">
+        <v>-6.0773480662983399</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>1.8979070954568581E-2</v>
+        <v>-8.6906077348066268E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5702,11 +5748,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>5.2325581395348797</v>
+        <v>-0.89020771513353103</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>7.4302325581395282E-2</v>
+        <v>-1.264094955489614E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5717,11 +5763,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>0.44709388971684</v>
+        <v>-0.38885288399222201</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>6.2593144560357597E-3</v>
+        <v>-5.4439403758911077E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5732,11 +5778,11 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>0.91563113145846897</v>
+        <v>4.76</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>1.2177894048397636E-2</v>
+        <v>6.3308000000000003E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5747,11 +5793,11 @@
         <v>1.25</v>
       </c>
       <c r="C26" s="27">
-        <v>4.76</v>
+        <v>0.19029495718363401</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>5.949999999999999E-2</v>
+        <v>2.3786869647954251E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5762,11 +5808,11 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>-0.189933523266856</v>
+        <v>-1.66</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>-2.2222222222222153E-3</v>
+        <v>-1.9421999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5777,11 +5823,11 @@
         <v>1.04</v>
       </c>
       <c r="C28" s="27">
-        <v>-1.66</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7263999999999998E-2</v>
+        <v>6.0319999999999992E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5792,11 +5838,11 @@
         <v>0.9</v>
       </c>
       <c r="C29" s="27">
-        <v>0.57999999999999996</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>5.2199999999999998E-3</v>
+        <v>4.1489999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5807,11 +5853,11 @@
         <v>0.84</v>
       </c>
       <c r="C30" s="27">
-        <v>4.6100000000000003</v>
+        <v>-0.81669691470054395</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>3.8724000000000001E-2</v>
+        <v>-6.8602540834845696E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5822,11 +5868,11 @@
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>0.73126142595978005</v>
+        <v>-0.31496062992125901</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>5.9963436928701964E-3</v>
+        <v>-2.5826771653543234E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5837,11 +5883,11 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>-0.62597809076682298</v>
+        <v>0.76</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>-5.007824726134584E-3</v>
+        <v>6.0800000000000012E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5852,11 +5898,11 @@
         <v>0.79</v>
       </c>
       <c r="C33" s="27">
-        <v>0.76</v>
+        <v>-1.19981541301338</v>
       </c>
       <c r="D33" s="7">
         <f t="shared" si="0"/>
-        <v>6.0040000000000007E-3</v>
+        <v>-9.4785417628057023E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5867,11 +5913,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>0.32407407407407401</v>
+        <v>0.53475935828876997</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>2.4629629629629628E-3</v>
+        <v>4.0641711229946519E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5882,11 +5928,11 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>4.5527156549520704</v>
+        <v>0.78</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>3.3234824281150113E-2</v>
+        <v>5.6940000000000003E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5897,11 +5943,11 @@
         <v>0.72</v>
       </c>
       <c r="C36" s="27">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="0"/>
-        <v>5.6159999999999995E-3</v>
+        <v>4.3920000000000001E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5912,11 +5958,11 @@
         <v>0.71</v>
       </c>
       <c r="C37" s="27">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="0"/>
-        <v>4.3309999999999998E-3</v>
+        <v>5.9639999999999997E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5927,11 +5973,11 @@
         <v>0.7</v>
       </c>
       <c r="C38" s="27">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="0"/>
-        <v>5.8799999999999998E-3</v>
+        <v>6.9999999999999988E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5942,11 +5988,11 @@
         <v>0.7</v>
       </c>
       <c r="C39" s="27">
-        <v>0.1</v>
+        <v>0.97</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="0"/>
-        <v>6.9999999999999988E-4</v>
+        <v>6.7899999999999992E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5957,11 +6003,11 @@
         <v>0.64</v>
       </c>
       <c r="C40" s="27">
-        <v>0.97</v>
+        <v>0.11</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="0"/>
-        <v>6.208E-3</v>
+        <v>7.0400000000000009E-4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5972,11 +6018,11 @@
         <v>0.63</v>
       </c>
       <c r="C41" s="27">
-        <v>0.11</v>
+        <v>4.43</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="0"/>
-        <v>6.9300000000000004E-4</v>
+        <v>2.7908999999999996E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5987,11 +6033,11 @@
         <v>0.61</v>
       </c>
       <c r="C42" s="27">
-        <v>4.43</v>
+        <v>1.82</v>
       </c>
       <c r="D42" s="7">
         <f t="shared" si="0"/>
-        <v>2.7022999999999998E-2</v>
+        <v>1.1102000000000001E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -6002,11 +6048,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C43" s="27">
-        <v>1.82</v>
+        <v>-0.05</v>
       </c>
       <c r="D43" s="7">
         <f t="shared" si="0"/>
-        <v>1.0374E-2</v>
+        <v>-2.8499999999999999E-4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -6017,11 +6063,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C44" s="27">
-        <v>-0.05</v>
+        <v>-1.91</v>
       </c>
       <c r="D44" s="7">
         <f t="shared" si="0"/>
-        <v>-2.7500000000000002E-4</v>
+        <v>-1.0505E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -6032,11 +6078,11 @@
         <v>0.5</v>
       </c>
       <c r="C45" s="27">
-        <v>-1.91</v>
+        <v>1.41</v>
       </c>
       <c r="D45" s="7">
         <f t="shared" si="0"/>
-        <v>-9.5499999999999995E-3</v>
+        <v>7.0499999999999998E-3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -6047,11 +6093,11 @@
         <v>0.5</v>
       </c>
       <c r="C46" s="27">
-        <v>1.41</v>
+        <v>0.32</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>7.0499999999999998E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -6062,11 +6108,11 @@
         <v>0.45</v>
       </c>
       <c r="C47" s="27">
-        <v>0.32</v>
+        <v>5.47</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>1.4400000000000001E-3</v>
+        <v>2.4615000000000001E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -6077,11 +6123,11 @@
         <v>0.4</v>
       </c>
       <c r="C48" s="27">
-        <v>5.47</v>
+        <v>2.52</v>
       </c>
       <c r="D48" s="7">
         <f t="shared" si="0"/>
-        <v>2.188E-2</v>
+        <v>1.008E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -6092,11 +6138,11 @@
         <v>0.33</v>
       </c>
       <c r="C49" s="27">
-        <v>2.52</v>
+        <v>-0.17</v>
       </c>
       <c r="D49" s="7">
         <f t="shared" si="0"/>
-        <v>8.3160000000000005E-3</v>
+        <v>-5.6100000000000008E-4</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -6125,7 +6171,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>0.4327340116223975</v>
+        <v>-6.5924462259540845E-3</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -6363,7 +6409,22 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F75" s="24"/>
+      <c r="A75" s="23">
+        <v>46244</v>
+      </c>
+      <c r="B75" s="29">
+        <v>22925</v>
+      </c>
+      <c r="C75" s="29"/>
+      <c r="D75" s="21">
+        <v>2826840748</v>
+      </c>
+      <c r="E75" s="21">
+        <v>254561602</v>
+      </c>
+      <c r="F75" s="24">
+        <v>2.8E-3</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F76" s="24"/>
@@ -6381,7 +6442,8 @@
       <c r="F80" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="B75:C75"/>
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="B73:C73"/>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2279B3-700D-4C95-B97F-1624E0CF8B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BB8CE2-FB2A-476A-B28E-8E848C13E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31635" yWindow="60" windowWidth="15015" windowHeight="20805" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23730" yWindow="105" windowWidth="12435" windowHeight="20475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="PBR" sheetId="3" r:id="rId3"/>
     <sheet name="DFI" sheetId="4" r:id="rId4"/>
     <sheet name="KHA" sheetId="7" r:id="rId5"/>
+    <sheet name="THF" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="99">
   <si>
     <t>DSTKF</t>
   </si>
@@ -193,12 +194,6 @@
     <t>HMV</t>
   </si>
   <si>
-    <t>Yatırımcı Sayısı</t>
-  </si>
-  <si>
-    <t>Fon Toplam Değer</t>
-  </si>
-  <si>
     <t>ETKİ ORANI</t>
   </si>
   <si>
@@ -238,15 +233,6 @@
     <t>PA2</t>
   </si>
   <si>
-    <t>Para Girişi/Çıkışı</t>
-  </si>
-  <si>
-    <t>Tarih</t>
-  </si>
-  <si>
-    <t>MARJ</t>
-  </si>
-  <si>
     <t>EUPWR</t>
   </si>
   <si>
@@ -323,6 +309,30 @@
   </si>
   <si>
     <t>İSVEA</t>
+  </si>
+  <si>
+    <t>AKRCL</t>
+  </si>
+  <si>
+    <t>ORZAX</t>
+  </si>
+  <si>
+    <t>NETCD</t>
+  </si>
+  <si>
+    <t>BARMA</t>
+  </si>
+  <si>
+    <t>MCARD</t>
+  </si>
+  <si>
+    <t>GLRMK</t>
+  </si>
+  <si>
+    <t>EGEGY</t>
+  </si>
+  <si>
+    <t>TABGD</t>
   </si>
 </sst>
 </file>
@@ -810,11 +820,11 @@
         <v>22.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-0.67681895093062605</v>
+        <v>0</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.15465313028764804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,11 +835,11 @@
         <v>14.3</v>
       </c>
       <c r="C3" s="3">
-        <v>1.5625</v>
+        <v>0</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.22343750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,11 +850,11 @@
         <v>8.14</v>
       </c>
       <c r="C4" s="3">
-        <v>-2.0408163265306101</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
-        <v>-0.16612244897959169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,11 +865,11 @@
         <v>7.14</v>
       </c>
       <c r="C5" s="3">
-        <v>0.80482897384305796</v>
+        <v>1.19760479041916</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>5.7464788732394335E-2</v>
+        <v>8.5508982035928008E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,11 +880,11 @@
         <v>6.63</v>
       </c>
       <c r="C6" s="3">
-        <v>-1.6189962223421399</v>
+        <v>-4.3076923076923004</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10733944954128388</v>
+        <v>-0.28559999999999952</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,11 +895,11 @@
         <v>5.61</v>
       </c>
       <c r="C7" s="3">
-        <v>1.0309278350515401</v>
+        <v>0.51020408163265296</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>5.7835051546391403E-2</v>
+        <v>2.8622448979591833E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -900,11 +910,11 @@
         <v>1.99</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>3.12249799839871</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.2137710168134325E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,11 +925,11 @@
         <v>1.04</v>
       </c>
       <c r="C9" s="3">
-        <v>-1.19981541301338</v>
+        <v>6.95936478281177</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-1.2478080295339153E-2</v>
+        <v>7.2377393741242413E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,11 +940,11 @@
         <v>0.54</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.47058823529411697</v>
+        <v>-0.70921985815602795</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5411764705882316E-3</v>
+        <v>-3.8297872340425508E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,26 +955,26 @@
         <v>0.52</v>
       </c>
       <c r="C11" s="3">
-        <v>3.30578512396694</v>
+        <v>3.1333333333333302</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.7190082644628089E-2</v>
+        <v>1.6293333333333316E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B12" s="4">
         <v>0.28000000000000003</v>
       </c>
       <c r="C12" s="3">
-        <v>-3.63636363636363</v>
+        <v>10</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-1.0181818181818165E-2</v>
+        <v>2.8000000000000004E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -975,11 +985,11 @@
         <v>0.27</v>
       </c>
       <c r="C13" s="3">
-        <v>-9.9719363891487305</v>
+        <v>-9.9750623441396495</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6924228250701576E-2</v>
+        <v>-2.6932668329177054E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,11 +1000,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C14" s="3">
-        <v>-0.13046314416177399</v>
+        <v>1.3063357282821599</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-1.8264840182648359E-4</v>
+        <v>1.8288700195950242E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1005,11 +1015,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C15" s="3">
-        <v>-6.0773480662983399</v>
+        <v>-0.70588235294117596</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-4.2541436464088381E-3</v>
+        <v>-4.9411764705882327E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,16 +1030,16 @@
         <v>1.27</v>
       </c>
       <c r="C16" s="3">
-        <v>1.66</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>2.1082E-2</v>
+        <v>-1.4731999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" s="5">
         <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16</f>
@@ -1038,7 +1048,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>-0.10766770113179223</v>
+        <v>-3.6819834932453055E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1111,256 +1121,116 @@
       <c r="D30" s="19"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>52</v>
-      </c>
+      <c r="A31" s="5"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="30"/>
-      <c r="D31" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="18">
-        <v>46226</v>
-      </c>
-      <c r="B32" s="29">
-        <v>98970</v>
-      </c>
+      <c r="A32" s="18"/>
+      <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="25">
-        <v>232874657613</v>
-      </c>
-      <c r="E32" s="21">
-        <v>1310146537</v>
-      </c>
-      <c r="F32" s="24">
-        <v>2.1100000000000001E-2</v>
-      </c>
+      <c r="D32" s="25"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="24"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="18">
-        <v>46227</v>
-      </c>
-      <c r="B33" s="29">
-        <v>99051</v>
-      </c>
+      <c r="A33" s="18"/>
+      <c r="B33" s="29"/>
       <c r="C33" s="29"/>
-      <c r="D33" s="25">
-        <v>227320292084</v>
-      </c>
-      <c r="E33" s="22">
-        <v>-6072488957</v>
-      </c>
-      <c r="F33" s="24">
-        <v>2.2000000000000001E-3</v>
-      </c>
+      <c r="D33" s="25"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="18">
-        <v>46230</v>
-      </c>
-      <c r="B34" s="29">
-        <v>98455</v>
-      </c>
+      <c r="A34" s="18"/>
+      <c r="B34" s="29"/>
       <c r="C34" s="29"/>
-      <c r="D34" s="25">
-        <v>229116006481</v>
-      </c>
-      <c r="E34" s="22">
-        <v>291803673</v>
-      </c>
-      <c r="F34" s="24">
-        <v>6.6E-3</v>
-      </c>
+      <c r="D34" s="25"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="18">
-        <v>46231</v>
-      </c>
-      <c r="B35" s="29">
-        <v>98583</v>
-      </c>
+      <c r="A35" s="18"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="29"/>
-      <c r="D35" s="25">
-        <v>232227975662</v>
-      </c>
-      <c r="E35" s="22">
-        <v>-464304680</v>
-      </c>
-      <c r="F35" s="24">
-        <v>1.5600000000000001E-2</v>
-      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="18">
-        <v>46232</v>
-      </c>
-      <c r="B36" s="29">
-        <v>98915</v>
-      </c>
+      <c r="A36" s="18"/>
+      <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="25">
-        <v>226192717226</v>
-      </c>
-      <c r="E36" s="22">
-        <v>-7041302653</v>
-      </c>
-      <c r="F36" s="24">
-        <v>4.3E-3</v>
-      </c>
+      <c r="D36" s="25"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="18">
-        <v>46233</v>
-      </c>
-      <c r="B37" s="29">
-        <v>97411</v>
-      </c>
+      <c r="A37" s="18"/>
+      <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="25">
-        <v>223802010766</v>
-      </c>
-      <c r="E37" s="22">
-        <v>-1443647505</v>
-      </c>
-      <c r="F37" s="24">
-        <v>-4.1999999999999997E-3</v>
-      </c>
+      <c r="D37" s="25"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="24"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="18">
-        <v>46234</v>
-      </c>
-      <c r="B38" s="29">
-        <v>97269</v>
-      </c>
+      <c r="A38" s="18"/>
+      <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="25">
-        <v>223121593370</v>
-      </c>
-      <c r="E38" s="22">
-        <v>-3172256453</v>
-      </c>
-      <c r="F38" s="24">
-        <v>1.11E-2</v>
-      </c>
+      <c r="D38" s="25"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="18">
-        <v>46237</v>
-      </c>
-      <c r="B39" s="29">
-        <v>96829</v>
-      </c>
+      <c r="A39" s="18"/>
+      <c r="B39" s="29"/>
       <c r="C39" s="29"/>
-      <c r="D39" s="25">
-        <v>222116113609</v>
-      </c>
-      <c r="E39" s="22">
-        <v>-2851667712</v>
-      </c>
-      <c r="F39" s="24">
-        <v>8.3000000000000001E-3</v>
-      </c>
+      <c r="D39" s="25"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="18">
-        <v>46238</v>
-      </c>
-      <c r="B40" s="29">
-        <v>95992</v>
-      </c>
+      <c r="A40" s="18"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="25">
-        <v>223759283155</v>
-      </c>
-      <c r="E40" s="22">
-        <v>-2851667712</v>
-      </c>
-      <c r="F40" s="24">
-        <v>7.4000000000000003E-3</v>
-      </c>
+      <c r="D40" s="25"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="18">
-        <v>46239</v>
-      </c>
-      <c r="B41" s="29">
-        <v>97092</v>
-      </c>
+      <c r="A41" s="18"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="29"/>
-      <c r="D41" s="25">
-        <v>230332113229</v>
-      </c>
-      <c r="E41" s="22">
-        <v>4240768585</v>
-      </c>
-      <c r="F41" s="24">
-        <v>1.04E-2</v>
-      </c>
+      <c r="D41" s="25"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="18">
-        <v>46240</v>
-      </c>
-      <c r="B42" s="29">
-        <v>98383</v>
-      </c>
+      <c r="A42" s="18"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="29"/>
-      <c r="D42" s="25">
-        <v>243191073731</v>
-      </c>
-      <c r="E42" s="22">
-        <v>5542399816</v>
-      </c>
-      <c r="F42" s="24">
-        <v>3.1800000000000002E-2</v>
-      </c>
+      <c r="D42" s="25"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="18">
-        <v>46241</v>
-      </c>
-      <c r="B43" s="29">
-        <v>99770</v>
-      </c>
+      <c r="A43" s="18"/>
+      <c r="B43" s="29"/>
       <c r="C43" s="29"/>
-      <c r="D43" s="25">
-        <v>251321783060</v>
-      </c>
-      <c r="E43" s="22">
-        <v>6496955531</v>
-      </c>
-      <c r="F43" s="24">
-        <v>5.4000000000000003E-3</v>
-      </c>
+      <c r="D43" s="25"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="18">
-        <v>46244</v>
-      </c>
-      <c r="B44" s="29">
-        <v>101266</v>
-      </c>
+      <c r="A44" s="18"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="29"/>
-      <c r="D44" s="25">
-        <v>257684170583</v>
-      </c>
-      <c r="E44" s="22">
-        <v>4255223231</v>
-      </c>
-      <c r="F44" s="24">
-        <v>5.8999999999999999E-3</v>
-      </c>
+      <c r="D44" s="25"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1403,7 +1273,7 @@
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -1420,11 +1290,11 @@
         <v>8.92</v>
       </c>
       <c r="C2" s="14">
-        <v>2.1110601193207801</v>
+        <v>9.97752808988764</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.18830656264341358</v>
+        <v>0.88999550561797747</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,11 +1305,11 @@
         <v>8.81</v>
       </c>
       <c r="C3" s="14">
-        <v>6.8119891008174296</v>
+        <v>4.7619047619047601</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.60013623978201558</v>
+        <v>0.41952380952380941</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,11 +1320,11 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="C4" s="14">
-        <v>9.9123767798466496</v>
+        <v>3.5874439461883401</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.82074479737130246</v>
+        <v>0.29704035874439449</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1465,11 +1335,11 @@
         <v>6.17</v>
       </c>
       <c r="C5" s="14">
-        <v>0.45924225028702598</v>
+        <v>-10</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>2.8335246842709504E-2</v>
+        <v>-0.61699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,11 +1350,11 @@
         <v>4.75</v>
       </c>
       <c r="C6" s="14">
-        <v>-9.9719363891487305</v>
+        <v>-9.9750623441396495</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47366697848456468</v>
+        <v>-0.47381546134663338</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1495,11 +1365,11 @@
         <v>4.42</v>
       </c>
       <c r="C7" s="14">
-        <v>-1.06122448979591</v>
+        <v>-0.66006600660065995</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6906122448979223E-2</v>
+        <v>-2.9174917491749167E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,11 +1380,11 @@
         <v>3.77</v>
       </c>
       <c r="C8" s="14">
-        <v>-0.89020771513353103</v>
+        <v>-0.97305389221556804</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-3.3560830860534116E-2</v>
+        <v>-3.6684131736526918E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,11 +1395,11 @@
         <v>3.6</v>
       </c>
       <c r="C9" s="14">
-        <v>3.0680728667305801</v>
+        <v>-9.0604651162790599</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>0.1104506232023009</v>
+        <v>-0.32617674418604614</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,26 +1410,26 @@
         <v>3.37</v>
       </c>
       <c r="C10" s="14">
-        <v>-5.8788947677836503E-2</v>
+        <v>0.17647058823529399</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9811875367430902E-3</v>
+        <v>5.9470588235294077E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="4">
         <v>2.68</v>
       </c>
       <c r="C11" s="14">
-        <v>-9.9848714069591509</v>
+        <v>-4.2016806722688997</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-0.26759455370650526</v>
+        <v>-0.11260504201680652</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1570,11 +1440,11 @@
         <v>2.58</v>
       </c>
       <c r="C12" s="14">
-        <v>-0.67681895093062605</v>
+        <v>0.39750141964792701</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7461928934010152E-2</v>
+        <v>1.0255536626916518E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,11 +1455,11 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="C13" s="14">
-        <v>-2.0226537216828402</v>
+        <v>-0.74318744838976003</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-4.9555016181229587E-2</v>
+        <v>-1.820809248554912E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,11 +1470,11 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="C14" s="14">
-        <v>0</v>
+        <v>3.12249799839871</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.401120896717355E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,11 +1485,11 @@
         <v>1.73</v>
       </c>
       <c r="C15" s="14">
-        <v>-9.9709583736689194</v>
+        <v>-3.97849462365591</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-0.17249757986447228</v>
+        <v>-6.8827956989247235E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,11 +1500,11 @@
         <v>1.64</v>
       </c>
       <c r="C16" s="14">
-        <v>0.53475935828876997</v>
+        <v>-4.2553191489361701</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>8.7700534759358271E-3</v>
+        <v>-6.9787234042553187E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,11 +1515,11 @@
         <v>1.62</v>
       </c>
       <c r="C17" s="14">
-        <v>0.51107325383304902</v>
+        <v>-1.0169491525423699</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>8.2793867120953945E-3</v>
+        <v>-1.6474576271186394E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,11 +1530,11 @@
         <v>1.48</v>
       </c>
       <c r="C18" s="14">
-        <v>-0.38885288399222201</v>
+        <v>-1.8217306441119001</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-5.7550226830848858E-3</v>
+        <v>-2.6961613532856123E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,11 +1545,11 @@
         <v>1.4</v>
       </c>
       <c r="C19" s="14">
-        <v>0.19029495718363401</v>
+        <v>-2.0892687559354202</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>2.6641294005708758E-3</v>
+        <v>-2.9249762583095879E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,11 +1560,11 @@
         <v>1.3</v>
       </c>
       <c r="C20" s="14">
-        <v>2.7204030226700202</v>
+        <v>-1.9617459538989701</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>3.5365239294710263E-2</v>
+        <v>-2.550269740068661E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1705,11 +1575,11 @@
         <v>1.26</v>
       </c>
       <c r="C21" s="14">
-        <v>2.75229357798165</v>
+        <v>-0.98214285714285698</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>3.4678899082568791E-2</v>
+        <v>-1.2374999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,11 +1590,11 @@
         <v>1.2</v>
       </c>
       <c r="C22" s="14">
-        <v>-0.31496062992125901</v>
+        <v>-7.89889415481832E-2</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-3.7795275590551082E-3</v>
+        <v>-9.4786729857819843E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1735,11 +1605,11 @@
         <v>0.73</v>
       </c>
       <c r="C23" s="14">
-        <v>-2.0408163265306101</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-1.4897959183673452E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1750,11 +1620,11 @@
         <v>0.71</v>
       </c>
       <c r="C24" s="14">
-        <v>-1.4332247557003199</v>
+        <v>-1.0575016523463301</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0175895765472271E-2</v>
+        <v>-7.5082617316589431E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,11 +1635,11 @@
         <v>0.59</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.47058823529411697</v>
+        <v>-0.70921985815602795</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-2.7764705882352904E-3</v>
+        <v>-4.1843971631205642E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,11 +1650,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="C26" s="8">
-        <v>-6.0773480662983399</v>
+        <v>-0.70588235294117596</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-3.4033149171270705E-2</v>
+        <v>-3.9529411764705862E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,11 +1665,11 @@
         <v>0.4</v>
       </c>
       <c r="C27" s="8">
-        <v>9.9650349650349597</v>
+        <v>0.47694753577106502</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>3.9860139860139837E-2</v>
+        <v>1.9077901430842603E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1810,11 +1680,11 @@
         <v>0.39</v>
       </c>
       <c r="C28" s="8">
-        <v>-9.9562363238512006</v>
+        <v>-4.2527339003645199</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8829321663019688E-2</v>
+        <v>-1.6585662211421628E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1825,11 +1695,11 @@
         <v>0.36</v>
       </c>
       <c r="C29" s="8">
-        <v>-0.173711638679791</v>
+        <v>-0.34802784222737798</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>-6.2536189924724758E-4</v>
+        <v>-1.2529002320185605E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,41 +1710,41 @@
         <v>0.34</v>
       </c>
       <c r="C30" s="8">
-        <v>-2.47272727272727</v>
+        <v>-3.8777032065622601</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-8.4072727272727181E-3</v>
+        <v>-1.3184190902311686E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B31" s="4">
         <v>0.34</v>
       </c>
       <c r="C31" s="8">
-        <v>-5.7205720572057199</v>
+        <v>0.35005834305717598</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9449944994499448E-2</v>
+        <v>1.1901983663943983E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B32" s="4">
         <v>0.33</v>
       </c>
       <c r="C32" s="8">
-        <v>-0.81669691470054395</v>
+        <v>0.45745654162854499</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-2.6950998185117951E-3</v>
+        <v>1.5096065873741985E-3</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,11 +1755,11 @@
         <v>0.26</v>
       </c>
       <c r="C33" s="15">
-        <v>-1.6189962223421399</v>
+        <v>-4.55293472298409</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>-4.2093901780895634E-3</v>
+        <v>-1.1837630279758635E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1900,11 +1770,11 @@
         <v>0.18</v>
       </c>
       <c r="C34" s="8">
-        <v>-9.9056603773584904</v>
+        <v>-9.4240837696334996</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7830188679245282E-2</v>
+        <v>-1.6963350785340298E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1915,71 +1785,71 @@
         <v>0.12</v>
       </c>
       <c r="C35" s="8">
-        <v>1.0309278350515401</v>
+        <v>0.51020408163265296</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>1.237113402061848E-3</v>
+        <v>6.1224489795918353E-4</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B36" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="8">
-        <v>-2.4647887323943598</v>
+        <v>-1.5162454873646201</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>-1.7253521126760522E-3</v>
+        <v>-1.0613718411552342E-3</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B37" s="4">
         <v>0.05</v>
       </c>
       <c r="C37" s="8">
-        <v>-4.6535677352637004</v>
+        <v>-5.4229934924078002E-2</v>
       </c>
       <c r="D37" s="4">
         <f t="shared" si="0"/>
-        <v>-2.3267838676318503E-3</v>
+        <v>-2.7114967462039E-5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B38" s="4">
         <v>0.04</v>
       </c>
       <c r="C38" s="8">
-        <v>2.0683453237410001</v>
+        <v>-8.1938325991189398</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="0"/>
-        <v>8.2733812949640009E-4</v>
+        <v>-3.277533039647576E-3</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B39" s="4">
         <v>0.04</v>
       </c>
       <c r="C39" s="8">
-        <v>0.14336917562724</v>
+        <v>-7.8024337866857501</v>
       </c>
       <c r="D39" s="4">
         <f t="shared" si="0"/>
-        <v>5.7347670250895995E-5</v>
+        <v>-3.1209735146743001E-3</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1990,11 +1860,11 @@
         <v>0.3</v>
       </c>
       <c r="C40" s="8">
-        <v>-1.00840336134453</v>
+        <v>-4.3010752688171996</v>
       </c>
       <c r="D40" s="4">
         <f t="shared" si="0"/>
-        <v>-3.0252100840335899E-3</v>
+        <v>-1.2903225806451599E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2005,11 +1875,11 @@
         <v>8.33</v>
       </c>
       <c r="C41" s="4">
-        <v>-2.25</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D41" s="4">
         <f t="shared" si="0"/>
-        <v>-0.18742500000000001</v>
+        <v>0.18159400000000001</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2020,16 +1890,16 @@
         <v>8.27</v>
       </c>
       <c r="C42" s="4">
-        <v>-3.42</v>
+        <v>2.09</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" si="0"/>
-        <v>-0.28283399999999997</v>
+        <v>0.17284299999999997</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43" s="4">
         <v>2.56</v>
@@ -2044,7 +1914,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B44" s="5">
         <f>SUM(B2:B43)</f>
@@ -2052,7 +1922,7 @@
       </c>
       <c r="D44" s="6">
         <f>SUM(D2:D43)</f>
-        <v>0.17901596787751528</v>
+        <v>9.0107667265606289E-2</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2077,256 +1947,116 @@
       <c r="D50" s="9"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>52</v>
-      </c>
+      <c r="A55" s="5"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="30"/>
-      <c r="D55" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D55" s="20"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="18">
-        <v>46226</v>
-      </c>
-      <c r="B56" s="29">
-        <v>160454</v>
-      </c>
+      <c r="A56" s="18"/>
+      <c r="B56" s="29"/>
       <c r="C56" s="29"/>
-      <c r="D56" s="21">
-        <v>74464707242</v>
-      </c>
-      <c r="E56" s="21">
-        <v>-1765745461</v>
-      </c>
-      <c r="F56" s="24">
-        <v>1.15E-2</v>
-      </c>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="18">
-        <v>46227</v>
-      </c>
-      <c r="B57" s="29">
-        <v>159246</v>
-      </c>
+      <c r="A57" s="18"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="29"/>
-      <c r="D57" s="21">
-        <v>74038207243</v>
-      </c>
-      <c r="E57" s="21">
-        <v>-535063133</v>
-      </c>
-      <c r="F57" s="24">
-        <v>1.5E-3</v>
-      </c>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="18">
-        <v>46230</v>
-      </c>
-      <c r="B58" s="29">
-        <v>159672</v>
-      </c>
+      <c r="A58" s="18"/>
+      <c r="B58" s="29"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="21">
-        <v>74765554505</v>
-      </c>
-      <c r="E58" s="21">
-        <v>831945602</v>
-      </c>
-      <c r="F58" s="24">
-        <v>-1.4E-3</v>
-      </c>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="18">
-        <v>46231</v>
-      </c>
-      <c r="B59" s="29">
-        <v>160788</v>
-      </c>
+      <c r="A59" s="18"/>
+      <c r="B59" s="29"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="21">
-        <v>74770957010</v>
-      </c>
-      <c r="E59" s="21">
-        <v>-37325878</v>
-      </c>
-      <c r="F59" s="24">
-        <v>5.9999999999999995E-4</v>
-      </c>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="18">
-        <v>46232</v>
-      </c>
-      <c r="B60" s="29">
-        <v>162385</v>
-      </c>
+      <c r="A60" s="18"/>
+      <c r="B60" s="29"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="21">
-        <v>72261693709</v>
-      </c>
-      <c r="E60" s="21">
-        <v>-2205788922</v>
-      </c>
-      <c r="F60" s="24">
-        <v>-4.1000000000000003E-3</v>
-      </c>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="18">
-        <v>46233</v>
-      </c>
-      <c r="B61" s="29">
-        <v>160805</v>
-      </c>
+      <c r="A61" s="18"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="21">
-        <v>69072635445</v>
-      </c>
-      <c r="E61" s="21">
-        <v>-1972729322</v>
-      </c>
-      <c r="F61" s="24">
-        <v>-1.6799999999999999E-2</v>
-      </c>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="18">
-        <v>46234</v>
-      </c>
-      <c r="B62" s="29">
-        <v>159675</v>
-      </c>
+      <c r="A62" s="18"/>
+      <c r="B62" s="29"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="21">
-        <v>63472489182</v>
-      </c>
-      <c r="E62" s="21">
-        <v>-4926393640</v>
-      </c>
-      <c r="F62" s="24">
-        <v>-9.7999999999999997E-3</v>
-      </c>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="18">
-        <v>46237</v>
-      </c>
-      <c r="B63" s="29">
-        <v>154990</v>
-      </c>
+      <c r="A63" s="18"/>
+      <c r="B63" s="29"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="21">
-        <v>57303637201</v>
-      </c>
-      <c r="E63" s="21">
-        <v>-6263046591</v>
-      </c>
-      <c r="F63" s="24">
-        <v>1.5E-3</v>
-      </c>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
-        <v>46238</v>
-      </c>
-      <c r="B64" s="29">
-        <v>147034</v>
-      </c>
+      <c r="A64" s="18"/>
+      <c r="B64" s="29"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="21">
-        <v>51950990933</v>
-      </c>
-      <c r="E64" s="21">
-        <v>-5284511372</v>
-      </c>
-      <c r="F64" s="24">
-        <v>-1.1999999999999999E-3</v>
-      </c>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="18">
-        <v>46239</v>
-      </c>
-      <c r="B65" s="29">
-        <v>14301</v>
-      </c>
+      <c r="A65" s="18"/>
+      <c r="B65" s="29"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="21">
-        <v>50985089717</v>
-      </c>
-      <c r="E65" s="21">
-        <v>-1176645528</v>
-      </c>
-      <c r="F65" s="24">
-        <v>4.1000000000000003E-3</v>
-      </c>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="18">
-        <v>46240</v>
-      </c>
-      <c r="B66" s="29">
-        <v>138786</v>
-      </c>
+      <c r="A66" s="18"/>
+      <c r="B66" s="29"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="21">
-        <v>46572819665</v>
-      </c>
-      <c r="E66" s="21">
-        <v>-4303178237</v>
-      </c>
-      <c r="F66" s="24">
-        <v>-2.0999999999999999E-3</v>
-      </c>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="18">
-        <v>46241</v>
-      </c>
-      <c r="B67" s="29">
-        <v>134555</v>
-      </c>
+      <c r="A67" s="18"/>
+      <c r="B67" s="29"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="21">
-        <v>46135293160</v>
-      </c>
-      <c r="E67" s="21">
-        <v>-735791355</v>
-      </c>
-      <c r="F67" s="24">
-        <v>6.4000000000000003E-3</v>
-      </c>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="18">
-        <v>46244</v>
-      </c>
-      <c r="B68" s="29">
-        <v>133320</v>
-      </c>
+      <c r="A68" s="18"/>
+      <c r="B68" s="29"/>
       <c r="C68" s="29"/>
-      <c r="D68" s="21">
-        <v>42920929089</v>
-      </c>
-      <c r="E68" s="21">
-        <v>-3497980445</v>
-      </c>
-      <c r="F68" s="24">
-        <v>6.1000000000000004E-3</v>
-      </c>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
@@ -2434,6 +2164,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2443,26 +2193,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2485,7 +2215,7 @@
         <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -2502,11 +2232,11 @@
         <v>9.65</v>
       </c>
       <c r="C2" s="8">
-        <v>6.8119891008174296</v>
+        <v>4.7619047619047601</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.65735694822888191</v>
+        <v>0.45952380952380933</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2517,11 +2247,11 @@
         <v>9.2899999999999991</v>
       </c>
       <c r="C3" s="8">
-        <v>2.1110601193207801</v>
+        <v>9.97752808988764</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>0.19611748508490046</v>
+        <v>0.92691235955056173</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2532,26 +2262,26 @@
         <v>9.24</v>
       </c>
       <c r="C4" s="8">
-        <v>9.9123767798466496</v>
+        <v>3.5874439461883401</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.91590361445783042</v>
+        <v>0.33147982062780268</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>6.09</v>
       </c>
       <c r="C5" s="8">
-        <v>-9.9848714069591509</v>
+        <v>-4.2016806722688997</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.60807866868381222</v>
+        <v>-0.25588235294117601</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2562,11 +2292,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>-9.9719363891487305</v>
+        <v>-9.9750623441396495</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47167259120673499</v>
+        <v>-0.4718204488778055</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2577,11 +2307,11 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>0.45924225028702598</v>
+        <v>-10</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>2.0757749712973571E-2</v>
+        <v>-0.45199999999999996</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2592,11 +2322,11 @@
         <v>3.4</v>
       </c>
       <c r="C8" s="8">
-        <v>3.0680728667305801</v>
+        <v>-9.0604651162790599</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.10431447746883972</v>
+        <v>-0.30805581395348802</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2607,11 +2337,11 @@
         <v>2.73</v>
       </c>
       <c r="C9" s="8">
-        <v>-1.06122448979591</v>
+        <v>-0.66006600660065995</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8971428571428343E-2</v>
+        <v>-1.8019801980198015E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2622,11 +2352,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>0</v>
+        <v>3.12249799839871</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.1817453963170325E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2637,11 +2367,11 @@
         <v>1.67</v>
       </c>
       <c r="C11" s="8">
-        <v>0.19029495718363401</v>
+        <v>-2.0892687559354202</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>3.1779257849666883E-3</v>
+        <v>-3.4890788224121512E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2652,11 +2382,11 @@
         <v>1.58</v>
       </c>
       <c r="C12" s="8">
-        <v>-9.9709583736689194</v>
+        <v>-3.97849462365591</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-0.15754114230396893</v>
+        <v>-6.286021505376338E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2667,11 +2397,11 @@
         <v>1.57</v>
       </c>
       <c r="C13" s="8">
-        <v>-0.67681895093062605</v>
+        <v>0.39750141964792701</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0626057529610829E-2</v>
+        <v>6.2407722884724546E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2682,11 +2412,11 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="C14" s="8">
-        <v>-0.89020771513353103</v>
+        <v>-0.97305389221556804</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>-1.00593471810089E-2</v>
+        <v>-1.0995508982035917E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2697,11 +2427,11 @@
         <v>1.03</v>
       </c>
       <c r="C15" s="8">
-        <v>-5.8788947677836503E-2</v>
+        <v>0.17647058823529399</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-6.05526161081716E-4</v>
+        <v>1.8176470588235282E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2712,11 +2442,11 @@
         <v>0.98</v>
       </c>
       <c r="C16" s="8">
-        <v>0.53475935828876997</v>
+        <v>-4.2553191489361701</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>5.2406417112299455E-3</v>
+        <v>-4.170212765957447E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2727,11 +2457,11 @@
         <v>0.87</v>
       </c>
       <c r="C17" s="8">
-        <v>-2.4630541871921099</v>
+        <v>1.34680134680134</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1428571428571356E-2</v>
+        <v>1.1717171717171657E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2742,26 +2472,26 @@
         <v>0.59</v>
       </c>
       <c r="C18" s="8">
-        <v>-6.0773480662983399</v>
+        <v>-0.70588235294117596</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-3.5856353591160205E-2</v>
+        <v>-4.1647058823529384E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" s="4">
         <v>0.5</v>
       </c>
       <c r="C19" s="8">
-        <v>-4.6535677352637004</v>
+        <v>-5.4229934924078002E-2</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.32678386763185E-2</v>
+        <v>-2.7114967462039003E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2772,11 +2502,11 @@
         <v>0.48</v>
       </c>
       <c r="C20" s="8">
-        <v>9.9650349650349597</v>
+        <v>0.47694753577106502</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>4.7832167832167809E-2</v>
+        <v>2.2893481717011122E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2787,11 +2517,11 @@
         <v>0.42</v>
       </c>
       <c r="C21" s="8">
-        <v>2.75229357798165</v>
+        <v>-0.98214285714285698</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>1.1559633027522928E-2</v>
+        <v>-4.1249999999999993E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2802,11 +2532,11 @@
         <v>0.4</v>
       </c>
       <c r="C22" s="8">
-        <v>0.58582308142940798</v>
+        <v>-1.4560279557367499</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>2.343292325717632E-3</v>
+        <v>-5.8241118229470003E-3</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2817,11 +2547,11 @@
         <v>0.38</v>
       </c>
       <c r="C23" s="8">
-        <v>-1.4332247557003199</v>
+        <v>-1.0575016523463301</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-5.4462540716612162E-3</v>
+        <v>-4.0185062789160541E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2832,11 +2562,11 @@
         <v>0.25</v>
       </c>
       <c r="C24" s="8">
-        <v>-1.6189962223421399</v>
+        <v>-4.55293472298409</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-4.0474905558553495E-3</v>
+        <v>-1.1382336807460225E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,11 +2577,11 @@
         <v>0.25</v>
       </c>
       <c r="C25" s="8">
-        <v>0.77720207253885998</v>
+        <v>-4.4987146529562896</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>1.94300518134715E-3</v>
+        <v>-1.1246786632390725E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2862,11 +2592,11 @@
         <v>0.24</v>
       </c>
       <c r="C26" s="8">
-        <v>-2.47272727272727</v>
+        <v>-3.8777032065622601</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-5.9345454545454476E-3</v>
+        <v>-9.3064876957494238E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2877,11 +2607,11 @@
         <v>0.23</v>
       </c>
       <c r="C27" s="8">
-        <v>-2.0408163265306101</v>
+        <v>0</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-4.6938775510204037E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2892,41 +2622,41 @@
         <v>0.2</v>
       </c>
       <c r="C28" s="8">
-        <v>2.72727272727272</v>
+        <v>-4.01633764465622</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>5.4545454545454394E-3</v>
+        <v>-8.0326752893124416E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B29" s="13">
         <v>0.08</v>
       </c>
       <c r="C29" s="15">
-        <v>2.0683453237410001</v>
+        <v>-8.1938325991189398</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>1.6546762589928002E-3</v>
+        <v>-6.5550660792951521E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" s="4">
         <v>0.01</v>
       </c>
       <c r="C30" s="8">
-        <v>-2.4647887323943598</v>
+        <v>-1.5162454873646201</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-2.4647887323943596E-4</v>
+        <v>-1.51624548736462E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2937,11 +2667,11 @@
         <v>7.99</v>
       </c>
       <c r="C31" s="4">
-        <v>-2.25</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-0.17977499999999999</v>
+        <v>0.17418200000000003</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2952,16 +2682,16 @@
         <v>7.7</v>
       </c>
       <c r="C32" s="4">
-        <v>-3.42</v>
+        <v>2.09</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-0.26334000000000002</v>
+        <v>0.16092999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B33" s="4">
         <v>2.5</v>
@@ -2976,52 +2706,52 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B34" s="4">
         <v>0.78</v>
       </c>
       <c r="C34" s="4">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>1.0140000000000001E-3</v>
+        <v>1.0920000000000001E-3</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B35" s="4">
         <v>0.57999999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>-9.92</v>
+        <v>-10.07</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-5.7535999999999997E-2</v>
+        <v>-5.8405999999999993E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B36" s="4">
         <v>0.06</v>
       </c>
       <c r="C36" s="4">
-        <v>1.36</v>
+        <v>0.5</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" si="0"/>
-        <v>8.160000000000001E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B37" s="5">
         <f>SUM(B2:B36)</f>
@@ -3029,7 +2759,7 @@
       </c>
       <c r="D37" s="6">
         <f>SUM(D2:D36)</f>
-        <v>8.9608990689898624E-2</v>
+        <v>0.37184087451756931</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3054,256 +2784,116 @@
       <c r="D45" s="9"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>52</v>
-      </c>
+      <c r="A53" s="5"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="30"/>
-      <c r="D53" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D53" s="20"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
-        <v>46226</v>
-      </c>
-      <c r="B54" s="29">
-        <v>78223</v>
-      </c>
+      <c r="A54" s="18"/>
+      <c r="B54" s="29"/>
       <c r="C54" s="29"/>
-      <c r="D54" s="21">
-        <v>38343912280</v>
-      </c>
-      <c r="E54" s="22">
-        <v>-656504519</v>
-      </c>
-      <c r="F54" s="24">
-        <v>8.0999999999999996E-3</v>
-      </c>
+      <c r="D54" s="21"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="18">
-        <v>46227</v>
-      </c>
-      <c r="B55" s="29">
-        <v>78055</v>
-      </c>
+      <c r="A55" s="18"/>
+      <c r="B55" s="29"/>
       <c r="C55" s="29"/>
-      <c r="D55" s="21">
-        <v>38547597437</v>
-      </c>
-      <c r="E55" s="22">
-        <v>45631782</v>
-      </c>
-      <c r="F55" s="24">
-        <v>4.1000000000000003E-3</v>
-      </c>
+      <c r="D55" s="21"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="18">
-        <v>46230</v>
-      </c>
-      <c r="B56" s="29">
-        <v>78840</v>
-      </c>
+      <c r="A56" s="18"/>
+      <c r="B56" s="29"/>
       <c r="C56" s="29"/>
-      <c r="D56" s="21">
-        <v>39148877217</v>
-      </c>
-      <c r="E56" s="22">
-        <v>706423581</v>
-      </c>
-      <c r="F56" s="24">
-        <v>-2.7000000000000001E-3</v>
-      </c>
+      <c r="D56" s="21"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="18">
-        <v>46231</v>
-      </c>
-      <c r="B57" s="29">
-        <v>79795</v>
-      </c>
+      <c r="A57" s="18"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="29"/>
-      <c r="D57" s="21">
-        <v>39293398935</v>
-      </c>
-      <c r="E57" s="22">
-        <v>119712414</v>
-      </c>
-      <c r="F57" s="24">
-        <v>5.9999999999999995E-4</v>
-      </c>
+      <c r="D57" s="21"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="23">
-        <v>46232</v>
-      </c>
-      <c r="B58" s="29">
-        <v>80830</v>
-      </c>
+      <c r="A58" s="23"/>
+      <c r="B58" s="29"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="21">
-        <v>38188651284</v>
-      </c>
-      <c r="E58" s="21">
-        <v>-933851594</v>
-      </c>
-      <c r="F58" s="24">
-        <v>-4.3E-3</v>
-      </c>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="18">
-        <v>46233</v>
-      </c>
-      <c r="B59" s="29">
-        <v>80272</v>
-      </c>
+      <c r="A59" s="18"/>
+      <c r="B59" s="29"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="21">
-        <v>36982629736</v>
-      </c>
-      <c r="E59" s="21">
-        <v>-1972729322</v>
-      </c>
-      <c r="F59" s="24">
-        <v>-1.4E-2</v>
-      </c>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="18">
-        <v>46234</v>
-      </c>
-      <c r="B60" s="29">
-        <v>79803</v>
-      </c>
+      <c r="A60" s="18"/>
+      <c r="B60" s="29"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="21">
-        <v>33560330080</v>
-      </c>
-      <c r="E60" s="21">
-        <v>-3201067093</v>
-      </c>
-      <c r="F60" s="24">
-        <v>-6.0000000000000001E-3</v>
-      </c>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="18">
-        <v>46237</v>
-      </c>
-      <c r="B61" s="29">
-        <v>77044</v>
-      </c>
+      <c r="A61" s="18"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="21">
-        <v>29529617301</v>
-      </c>
-      <c r="E61" s="21">
-        <v>-4237217388</v>
-      </c>
-      <c r="F61" s="24">
-        <v>6.1999999999999998E-3</v>
-      </c>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="18">
-        <v>46238</v>
-      </c>
-      <c r="B62" s="29">
-        <v>72101</v>
-      </c>
+      <c r="A62" s="18"/>
+      <c r="B62" s="29"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="21">
-        <v>26219512523</v>
-      </c>
-      <c r="E62" s="21">
-        <v>-3580010999</v>
-      </c>
-      <c r="F62" s="24">
-        <v>9.1000000000000004E-3</v>
-      </c>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="18">
-        <v>46239</v>
-      </c>
-      <c r="B63" s="29">
-        <v>69071</v>
-      </c>
+      <c r="A63" s="18"/>
+      <c r="B63" s="29"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="21">
-        <v>26446162886</v>
-      </c>
-      <c r="E63" s="21">
-        <v>-148518068</v>
-      </c>
-      <c r="F63" s="24">
-        <v>1.43E-2</v>
-      </c>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
-        <v>46240</v>
-      </c>
-      <c r="B64" s="29">
-        <v>68911</v>
-      </c>
+      <c r="A64" s="18"/>
+      <c r="B64" s="29"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="21">
-        <v>26257978960</v>
-      </c>
-      <c r="E64" s="21">
-        <v>-4303178237</v>
-      </c>
-      <c r="F64" s="24">
-        <v>-1.7899999999999999E-2</v>
-      </c>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="18">
-        <v>46241</v>
-      </c>
-      <c r="B65" s="29">
-        <v>70356</v>
-      </c>
+      <c r="A65" s="18"/>
+      <c r="B65" s="29"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="21">
-        <v>27495305201</v>
-      </c>
-      <c r="E65" s="21">
-        <v>1190923365</v>
-      </c>
-      <c r="F65" s="24">
-        <v>1.8E-3</v>
-      </c>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="18">
-        <v>46244</v>
-      </c>
-      <c r="B66" s="29">
-        <v>70743</v>
-      </c>
+      <c r="A66" s="18"/>
+      <c r="B66" s="29"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="21">
-        <v>25035325105</v>
-      </c>
-      <c r="E66" s="21">
-        <v>-2430448566</v>
-      </c>
-      <c r="F66" s="24">
-        <v>-1.1000000000000001E-3</v>
-      </c>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
@@ -4011,6 +3601,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -4024,97 +3705,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -4155,11 +3745,11 @@
         <v>52.75</v>
       </c>
       <c r="C2" s="8">
-        <v>2.3536165327210101</v>
+        <v>0.28042624789680298</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>1.2415327210103329</v>
+        <v>0.14792484576556358</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4170,11 +3760,11 @@
         <v>11.12</v>
       </c>
       <c r="C3" s="8">
-        <v>-3.8095238095238</v>
+        <v>-2.26308345120226</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.42361904761904656</v>
+        <v>-0.25165487977369128</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4185,11 +3775,11 @@
         <v>0.53</v>
       </c>
       <c r="C4" s="8">
-        <v>-9.8958333333333304</v>
+        <v>9.6339113680154104E-2</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-5.244791666666665E-2</v>
+        <v>5.1059730250481677E-4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -4200,16 +3790,16 @@
         <v>29.82</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.53</v>
+        <v>1.98</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.15804600000000002</v>
+        <v>0.59043599999999996</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B6" s="5">
         <f>B2++B3+B4+B5</f>
@@ -4218,7 +3808,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="6">
         <f>D2+D3+D4+D5</f>
-        <v>0.60741975672461967</v>
+        <v>0.48721656329437707</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4252,256 +3842,116 @@
       <c r="D11" s="10"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>52</v>
-      </c>
+      <c r="A31" s="5"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="30"/>
-      <c r="D31" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="23">
-        <v>46226</v>
-      </c>
-      <c r="B32" s="29">
-        <v>48221</v>
-      </c>
+      <c r="A32" s="23"/>
+      <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="21">
-        <v>28591206600</v>
-      </c>
-      <c r="E32" s="21">
-        <v>578476685</v>
-      </c>
-      <c r="F32" s="24">
-        <v>3.3999999999999998E-3</v>
-      </c>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="24"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="23">
-        <v>46227</v>
-      </c>
-      <c r="B33" s="29">
-        <v>48802</v>
-      </c>
+      <c r="A33" s="23"/>
+      <c r="B33" s="29"/>
       <c r="C33" s="29"/>
-      <c r="D33" s="21">
-        <v>29255953804</v>
-      </c>
-      <c r="E33" s="21">
-        <v>630289948</v>
-      </c>
-      <c r="F33" s="24">
-        <v>1.1999999999999999E-3</v>
-      </c>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="23">
-        <v>46230</v>
-      </c>
-      <c r="B34" s="29">
-        <v>49403</v>
-      </c>
+      <c r="A34" s="23"/>
+      <c r="B34" s="29"/>
       <c r="C34" s="29"/>
-      <c r="D34" s="21">
-        <v>30359209400</v>
-      </c>
-      <c r="E34" s="21">
-        <v>781254453</v>
-      </c>
-      <c r="F34" s="24">
-        <v>1.0999999999999999E-2</v>
-      </c>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="23">
-        <v>46231</v>
-      </c>
-      <c r="B35" s="29">
-        <v>49817</v>
-      </c>
+      <c r="A35" s="23"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="29"/>
-      <c r="D35" s="21">
-        <v>30985486603</v>
-      </c>
-      <c r="E35" s="21">
-        <v>577239728</v>
-      </c>
-      <c r="F35" s="24">
-        <v>1.6000000000000001E-3</v>
-      </c>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="23">
-        <v>46232</v>
-      </c>
-      <c r="B36" s="29">
-        <v>50631</v>
-      </c>
+      <c r="A36" s="23"/>
+      <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="21">
-        <v>32047144824</v>
-      </c>
-      <c r="E36" s="21">
-        <v>1031302629</v>
-      </c>
-      <c r="F36" s="24">
-        <v>1E-3</v>
-      </c>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="23">
-        <v>46233</v>
-      </c>
-      <c r="B37" s="29">
-        <v>50968</v>
-      </c>
+      <c r="A37" s="23"/>
+      <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="21">
-        <v>32438714789</v>
-      </c>
-      <c r="E37" s="21">
-        <v>329409310</v>
-      </c>
-      <c r="F37" s="24">
-        <v>1.9E-3</v>
-      </c>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="24"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="23">
-        <v>46234</v>
-      </c>
-      <c r="B38" s="29">
-        <v>51171</v>
-      </c>
+      <c r="A38" s="23"/>
+      <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="21">
-        <v>31996446996</v>
-      </c>
-      <c r="E38" s="21">
-        <v>-281801311</v>
-      </c>
-      <c r="F38" s="24">
-        <v>-4.8999999999999998E-3</v>
-      </c>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="23">
-        <v>46237</v>
-      </c>
-      <c r="B39" s="29">
-        <v>51266</v>
-      </c>
+      <c r="A39" s="23"/>
+      <c r="B39" s="29"/>
       <c r="C39" s="29"/>
-      <c r="D39" s="21">
-        <v>32456533228</v>
-      </c>
-      <c r="E39" s="21">
-        <v>257679653</v>
-      </c>
-      <c r="F39" s="24">
-        <v>6.3E-3</v>
-      </c>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="23">
-        <v>46238</v>
-      </c>
-      <c r="B40" s="29">
-        <v>51083</v>
-      </c>
+      <c r="A40" s="23"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="21">
-        <v>31890486608</v>
-      </c>
-      <c r="E40" s="21">
-        <v>-821515583</v>
-      </c>
-      <c r="F40" s="24">
-        <v>7.9000000000000008E-3</v>
-      </c>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="23">
-        <v>46239</v>
-      </c>
-      <c r="B41" s="29">
-        <v>51200</v>
-      </c>
+      <c r="A41" s="23"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="29"/>
-      <c r="D41" s="21">
-        <v>32440313296</v>
-      </c>
-      <c r="E41" s="21">
-        <v>642330037</v>
-      </c>
-      <c r="F41" s="24">
-        <v>-2.8999999999999998E-3</v>
-      </c>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="23">
-        <v>46240</v>
-      </c>
-      <c r="B42" s="29">
-        <v>51726</v>
-      </c>
+      <c r="A42" s="23"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="29"/>
-      <c r="D42" s="21">
-        <v>34436195517</v>
-      </c>
-      <c r="E42" s="21">
-        <v>1878923846</v>
-      </c>
-      <c r="F42" s="24">
-        <v>3.5999999999999999E-3</v>
-      </c>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="23">
-        <v>46241</v>
-      </c>
-      <c r="B43" s="29">
-        <v>52189</v>
-      </c>
+      <c r="A43" s="23"/>
+      <c r="B43" s="29"/>
       <c r="C43" s="29"/>
-      <c r="D43" s="21">
-        <v>34489939181</v>
-      </c>
-      <c r="E43" s="21">
-        <v>-25196290</v>
-      </c>
-      <c r="F43" s="24">
-        <v>2.3E-3</v>
-      </c>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="23">
-        <v>46244</v>
-      </c>
-      <c r="B44" s="29">
-        <v>52228</v>
-      </c>
+      <c r="A44" s="23"/>
+      <c r="B44" s="29"/>
       <c r="C44" s="29"/>
-      <c r="D44" s="21">
-        <v>34191459593</v>
-      </c>
-      <c r="E44" s="21">
-        <v>-347610039</v>
-      </c>
-      <c r="F44" s="24">
-        <v>1.1000000000000001E-3</v>
-      </c>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
@@ -5281,6 +4731,107 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -5293,107 +4844,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5433,11 +4883,11 @@
         <v>9.14</v>
       </c>
       <c r="C2" s="3">
-        <v>0.80482897384305796</v>
+        <v>1.3063357282821599</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>7.3561368209255504E-2</v>
+        <v>0.11939908556498942</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5448,11 +4898,11 @@
         <v>8.17</v>
       </c>
       <c r="C3" s="3">
-        <v>-2.0408163265306101</v>
+        <v>1.19760479041916</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>-0.16673469387755083</v>
+        <v>9.7844311377245377E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5463,11 +4913,11 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="C4" s="3">
-        <v>1.5625</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>0.12687499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5493,26 +4943,26 @@
         <v>5.99</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.87</v>
+        <v>3.12249799839871</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-5.2113000000000007E-2</v>
+        <v>0.18703763010408272</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B7" s="4">
         <v>4.88</v>
       </c>
-      <c r="C7" s="27">
-        <v>-0.47058823529411697</v>
+      <c r="C7" s="3">
+        <v>-0.87</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>-2.2964705882352908E-2</v>
+        <v>-4.2455999999999994E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5522,12 +4972,12 @@
       <c r="B8" s="26">
         <v>4.46</v>
       </c>
-      <c r="C8" s="3">
-        <v>3.30578512396694</v>
+      <c r="C8" s="27">
+        <v>-0.70921985815602795</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.14743801652892552</v>
+        <v>-3.163120567375885E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5538,11 +4988,11 @@
         <v>4.17</v>
       </c>
       <c r="C9" s="3">
-        <v>1.0309278350515401</v>
+        <v>3.1333333333333302</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>4.2989690721649217E-2</v>
+        <v>0.13065999999999986</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5553,11 +5003,11 @@
         <v>3.23</v>
       </c>
       <c r="C10" s="3">
-        <v>-1.06122448979591</v>
+        <v>0.51020408163265296</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-3.4277551020407894E-2</v>
+        <v>1.647959183673469E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5567,12 +5017,12 @@
       <c r="B11" s="4">
         <v>2.84</v>
       </c>
-      <c r="C11" s="28">
-        <v>-1.4332247557003199</v>
+      <c r="C11" s="3">
+        <v>-0.66006600660065995</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-4.0703583061889086E-2</v>
+        <v>-1.8745874587458741E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5582,12 +5032,12 @@
       <c r="B12" s="4">
         <v>2.54</v>
       </c>
-      <c r="C12" s="3">
-        <v>3.0680728667305801</v>
+      <c r="C12" s="28">
+        <v>-1.0575016523463301</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>7.7929050814956741E-2</v>
+        <v>-2.6860541969596783E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5598,41 +5048,41 @@
         <v>2.37</v>
       </c>
       <c r="C13" s="3">
-        <v>-2.9</v>
+        <v>-9.0604651162790599</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-6.8729999999999999E-2</v>
+        <v>-0.21473302325581373</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B14" s="26">
         <v>2.37</v>
       </c>
-      <c r="C14" s="27">
-        <v>-4.6535677352637004</v>
+      <c r="C14" s="3">
+        <v>-2.9</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-0.1102895553257497</v>
+        <v>-6.8729999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B15" s="26">
         <v>2.21</v>
       </c>
-      <c r="C15" s="3">
-        <v>-1.6189962223421399</v>
+      <c r="C15" s="27">
+        <v>-5.4229934924078002E-2</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-3.5779816513761296E-2</v>
+        <v>-1.1984815618221239E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5643,11 +5093,11 @@
         <v>1.93</v>
       </c>
       <c r="C16" s="3">
-        <v>0.51107325383304902</v>
+        <v>-4.55293472298409</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>9.8637137989778453E-3</v>
+        <v>-8.7871640153592931E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5658,26 +5108,26 @@
         <v>1.77</v>
       </c>
       <c r="C17" s="3">
-        <v>-0.91</v>
+        <v>-1.0169491525423699</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6107E-2</v>
+        <v>-1.799999999999995E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B18" s="4">
         <v>1.53</v>
       </c>
       <c r="C18" s="3">
-        <v>-2.0226537216828402</v>
+        <v>-0.91</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-3.0946601941747455E-2</v>
+        <v>-1.3923000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5688,41 +5138,41 @@
         <v>1.51</v>
       </c>
       <c r="C19" s="3">
-        <v>0.36</v>
+        <v>-0.74318744838976003</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>5.4359999999999999E-3</v>
+        <v>-1.1222130470685376E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B20" s="4">
         <v>1.44</v>
       </c>
       <c r="C20" s="3">
-        <v>-1.82</v>
+        <v>0.36</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6207999999999999E-2</v>
+        <v>5.1839999999999994E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B21" s="4">
         <v>1.44</v>
       </c>
       <c r="C21" s="3">
-        <v>2.7204030226700202</v>
+        <v>-1.82</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>3.9173803526448288E-2</v>
+        <v>-2.6207999999999999E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5732,12 +5182,12 @@
       <c r="B22" s="4">
         <v>1.43</v>
       </c>
-      <c r="C22" s="27">
-        <v>-6.0773480662983399</v>
+      <c r="C22" s="3">
+        <v>-1.9617459538989701</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>-8.6906077348066268E-2</v>
+        <v>-2.805296714075527E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5748,11 +5198,11 @@
         <v>1.42</v>
       </c>
       <c r="C23" s="27">
-        <v>-0.89020771513353103</v>
+        <v>-0.70588235294117596</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-1.264094955489614E-2</v>
+        <v>-1.0023529411764698E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5763,11 +5213,11 @@
         <v>1.4</v>
       </c>
       <c r="C24" s="27">
-        <v>-0.38885288399222201</v>
+        <v>-0.97305389221556804</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>-5.4439403758911077E-3</v>
+        <v>-1.3622754491017953E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5778,26 +5228,26 @@
         <v>1.33</v>
       </c>
       <c r="C25" s="27">
-        <v>4.76</v>
+        <v>-1.8217306441119001</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>6.3308000000000003E-2</v>
+        <v>-2.4229017566688271E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B26" s="26">
         <v>1.25</v>
       </c>
       <c r="C26" s="27">
-        <v>0.19029495718363401</v>
+        <v>4.76</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>2.3786869647954251E-3</v>
+        <v>5.949999999999999E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5808,71 +5258,71 @@
         <v>1.17</v>
       </c>
       <c r="C27" s="27">
-        <v>-1.66</v>
+        <v>-2.0892687559354202</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>-1.9421999999999998E-2</v>
+        <v>-2.4444444444444414E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B28" s="26">
         <v>1.04</v>
       </c>
       <c r="C28" s="27">
-        <v>0.57999999999999996</v>
+        <v>-1.66</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>6.0319999999999992E-3</v>
+        <v>-1.7263999999999998E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B29" s="26">
         <v>0.9</v>
       </c>
       <c r="C29" s="27">
-        <v>4.6100000000000003</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>4.1489999999999999E-2</v>
+        <v>5.2199999999999998E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" s="26">
         <v>0.84</v>
       </c>
       <c r="C30" s="27">
-        <v>-0.81669691470054395</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>-6.8602540834845696E-3</v>
+        <v>3.8724000000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="26">
         <v>0.82</v>
       </c>
       <c r="C31" s="27">
-        <v>-0.31496062992125901</v>
+        <v>0.45745654162854499</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5826771653543234E-3</v>
+        <v>3.751143641354069E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5883,26 +5333,26 @@
         <v>0.8</v>
       </c>
       <c r="C32" s="27">
-        <v>0.76</v>
+        <v>-7.89889415481832E-2</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>6.0800000000000012E-3</v>
+        <v>-6.3191153238546555E-4</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B33" s="26">
         <v>0.79</v>
       </c>
       <c r="C33" s="27">
-        <v>-1.19981541301338</v>
+        <v>0.76</v>
       </c>
       <c r="D33" s="7">
         <f t="shared" si="0"/>
-        <v>-9.4785417628057023E-3</v>
+        <v>6.0040000000000007E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5913,11 +5363,11 @@
         <v>0.76</v>
       </c>
       <c r="C34" s="27">
-        <v>0.53475935828876997</v>
+        <v>6.95936478281177</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>4.0641711229946519E-3</v>
+        <v>5.2891172349369457E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5928,226 +5378,226 @@
         <v>0.73</v>
       </c>
       <c r="C35" s="27">
-        <v>0.78</v>
+        <v>-4.2553191489361701</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>5.6940000000000003E-3</v>
+        <v>-3.106382978723404E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B36" s="26">
         <v>0.72</v>
       </c>
       <c r="C36" s="27">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="0"/>
-        <v>4.3920000000000001E-3</v>
+        <v>5.6159999999999995E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B37" s="26">
         <v>0.71</v>
       </c>
       <c r="C37" s="27">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="0"/>
-        <v>5.9639999999999997E-3</v>
+        <v>4.3309999999999998E-3</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B38" s="26">
         <v>0.7</v>
       </c>
       <c r="C38" s="27">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="0"/>
-        <v>6.9999999999999988E-4</v>
+        <v>5.8799999999999998E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B39" s="26">
         <v>0.7</v>
       </c>
       <c r="C39" s="27">
-        <v>0.97</v>
+        <v>0.1</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="0"/>
-        <v>6.7899999999999992E-3</v>
+        <v>6.9999999999999988E-4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B40" s="26">
         <v>0.64</v>
       </c>
       <c r="C40" s="27">
-        <v>0.11</v>
+        <v>0.97</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="0"/>
-        <v>7.0400000000000009E-4</v>
+        <v>6.208E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B41" s="26">
         <v>0.63</v>
       </c>
       <c r="C41" s="27">
-        <v>4.43</v>
+        <v>0.11</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="0"/>
-        <v>2.7908999999999996E-2</v>
+        <v>6.9300000000000004E-4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B42" s="26">
         <v>0.61</v>
       </c>
       <c r="C42" s="27">
-        <v>1.82</v>
+        <v>4.43</v>
       </c>
       <c r="D42" s="7">
         <f t="shared" si="0"/>
-        <v>1.1102000000000001E-2</v>
+        <v>2.7022999999999998E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B43" s="26">
         <v>0.56999999999999995</v>
       </c>
       <c r="C43" s="27">
-        <v>-0.05</v>
+        <v>1.82</v>
       </c>
       <c r="D43" s="7">
         <f t="shared" si="0"/>
-        <v>-2.8499999999999999E-4</v>
+        <v>1.0374E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B44" s="26">
         <v>0.55000000000000004</v>
       </c>
       <c r="C44" s="27">
-        <v>-1.91</v>
+        <v>-0.05</v>
       </c>
       <c r="D44" s="7">
         <f t="shared" si="0"/>
-        <v>-1.0505E-2</v>
+        <v>-2.7500000000000002E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B45" s="26">
         <v>0.5</v>
       </c>
       <c r="C45" s="27">
-        <v>1.41</v>
+        <v>-1.91</v>
       </c>
       <c r="D45" s="7">
         <f t="shared" si="0"/>
-        <v>7.0499999999999998E-3</v>
+        <v>-9.5499999999999995E-3</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B46" s="26">
         <v>0.5</v>
       </c>
       <c r="C46" s="27">
-        <v>0.32</v>
+        <v>1.41</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>1.6000000000000001E-3</v>
+        <v>7.0499999999999998E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B47" s="26">
         <v>0.45</v>
       </c>
       <c r="C47" s="27">
-        <v>5.47</v>
+        <v>0.32</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>2.4615000000000001E-2</v>
+        <v>1.4400000000000001E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B48" s="26">
         <v>0.4</v>
       </c>
       <c r="C48" s="27">
-        <v>2.52</v>
+        <v>5.47</v>
       </c>
       <c r="D48" s="7">
         <f t="shared" si="0"/>
-        <v>1.008E-2</v>
+        <v>2.188E-2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B49" s="26">
         <v>0.33</v>
       </c>
       <c r="C49" s="27">
-        <v>-0.17</v>
+        <v>2.52</v>
       </c>
       <c r="D49" s="7">
         <f t="shared" si="0"/>
-        <v>-5.6100000000000008E-4</v>
+        <v>8.3160000000000005E-3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B50" s="26">
         <v>0.16</v>
@@ -6162,7 +5612,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B51" s="5">
         <f>SUM(B2:B50)</f>
@@ -6171,260 +5621,120 @@
       <c r="C51" s="5"/>
       <c r="D51" s="6">
         <f>SUM(D2:D50)</f>
-        <v>-6.5924462259540845E-3</v>
+        <v>0.10119658282675704</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="30" t="s">
-        <v>52</v>
-      </c>
+      <c r="A62" s="5"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="30"/>
-      <c r="D62" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="D62" s="20"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="23">
-        <v>46226</v>
-      </c>
-      <c r="B63" s="29">
-        <v>18186</v>
-      </c>
+      <c r="A63" s="23"/>
+      <c r="B63" s="29"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="21">
-        <v>1825486354</v>
-      </c>
-      <c r="E63" s="21">
-        <v>49785912</v>
-      </c>
-      <c r="F63" s="24">
-        <v>4.7000000000000002E-3</v>
-      </c>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="23">
-        <v>46227</v>
-      </c>
-      <c r="B64" s="29">
-        <v>18753</v>
-      </c>
+      <c r="A64" s="23"/>
+      <c r="B64" s="29"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="21">
-        <v>1898338108</v>
-      </c>
-      <c r="E64" s="21">
-        <v>79391973</v>
-      </c>
-      <c r="F64" s="24">
-        <v>-3.5999999999999999E-3</v>
-      </c>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="23">
-        <v>46230</v>
-      </c>
-      <c r="B65" s="29">
-        <v>19293</v>
-      </c>
+      <c r="A65" s="23"/>
+      <c r="B65" s="29"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="21">
-        <v>2016158831</v>
-      </c>
-      <c r="E65" s="21">
-        <v>115257058</v>
-      </c>
-      <c r="F65" s="24">
-        <v>1.4E-3</v>
-      </c>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="23">
-        <v>46231</v>
-      </c>
-      <c r="B66" s="29">
-        <v>19624</v>
-      </c>
+      <c r="A66" s="23"/>
+      <c r="B66" s="29"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="21">
-        <v>2053257616</v>
-      </c>
-      <c r="E66" s="21">
-        <v>37759305</v>
-      </c>
-      <c r="F66" s="24">
-        <v>-2.9999999999999997E-4</v>
-      </c>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="23">
-        <v>46232</v>
-      </c>
-      <c r="B67" s="29">
-        <v>20120</v>
-      </c>
+      <c r="A67" s="23"/>
+      <c r="B67" s="29"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="21">
-        <v>2073450735</v>
-      </c>
-      <c r="E67" s="21">
-        <v>45076881</v>
-      </c>
-      <c r="F67" s="24">
-        <v>-1.21E-2</v>
-      </c>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="23">
-        <v>46233</v>
-      </c>
-      <c r="B68" s="29">
-        <v>20320</v>
-      </c>
+      <c r="A68" s="23"/>
+      <c r="B68" s="29"/>
       <c r="C68" s="29"/>
-      <c r="D68" s="21">
-        <v>2050352793</v>
-      </c>
-      <c r="E68" s="21">
-        <v>-24388706</v>
-      </c>
-      <c r="F68" s="24">
-        <v>5.9999999999999995E-4</v>
-      </c>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="23">
-        <v>46234</v>
-      </c>
-      <c r="B69" s="29">
-        <v>20380</v>
-      </c>
+      <c r="A69" s="23"/>
+      <c r="B69" s="29"/>
       <c r="C69" s="29"/>
-      <c r="D69" s="21">
-        <v>1988789335</v>
-      </c>
-      <c r="E69" s="21">
-        <v>-68771429</v>
-      </c>
-      <c r="F69" s="24">
-        <v>3.5000000000000001E-3</v>
-      </c>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="23">
-        <v>46237</v>
-      </c>
-      <c r="B70" s="29">
-        <v>20094</v>
-      </c>
+      <c r="A70" s="23"/>
+      <c r="B70" s="29"/>
       <c r="C70" s="29"/>
-      <c r="D70" s="21">
-        <v>1984485111</v>
-      </c>
-      <c r="E70" s="21">
-        <v>-13488765</v>
-      </c>
-      <c r="F70" s="24">
-        <v>4.5999999999999999E-3</v>
-      </c>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="23">
-        <v>46238</v>
-      </c>
-      <c r="B71" s="29">
-        <v>20026</v>
-      </c>
+      <c r="A71" s="23"/>
+      <c r="B71" s="29"/>
       <c r="C71" s="29"/>
-      <c r="D71" s="21">
-        <v>1998771298</v>
-      </c>
-      <c r="E71" s="21">
-        <v>5725163</v>
-      </c>
-      <c r="F71" s="24">
-        <v>4.3E-3</v>
-      </c>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="23">
-        <v>46239</v>
-      </c>
-      <c r="B72" s="29">
-        <v>20393</v>
-      </c>
+      <c r="A72" s="23"/>
+      <c r="B72" s="29"/>
       <c r="C72" s="29"/>
-      <c r="D72" s="21">
-        <v>2081639950</v>
-      </c>
-      <c r="E72" s="21">
-        <v>54568901</v>
-      </c>
-      <c r="F72" s="24">
-        <v>1.4200000000000001E-2</v>
-      </c>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="23">
-        <v>46240</v>
-      </c>
-      <c r="B73" s="29">
-        <v>20807</v>
-      </c>
+      <c r="A73" s="23"/>
+      <c r="B73" s="29"/>
       <c r="C73" s="29"/>
-      <c r="D73" s="21">
-        <v>2244184283</v>
-      </c>
-      <c r="E73" s="21">
-        <v>134383884</v>
-      </c>
-      <c r="F73" s="24">
-        <v>1.35E-2</v>
-      </c>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="23">
-        <v>46241</v>
-      </c>
-      <c r="B74" s="29">
-        <v>21724</v>
-      </c>
+      <c r="A74" s="23"/>
+      <c r="B74" s="29"/>
       <c r="C74" s="29"/>
-      <c r="D74" s="21">
-        <v>2555268873</v>
-      </c>
-      <c r="E74" s="21">
-        <v>295774874</v>
-      </c>
-      <c r="F74" s="24">
-        <v>6.7999999999999996E-3</v>
-      </c>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="23">
-        <v>46244</v>
-      </c>
-      <c r="B75" s="29">
-        <v>22925</v>
-      </c>
+      <c r="A75" s="23"/>
+      <c r="B75" s="29"/>
       <c r="C75" s="29"/>
-      <c r="D75" s="21">
-        <v>2826840748</v>
-      </c>
-      <c r="E75" s="21">
-        <v>254561602</v>
-      </c>
-      <c r="F75" s="24">
-        <v>2.8E-3</v>
-      </c>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F76" s="24"/>
@@ -6460,4 +5770,557 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E8BA3D-B712-4741-9640-DE3E472A475C}">
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="4">
+        <v>7.83</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7">
+        <f>B2*C2/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>7.91</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <f>B3*C3/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>7.32</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-4.55293472298409</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" ref="D4:D25" si="0">B4*C4/100</f>
+        <v>-0.33327482172243544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6.1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.19760479041916</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>7.3053892215568753E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="C6" s="3">
+        <v>9.9551569506726398</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>0.50870852017937196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.75</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.3063357282821599</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>6.2050947093402593E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4">
+        <v>4.49</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.51020408163265296</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="0"/>
+        <v>2.290816326530612E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4.16</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.17647058823529399</v>
+      </c>
+      <c r="D9" s="7">
+        <f t="shared" si="0"/>
+        <v>7.3411764705882294E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3.99</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-0.66006600660065995</v>
+      </c>
+      <c r="D10" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.6336633663366332E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4">
+        <v>3.98</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.47694753577106502</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" si="0"/>
+        <v>1.8982511923688387E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3.97</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-2.0686175580221899</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="0"/>
+        <v>-8.2124117053480938E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3.96</v>
+      </c>
+      <c r="C13" s="3">
+        <v>8.1138040042149608</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.32130663856691244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="4">
+        <v>3.55</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-8</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.28399999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3.41</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-9.9550898203592801</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.33946856287425148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3.36</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-10</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.33600000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4">
+        <v>3.08</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.12249799839871</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="0"/>
+        <v>9.6172938350680276E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2.86</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-3.79596678529062</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.10856465005931172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2.66</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-2.3635340461451801</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="0"/>
+        <v>-6.2870005627461797E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2.62</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2.58</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-1.56782549420586</v>
+      </c>
+      <c r="D21" s="7">
+        <f t="shared" si="0"/>
+        <v>-4.0449897750511193E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2.31</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3.1333333333333302</v>
+      </c>
+      <c r="D22" s="7">
+        <f t="shared" si="0"/>
+        <v>7.2379999999999931E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2.25</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-1.02941176470588</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.3161764705882302E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="4">
+        <v>1.85</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9.6525096525096499E-2</v>
+      </c>
+      <c r="D24" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7857142857142852E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="4">
+        <v>1.74</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-3.6910457963089498</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" si="0"/>
+        <v>-6.4224196855775725E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="5">
+        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25</f>
+        <v>95.839999999999989</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D25</f>
+        <v>-0.51578414796124394</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="17"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="18"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="21"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="22"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="18"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="22"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="18"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="22"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="18"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="22"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="18"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="22"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="18"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="22"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="18"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="22"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="18"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="22"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="18"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="22"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="18"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="22"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="18"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="22"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="18"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="22"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="18"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BB8CE2-FB2A-476A-B28E-8E848C13E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2362F94F-228A-48EB-8E43-44181027B182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23730" yWindow="105" windowWidth="12435" windowHeight="20475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="120" windowWidth="12720" windowHeight="20595" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="106">
   <si>
     <t>DSTKF</t>
   </si>
@@ -122,15 +122,9 @@
     <t>DAPGM</t>
   </si>
   <si>
-    <t>TTKOM</t>
-  </si>
-  <si>
     <t>GARAN</t>
   </si>
   <si>
-    <t>ENKAI</t>
-  </si>
-  <si>
     <t>AKSEN</t>
   </si>
   <si>
@@ -143,24 +137,12 @@
     <t>IZFAS</t>
   </si>
   <si>
-    <t>GUBRF</t>
-  </si>
-  <si>
     <t>SKBNK</t>
   </si>
   <si>
-    <t>MPARK</t>
-  </si>
-  <si>
-    <t>DCTTR</t>
-  </si>
-  <si>
     <t>BRSAN</t>
   </si>
   <si>
-    <t>ANSGR</t>
-  </si>
-  <si>
     <t>PKZ</t>
   </si>
   <si>
@@ -215,21 +197,9 @@
     <t>EREGL</t>
   </si>
   <si>
-    <t>BETAE</t>
-  </si>
-  <si>
-    <t>TRMET</t>
-  </si>
-  <si>
     <t>Toplam</t>
   </si>
   <si>
-    <t>PNU</t>
-  </si>
-  <si>
-    <t>PGH</t>
-  </si>
-  <si>
     <t>PA2</t>
   </si>
   <si>
@@ -263,30 +233,18 @@
     <t>ISMEN</t>
   </si>
   <si>
-    <t>KRDMD</t>
-  </si>
-  <si>
     <t>CCOLA</t>
   </si>
   <si>
-    <t>CANTE</t>
-  </si>
-  <si>
     <t>ALARK</t>
   </si>
   <si>
-    <t>SISE</t>
-  </si>
-  <si>
     <t>AGHOL</t>
   </si>
   <si>
     <t>FROTO</t>
   </si>
   <si>
-    <t>EGEPO</t>
-  </si>
-  <si>
     <t>MAVI</t>
   </si>
   <si>
@@ -308,12 +266,6 @@
     <t>BIZIM</t>
   </si>
   <si>
-    <t>İSVEA</t>
-  </si>
-  <si>
-    <t>AKRCL</t>
-  </si>
-  <si>
     <t>ORZAX</t>
   </si>
   <si>
@@ -333,17 +285,87 @@
   </si>
   <si>
     <t>TABGD</t>
+  </si>
+  <si>
+    <t>BIGEN</t>
+  </si>
+  <si>
+    <t>SARAE</t>
+  </si>
+  <si>
+    <t>GESAN</t>
+  </si>
+  <si>
+    <t>TMPOL</t>
+  </si>
+  <si>
+    <t>METEN</t>
+  </si>
+  <si>
+    <t>T3B</t>
+  </si>
+  <si>
+    <t>PDG</t>
+  </si>
+  <si>
+    <t>PHN</t>
+  </si>
+  <si>
+    <t>PSE</t>
+  </si>
+  <si>
+    <t>BAC</t>
+  </si>
+  <si>
+    <t>KVR</t>
+  </si>
+  <si>
+    <t>PFS</t>
+  </si>
+  <si>
+    <t>CWENE</t>
+  </si>
+  <si>
+    <t>PSGYO</t>
+  </si>
+  <si>
+    <t>GLRYH</t>
+  </si>
+  <si>
+    <t>A1CAP</t>
+  </si>
+  <si>
+    <t>KARCL</t>
+  </si>
+  <si>
+    <t>PKV</t>
+  </si>
+  <si>
+    <t>PIS</t>
+  </si>
+  <si>
+    <t>MOBTL</t>
+  </si>
+  <si>
+    <t>BSOKE</t>
+  </si>
+  <si>
+    <t>RUZYE</t>
+  </si>
+  <si>
+    <t>RNPOL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;₺&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;₺&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -404,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -486,6 +508,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -800,10 +826,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -814,62 +840,62 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>22.85</v>
+        <v>32.590000000000003</v>
       </c>
       <c r="C2" s="3">
-        <v>0</v>
+        <v>-1.0989010989010899</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0</v>
+        <v>-0.35813186813186526</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="4">
-        <v>14.3</v>
+        <v>11.57</v>
       </c>
       <c r="C3" s="3">
-        <v>0</v>
+        <v>5.9389140271493197</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0</v>
+        <v>0.68713235294117625</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>8.14</v>
+        <v>9.02</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" ref="D4:D16" si="0">B4*C4/100</f>
+        <f t="shared" ref="D4:D23" si="0">B4*C4/100</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>7.14</v>
+        <v>5.94</v>
       </c>
       <c r="C5" s="3">
-        <v>1.19760479041916</v>
+        <v>2.7777777777777701</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>8.5508982035928008E-2</v>
+        <v>0.16499999999999956</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -877,14 +903,14 @@
         <v>2</v>
       </c>
       <c r="B6" s="4">
-        <v>6.63</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="C6" s="3">
-        <v>-4.3076923076923004</v>
+        <v>1.4942528735632099</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-0.28559999999999952</v>
+        <v>6.006896551724103E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -892,14 +918,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="4">
-        <v>5.61</v>
+        <v>3.93</v>
       </c>
       <c r="C7" s="3">
-        <v>0.51020408163265296</v>
+        <v>1.5228426395939001</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>2.8622448979591833E-2</v>
+        <v>5.984771573604028E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -907,191 +933,254 @@
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="C8" s="3">
-        <v>3.12249799839871</v>
+        <v>4.6583850931677002</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>6.2137710168134325E-2</v>
+        <v>0.10015527950310554</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="C9" s="3">
-        <v>6.95936478281177</v>
+        <v>1.4880952380952299</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>7.2377393741242413E-2</v>
+        <v>2.7827380952380801E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B10" s="4">
-        <v>0.54</v>
+        <v>1.67</v>
       </c>
       <c r="C10" s="3">
-        <v>-0.70921985815602795</v>
+        <v>3.4934497816593799</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-3.8297872340425508E-3</v>
+        <v>5.8340611353711644E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="B11" s="4">
-        <v>0.52</v>
+        <v>1.39</v>
       </c>
       <c r="C11" s="3">
-        <v>3.1333333333333302</v>
+        <v>-2.7928626842513502</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.6293333333333316E-2</v>
+        <v>-3.8820791311093762E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4">
-        <v>0.28000000000000003</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C12" s="3">
-        <v>10</v>
+        <v>-9.9722991689750593</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>2.8000000000000004E-2</v>
+        <v>-5.484764542936283E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="4">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="C13" s="3">
-        <v>-9.9750623441396495</v>
+        <v>-1.4867485455720699</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6932668329177054E-2</v>
+        <v>-7.5824175824175562E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B14" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="C14" s="3">
-        <v>1.3063357282821599</v>
+        <v>6.2429057888762696</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>1.8288700195950242E-3</v>
+        <v>2.4347332576617454E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B15" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.27</v>
       </c>
       <c r="C15" s="3">
-        <v>-0.70588235294117596</v>
+        <v>0.25789813023855501</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-4.9411764705882327E-4</v>
+        <v>6.963249516440986E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B16" s="4">
-        <v>1.27</v>
+        <v>0.12</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.1599999999999999</v>
+        <v>-1.21621621621621</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-1.4731999999999999E-2</v>
+        <v>-1.459459459459452E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="5">
-        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16</f>
-        <v>70.790000000000006</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6">
-        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16</f>
-        <v>-3.6819834932453055E-2</v>
+      <c r="A17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.8957345971563899</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="0"/>
+        <v>9.4786729857819496E-4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
+      <c r="A18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.49140049140049102</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="0"/>
+        <v>1.9656019656019643E-4</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
+      <c r="A19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2.7426160337552701</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="0"/>
+        <v>8.2278481012658096E-4</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
+      <c r="A20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4.8150322959483196</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="0"/>
+        <v>1.4445096887844957E-3</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
+      <c r="A21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="C21" s="3">
+        <v>-2.33863423760523</v>
+      </c>
+      <c r="D21" s="7">
+        <f t="shared" si="0"/>
+        <v>-4.6772684752104603E-4</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
+      <c r="A22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="4">
+        <v>5.62</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-0.2</v>
+      </c>
+      <c r="D22" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.1240000000000002E-2</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
+      <c r="A23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="0"/>
+        <v>4.7000000000000004E-5</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="5">
+        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20+B21</f>
+        <v>76.160000000000025</v>
+      </c>
       <c r="C24" s="5"/>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21</f>
+        <v>0.72551777676424634</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
@@ -1270,10 +1359,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -1284,32 +1373,32 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4">
-        <v>8.92</v>
-      </c>
-      <c r="C2" s="14">
-        <v>9.97752808988764</v>
+        <v>15.5</v>
+      </c>
+      <c r="C2" s="27">
+        <v>7.4675324675324601</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.88999550561797747</v>
+        <v>1.1574675324675312</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4">
-        <v>8.81</v>
-      </c>
-      <c r="C3" s="14">
-        <v>4.7619047619047601</v>
+        <v>11.91</v>
+      </c>
+      <c r="C3" s="27">
+        <v>-9.9682539682539595</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3:D43" si="0">B3*C3/100</f>
-        <v>0.41952380952380941</v>
+        <f t="shared" ref="D3:D26" si="0">B3*C3/100</f>
+        <v>-1.1872190476190465</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,29 +1406,29 @@
         <v>12</v>
       </c>
       <c r="B4" s="4">
-        <v>8.2799999999999994</v>
-      </c>
-      <c r="C4" s="14">
-        <v>3.5874439461883401</v>
+        <v>10.17</v>
+      </c>
+      <c r="C4" s="27">
+        <v>-9.9567099567099504</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.29704035874439449</v>
+        <v>-1.0125974025974021</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4">
-        <v>6.17</v>
-      </c>
-      <c r="C5" s="14">
-        <v>-10</v>
+        <v>9.48</v>
+      </c>
+      <c r="C5" s="27">
+        <v>7.2742133224356298</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-0.61699999999999999</v>
+        <v>0.6895954229668978</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,583 +1436,429 @@
         <v>9</v>
       </c>
       <c r="B6" s="4">
-        <v>4.75</v>
-      </c>
-      <c r="C6" s="14">
-        <v>-9.9750623441396495</v>
+        <v>8</v>
+      </c>
+      <c r="C6" s="27">
+        <v>-9.9722991689750593</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47381546134663338</v>
+        <v>-0.7977839335180047</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B7" s="4">
-        <v>4.42</v>
-      </c>
-      <c r="C7" s="14">
-        <v>-0.66006600660065995</v>
+        <v>5.28</v>
+      </c>
+      <c r="C7" s="27">
+        <v>5.9389140271493197</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9174917491749167E-2</v>
+        <v>0.3135746606334841</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4">
-        <v>3.77</v>
-      </c>
-      <c r="C8" s="14">
-        <v>-0.97305389221556804</v>
+        <v>5.08</v>
+      </c>
+      <c r="C8" s="27">
+        <v>4.4416243654822303</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6684131736526918E-2</v>
+        <v>0.22563451776649732</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="C9" s="14">
-        <v>-9.0604651162790599</v>
+        <v>2.82</v>
+      </c>
+      <c r="C9" s="27">
+        <v>-2.6315789473684199</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-0.32617674418604614</v>
+        <v>-7.4210526315789435E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B10" s="4">
-        <v>3.37</v>
-      </c>
-      <c r="C10" s="14">
-        <v>0.17647058823529399</v>
+        <v>2.75</v>
+      </c>
+      <c r="C10" s="27">
+        <v>4.6583850931677002</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>5.9470588235294077E-3</v>
+        <v>0.12810559006211175</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4">
-        <v>2.68</v>
-      </c>
-      <c r="C11" s="14">
-        <v>-4.2016806722688997</v>
+        <v>1.89</v>
+      </c>
+      <c r="C11" s="27">
+        <v>-6.4949608062709903</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-0.11260504201680652</v>
+        <v>-0.12275475923852172</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4">
-        <v>2.58</v>
-      </c>
-      <c r="C12" s="14">
-        <v>0.39750141964792701</v>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C12" s="27">
+        <v>-2.5601241272304098</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>1.0255536626916518E-2</v>
+        <v>-2.8417377812257553E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="B13" s="4">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="C13" s="14">
-        <v>-0.74318744838976003</v>
+        <v>1.07</v>
+      </c>
+      <c r="C13" s="27">
+        <v>2.7426160337552701</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>-1.820809248554912E-2</v>
+        <v>2.9345991561181391E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B14" s="4">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="C14" s="14">
-        <v>3.12249799839871</v>
+        <v>1.01</v>
+      </c>
+      <c r="C14" s="27">
+        <v>2.7777777777777701</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>6.401120896717355E-2</v>
+        <v>2.8055555555555479E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B15" s="4">
-        <v>1.73</v>
-      </c>
-      <c r="C15" s="14">
-        <v>-3.97849462365591</v>
+        <v>0.66</v>
+      </c>
+      <c r="C15" s="27">
+        <v>1.4880952380952299</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-6.8827956989247235E-2</v>
+        <v>9.8214285714285175E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B16" s="4">
-        <v>1.64</v>
-      </c>
-      <c r="C16" s="14">
-        <v>-4.2553191489361701</v>
+        <v>0.53</v>
+      </c>
+      <c r="C16" s="27">
+        <v>1.8957345971563899</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-6.9787234042553187E-2</v>
+        <v>1.0047393364928867E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B17" s="4">
-        <v>1.62</v>
-      </c>
-      <c r="C17" s="14">
-        <v>-1.0169491525423699</v>
+        <v>0.38</v>
+      </c>
+      <c r="C17" s="27">
+        <v>0.46511627906976699</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-1.6474576271186394E-2</v>
+        <v>1.7674418604651145E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B18" s="4">
-        <v>1.48</v>
-      </c>
-      <c r="C18" s="14">
-        <v>-1.8217306441119001</v>
+        <v>0.13</v>
+      </c>
+      <c r="C18" s="27">
+        <v>5.2023121387283204</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.6961613532856123E-2</v>
+        <v>6.7630057803468166E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B19" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="C19" s="14">
-        <v>-2.0892687559354202</v>
+        <v>0.13</v>
+      </c>
+      <c r="C19" s="27">
+        <v>1.5228426395939001</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-2.9249762583095879E-2</v>
+        <v>1.9796954314720704E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="B20" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="C20" s="14">
-        <v>-1.9617459538989701</v>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C20" s="27">
+        <v>0.63795853269537395</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-2.550269740068661E-2</v>
+        <v>4.465709728867618E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4">
-        <v>1.26</v>
-      </c>
-      <c r="C21" s="14">
-        <v>-0.98214285714285698</v>
+        <v>0.04</v>
+      </c>
+      <c r="C21" s="27">
+        <v>-2.4140752864157098</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2374999999999999E-2</v>
+        <v>-9.6563011456628396E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="C22" s="14">
-        <v>-7.89889415481832E-2</v>
+        <v>0.04</v>
+      </c>
+      <c r="C22" s="27">
+        <v>1.2463343108504299</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-9.4786729857819843E-4</v>
+        <v>4.9853372434017194E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B23" s="4">
-        <v>0.73</v>
-      </c>
-      <c r="C23" s="14">
-        <v>0</v>
+        <v>9.73</v>
+      </c>
+      <c r="C23" s="27">
+        <v>10.46</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.0177580000000002</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B24" s="4">
-        <v>0.71</v>
-      </c>
-      <c r="C24" s="14">
-        <v>-1.0575016523463301</v>
+        <v>9.19</v>
+      </c>
+      <c r="C24" s="27">
+        <v>6.55</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-7.5082617316589431E-3</v>
+        <v>0.60194499999999995</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B25" s="4">
-        <v>0.59</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-0.70921985815602795</v>
+        <v>1.66</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.13</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-4.1843971631205642E-3</v>
+        <v>2.1579999999999998E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="B26" s="4">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-0.70588235294117596</v>
+        <v>0.02</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.32</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-3.9529411764705862E-3</v>
+        <v>6.3999999999999997E-5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0.47694753577106502</v>
-      </c>
-      <c r="D27" s="4">
-        <f t="shared" si="0"/>
-        <v>1.9077901430842603E-3</v>
+      <c r="A27" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="5">
+        <f>SUM(B2:B26)</f>
+        <v>98.649999999999977</v>
+      </c>
+      <c r="D27" s="6">
+        <f>SUM(D2:D26)</f>
+        <v>1.0010796635035395</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="4">
-        <v>0.39</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-4.2527339003645199</v>
-      </c>
-      <c r="D28" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.6585662211421628E-2</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="4">
-        <v>0.36</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-0.34802784222737798</v>
-      </c>
-      <c r="D29" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.2529002320185605E-3</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="4">
-        <v>0.34</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-3.8777032065622601</v>
-      </c>
-      <c r="D30" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.3184190902311686E-2</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="4">
-        <v>0.34</v>
-      </c>
-      <c r="C31" s="8">
-        <v>0.35005834305717598</v>
-      </c>
-      <c r="D31" s="4">
-        <f t="shared" si="0"/>
-        <v>1.1901983663943983E-3</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="4">
-        <v>0.33</v>
-      </c>
-      <c r="C32" s="8">
-        <v>0.45745654162854499</v>
-      </c>
-      <c r="D32" s="4">
-        <f t="shared" si="0"/>
-        <v>1.5096065873741985E-3</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" s="11">
-        <v>0.26</v>
-      </c>
-      <c r="C33" s="15">
-        <v>-4.55293472298409</v>
-      </c>
-      <c r="D33" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.1837630279758635E-2</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="4">
-        <v>0.18</v>
-      </c>
-      <c r="C34" s="8">
-        <v>-9.4240837696334996</v>
-      </c>
-      <c r="D34" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.6963350785340298E-2</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="4">
-        <v>0.12</v>
-      </c>
-      <c r="C35" s="8">
-        <v>0.51020408163265296</v>
-      </c>
-      <c r="D35" s="4">
-        <f t="shared" si="0"/>
-        <v>6.1224489795918353E-4</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="4">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-1.5162454873646201</v>
-      </c>
-      <c r="D36" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.0613718411552342E-3</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="C37" s="8">
-        <v>-5.4229934924078002E-2</v>
-      </c>
-      <c r="D37" s="4">
-        <f t="shared" si="0"/>
-        <v>-2.7114967462039E-5</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="4"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-8.1938325991189398</v>
-      </c>
-      <c r="D38" s="4">
-        <f t="shared" si="0"/>
-        <v>-3.277533039647576E-3</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="4">
-        <v>0.04</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-7.8024337866857501</v>
-      </c>
-      <c r="D39" s="4">
-        <f t="shared" si="0"/>
-        <v>-3.1209735146743001E-3</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="4"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-4.3010752688171996</v>
-      </c>
-      <c r="D40" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.2903225806451599E-2</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="4">
-        <v>8.33</v>
-      </c>
-      <c r="C41" s="4">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="D41" s="4">
-        <f t="shared" si="0"/>
-        <v>0.18159400000000001</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="4">
-        <v>8.27</v>
-      </c>
-      <c r="C42" s="4">
-        <v>2.09</v>
-      </c>
-      <c r="D42" s="4">
-        <f t="shared" si="0"/>
-        <v>0.17284299999999997</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="4">
-        <v>2.56</v>
-      </c>
-      <c r="C43" s="4">
-        <v>0.13</v>
-      </c>
-      <c r="D43" s="4">
-        <f t="shared" si="0"/>
-        <v>3.3280000000000002E-3</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44" s="5">
-        <f>SUM(B2:B43)</f>
-        <v>98.450000000000045</v>
-      </c>
-      <c r="D44" s="6">
-        <f>SUM(D2:D43)</f>
-        <v>9.0107667265606289E-2</v>
-      </c>
+      <c r="A44" s="12"/>
+      <c r="B44" s="5"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C47" s="5"/>
@@ -2164,26 +2099,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2193,6 +2108,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2212,10 +2147,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -2226,32 +2161,32 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4">
-        <v>9.65</v>
-      </c>
-      <c r="C2" s="8">
-        <v>4.7619047619047601</v>
-      </c>
-      <c r="D2" s="4">
+        <v>15.85</v>
+      </c>
+      <c r="C2" s="3">
+        <v>-9.9722991689750593</v>
+      </c>
+      <c r="D2" s="31">
         <f>B2*C2/100</f>
-        <v>0.45952380952380933</v>
+        <v>-1.580609418282547</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="C3" s="8">
-        <v>9.97752808988764</v>
-      </c>
-      <c r="D3" s="4">
-        <f t="shared" ref="D3:D36" si="0">B3*C3/100</f>
-        <v>0.92691235955056173</v>
+        <v>14.37</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7.4675324675324601</v>
+      </c>
+      <c r="D3" s="31">
+        <f t="shared" ref="D3:D22" si="0">B3*C3/100</f>
+        <v>1.0730844155844144</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2259,194 +2194,194 @@
         <v>12</v>
       </c>
       <c r="B4" s="4">
-        <v>9.24</v>
-      </c>
-      <c r="C4" s="8">
-        <v>3.5874439461883401</v>
-      </c>
-      <c r="D4" s="4">
-        <f t="shared" si="0"/>
-        <v>0.33147982062780268</v>
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-9.9567099567099504</v>
+      </c>
+      <c r="D4" s="31">
+        <f t="shared" si="0"/>
+        <v>-0.99069264069263996</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4">
-        <v>6.09</v>
-      </c>
-      <c r="C5" s="8">
-        <v>-4.2016806722688997</v>
-      </c>
-      <c r="D5" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.25588235294117601</v>
+        <v>9.31</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7.2742133224356298</v>
+      </c>
+      <c r="D5" s="31">
+        <f t="shared" si="0"/>
+        <v>0.67722926031875719</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="C6" s="8">
-        <v>-9.9750623441396495</v>
-      </c>
-      <c r="D6" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.4718204488778055</v>
+        <v>7.94</v>
+      </c>
+      <c r="C6" s="3">
+        <v>-9.9682539682539595</v>
+      </c>
+      <c r="D6" s="31">
+        <f t="shared" si="0"/>
+        <v>-0.79147936507936434</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B7" s="4">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="C7" s="8">
-        <v>-10</v>
-      </c>
-      <c r="D7" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.45199999999999996</v>
+        <v>3.39</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5.9389140271493197</v>
+      </c>
+      <c r="D7" s="31">
+        <f t="shared" si="0"/>
+        <v>0.20132918552036194</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="C8" s="8">
-        <v>-9.0604651162790599</v>
-      </c>
-      <c r="D8" s="4">
-        <f t="shared" si="0"/>
-        <v>-0.30805581395348802</v>
+        <v>5.47</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-2.6315789473684199</v>
+      </c>
+      <c r="D8" s="31">
+        <f t="shared" si="0"/>
+        <v>-0.14394736842105257</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>2.73</v>
-      </c>
-      <c r="C9" s="8">
-        <v>-0.66006600660065995</v>
-      </c>
-      <c r="D9" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.8019801980198015E-2</v>
+        <v>5.29</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.6583850931677002</v>
+      </c>
+      <c r="D9" s="31">
+        <f t="shared" si="0"/>
+        <v>0.24642857142857136</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B10" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C10" s="8">
-        <v>3.12249799839871</v>
-      </c>
-      <c r="D10" s="4">
-        <f t="shared" si="0"/>
-        <v>7.1817453963170325E-2</v>
+        <v>3.04</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4.4416243654822303</v>
+      </c>
+      <c r="D10" s="31">
+        <f t="shared" si="0"/>
+        <v>0.13502538071065981</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="B11" s="4">
-        <v>1.67</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-2.0892687559354202</v>
-      </c>
-      <c r="D11" s="4">
-        <f t="shared" si="0"/>
-        <v>-3.4890788224121512E-2</v>
+        <v>2.08</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.7426160337552701</v>
+      </c>
+      <c r="D11" s="31">
+        <f t="shared" si="0"/>
+        <v>5.7046413502109622E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4">
-        <v>1.58</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-3.97849462365591</v>
-      </c>
-      <c r="D12" s="4">
-        <f t="shared" si="0"/>
-        <v>-6.286021505376338E-2</v>
+        <v>1.81</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-2.5601241272304098</v>
+      </c>
+      <c r="D12" s="31">
+        <f t="shared" si="0"/>
+        <v>-4.6338246702870414E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4">
-        <v>1.57</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0.39750141964792701</v>
-      </c>
-      <c r="D13" s="4">
-        <f t="shared" si="0"/>
-        <v>6.2407722884724546E-3</v>
+        <v>1.39</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-6.4949608062709903</v>
+      </c>
+      <c r="D13" s="31">
+        <f t="shared" si="0"/>
+        <v>-9.0279955207166751E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-0.97305389221556804</v>
-      </c>
-      <c r="D14" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.0995508982035917E-2</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.8957345971563899</v>
+      </c>
+      <c r="D14" s="31">
+        <f t="shared" si="0"/>
+        <v>1.0805687203791421E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B15" s="4">
-        <v>1.03</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0.17647058823529399</v>
-      </c>
-      <c r="D15" s="4">
-        <f t="shared" si="0"/>
-        <v>1.8176470588235282E-3</v>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.66445182724252405</v>
+      </c>
+      <c r="D15" s="31">
+        <f t="shared" si="0"/>
+        <v>9.3023255813953374E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="B16" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-4.2553191489361701</v>
-      </c>
-      <c r="D16" s="4">
-        <f t="shared" si="0"/>
-        <v>-4.170212765957447E-2</v>
+        <v>0.11</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-1.21621621621621</v>
+      </c>
+      <c r="D16" s="31">
+        <f t="shared" si="0"/>
+        <v>-1.3378378378378312E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2454,313 +2389,177 @@
         <v>36</v>
       </c>
       <c r="B17" s="4">
-        <v>0.87</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1.34680134680134</v>
-      </c>
-      <c r="D17" s="4">
-        <f t="shared" si="0"/>
-        <v>1.1717171717171657E-2</v>
+        <v>8.98</v>
+      </c>
+      <c r="C17" s="3">
+        <v>6.55</v>
+      </c>
+      <c r="D17" s="31">
+        <f t="shared" si="0"/>
+        <v>0.58818999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B18" s="4">
-        <v>0.59</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-0.70588235294117596</v>
-      </c>
-      <c r="D18" s="4">
-        <f t="shared" si="0"/>
-        <v>-4.1647058823529384E-3</v>
+        <v>8.66</v>
+      </c>
+      <c r="C18" s="3">
+        <v>10.46</v>
+      </c>
+      <c r="D18" s="31">
+        <f t="shared" si="0"/>
+        <v>0.90583600000000009</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="B19" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-5.4229934924078002E-2</v>
-      </c>
-      <c r="D19" s="4">
-        <f t="shared" si="0"/>
-        <v>-2.7114967462039003E-4</v>
+        <v>0.69</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D19" s="31">
+        <f t="shared" si="0"/>
+        <v>1.3868999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B20" s="4">
-        <v>0.48</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0.47694753577106502</v>
-      </c>
-      <c r="D20" s="4">
-        <f t="shared" si="0"/>
-        <v>2.2893481717011122E-3</v>
+        <v>0.09</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="D20" s="31">
+        <f t="shared" si="0"/>
+        <v>6.0300000000000002E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B21" s="4">
-        <v>0.42</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-0.98214285714285698</v>
-      </c>
-      <c r="D21" s="4">
-        <f t="shared" si="0"/>
-        <v>-4.1249999999999993E-3</v>
+        <v>0.01</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="D21" s="31">
+        <f t="shared" si="0"/>
+        <v>1.3000000000000001E-5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-1.4560279557367499</v>
-      </c>
-      <c r="D22" s="4">
-        <f t="shared" si="0"/>
-        <v>-5.8241118229470003E-3</v>
+      <c r="A22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="5">
+        <f>SUM(B2:B21)</f>
+        <v>99.140000000000015</v>
+      </c>
+      <c r="D22" s="6">
+        <f>SUM(D2:D21)</f>
+        <v>0.26570531460332675</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0.38</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-1.0575016523463301</v>
-      </c>
-      <c r="D23" s="4">
-        <f t="shared" si="0"/>
-        <v>-4.0185062789160541E-3</v>
-      </c>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="C24" s="8">
-        <v>-4.55293472298409</v>
-      </c>
-      <c r="D24" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.1382336807460225E-2</v>
-      </c>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-4.4987146529562896</v>
-      </c>
-      <c r="D25" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.1246786632390725E-2</v>
-      </c>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="4">
-        <v>0.24</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-3.8777032065622601</v>
-      </c>
-      <c r="D26" s="4">
-        <f t="shared" si="0"/>
-        <v>-9.3064876957494238E-3</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="4">
-        <v>0.23</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-4.01633764465622</v>
-      </c>
-      <c r="D28" s="4">
-        <f t="shared" si="0"/>
-        <v>-8.0326752893124416E-3</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="13">
-        <v>0.08</v>
-      </c>
-      <c r="C29" s="15">
-        <v>-8.1938325991189398</v>
-      </c>
-      <c r="D29" s="4">
-        <f t="shared" si="0"/>
-        <v>-6.5550660792951521E-3</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-1.5162454873646201</v>
-      </c>
-      <c r="D30" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.51624548736462E-4</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="4">
-        <v>7.99</v>
-      </c>
-      <c r="C31" s="4">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="D31" s="4">
-        <f t="shared" si="0"/>
-        <v>0.17418200000000003</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="4">
-        <v>7.7</v>
-      </c>
-      <c r="C32" s="4">
-        <v>2.09</v>
-      </c>
-      <c r="D32" s="4">
-        <f t="shared" si="0"/>
-        <v>0.16092999999999999</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="C33" s="4">
-        <v>0.13</v>
-      </c>
-      <c r="D33" s="4">
-        <f t="shared" si="0"/>
-        <v>3.2500000000000003E-3</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B34" s="4">
-        <v>0.78</v>
-      </c>
-      <c r="C34" s="4">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D34" s="4">
-        <f t="shared" si="0"/>
-        <v>1.0920000000000001E-3</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="4">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="C35" s="4">
-        <v>-10.07</v>
-      </c>
-      <c r="D35" s="4">
-        <f t="shared" si="0"/>
-        <v>-5.8405999999999993E-2</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="C36" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D36" s="4">
-        <f t="shared" si="0"/>
-        <v>2.9999999999999997E-4</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="5">
-        <f>SUM(B2:B36)</f>
-        <v>84.419999999999987</v>
-      </c>
-      <c r="D37" s="6">
-        <f>SUM(D2:D36)</f>
-        <v>0.37184087451756931</v>
-      </c>
+      <c r="A37" s="12"/>
+      <c r="B37" s="5"/>
+      <c r="D37" s="6"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C42" s="5"/>
@@ -3601,97 +3400,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3705,6 +3413,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3725,10 +3524,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -3739,100 +3538,138 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4">
-        <v>52.75</v>
+        <v>41.32</v>
       </c>
       <c r="C2" s="8">
-        <v>0.28042624789680298</v>
-      </c>
-      <c r="D2" s="4">
+        <v>0.111856823266219</v>
+      </c>
+      <c r="D2" s="31">
         <f>B2*C2/100</f>
-        <v>0.14792484576556358</v>
+        <v>4.6219239373601687E-2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4">
-        <v>11.12</v>
+        <v>3.28</v>
       </c>
       <c r="C3" s="8">
-        <v>-2.26308345120226</v>
-      </c>
-      <c r="D3" s="4">
-        <f t="shared" ref="D3:D5" si="0">B3*C3/100</f>
-        <v>-0.25165487977369128</v>
+        <v>-1.59189580318379</v>
+      </c>
+      <c r="D3" s="31">
+        <f t="shared" ref="D3:D9" si="0">B3*C3/100</f>
+        <v>-5.221418234442831E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="C4" s="8">
-        <v>9.6339113680154104E-2</v>
-      </c>
-      <c r="D4" s="4">
-        <f t="shared" si="0"/>
-        <v>5.1059730250481677E-4</v>
+        <v>2.9836381135707399</v>
+      </c>
+      <c r="D4" s="31">
+        <f t="shared" si="0"/>
+        <v>5.6689124157844059E-3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4">
-        <v>29.82</v>
+        <v>22.96</v>
       </c>
       <c r="C5" s="4">
-        <v>1.98</v>
-      </c>
-      <c r="D5" s="4">
-        <f t="shared" si="0"/>
-        <v>0.59043599999999996</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D5" s="31">
+        <f t="shared" si="0"/>
+        <v>0.12628000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="5">
-        <f>B2++B3+B4+B5</f>
-        <v>94.22</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="6">
-        <f>D2+D3+D4+D5</f>
-        <v>0.48721656329437707</v>
+      <c r="A6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.29</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="D6" s="31">
+        <f t="shared" si="0"/>
+        <v>6.3480000000000003E-3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.07</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="D7" s="31">
+        <f t="shared" si="0"/>
+        <v>1.2840000000000002E-3</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="31">
+        <f t="shared" si="0"/>
+        <v>1.3000000000000002E-4</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D9" s="31">
+        <f t="shared" si="0"/>
+        <v>8.4000000000000009E-5</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
+      <c r="A10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="5">
+        <f>B2++B3+B4+B5+B6+B7+B8+B9</f>
+        <v>74.27</v>
+      </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9</f>
+        <v>0.13379996944495781</v>
+      </c>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4730,108 +4567,7 @@
       <c r="F141" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
+  <mergeCells count="112">
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4844,6 +4580,106 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4863,10 +4699,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -4876,753 +4712,744 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>50</v>
+      <c r="A2" t="s">
+        <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>9.14</v>
+        <v>8.27</v>
       </c>
       <c r="C2" s="3">
-        <v>1.3063357282821599</v>
+        <v>5.9389140271493197</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.11939908556498942</v>
+        <v>0.49114819004524868</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
+      <c r="A3" t="s">
+        <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>8.17</v>
+        <v>8.11</v>
       </c>
       <c r="C3" s="3">
-        <v>1.19760479041916</v>
+        <v>-1.0989010989010899</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>9.7844311377245377E-2</v>
+        <v>-8.9120879120878377E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6.92</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.4942528735632099</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10340229885057413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>8.1199999999999992</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B5" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.7777777777777701</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.19166666666666615</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.76</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.49140049140049102</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>2.8304668304668282E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.4934497816593799</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15930131004366771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="26">
+        <v>4.28</v>
+      </c>
+      <c r="C8" s="27">
+        <v>6.2429057888762696</v>
+      </c>
+      <c r="D8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.26719636776390432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4.21</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.6583850931677002</v>
+      </c>
+      <c r="D9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.19611801242236018</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4">
+        <v>4.08</v>
+      </c>
+      <c r="C10" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D10" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4">
-        <v>6.99</v>
-      </c>
-      <c r="C5" s="3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2.88</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.25789813023855501</v>
+      </c>
+      <c r="D11" s="7">
+        <f t="shared" si="0"/>
+        <v>7.4274661508703845E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2.62</v>
+      </c>
+      <c r="C12" s="28">
+        <v>1.5228426395939001</v>
+      </c>
+      <c r="D12" s="7">
+        <f t="shared" si="0"/>
+        <v>3.9898477157360189E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="26">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.4880952380952299</v>
+      </c>
+      <c r="D13" s="7">
+        <f t="shared" si="0"/>
+        <v>3.7053571428571228E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-3.2023289665211001</v>
+      </c>
+      <c r="D14" s="7">
+        <f t="shared" si="0"/>
+        <v>-7.6855895196506402E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="26">
+        <v>1.77</v>
+      </c>
+      <c r="C15" s="27">
+        <v>0.969932104752667</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7167798254122207E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1.76</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.87976539589442804</v>
+      </c>
+      <c r="D16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.5483870967741932E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1.61</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.86814975583288101</v>
+      </c>
+      <c r="D17" s="7">
+        <f t="shared" si="0"/>
+        <v>1.3977211068909385E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1.58</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2.5747508305647799</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" si="0"/>
+        <v>4.0681063122923522E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1.54</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1.46960587842351</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="0"/>
+        <v>2.2631930527722055E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C20" s="3">
+        <v>-7.13606089438629</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="0"/>
+        <v>-7.8496669838249197E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4">
+        <v>1.06</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.74200913242009103</v>
+      </c>
+      <c r="D21" s="7">
+        <f t="shared" si="0"/>
+        <v>7.8652968036529661E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.9514757378689298</v>
+      </c>
+      <c r="D22" s="7">
+        <f t="shared" si="0"/>
+        <v>2.9219609804902406E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="26">
+        <v>0.98</v>
+      </c>
+      <c r="C23" s="27">
+        <v>0.15463917525773099</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="0"/>
+        <v>1.5154639175257636E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="26">
+        <v>0.98</v>
+      </c>
+      <c r="C24" s="27">
+        <v>1.78926441351888</v>
+      </c>
+      <c r="D24" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7534791252485023E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="26">
+        <v>0.88</v>
+      </c>
+      <c r="C25" s="27">
+        <v>4.4925124792013298</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" si="0"/>
+        <v>3.9534109816971703E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="26">
+        <v>0.87</v>
+      </c>
+      <c r="C26" s="27">
+        <v>-0.398633257403189</v>
+      </c>
+      <c r="D26" s="7">
+        <f t="shared" si="0"/>
+        <v>-3.4681093394077446E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="26">
+        <v>0.8</v>
+      </c>
+      <c r="C27" s="27">
+        <v>4.0060468631897201</v>
+      </c>
+      <c r="D27" s="7">
+        <f t="shared" si="0"/>
+        <v>3.2048374905517762E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="26">
+        <v>0.75</v>
+      </c>
+      <c r="C28" s="27">
+        <v>6.2885326757089999</v>
+      </c>
+      <c r="D28" s="7">
+        <f t="shared" si="0"/>
+        <v>4.7163995067817502E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="26">
+        <v>0.59</v>
+      </c>
+      <c r="C29" s="27">
+        <v>10</v>
+      </c>
+      <c r="D29" s="7">
+        <f t="shared" si="0"/>
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="26">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C30" s="27">
+        <v>1.63934426229508</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" si="0"/>
+        <v>9.0163934426229411E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="26">
+        <v>0.52</v>
+      </c>
+      <c r="C31" s="27">
+        <v>1.5700483091787401</v>
+      </c>
+      <c r="D31" s="7">
+        <f t="shared" si="0"/>
+        <v>8.1642512077294491E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="C32" s="27">
+        <v>3.5573122529644201</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7786561264822101E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="26">
+        <v>0.48</v>
+      </c>
+      <c r="C33" s="27">
+        <v>0.86720867208672003</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" si="0"/>
+        <v>4.1626016260162563E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="26">
+        <v>0.47</v>
+      </c>
+      <c r="C34" s="27">
+        <v>-9.2063492063492003</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" si="0"/>
+        <v>-4.3269841269841243E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="26">
+        <v>0.46</v>
+      </c>
+      <c r="C35" s="27">
+        <v>-3.9238315060588498</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.8049624927870708E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="26">
+        <v>0.46</v>
+      </c>
+      <c r="C36" s="27">
+        <v>-3.0563514804202399</v>
+      </c>
+      <c r="D36" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.4059216809933104E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="26">
+        <v>0.45</v>
+      </c>
+      <c r="C37" s="27">
+        <v>-6.0623229461756303</v>
+      </c>
+      <c r="D37" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.7280453257790337E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="C38" s="27">
+        <v>1.14140773620798</v>
+      </c>
+      <c r="D38" s="7">
+        <f t="shared" si="0"/>
+        <v>4.5656309448319195E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="26">
+        <v>0.39</v>
+      </c>
+      <c r="C39" s="27">
+        <v>0.15408320493066199</v>
+      </c>
+      <c r="D39" s="7">
+        <f t="shared" si="0"/>
+        <v>6.009244992295818E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="26">
+        <v>0.34</v>
+      </c>
+      <c r="C40" s="27">
+        <v>6.9473684210526301</v>
+      </c>
+      <c r="D40" s="7">
+        <f t="shared" si="0"/>
+        <v>2.3621052631578942E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="26">
+        <v>0.3</v>
+      </c>
+      <c r="C41" s="27">
+        <v>1.7182130584192401</v>
+      </c>
+      <c r="D41" s="7">
+        <f t="shared" si="0"/>
+        <v>5.1546391752577206E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="26">
+        <v>0.25</v>
+      </c>
+      <c r="C42" s="27">
+        <v>4.6622264509990403</v>
+      </c>
+      <c r="D42" s="7">
+        <f t="shared" si="0"/>
+        <v>1.16555661274976E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="26">
+        <v>0.25</v>
+      </c>
+      <c r="C43" s="27">
+        <v>-9.9722991689750593</v>
+      </c>
+      <c r="D43" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.4930747922437647E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="26">
+        <v>0.22</v>
+      </c>
+      <c r="C44" s="27">
         <v>0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D44" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
-        <v>5.99</v>
-      </c>
-      <c r="C6" s="3">
-        <v>3.12249799839871</v>
-      </c>
-      <c r="D6" s="7">
-        <f t="shared" si="0"/>
-        <v>0.18703763010408272</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="4">
-        <v>4.88</v>
-      </c>
-      <c r="C7" s="3">
-        <v>-0.87</v>
-      </c>
-      <c r="D7" s="7">
-        <f t="shared" si="0"/>
-        <v>-4.2455999999999994E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="26">
-        <v>4.46</v>
-      </c>
-      <c r="C8" s="27">
-        <v>-0.70921985815602795</v>
-      </c>
-      <c r="D8" s="7">
-        <f t="shared" si="0"/>
-        <v>-3.163120567375885E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4">
-        <v>4.17</v>
-      </c>
-      <c r="C9" s="3">
-        <v>3.1333333333333302</v>
-      </c>
-      <c r="D9" s="7">
-        <f t="shared" si="0"/>
-        <v>0.13065999999999986</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4">
-        <v>3.23</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.51020408163265296</v>
-      </c>
-      <c r="D10" s="7">
-        <f t="shared" si="0"/>
-        <v>1.647959183673469E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4">
-        <v>2.84</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-0.66006600660065995</v>
-      </c>
-      <c r="D11" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.8745874587458741E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="4">
-        <v>2.54</v>
-      </c>
-      <c r="C12" s="28">
-        <v>-1.0575016523463301</v>
-      </c>
-      <c r="D12" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.6860541969596783E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="26">
-        <v>2.37</v>
-      </c>
-      <c r="C13" s="3">
-        <v>-9.0604651162790599</v>
-      </c>
-      <c r="D13" s="7">
-        <f t="shared" si="0"/>
-        <v>-0.21473302325581373</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="26">
-        <v>2.37</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-2.9</v>
-      </c>
-      <c r="D14" s="7">
-        <f t="shared" si="0"/>
-        <v>-6.8729999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="26">
-        <v>2.21</v>
-      </c>
-      <c r="C15" s="27">
-        <v>-5.4229934924078002E-2</v>
-      </c>
-      <c r="D15" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.1984815618221239E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="4">
-        <v>1.93</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-4.55293472298409</v>
-      </c>
-      <c r="D16" s="7">
-        <f t="shared" si="0"/>
-        <v>-8.7871640153592931E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="4">
-        <v>1.77</v>
-      </c>
-      <c r="C17" s="3">
-        <v>-1.0169491525423699</v>
-      </c>
-      <c r="D17" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.799999999999995E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1.53</v>
-      </c>
-      <c r="C18" s="3">
-        <v>-0.91</v>
-      </c>
-      <c r="D18" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.3923000000000001E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="4">
-        <v>1.51</v>
-      </c>
-      <c r="C19" s="3">
-        <v>-0.74318744838976003</v>
-      </c>
-      <c r="D19" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.1222130470685376E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="4">
-        <v>1.44</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0.36</v>
-      </c>
-      <c r="D20" s="7">
-        <f t="shared" si="0"/>
-        <v>5.1839999999999994E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="4">
-        <v>1.44</v>
-      </c>
-      <c r="C21" s="3">
-        <v>-1.82</v>
-      </c>
-      <c r="D21" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.6207999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="4">
-        <v>1.43</v>
-      </c>
-      <c r="C22" s="3">
-        <v>-1.9617459538989701</v>
-      </c>
-      <c r="D22" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.805296714075527E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="26">
-        <v>1.42</v>
-      </c>
-      <c r="C23" s="27">
-        <v>-0.70588235294117596</v>
-      </c>
-      <c r="D23" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.0023529411764698E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="26">
-        <v>1.4</v>
-      </c>
-      <c r="C24" s="27">
-        <v>-0.97305389221556804</v>
-      </c>
-      <c r="D24" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.3622754491017953E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="26">
-        <v>1.33</v>
-      </c>
-      <c r="C25" s="27">
-        <v>-1.8217306441119001</v>
-      </c>
-      <c r="D25" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.4229017566688271E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="26">
-        <v>1.25</v>
-      </c>
-      <c r="C26" s="27">
-        <v>4.76</v>
-      </c>
-      <c r="D26" s="7">
-        <f t="shared" si="0"/>
-        <v>5.949999999999999E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="26">
-        <v>1.17</v>
-      </c>
-      <c r="C27" s="27">
-        <v>-2.0892687559354202</v>
-      </c>
-      <c r="D27" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.4444444444444414E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="26">
-        <v>1.04</v>
-      </c>
-      <c r="C28" s="27">
-        <v>-1.66</v>
-      </c>
-      <c r="D28" s="7">
-        <f t="shared" si="0"/>
-        <v>-1.7263999999999998E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="26">
-        <v>0.9</v>
-      </c>
-      <c r="C29" s="27">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="D29" s="7">
-        <f t="shared" si="0"/>
-        <v>5.2199999999999998E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="26">
-        <v>0.84</v>
-      </c>
-      <c r="C30" s="27">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="D30" s="7">
-        <f t="shared" si="0"/>
-        <v>3.8724000000000001E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="26">
-        <v>0.82</v>
-      </c>
-      <c r="C31" s="27">
-        <v>0.45745654162854499</v>
-      </c>
-      <c r="D31" s="7">
-        <f t="shared" si="0"/>
-        <v>3.751143641354069E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="26">
-        <v>0.8</v>
-      </c>
-      <c r="C32" s="27">
-        <v>-7.89889415481832E-2</v>
-      </c>
-      <c r="D32" s="7">
-        <f t="shared" si="0"/>
-        <v>-6.3191153238546555E-4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="26">
-        <v>0.79</v>
-      </c>
-      <c r="C33" s="27">
-        <v>0.76</v>
-      </c>
-      <c r="D33" s="7">
-        <f t="shared" si="0"/>
-        <v>6.0040000000000007E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34" s="26">
-        <v>0.76</v>
-      </c>
-      <c r="C34" s="27">
-        <v>6.95936478281177</v>
-      </c>
-      <c r="D34" s="7">
-        <f t="shared" si="0"/>
-        <v>5.2891172349369457E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="26">
-        <v>0.73</v>
-      </c>
-      <c r="C35" s="27">
-        <v>-4.2553191489361701</v>
-      </c>
-      <c r="D35" s="7">
-        <f t="shared" si="0"/>
-        <v>-3.106382978723404E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="26">
+        <v>0.19</v>
+      </c>
+      <c r="C45" s="27">
+        <v>9.9510603588907003</v>
+      </c>
+      <c r="D45" s="7">
+        <f t="shared" si="0"/>
+        <v>1.8907014681892331E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="26">
-        <v>0.72</v>
-      </c>
-      <c r="C36" s="27">
-        <v>0.78</v>
-      </c>
-      <c r="D36" s="7">
-        <f t="shared" si="0"/>
-        <v>5.6159999999999995E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="26">
-        <v>0.71</v>
-      </c>
-      <c r="C37" s="27">
-        <v>0.61</v>
-      </c>
-      <c r="D37" s="7">
-        <f t="shared" si="0"/>
-        <v>4.3309999999999998E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="C38" s="27">
-        <v>0.84</v>
-      </c>
-      <c r="D38" s="7">
-        <f t="shared" si="0"/>
-        <v>5.8799999999999998E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="C39" s="27">
-        <v>0.1</v>
-      </c>
-      <c r="D39" s="7">
-        <f t="shared" si="0"/>
-        <v>6.9999999999999988E-4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="26">
-        <v>0.64</v>
-      </c>
-      <c r="C40" s="27">
-        <v>0.97</v>
-      </c>
-      <c r="D40" s="7">
-        <f t="shared" si="0"/>
-        <v>6.208E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="26">
-        <v>0.63</v>
-      </c>
-      <c r="C41" s="27">
-        <v>0.11</v>
-      </c>
-      <c r="D41" s="7">
-        <f t="shared" si="0"/>
-        <v>6.9300000000000004E-4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="26">
-        <v>0.61</v>
-      </c>
-      <c r="C42" s="27">
-        <v>4.43</v>
-      </c>
-      <c r="D42" s="7">
-        <f t="shared" si="0"/>
-        <v>2.7022999999999998E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="26">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="C43" s="27">
-        <v>1.82</v>
-      </c>
-      <c r="D43" s="7">
-        <f t="shared" si="0"/>
-        <v>1.0374E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="26">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C44" s="27">
-        <v>-0.05</v>
-      </c>
-      <c r="D44" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.7500000000000002E-4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B45" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="C45" s="27">
-        <v>-1.91</v>
-      </c>
-      <c r="D45" s="7">
-        <f t="shared" si="0"/>
-        <v>-9.5499999999999995E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="B46" s="26">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="C46" s="27">
-        <v>1.41</v>
+        <v>-0.58284762697751802</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>7.0499999999999998E-3</v>
+        <v>-4.6627810158201443E-4</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>86</v>
+      <c r="A47" t="s">
+        <v>63</v>
       </c>
       <c r="B47" s="26">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
       <c r="C47" s="27">
-        <v>0.32</v>
+        <v>0.46816479400749</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>1.4400000000000001E-3</v>
+        <v>4.6816479400749005E-5</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>87</v>
+      <c r="A48" t="s">
+        <v>100</v>
       </c>
       <c r="B48" s="26">
-        <v>0.4</v>
+        <v>3.34</v>
       </c>
       <c r="C48" s="27">
-        <v>5.47</v>
+        <v>0.12</v>
       </c>
       <c r="D48" s="7">
         <f t="shared" si="0"/>
-        <v>2.188E-2</v>
+        <v>4.0080000000000003E-3</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>88</v>
+      <c r="A49" t="s">
+        <v>101</v>
       </c>
       <c r="B49" s="26">
-        <v>0.33</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="C49" s="27">
-        <v>2.52</v>
+        <v>0.12</v>
       </c>
       <c r="D49" s="7">
         <f t="shared" si="0"/>
-        <v>8.3160000000000005E-3</v>
+        <v>3.0599999999999998E-3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="26">
-        <v>0.16</v>
-      </c>
-      <c r="C50" s="27">
-        <v>-0.17</v>
-      </c>
-      <c r="D50" s="7">
-        <f t="shared" si="0"/>
-        <v>-2.72E-4</v>
+      <c r="A50" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="5">
+        <f>SUM(B2:B49)</f>
+        <v>92.95</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="6">
+        <f>SUM(D2:D49)</f>
+        <v>1.6000922806405657</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" s="5">
-        <f>SUM(B2:B50)</f>
-        <v>99.950000000000031</v>
-      </c>
+      <c r="A51" s="16"/>
+      <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="6">
-        <f>SUM(D2:D50)</f>
-        <v>0.10119658282675704</v>
-      </c>
+      <c r="D51" s="6"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
@@ -5785,10 +5612,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -5799,17 +5626,17 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B2" s="4">
-        <v>7.83</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
+        <v>7.18</v>
+      </c>
+      <c r="C2" s="8">
+        <v>6.9473684210526301</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0</v>
+        <v>0.49882105263157883</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5817,14 +5644,14 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>7.91</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
+        <v>7.24</v>
+      </c>
+      <c r="C3" s="8">
+        <v>-1.0989010989010899</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0</v>
+        <v>-7.9560439560438914E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5832,14 +5659,14 @@
         <v>2</v>
       </c>
       <c r="B4" s="4">
-        <v>7.32</v>
-      </c>
-      <c r="C4" s="3">
-        <v>-4.55293472298409</v>
+        <v>6.71</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.4942528735632099</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" ref="D4:D25" si="0">B4*C4/100</f>
-        <v>-0.33327482172243544</v>
+        <f t="shared" ref="D4:D30" si="0">B4*C4/100</f>
+        <v>0.10026436781609138</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5847,44 +5674,44 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>6.1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1.19760479041916</v>
+        <v>5.6</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>7.3053892215568753E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="C6" s="3">
-        <v>9.9551569506726398</v>
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="C6" s="8">
+        <v>9.9510603588907003</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.50870852017937196</v>
+        <v>0.46670473083197384</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B7" s="4">
-        <v>4.75</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1.3063357282821599</v>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.25789813023855501</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>6.2050947093402593E-2</v>
+        <v>1.1218568665377142E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5892,14 +5719,14 @@
         <v>4</v>
       </c>
       <c r="B8" s="4">
-        <v>4.49</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.51020408163265296</v>
+        <v>4.12</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.5228426395939001</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>2.290816326530612E-2</v>
+        <v>6.2741116751268686E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5907,14 +5734,14 @@
         <v>20</v>
       </c>
       <c r="B9" s="4">
-        <v>4.16</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.17647058823529399</v>
+        <v>3.82</v>
+      </c>
+      <c r="C9" s="8">
+        <v>4.8150322959483196</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>7.3411764705882294E-3</v>
+        <v>0.1839342337052258</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5922,104 +5749,104 @@
         <v>16</v>
       </c>
       <c r="B10" s="4">
-        <v>3.99</v>
-      </c>
-      <c r="C10" s="3">
-        <v>-0.66006600660065995</v>
+        <v>3.66</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.5747508305647799</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-2.6336633663366332E-2</v>
+        <v>9.4235880398670951E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B11" s="4">
-        <v>3.98</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.47694753577106502</v>
+        <v>3.65</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-0.474683544303797</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>1.8982511923688387E-2</v>
+        <v>-1.7325949367088592E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B12" s="4">
-        <v>3.97</v>
-      </c>
-      <c r="C12" s="3">
-        <v>-2.0686175580221899</v>
+        <v>3.64</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-0.36063884595569201</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-8.2124117053480938E-2</v>
+        <v>-1.3127253992787189E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B13" s="4">
-        <v>3.96</v>
-      </c>
-      <c r="C13" s="3">
-        <v>8.1138040042149608</v>
+        <v>3.63</v>
+      </c>
+      <c r="C13" s="8">
+        <v>9.9415204678362503</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>0.32130663856691244</v>
+        <v>0.36087719298245591</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B14" s="4">
-        <v>3.55</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-8</v>
+        <v>3.26</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-2.0289855072463698</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-0.28399999999999997</v>
+        <v>-6.6144927536231649E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B15" s="4">
-        <v>3.41</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-9.9550898203592801</v>
+        <v>3.13</v>
+      </c>
+      <c r="C15" s="8">
+        <v>-9.9750623441396495</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-0.33946856287425148</v>
+        <v>-0.31221945137157103</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B16" s="4">
-        <v>3.36</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-10</v>
+        <v>3.09</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-4.0404040404040398</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-0.33600000000000002</v>
+        <v>-0.12484848484848482</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6027,44 +5854,44 @@
         <v>6</v>
       </c>
       <c r="B17" s="4">
-        <v>3.08</v>
-      </c>
-      <c r="C17" s="3">
-        <v>3.12249799839871</v>
+        <v>2.82</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4.6583850931677002</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>9.6172938350680276E-2</v>
+        <v>0.13136645962732912</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B18" s="4">
-        <v>2.86</v>
-      </c>
-      <c r="C18" s="3">
-        <v>-3.79596678529062</v>
+        <v>2.62</v>
+      </c>
+      <c r="C18" s="8">
+        <v>6.2885326757089999</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10856465005931172</v>
+        <v>0.16475955610357582</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B19" s="4">
-        <v>2.66</v>
-      </c>
-      <c r="C19" s="3">
-        <v>-2.3635340461451801</v>
+        <v>2.44</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2.0172910662824202</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>-6.2870005627461797E-2</v>
+        <v>4.9221902017291048E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6072,29 +5899,29 @@
         <v>3</v>
       </c>
       <c r="B20" s="4">
-        <v>2.62</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0</v>
+        <v>2.4</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2.7777777777777701</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.6666666666666485E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B21" s="4">
-        <v>2.58</v>
-      </c>
-      <c r="C21" s="3">
-        <v>-1.56782549420586</v>
+        <v>2.36</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-4.3628808864265904</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-4.0449897750511193E-2</v>
+        <v>-0.10296398891966753</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -6102,99 +5929,151 @@
         <v>8</v>
       </c>
       <c r="B22" s="4">
-        <v>2.31</v>
-      </c>
-      <c r="C22" s="3">
-        <v>3.1333333333333302</v>
+        <v>2.12</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-1.4867485455720699</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>7.2379999999999931E-2</v>
+        <v>-3.1519069166127879E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4">
-        <v>2.25</v>
-      </c>
-      <c r="C23" s="3">
-        <v>-1.02941176470588</v>
+        <v>2.06</v>
+      </c>
+      <c r="C23" s="8">
+        <v>4.3833580980683502</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-2.3161764705882302E-2</v>
+        <v>9.0297176820208019E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B24" s="4">
-        <v>1.85</v>
-      </c>
-      <c r="C24" s="3">
-        <v>9.6525096525096499E-2</v>
+        <v>1.7</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1.25361620057859</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>1.7857142857142852E-3</v>
+        <v>2.1311475409836033E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B25" s="4">
-        <v>1.74</v>
-      </c>
-      <c r="C25" s="3">
-        <v>-3.6910457963089498</v>
+        <v>1.59</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-0.92264017033356904</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>-6.4224196855775725E-2</v>
+        <v>-1.4669978708303747E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="5">
-        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25</f>
-        <v>95.839999999999989</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="6">
-        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D25</f>
-        <v>-0.51578414796124394</v>
+      <c r="A26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="4">
+        <v>0.99</v>
+      </c>
+      <c r="C26" s="14">
+        <v>-2.41477272727272</v>
+      </c>
+      <c r="D26" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.3906249999999928E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="7"/>
+      <c r="A27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="C27" s="8">
+        <v>6.2429057888762696</v>
+      </c>
+      <c r="D27" s="7">
+        <f t="shared" si="0"/>
+        <v>5.9307604994324553E-2</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="5"/>
+      <c r="A28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.83148558758314794</v>
+      </c>
+      <c r="D28" s="7">
+        <f t="shared" si="0"/>
+        <v>7.5665188470066466E-3</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="4">
+        <v>0.91</v>
+      </c>
+      <c r="C29" s="14">
+        <v>6.0096153846153797</v>
+      </c>
+      <c r="D29" s="7">
+        <f t="shared" si="0"/>
+        <v>5.4687499999999958E-2</v>
+      </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="A30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0.84388185654008396</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" si="0"/>
+        <v>4.2194092827004204E-4</v>
+      </c>
       <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="19"/>
+      <c r="A31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="5">
+        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20+B21+B22+B23+B24+B25+B26+B27+B28+B29+B30</f>
+        <v>91.69</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D25+D26+D27+D28+D29+D30</f>
+        <v>1.6381181517264491</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
@@ -6302,15 +6181,8 @@
       <c r="E46" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
+  <mergeCells count="15">
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
@@ -6320,6 +6192,11 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2362F94F-228A-48EB-8E43-44181027B182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0DE09A-44AB-47AE-8F27-599182CE94F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="120" windowWidth="12720" windowHeight="20595" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13275" yWindow="150" windowWidth="12750" windowHeight="20745" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="KHA" sheetId="7" r:id="rId5"/>
     <sheet name="THF" sheetId="8" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,6 +36,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,16 +527,16 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,6 +552,37 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <ddeLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ddeService="MTXIQ" ddeTopic="DATA">
+    <ddeItems>
+      <ddeItem name="IEYHO.GUNFY" advise="1">
+        <values>
+          <value>
+            <val>0.55865921787709405</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="ISKPL.GUNFY" advise="1">
+        <values>
+          <value>
+            <val>10</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="LIDER.GUNFY" advise="1">
+        <values>
+          <value>
+            <val>-9.9813084112149504</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="StdDocumentName" ole="1" advise="1"/>
+    </ddeItems>
+  </ddeLink>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -846,11 +902,11 @@
         <v>32.590000000000003</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.0989010989010899</v>
+        <v>-1.1111111111111101</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.35813186813186526</v>
+        <v>-0.36211111111111083</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,11 +917,11 @@
         <v>11.57</v>
       </c>
       <c r="C3" s="3">
-        <v>5.9389140271493197</v>
+        <v>0.90763481046449501</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.68713235294117625</v>
+        <v>0.10501334757074207</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -876,11 +932,11 @@
         <v>9.02</v>
       </c>
       <c r="C4" s="3">
-        <v>0</v>
+        <v>0.69033530571992097</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D23" si="0">B4*C4/100</f>
-        <v>0</v>
+        <v>6.2268244575936868E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -891,11 +947,11 @@
         <v>5.94</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7777777777777701</v>
+        <v>3.3783783783783701</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.16499999999999956</v>
+        <v>0.20067567567567518</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -906,11 +962,11 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="C6" s="3">
-        <v>1.4942528735632099</v>
+        <v>0.90600226500566206</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>6.006896551724103E-2</v>
+        <v>3.6421291053227611E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -921,11 +977,11 @@
         <v>3.93</v>
       </c>
       <c r="C7" s="3">
-        <v>1.5228426395939001</v>
+        <v>8.5</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>5.984771573604028E-2</v>
+        <v>0.33405000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,11 +992,11 @@
         <v>2.15</v>
       </c>
       <c r="C8" s="3">
-        <v>4.6583850931677002</v>
+        <v>2.29970326409495</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.10015527950310554</v>
+        <v>4.9443620178041423E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -951,11 +1007,11 @@
         <v>1.87</v>
       </c>
       <c r="C9" s="3">
-        <v>1.4880952380952299</v>
+        <v>-0.29325513196480901</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>2.7827380952380801E-2</v>
+        <v>-5.4838709677419283E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -966,11 +1022,11 @@
         <v>1.67</v>
       </c>
       <c r="C10" s="3">
-        <v>3.4934497816593799</v>
+        <v>4.0084388185654003</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>5.8340611353711644E-2</v>
+        <v>6.694092827004218E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -981,11 +1037,11 @@
         <v>1.39</v>
       </c>
       <c r="C11" s="3">
-        <v>-2.7928626842513502</v>
+        <v>0.55865921787709405</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-3.8820791311093762E-2</v>
+        <v>7.7653631284916071E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -996,11 +1052,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C12" s="3">
-        <v>-9.9722991689750593</v>
+        <v>-10</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-5.484764542936283E-2</v>
+        <v>-5.5E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1011,11 +1067,11 @@
         <v>0.51</v>
       </c>
       <c r="C13" s="3">
-        <v>-1.4867485455720699</v>
+        <v>1.2467191601049801</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-7.5824175824175562E-3</v>
+        <v>6.3582677165353986E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1026,11 +1082,11 @@
         <v>0.39</v>
       </c>
       <c r="C14" s="3">
-        <v>6.2429057888762696</v>
+        <v>-1.7628205128205101</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>2.4347332576617454E-2</v>
+        <v>-6.8749999999999896E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,11 +1097,11 @@
         <v>0.27</v>
       </c>
       <c r="C15" s="3">
-        <v>0.25789813023855501</v>
+        <v>4.1157556270096398</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>6.963249516440986E-4</v>
+        <v>1.1112540192926028E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1056,11 +1112,11 @@
         <v>0.12</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.21621621621621</v>
+        <v>4.5827633378932902</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-1.459459459459452E-3</v>
+        <v>5.4993160054719482E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1071,11 +1127,11 @@
         <v>0.05</v>
       </c>
       <c r="C17" s="3">
-        <v>1.8957345971563899</v>
+        <v>0.581395348837209</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>9.4786729857819496E-4</v>
+        <v>2.9069767441860448E-4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1086,11 +1142,11 @@
         <v>0.04</v>
       </c>
       <c r="C18" s="3">
-        <v>0.49140049140049102</v>
+        <v>-0.48899755501222397</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>1.9656019656019643E-4</v>
+        <v>-1.955990220048896E-4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1101,11 +1157,11 @@
         <v>0.03</v>
       </c>
       <c r="C19" s="3">
-        <v>2.7426160337552701</v>
+        <v>9.9589322381930092</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>8.2278481012658096E-4</v>
+        <v>2.9876796714579028E-3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,11 +1172,11 @@
         <v>0.03</v>
       </c>
       <c r="C20" s="3">
-        <v>4.8150322959483196</v>
+        <v>-0.44817927170868299</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>1.4445096887844957E-3</v>
+        <v>-1.3445378151260488E-4</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1131,11 +1187,11 @@
         <v>0.02</v>
       </c>
       <c r="C21" s="3">
-        <v>-2.33863423760523</v>
+        <v>-2.5862068965517202</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-4.6772684752104603E-4</v>
+        <v>-5.1724137931034408E-4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1146,11 +1202,11 @@
         <v>5.62</v>
       </c>
       <c r="C22" s="3">
-        <v>-0.2</v>
+        <v>2.92</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1240000000000002E-2</v>
+        <v>0.164104</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1161,11 +1217,11 @@
         <v>0.01</v>
       </c>
       <c r="C23" s="3">
-        <v>0.47</v>
+        <v>3.56</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>4.7000000000000004E-5</v>
+        <v>3.5599999999999998E-4</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1179,7 +1235,7 @@
       <c r="C24" s="5"/>
       <c r="D24" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21</f>
-        <v>0.72551777676424634</v>
+        <v>0.45850969545128628</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1197,126 +1253,126 @@
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
       <c r="C30" s="9"/>
       <c r="D30" s="19"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="20"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="25"/>
       <c r="E32" s="21"/>
       <c r="F32" s="24"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="18"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="25"/>
       <c r="E33" s="22"/>
       <c r="F33" s="24"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="25"/>
       <c r="E34" s="22"/>
       <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="25"/>
       <c r="E35" s="22"/>
       <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="18"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="25"/>
       <c r="E36" s="22"/>
       <c r="F36" s="24"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="18"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
       <c r="D37" s="25"/>
       <c r="E37" s="22"/>
       <c r="F37" s="24"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="18"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="25"/>
       <c r="E38" s="22"/>
       <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="18"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
       <c r="D39" s="25"/>
       <c r="E39" s="22"/>
       <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="18"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="25"/>
       <c r="E40" s="22"/>
       <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="18"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="25"/>
       <c r="E41" s="22"/>
       <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="18"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
       <c r="D42" s="25"/>
       <c r="E42" s="22"/>
       <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="18"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
       <c r="D43" s="25"/>
       <c r="E43" s="22"/>
       <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="18"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
       <c r="D44" s="25"/>
       <c r="E44" s="22"/>
       <c r="F44" s="24"/>
@@ -1379,11 +1435,11 @@
         <v>15.5</v>
       </c>
       <c r="C2" s="27">
-        <v>7.4675324675324601</v>
+        <v>-3.62537764350453</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>1.1574675324675312</v>
+        <v>-0.56193353474320207</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,11 +1450,11 @@
         <v>11.91</v>
       </c>
       <c r="C3" s="27">
-        <v>-9.9682539682539595</v>
+        <v>9.3088857545839208</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D26" si="0">B3*C3/100</f>
-        <v>-1.1872190476190465</v>
+        <v>1.108688293370945</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,11 +1465,11 @@
         <v>10.17</v>
       </c>
       <c r="C4" s="27">
-        <v>-9.9567099567099504</v>
+        <v>-9.9893162393162296</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0125974025974021</v>
+        <v>-1.0159134615384606</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,11 +1480,11 @@
         <v>9.48</v>
       </c>
       <c r="C5" s="27">
-        <v>7.2742133224356298</v>
+        <v>-0.38095238095237999</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.6895954229668978</v>
+        <v>-3.6114285714285627E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1439,11 +1495,11 @@
         <v>8</v>
       </c>
       <c r="C6" s="27">
-        <v>-9.9722991689750593</v>
+        <v>-10</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.7977839335180047</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,11 +1510,11 @@
         <v>5.28</v>
       </c>
       <c r="C7" s="27">
-        <v>5.9389140271493197</v>
+        <v>0.90763481046449501</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.3135746606334841</v>
+        <v>4.7923117992525341E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,11 +1525,11 @@
         <v>5.08</v>
       </c>
       <c r="C8" s="27">
-        <v>4.4416243654822303</v>
+        <v>1.8226002430133601</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.22563451776649732</v>
+        <v>9.2588092345078699E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,11 +1540,11 @@
         <v>2.82</v>
       </c>
       <c r="C9" s="27">
-        <v>-2.6315789473684199</v>
+        <v>-1.9819819819819799</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-7.4210526315789435E-2</v>
+        <v>-5.589189189189183E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,11 +1555,11 @@
         <v>2.75</v>
       </c>
       <c r="C10" s="27">
-        <v>4.6583850931677002</v>
+        <v>2.29970326409495</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.12810559006211175</v>
+        <v>6.3241839762611121E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1514,11 +1570,11 @@
         <v>1.89</v>
       </c>
       <c r="C11" s="27">
-        <v>-6.4949608062709903</v>
+        <v>2.2754491017963998</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12275475923852172</v>
+        <v>4.3005988023951953E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,11 +1585,11 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="C12" s="27">
-        <v>-2.5601241272304098</v>
+        <v>-1.3535031847133701</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8417377812257553E-2</v>
+        <v>-1.5023885350318409E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,11 +1600,11 @@
         <v>1.07</v>
       </c>
       <c r="C13" s="27">
-        <v>2.7426160337552701</v>
+        <v>9.9589322381930092</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>2.9345991561181391E-2</v>
+        <v>0.10656057494866519</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1559,11 +1615,11 @@
         <v>1.01</v>
       </c>
       <c r="C14" s="27">
-        <v>2.7777777777777701</v>
+        <v>3.3783783783783701</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>2.8055555555555479E-2</v>
+        <v>3.4121621621621537E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,11 +1630,11 @@
         <v>0.66</v>
       </c>
       <c r="C15" s="27">
-        <v>1.4880952380952299</v>
+        <v>-0.29325513196480901</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>9.8214285714285175E-3</v>
+        <v>-1.9354838709677398E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,11 +1645,11 @@
         <v>0.53</v>
       </c>
       <c r="C16" s="27">
-        <v>1.8957345971563899</v>
+        <v>0.581395348837209</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>1.0047393364928867E-2</v>
+        <v>3.081395348837208E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,11 +1660,11 @@
         <v>0.38</v>
       </c>
       <c r="C17" s="27">
-        <v>0.46511627906976699</v>
+        <v>-0.11574074074074001</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>1.7674418604651145E-3</v>
+        <v>-4.3981481481481205E-4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,11 +1675,11 @@
         <v>0.13</v>
       </c>
       <c r="C18" s="27">
-        <v>5.2023121387283204</v>
+        <v>-2.19780219780219</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>6.7630057803468166E-3</v>
+        <v>-2.8571428571428472E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,11 +1690,11 @@
         <v>0.13</v>
       </c>
       <c r="C19" s="27">
-        <v>1.5228426395939001</v>
+        <v>8.5</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>1.9796954314720704E-3</v>
+        <v>1.1049999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1649,11 +1705,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C20" s="27">
-        <v>0.63795853269537395</v>
+        <v>-1.42630744849445</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>4.465709728867618E-4</v>
+        <v>-9.9841521394611506E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,11 +1720,11 @@
         <v>0.04</v>
       </c>
       <c r="C21" s="27">
-        <v>-2.4140752864157098</v>
+        <v>0.83857442348008304</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-9.6563011456628396E-4</v>
+        <v>3.354297693920332E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,11 +1735,11 @@
         <v>0.04</v>
       </c>
       <c r="C22" s="27">
-        <v>1.2463343108504299</v>
+        <v>-7.2411296162201294E-2</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>4.9853372434017194E-4</v>
+        <v>-2.8964518464880521E-5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1694,11 +1750,11 @@
         <v>9.73</v>
       </c>
       <c r="C23" s="27">
-        <v>10.46</v>
+        <v>7.61</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>1.0177580000000002</v>
+        <v>0.74045300000000014</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,11 +1765,11 @@
         <v>9.19</v>
       </c>
       <c r="C24" s="27">
-        <v>6.55</v>
+        <v>5.51</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>0.60194499999999995</v>
+        <v>0.50636899999999996</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1739,11 +1795,11 @@
         <v>0.02</v>
       </c>
       <c r="C26" s="3">
-        <v>0.32</v>
+        <v>-5.81</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>6.3999999999999997E-5</v>
+        <v>-1.1620000000000001E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1756,7 +1812,7 @@
       </c>
       <c r="D27" s="6">
         <f>SUM(D2:D26)</f>
-        <v>1.0010796635035395</v>
+        <v>0.26727747267013302</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1869,236 +1925,256 @@
       <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="31"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="31"/>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
       <c r="D55" s="20"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="31"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="19"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
       <c r="D70" s="19"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
       <c r="D71" s="19"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
       <c r="D72" s="19"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="19"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
       <c r="D74" s="19"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
       <c r="D75" s="19"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
       <c r="D76" s="19"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="31"/>
       <c r="D77" s="19"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
       <c r="D78" s="19"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
       <c r="D79" s="19"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
       <c r="D80" s="19"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
       <c r="D81" s="19"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2108,26 +2184,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2167,11 +2223,11 @@
         <v>15.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-9.9722991689750593</v>
-      </c>
-      <c r="D2" s="31">
+        <v>-10</v>
+      </c>
+      <c r="D2" s="29">
         <f>B2*C2/100</f>
-        <v>-1.580609418282547</v>
+        <v>-1.585</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,11 +2238,11 @@
         <v>14.37</v>
       </c>
       <c r="C3" s="3">
-        <v>7.4675324675324601</v>
-      </c>
-      <c r="D3" s="31">
-        <f t="shared" ref="D3:D22" si="0">B3*C3/100</f>
-        <v>1.0730844155844144</v>
+        <v>-3.62537764350453</v>
+      </c>
+      <c r="D3" s="29">
+        <f t="shared" ref="D3:D21" si="0">B3*C3/100</f>
+        <v>-0.52096676737160097</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2197,11 +2253,11 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="C4" s="3">
-        <v>-9.9567099567099504</v>
-      </c>
-      <c r="D4" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.99069264069263996</v>
+        <v>-9.9893162393162296</v>
+      </c>
+      <c r="D4" s="29">
+        <f t="shared" si="0"/>
+        <v>-0.99393696581196478</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2268,11 @@
         <v>9.31</v>
       </c>
       <c r="C5" s="3">
-        <v>7.2742133224356298</v>
-      </c>
-      <c r="D5" s="31">
-        <f t="shared" si="0"/>
-        <v>0.67722926031875719</v>
+        <v>-0.38095238095237999</v>
+      </c>
+      <c r="D5" s="29">
+        <f t="shared" si="0"/>
+        <v>-3.5466666666666577E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,11 +2283,11 @@
         <v>7.94</v>
       </c>
       <c r="C6" s="3">
-        <v>-9.9682539682539595</v>
-      </c>
-      <c r="D6" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.79147936507936434</v>
+        <v>9.3088857545839208</v>
+      </c>
+      <c r="D6" s="29">
+        <f t="shared" si="0"/>
+        <v>0.73912552891396333</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2242,11 +2298,11 @@
         <v>3.39</v>
       </c>
       <c r="C7" s="3">
-        <v>5.9389140271493197</v>
-      </c>
-      <c r="D7" s="31">
-        <f t="shared" si="0"/>
-        <v>0.20132918552036194</v>
+        <v>0.90763481046449501</v>
+      </c>
+      <c r="D7" s="29">
+        <f t="shared" si="0"/>
+        <v>3.0768820074746382E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,11 +2313,11 @@
         <v>5.47</v>
       </c>
       <c r="C8" s="3">
-        <v>-2.6315789473684199</v>
-      </c>
-      <c r="D8" s="31">
-        <f t="shared" si="0"/>
-        <v>-0.14394736842105257</v>
+        <v>-1.9819819819819799</v>
+      </c>
+      <c r="D8" s="29">
+        <f t="shared" si="0"/>
+        <v>-0.10841441441441431</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,11 +2328,11 @@
         <v>5.29</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6583850931677002</v>
-      </c>
-      <c r="D9" s="31">
-        <f t="shared" si="0"/>
-        <v>0.24642857142857136</v>
+        <v>2.29970326409495</v>
+      </c>
+      <c r="D9" s="29">
+        <f t="shared" si="0"/>
+        <v>0.12165430267062285</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,11 +2343,11 @@
         <v>3.04</v>
       </c>
       <c r="C10" s="3">
-        <v>4.4416243654822303</v>
-      </c>
-      <c r="D10" s="31">
-        <f t="shared" si="0"/>
-        <v>0.13502538071065981</v>
+        <v>1.8226002430133601</v>
+      </c>
+      <c r="D10" s="29">
+        <f t="shared" si="0"/>
+        <v>5.540704738760615E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,11 +2358,11 @@
         <v>2.08</v>
       </c>
       <c r="C11" s="3">
-        <v>2.7426160337552701</v>
-      </c>
-      <c r="D11" s="31">
-        <f t="shared" si="0"/>
-        <v>5.7046413502109622E-2</v>
+        <v>9.9589322381930092</v>
+      </c>
+      <c r="D11" s="29">
+        <f t="shared" si="0"/>
+        <v>0.20714579055441459</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,11 +2373,11 @@
         <v>1.81</v>
       </c>
       <c r="C12" s="3">
-        <v>-2.5601241272304098</v>
-      </c>
-      <c r="D12" s="31">
-        <f t="shared" si="0"/>
-        <v>-4.6338246702870414E-2</v>
+        <v>-1.3535031847133701</v>
+      </c>
+      <c r="D12" s="29">
+        <f t="shared" si="0"/>
+        <v>-2.4498407643311997E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,11 +2388,11 @@
         <v>1.39</v>
       </c>
       <c r="C13" s="3">
-        <v>-6.4949608062709903</v>
-      </c>
-      <c r="D13" s="31">
-        <f t="shared" si="0"/>
-        <v>-9.0279955207166751E-2</v>
+        <v>2.2754491017963998</v>
+      </c>
+      <c r="D13" s="29">
+        <f t="shared" si="0"/>
+        <v>3.1628742514969957E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,11 +2403,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C14" s="3">
-        <v>1.8957345971563899</v>
-      </c>
-      <c r="D14" s="31">
-        <f t="shared" si="0"/>
-        <v>1.0805687203791421E-2</v>
+        <v>0.581395348837209</v>
+      </c>
+      <c r="D14" s="29">
+        <f t="shared" si="0"/>
+        <v>3.3139534883720912E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,11 +2418,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C15" s="3">
-        <v>0.66445182724252405</v>
-      </c>
-      <c r="D15" s="31">
-        <f t="shared" si="0"/>
-        <v>9.3023255813953374E-4</v>
+        <v>-0.49504950495049499</v>
+      </c>
+      <c r="D15" s="29">
+        <f t="shared" si="0"/>
+        <v>-6.9306930693069303E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2377,11 +2433,11 @@
         <v>0.11</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.21621621621621</v>
-      </c>
-      <c r="D16" s="31">
-        <f t="shared" si="0"/>
-        <v>-1.3378378378378312E-3</v>
+        <v>4.5827633378932902</v>
+      </c>
+      <c r="D16" s="29">
+        <f t="shared" si="0"/>
+        <v>5.041039671682619E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2392,11 +2448,11 @@
         <v>8.98</v>
       </c>
       <c r="C17" s="3">
-        <v>6.55</v>
-      </c>
-      <c r="D17" s="31">
-        <f t="shared" si="0"/>
-        <v>0.58818999999999999</v>
+        <v>5.51</v>
+      </c>
+      <c r="D17" s="29">
+        <f t="shared" si="0"/>
+        <v>0.49479799999999996</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2407,11 +2463,11 @@
         <v>8.66</v>
       </c>
       <c r="C18" s="3">
-        <v>10.46</v>
-      </c>
-      <c r="D18" s="31">
-        <f t="shared" si="0"/>
-        <v>0.90583600000000009</v>
+        <v>7.61</v>
+      </c>
+      <c r="D18" s="29">
+        <f t="shared" si="0"/>
+        <v>0.65902600000000011</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,11 +2478,11 @@
         <v>0.69</v>
       </c>
       <c r="C19" s="3">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="D19" s="31">
-        <f t="shared" si="0"/>
-        <v>1.3868999999999998E-2</v>
+        <v>7.59</v>
+      </c>
+      <c r="D19" s="29">
+        <f t="shared" si="0"/>
+        <v>5.2371000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2437,11 +2493,11 @@
         <v>0.09</v>
       </c>
       <c r="C20" s="3">
-        <v>0.67</v>
-      </c>
-      <c r="D20" s="31">
-        <f t="shared" si="0"/>
-        <v>6.0300000000000002E-4</v>
+        <v>0.62</v>
+      </c>
+      <c r="D20" s="29">
+        <f t="shared" si="0"/>
+        <v>5.579999999999999E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2454,7 +2510,7 @@
       <c r="C21" s="3">
         <v>0.13</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="29">
         <f t="shared" si="0"/>
         <v>1.3000000000000001E-5</v>
       </c>
@@ -2469,7 +2525,7 @@
       </c>
       <c r="D22" s="6">
         <f>SUM(D2:D21)</f>
-        <v>0.26570531460332675</v>
+        <v>-0.86812506593851124</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2570,836 +2626,927 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="31"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="17"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="31"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
       <c r="D53" s="20"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="18"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
       <c r="D54" s="21"/>
       <c r="E54" s="22"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="18"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="21"/>
       <c r="E55" s="22"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="18"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
       <c r="D56" s="21"/>
       <c r="E56" s="22"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
       <c r="D57" s="21"/>
       <c r="E57" s="22"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="31"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="21"/>
       <c r="E67" s="22"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
       <c r="D68" s="21"/>
       <c r="E68" s="22"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="21"/>
       <c r="E69" s="22"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="18"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
       <c r="D70" s="21"/>
       <c r="E70" s="22"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="18"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
       <c r="D71" s="21"/>
       <c r="E71" s="22"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="18"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
       <c r="D72" s="21"/>
       <c r="E72" s="22"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="21"/>
       <c r="E73" s="22"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="18"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
       <c r="D74" s="21"/>
       <c r="E74" s="22"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="18"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="18"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
       <c r="D76" s="21"/>
       <c r="E76" s="22"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="18"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="31"/>
       <c r="D77" s="21"/>
       <c r="E77" s="22"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="18"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
       <c r="D78" s="21"/>
       <c r="E78" s="22"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="18"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
       <c r="D79" s="21"/>
       <c r="E79" s="22"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="18"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
       <c r="D80" s="21"/>
       <c r="E80" s="22"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
       <c r="D81" s="21"/>
       <c r="E81" s="22"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="31"/>
       <c r="D82" s="21"/>
       <c r="E82" s="22"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="18"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
+      <c r="B83" s="31"/>
+      <c r="C83" s="31"/>
       <c r="D83" s="21"/>
       <c r="E83" s="22"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="29"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="31"/>
       <c r="D84" s="21"/>
       <c r="E84" s="22"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="18"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
       <c r="D85" s="21"/>
       <c r="E85" s="22"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="18"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="31"/>
       <c r="D86" s="21"/>
       <c r="E86" s="22"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="18"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
       <c r="D87" s="21"/>
       <c r="E87" s="22"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="18"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="29"/>
+      <c r="B88" s="31"/>
+      <c r="C88" s="31"/>
       <c r="D88" s="21"/>
       <c r="E88" s="22"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="18"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="31"/>
       <c r="D89" s="21"/>
       <c r="E89" s="22"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="18"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="29"/>
+      <c r="B90" s="31"/>
+      <c r="C90" s="31"/>
       <c r="D90" s="21"/>
       <c r="E90" s="22"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="18"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="29"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="31"/>
       <c r="D91" s="21"/>
       <c r="E91" s="22"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="31"/>
       <c r="D92" s="21"/>
       <c r="E92" s="22"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="31"/>
       <c r="D93" s="21"/>
       <c r="E93" s="22"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
+      <c r="B94" s="31"/>
+      <c r="C94" s="31"/>
       <c r="D94" s="21"/>
       <c r="E94" s="22"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="31"/>
       <c r="D95" s="21"/>
       <c r="E95" s="22"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="29"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="31"/>
       <c r="D96" s="21"/>
       <c r="E96" s="22"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="31"/>
       <c r="D97" s="21"/>
       <c r="E97" s="22"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
+      <c r="B98" s="31"/>
+      <c r="C98" s="31"/>
       <c r="D98" s="21"/>
       <c r="E98" s="22"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="29"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
       <c r="D99" s="21"/>
       <c r="E99" s="22"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
       <c r="D100" s="21"/>
       <c r="E100" s="22"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
+      <c r="B101" s="31"/>
+      <c r="C101" s="31"/>
       <c r="D101" s="21"/>
       <c r="E101" s="22"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
+      <c r="B102" s="31"/>
+      <c r="C102" s="31"/>
       <c r="D102" s="21"/>
       <c r="E102" s="22"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="31"/>
       <c r="D103" s="21"/>
       <c r="E103" s="22"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="18"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="29"/>
+      <c r="B104" s="31"/>
+      <c r="C104" s="31"/>
       <c r="D104" s="21"/>
       <c r="E104" s="22"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="18"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
+      <c r="B105" s="31"/>
+      <c r="C105" s="31"/>
       <c r="D105" s="21"/>
       <c r="E105" s="22"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="18"/>
-      <c r="B106" s="29"/>
-      <c r="C106" s="29"/>
+      <c r="B106" s="31"/>
+      <c r="C106" s="31"/>
       <c r="D106" s="21"/>
       <c r="E106" s="22"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="18"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
+      <c r="B107" s="31"/>
+      <c r="C107" s="31"/>
       <c r="D107" s="21"/>
       <c r="E107" s="22"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="18"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="29"/>
+      <c r="B108" s="31"/>
+      <c r="C108" s="31"/>
       <c r="D108" s="21"/>
       <c r="E108" s="22"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="18"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="29"/>
+      <c r="B109" s="31"/>
+      <c r="C109" s="31"/>
       <c r="D109" s="21"/>
       <c r="E109" s="22"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="18"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="29"/>
+      <c r="B110" s="31"/>
+      <c r="C110" s="31"/>
       <c r="D110" s="21"/>
       <c r="E110" s="22"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="18"/>
-      <c r="B111" s="29"/>
-      <c r="C111" s="29"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="31"/>
       <c r="D111" s="21"/>
       <c r="E111" s="22"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="18"/>
-      <c r="B112" s="29"/>
-      <c r="C112" s="29"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="31"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="18"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="29"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="31"/>
       <c r="D113" s="21"/>
       <c r="E113" s="22"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="18"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="29"/>
+      <c r="B114" s="31"/>
+      <c r="C114" s="31"/>
       <c r="D114" s="21"/>
       <c r="E114" s="22"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="18"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="29"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="31"/>
       <c r="D115" s="21"/>
       <c r="E115" s="22"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="18"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="29"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="31"/>
       <c r="D116" s="21"/>
       <c r="E116" s="22"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="18"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="29"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="31"/>
       <c r="D117" s="21"/>
       <c r="E117" s="22"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="18"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="29"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="31"/>
       <c r="D118" s="21"/>
       <c r="E118" s="22"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="18"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="29"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="31"/>
       <c r="D119" s="21"/>
       <c r="E119" s="22"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="18"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="29"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="31"/>
       <c r="D120" s="21"/>
       <c r="E120" s="22"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="18"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="29"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="31"/>
       <c r="D121" s="21"/>
       <c r="E121" s="22"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="29"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="31"/>
       <c r="D122" s="21"/>
       <c r="E122" s="22"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="18"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="29"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="31"/>
       <c r="D123" s="21"/>
       <c r="E123" s="22"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="18"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="29"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="31"/>
       <c r="D124" s="21"/>
       <c r="E124" s="22"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="18"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="29"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="31"/>
       <c r="D125" s="21"/>
       <c r="E125" s="22"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="18"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="29"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="31"/>
       <c r="D126" s="21"/>
       <c r="E126" s="22"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="18"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="29"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="31"/>
       <c r="D127" s="21"/>
       <c r="E127" s="22"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="18"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="29"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="31"/>
       <c r="D128" s="21"/>
       <c r="E128" s="22"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="18"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="29"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="31"/>
       <c r="D129" s="21"/>
       <c r="E129" s="22"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="18"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="29"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="31"/>
       <c r="D130" s="21"/>
       <c r="E130" s="22"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="18"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="29"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="31"/>
       <c r="D131" s="21"/>
       <c r="E131" s="22"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="18"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="29"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="31"/>
       <c r="D132" s="21"/>
       <c r="E132" s="22"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="18"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="29"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="31"/>
       <c r="D133" s="21"/>
       <c r="E133" s="22"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="29"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="31"/>
       <c r="D134" s="21"/>
       <c r="E134" s="22"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="18"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="29"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="31"/>
       <c r="D135" s="21"/>
       <c r="E135" s="22"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="18"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="29"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="31"/>
       <c r="D136" s="21"/>
       <c r="E136" s="22"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="18"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="29"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="31"/>
       <c r="D137" s="21"/>
       <c r="E137" s="22"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="18"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="29"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="31"/>
       <c r="D138" s="21"/>
       <c r="E138" s="22"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="18"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="29"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="31"/>
       <c r="D139" s="21"/>
       <c r="E139" s="22"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="18"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="29"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="31"/>
       <c r="D140" s="21"/>
       <c r="E140" s="22"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="18"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="29"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="31"/>
       <c r="D141" s="21"/>
       <c r="E141" s="22"/>
       <c r="F141" s="24"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="18"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="29"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="31"/>
       <c r="D142" s="21"/>
       <c r="E142" s="22"/>
       <c r="F142" s="24"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="18"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="29"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="31"/>
       <c r="D143" s="21"/>
       <c r="E143" s="22"/>
       <c r="F143" s="24"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="18"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="29"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="31"/>
       <c r="D144" s="21"/>
       <c r="E144" s="22"/>
       <c r="F144" s="24"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="18"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="29"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="31"/>
       <c r="D145" s="21"/>
       <c r="E145" s="22"/>
       <c r="F145" s="24"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="18"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="29"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="31"/>
       <c r="D146" s="21"/>
       <c r="E146" s="22"/>
       <c r="F146" s="24"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="18"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="29"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="31"/>
       <c r="D147" s="21"/>
       <c r="E147" s="22"/>
       <c r="F147" s="24"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="18"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="29"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="31"/>
       <c r="D148" s="21"/>
       <c r="E148" s="22"/>
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="18"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="29"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="31"/>
       <c r="D149" s="21"/>
       <c r="E149" s="22"/>
       <c r="F149" s="24"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="18"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="29"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="31"/>
       <c r="D150" s="21"/>
       <c r="E150" s="22"/>
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="18"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="29"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="31"/>
       <c r="D151" s="21"/>
       <c r="E151" s="22"/>
       <c r="F151" s="24"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="29"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="31"/>
       <c r="D152" s="21"/>
       <c r="E152" s="22"/>
       <c r="F152" s="24"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="18"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="29"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="31"/>
       <c r="D153" s="21"/>
       <c r="E153" s="22"/>
       <c r="F153" s="24"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="18"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="29"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="31"/>
       <c r="D154" s="21"/>
       <c r="E154" s="22"/>
       <c r="F154" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3413,97 +3560,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3543,12 +3599,13 @@
       <c r="B2" s="4">
         <v>41.32</v>
       </c>
-      <c r="C2" s="8">
-        <v>0.111856823266219</v>
-      </c>
-      <c r="D2" s="31">
+      <c r="C2" s="8" cm="1">
+        <f t="array" ref="C2">[1]!IEYHO.GUNFY</f>
+        <v>0.55865921787709405</v>
+      </c>
+      <c r="D2" s="29">
         <f>B2*C2/100</f>
-        <v>4.6219239373601687E-2</v>
+        <v>0.23083798882681528</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3558,12 +3615,13 @@
       <c r="B3" s="4">
         <v>3.28</v>
       </c>
-      <c r="C3" s="8">
-        <v>-1.59189580318379</v>
-      </c>
-      <c r="D3" s="31">
+      <c r="C3" s="8" cm="1">
+        <f t="array" ref="C3">[1]!ISKPL.GUNFY</f>
+        <v>10</v>
+      </c>
+      <c r="D3" s="29">
         <f t="shared" ref="D3:D9" si="0">B3*C3/100</f>
-        <v>-5.221418234442831E-2</v>
+        <v>0.32799999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3573,12 +3631,13 @@
       <c r="B4" s="4">
         <v>0.19</v>
       </c>
-      <c r="C4" s="8">
-        <v>2.9836381135707399</v>
-      </c>
-      <c r="D4" s="31">
-        <f t="shared" si="0"/>
-        <v>5.6689124157844059E-3</v>
+      <c r="C4" s="8" cm="1">
+        <f t="array" ref="C4">[1]!LIDER.GUNFY</f>
+        <v>-9.9813084112149504</v>
+      </c>
+      <c r="D4" s="29">
+        <f t="shared" si="0"/>
+        <v>-1.8964485981308406E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3589,11 +3648,11 @@
         <v>22.96</v>
       </c>
       <c r="C5" s="4">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D5" s="31">
-        <f t="shared" si="0"/>
-        <v>0.12628000000000003</v>
+        <v>-0.35</v>
+      </c>
+      <c r="D5" s="29">
+        <f t="shared" si="0"/>
+        <v>-8.0360000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3606,7 +3665,7 @@
       <c r="C6" s="4">
         <v>0.12</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="29">
         <f t="shared" si="0"/>
         <v>6.3480000000000003E-3</v>
       </c>
@@ -3619,11 +3678,11 @@
         <v>1.07</v>
       </c>
       <c r="C7" s="4">
-        <v>0.12</v>
-      </c>
-      <c r="D7" s="31">
-        <f t="shared" si="0"/>
-        <v>1.2840000000000002E-3</v>
+        <v>2.93</v>
+      </c>
+      <c r="D7" s="29">
+        <f t="shared" si="0"/>
+        <v>3.1351000000000004E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3634,11 +3693,11 @@
         <v>0.13</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="31">
-        <f t="shared" si="0"/>
-        <v>1.3000000000000002E-4</v>
+        <v>0.11</v>
+      </c>
+      <c r="D8" s="29">
+        <f t="shared" si="0"/>
+        <v>1.4300000000000001E-4</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3649,11 +3708,11 @@
         <v>0.03</v>
       </c>
       <c r="C9" s="4">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="D9" s="31">
-        <f t="shared" si="0"/>
-        <v>8.4000000000000009E-5</v>
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="D9" s="29">
+        <f t="shared" si="0"/>
+        <v>-2.1000000000000002E-5</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -3668,906 +3727,1006 @@
       <c r="C10" s="4"/>
       <c r="D10" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9</f>
-        <v>0.13379996944495781</v>
+        <v>0.4973345028455069</v>
       </c>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="20"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="23"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="21"/>
       <c r="E32" s="21"/>
       <c r="F32" s="24"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="21"/>
       <c r="E33" s="21"/>
       <c r="F33" s="24"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="21"/>
       <c r="E34" s="21"/>
       <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="21"/>
       <c r="E35" s="21"/>
       <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="21"/>
       <c r="E36" s="21"/>
       <c r="F36" s="24"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
       <c r="D37" s="21"/>
       <c r="E37" s="21"/>
       <c r="F37" s="24"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="24"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
       <c r="D39" s="21"/>
       <c r="E39" s="21"/>
       <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="24"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="24"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
       <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="24"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
       <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="24"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
       <c r="D44" s="21"/>
       <c r="E44" s="21"/>
       <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
       <c r="D45" s="21"/>
       <c r="E45" s="21"/>
       <c r="F45" s="24"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
       <c r="D46" s="21"/>
       <c r="E46" s="21"/>
       <c r="F46" s="24"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
       <c r="D47" s="21"/>
       <c r="E47" s="21"/>
       <c r="F47" s="24"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="21"/>
       <c r="E48" s="21"/>
       <c r="F48" s="24"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
       <c r="D49" s="21"/>
       <c r="E49" s="21"/>
       <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
       <c r="D50" s="21"/>
       <c r="E50" s="21"/>
       <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
       <c r="F51" s="24"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="24"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="23"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="24"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="24"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="23"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="24"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="23"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="31"/>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="24"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="24"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
       <c r="F58" s="24"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
       <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
       <c r="D60" s="21"/>
       <c r="E60" s="21"/>
       <c r="F60" s="24"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
       <c r="D61" s="21"/>
       <c r="E61" s="21"/>
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="31"/>
       <c r="D62" s="21"/>
       <c r="E62" s="21"/>
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="23"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
       <c r="F76" s="24"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="23"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="31"/>
       <c r="D77" s="21"/>
       <c r="E77" s="21"/>
       <c r="F77" s="24"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="23"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
       <c r="F78" s="24"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="23"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
       <c r="D79" s="21"/>
       <c r="E79" s="21"/>
       <c r="F79" s="24"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="23"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="24"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="24"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="31"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="24"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
+      <c r="B83" s="31"/>
+      <c r="C83" s="31"/>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="24"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="29"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="31"/>
       <c r="D84" s="21"/>
       <c r="E84" s="21"/>
       <c r="F84" s="24"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
       <c r="D85" s="21"/>
       <c r="E85" s="21"/>
       <c r="F85" s="24"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="31"/>
       <c r="D86" s="21"/>
       <c r="E86" s="21"/>
       <c r="F86" s="24"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="31"/>
       <c r="D87" s="21"/>
       <c r="E87" s="21"/>
       <c r="F87" s="24"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="29"/>
+      <c r="B88" s="31"/>
+      <c r="C88" s="31"/>
       <c r="D88" s="21"/>
       <c r="E88" s="21"/>
       <c r="F88" s="24"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
+      <c r="B89" s="31"/>
+      <c r="C89" s="31"/>
       <c r="D89" s="21"/>
       <c r="E89" s="21"/>
       <c r="F89" s="24"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="29"/>
+      <c r="B90" s="31"/>
+      <c r="C90" s="31"/>
       <c r="D90" s="21"/>
       <c r="E90" s="21"/>
       <c r="F90" s="24"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="29"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="31"/>
       <c r="D91" s="21"/>
       <c r="E91" s="21"/>
       <c r="F91" s="24"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="31"/>
       <c r="D92" s="21"/>
       <c r="E92" s="21"/>
       <c r="F92" s="24"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
+      <c r="B93" s="31"/>
+      <c r="C93" s="31"/>
       <c r="D93" s="21"/>
       <c r="E93" s="21"/>
       <c r="F93" s="24"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
+      <c r="B94" s="31"/>
+      <c r="C94" s="31"/>
       <c r="D94" s="21"/>
       <c r="E94" s="21"/>
       <c r="F94" s="24"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
+      <c r="B95" s="31"/>
+      <c r="C95" s="31"/>
       <c r="D95" s="21"/>
       <c r="E95" s="21"/>
       <c r="F95" s="24"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="29"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="31"/>
       <c r="D96" s="21"/>
       <c r="E96" s="21"/>
       <c r="F96" s="24"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="23"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="31"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
       <c r="F97" s="24"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="23"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
+      <c r="B98" s="31"/>
+      <c r="C98" s="31"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
       <c r="F98" s="24"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="29"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="24"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="31"/>
       <c r="D100" s="21"/>
       <c r="E100" s="21"/>
       <c r="F100" s="24"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
+      <c r="B101" s="31"/>
+      <c r="C101" s="31"/>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="24"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="23"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
+      <c r="B102" s="31"/>
+      <c r="C102" s="31"/>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="24"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="23"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
+      <c r="B103" s="31"/>
+      <c r="C103" s="31"/>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="24"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="23"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="29"/>
+      <c r="B104" s="31"/>
+      <c r="C104" s="31"/>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="24"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="23"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
+      <c r="B105" s="31"/>
+      <c r="C105" s="31"/>
       <c r="D105" s="21"/>
       <c r="E105" s="21"/>
       <c r="F105" s="24"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="23"/>
-      <c r="B106" s="29"/>
-      <c r="C106" s="29"/>
+      <c r="B106" s="31"/>
+      <c r="C106" s="31"/>
       <c r="D106" s="21"/>
       <c r="E106" s="21"/>
       <c r="F106" s="24"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="23"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
+      <c r="B107" s="31"/>
+      <c r="C107" s="31"/>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="24"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="23"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="29"/>
+      <c r="B108" s="31"/>
+      <c r="C108" s="31"/>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="24"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="23"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="29"/>
+      <c r="B109" s="31"/>
+      <c r="C109" s="31"/>
       <c r="D109" s="21"/>
       <c r="E109" s="21"/>
       <c r="F109" s="24"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="23"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="29"/>
+      <c r="B110" s="31"/>
+      <c r="C110" s="31"/>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="24"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="23"/>
-      <c r="B111" s="29"/>
-      <c r="C111" s="29"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="31"/>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="24"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="23"/>
-      <c r="B112" s="29"/>
-      <c r="C112" s="29"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="31"/>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="24"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="23"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="29"/>
+      <c r="B113" s="31"/>
+      <c r="C113" s="31"/>
       <c r="D113" s="21"/>
       <c r="E113" s="21"/>
       <c r="F113" s="24"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="23"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="29"/>
+      <c r="B114" s="31"/>
+      <c r="C114" s="31"/>
       <c r="D114" s="21"/>
       <c r="E114" s="21"/>
       <c r="F114" s="24"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="23"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="29"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="31"/>
       <c r="D115" s="21"/>
       <c r="E115" s="21"/>
       <c r="F115" s="24"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="23"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="29"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="31"/>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="24"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="23"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="29"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="31"/>
       <c r="D117" s="21"/>
       <c r="E117" s="21"/>
       <c r="F117" s="24"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="23"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="29"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="31"/>
       <c r="D118" s="21"/>
       <c r="E118" s="21"/>
       <c r="F118" s="24"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="23"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="29"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="31"/>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="23"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="29"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="31"/>
       <c r="D120" s="21"/>
       <c r="E120" s="21"/>
       <c r="F120" s="24"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="23"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="29"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="31"/>
       <c r="D121" s="21"/>
       <c r="E121" s="21"/>
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="23"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="29"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="31"/>
       <c r="D122" s="21"/>
       <c r="E122" s="21"/>
       <c r="F122" s="24"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="23"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="29"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="31"/>
       <c r="D123" s="21"/>
       <c r="E123" s="21"/>
       <c r="F123" s="24"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="23"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="29"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="31"/>
       <c r="D124" s="21"/>
       <c r="E124" s="21"/>
       <c r="F124" s="24"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="23"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="29"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="31"/>
       <c r="D125" s="21"/>
       <c r="E125" s="21"/>
       <c r="F125" s="24"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="23"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="29"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="31"/>
       <c r="D126" s="21"/>
       <c r="E126" s="21"/>
       <c r="F126" s="24"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="23"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="29"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="31"/>
       <c r="D127" s="21"/>
       <c r="E127" s="21"/>
       <c r="F127" s="24"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="23"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="29"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="31"/>
       <c r="D128" s="21"/>
       <c r="E128" s="21"/>
       <c r="F128" s="24"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="23"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="29"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="31"/>
       <c r="D129" s="21"/>
       <c r="E129" s="21"/>
       <c r="F129" s="24"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="23"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="29"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="31"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
       <c r="F130" s="24"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="23"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="29"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="31"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
       <c r="F131" s="24"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="23"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="29"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="31"/>
       <c r="D132" s="21"/>
       <c r="E132" s="21"/>
       <c r="F132" s="24"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="23"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="29"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="31"/>
       <c r="D133" s="21"/>
       <c r="E133" s="21"/>
       <c r="F133" s="24"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="23"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="29"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="31"/>
       <c r="D134" s="21"/>
       <c r="E134" s="21"/>
       <c r="F134" s="24"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="23"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="29"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="31"/>
       <c r="D135" s="21"/>
       <c r="E135" s="21"/>
       <c r="F135" s="24"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="23"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="29"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="31"/>
       <c r="D136" s="21"/>
       <c r="E136" s="21"/>
       <c r="F136" s="24"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="23"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="29"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="31"/>
       <c r="D137" s="21"/>
       <c r="E137" s="21"/>
       <c r="F137" s="24"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="23"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="29"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="31"/>
       <c r="D138" s="21"/>
       <c r="E138" s="21"/>
       <c r="F138" s="24"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="23"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="29"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="31"/>
       <c r="D139" s="21"/>
       <c r="E139" s="21"/>
       <c r="F139" s="24"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="23"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="29"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="31"/>
       <c r="D140" s="21"/>
       <c r="E140" s="21"/>
       <c r="F140" s="24"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="23"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="29"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="31"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4580,106 +4739,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4719,11 +4778,11 @@
         <v>8.27</v>
       </c>
       <c r="C2" s="3">
-        <v>5.9389140271493197</v>
+        <v>0.90763481046449501</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.49114819004524868</v>
+        <v>7.5061398825413739E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4734,11 +4793,11 @@
         <v>8.11</v>
       </c>
       <c r="C3" s="3">
-        <v>-1.0989010989010899</v>
+        <v>-1.1111111111111101</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D50" si="0">B3*C3/100</f>
-        <v>-8.9120879120878377E-2</v>
+        <f t="shared" ref="D3:D49" si="0">B3*C3/100</f>
+        <v>-9.0111111111111017E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4749,11 +4808,11 @@
         <v>6.92</v>
       </c>
       <c r="C4" s="3">
-        <v>1.4942528735632099</v>
+        <v>0.90600226500566206</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>0.10340229885057413</v>
+        <v>6.2695356738391814E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4764,11 +4823,11 @@
         <v>6.9</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7777777777777701</v>
+        <v>3.3783783783783701</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.19166666666666615</v>
+        <v>0.23310810810810753</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4779,11 +4838,11 @@
         <v>5.76</v>
       </c>
       <c r="C6" s="3">
-        <v>0.49140049140049102</v>
+        <v>-0.48899755501222397</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>2.8304668304668282E-2</v>
+        <v>-2.8166259168704098E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4794,11 +4853,11 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="C7" s="3">
-        <v>3.4934497816593799</v>
+        <v>4.0084388185654003</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.15930131004366771</v>
+        <v>0.18278481012658221</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4809,11 +4868,11 @@
         <v>4.28</v>
       </c>
       <c r="C8" s="27">
-        <v>6.2429057888762696</v>
+        <v>-1.7628205128205101</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.26719636776390432</v>
+        <v>-7.5448717948717839E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4824,11 +4883,11 @@
         <v>4.21</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6583850931677002</v>
+        <v>2.29970326409495</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>0.19611801242236018</v>
+        <v>9.6817507418397397E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4839,11 +4898,11 @@
         <v>4.08</v>
       </c>
       <c r="C10" s="3">
-        <v>0</v>
+        <v>0.69033530571992097</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.8165680473372774E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -4854,11 +4913,11 @@
         <v>2.88</v>
       </c>
       <c r="C11" s="3">
-        <v>0.25789813023855501</v>
+        <v>4.1157556270096398</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>7.4274661508703845E-3</v>
+        <v>0.11853376205787763</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4869,11 +4928,11 @@
         <v>2.62</v>
       </c>
       <c r="C12" s="28">
-        <v>1.5228426395939001</v>
+        <v>8.5</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>3.9898477157360189E-2</v>
+        <v>0.22270000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -4884,11 +4943,11 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="C13" s="3">
-        <v>1.4880952380952299</v>
+        <v>-0.29325513196480901</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>3.7053571428571228E-2</v>
+        <v>-7.3020527859237452E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4899,11 +4958,11 @@
         <v>2.4</v>
       </c>
       <c r="C14" s="3">
-        <v>-3.2023289665211001</v>
+        <v>-4.7619047619047601</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-7.6855895196506402E-2</v>
+        <v>-0.11428571428571424</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -4914,11 +4973,11 @@
         <v>1.77</v>
       </c>
       <c r="C15" s="27">
-        <v>0.969932104752667</v>
+        <v>-0.96061479346781897</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>1.7167798254122207E-2</v>
+        <v>-1.7002881844380396E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -4929,11 +4988,11 @@
         <v>1.76</v>
       </c>
       <c r="C16" s="3">
-        <v>0.87976539589442804</v>
+        <v>3.7790697674418601</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>1.5483870967741932E-2</v>
+        <v>6.6511627906976734E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -4944,11 +5003,11 @@
         <v>1.61</v>
       </c>
       <c r="C17" s="3">
-        <v>0.86814975583288101</v>
+        <v>2.8509951586874598</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>1.3977211068909385E-2</v>
+        <v>4.5901022054868103E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -4959,11 +5018,11 @@
         <v>1.58</v>
       </c>
       <c r="C18" s="3">
-        <v>2.5747508305647799</v>
+        <v>-0.24291497975708501</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>4.0681063122923522E-2</v>
+        <v>-3.8380566801619431E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -4974,11 +5033,11 @@
         <v>1.54</v>
       </c>
       <c r="C19" s="3">
-        <v>1.46960587842351</v>
+        <v>0.197498354180381</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>2.2631930527722055E-2</v>
+        <v>3.0414746543778676E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4989,11 +5048,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C20" s="3">
-        <v>-7.13606089438629</v>
+        <v>-1.38319672131147</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>-7.8496669838249197E-2</v>
+        <v>-1.521516393442617E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5004,11 +5063,11 @@
         <v>1.06</v>
       </c>
       <c r="C21" s="3">
-        <v>0.74200913242009103</v>
+        <v>0.62322946175637395</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>7.8652968036529661E-3</v>
+        <v>6.6062322946175648E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5019,11 +5078,11 @@
         <v>0.99</v>
       </c>
       <c r="C22" s="3">
-        <v>2.9514757378689298</v>
+        <v>-1.65208940719144</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>2.9219609804902406E-2</v>
+        <v>-1.6355685131195258E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5034,11 +5093,11 @@
         <v>0.98</v>
       </c>
       <c r="C23" s="27">
-        <v>0.15463917525773099</v>
+        <v>-2.57334019557385</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>1.5154639175257636E-3</v>
+        <v>-2.5218733916623728E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5049,11 +5108,11 @@
         <v>0.98</v>
       </c>
       <c r="C24" s="27">
-        <v>1.78926441351888</v>
+        <v>-1.953125</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>1.7534791252485023E-2</v>
+        <v>-1.9140625000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5064,11 +5123,11 @@
         <v>0.88</v>
       </c>
       <c r="C25" s="27">
-        <v>4.4925124792013298</v>
+        <v>-0.39808917197452198</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>3.9534109816971703E-2</v>
+        <v>-3.5031847133757937E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5079,11 +5138,11 @@
         <v>0.87</v>
       </c>
       <c r="C26" s="27">
-        <v>-0.398633257403189</v>
+        <v>0.62893081761006298</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>-3.4681093394077446E-3</v>
+        <v>5.471698113207548E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5094,11 +5153,11 @@
         <v>0.8</v>
       </c>
       <c r="C27" s="27">
-        <v>4.0060468631897201</v>
+        <v>0.36337209302325502</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>3.2048374905517762E-2</v>
+        <v>2.90697674418604E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5109,11 +5168,11 @@
         <v>0.75</v>
       </c>
       <c r="C28" s="27">
-        <v>6.2885326757089999</v>
+        <v>0.46403712296983701</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>4.7163995067817502E-2</v>
+        <v>3.4802784222737774E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5124,11 +5183,11 @@
         <v>0.59</v>
       </c>
       <c r="C29" s="27">
-        <v>10</v>
+        <v>9.9472990777338595</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>5.8999999999999997E-2</v>
+        <v>5.8689064558629767E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5139,11 +5198,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C30" s="27">
-        <v>1.63934426229508</v>
+        <v>-8.9605734767025005E-2</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>9.0163934426229411E-3</v>
+        <v>-4.9283154121863761E-4</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5154,11 +5213,11 @@
         <v>0.52</v>
       </c>
       <c r="C31" s="27">
-        <v>1.5700483091787401</v>
+        <v>-1.42687277051129</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>8.1642512077294491E-3</v>
+        <v>-7.419738406658708E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5169,11 +5228,11 @@
         <v>0.5</v>
       </c>
       <c r="C32" s="27">
-        <v>3.5573122529644201</v>
+        <v>-1.0687022900763301</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>1.7786561264822101E-2</v>
+        <v>-5.3435114503816508E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5184,11 +5243,11 @@
         <v>0.48</v>
       </c>
       <c r="C33" s="27">
-        <v>0.86720867208672003</v>
+        <v>1.0746910263299301</v>
       </c>
       <c r="D33" s="7">
         <f t="shared" si="0"/>
-        <v>4.1626016260162563E-3</v>
+        <v>5.1585169263836635E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5199,11 +5258,11 @@
         <v>0.47</v>
       </c>
       <c r="C34" s="27">
-        <v>-9.2063492063492003</v>
+        <v>-3.49650349650349</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>-4.3269841269841243E-2</v>
+        <v>-1.6433566433566402E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5214,11 +5273,11 @@
         <v>0.46</v>
       </c>
       <c r="C35" s="27">
-        <v>-3.9238315060588498</v>
+        <v>2.04204204204204</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>-1.8049624927870708E-2</v>
+        <v>9.3933933933933837E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5229,11 +5288,11 @@
         <v>0.46</v>
       </c>
       <c r="C36" s="27">
-        <v>-3.0563514804202399</v>
+        <v>0.98522167487684698</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="0"/>
-        <v>-1.4059216809933104E-2</v>
+        <v>4.5320197044334968E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5244,11 +5303,11 @@
         <v>0.45</v>
       </c>
       <c r="C37" s="27">
-        <v>-6.0623229461756303</v>
+        <v>-3.73944511459589</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="0"/>
-        <v>-2.7280453257790337E-2</v>
+        <v>-1.6827503015681505E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5259,11 +5318,11 @@
         <v>0.4</v>
       </c>
       <c r="C38" s="27">
-        <v>1.14140773620798</v>
+        <v>-6.2695924764890207E-2</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="0"/>
-        <v>4.5656309448319195E-3</v>
+        <v>-2.5078369905956086E-4</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5274,11 +5333,11 @@
         <v>0.39</v>
       </c>
       <c r="C39" s="27">
-        <v>0.15408320493066199</v>
+        <v>-0.61538461538461497</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="0"/>
-        <v>6.009244992295818E-4</v>
+        <v>-2.3999999999999985E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5289,11 +5348,11 @@
         <v>0.34</v>
       </c>
       <c r="C40" s="27">
-        <v>6.9473684210526301</v>
+        <v>3.8713910761154802</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="0"/>
-        <v>2.3621052631578942E-2</v>
+        <v>1.3162729658792633E-2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5304,11 +5363,11 @@
         <v>0.3</v>
       </c>
       <c r="C41" s="27">
-        <v>1.7182130584192401</v>
+        <v>5.4054054054053999</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="0"/>
-        <v>5.1546391752577206E-3</v>
+        <v>1.62162162162162E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5319,11 +5378,11 @@
         <v>0.25</v>
       </c>
       <c r="C42" s="27">
-        <v>4.6622264509990403</v>
+        <v>10</v>
       </c>
       <c r="D42" s="7">
         <f t="shared" si="0"/>
-        <v>1.16555661274976E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -5334,11 +5393,11 @@
         <v>0.25</v>
       </c>
       <c r="C43" s="27">
-        <v>-9.9722991689750593</v>
+        <v>-10</v>
       </c>
       <c r="D43" s="7">
         <f t="shared" si="0"/>
-        <v>-2.4930747922437647E-2</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -5349,11 +5408,11 @@
         <v>0.22</v>
       </c>
       <c r="C44" s="27">
-        <v>0</v>
+        <v>1.11386138613861</v>
       </c>
       <c r="D44" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.4504950495049418E-3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -5364,11 +5423,11 @@
         <v>0.19</v>
       </c>
       <c r="C45" s="27">
-        <v>9.9510603588907003</v>
+        <v>9.9406528189910901</v>
       </c>
       <c r="D45" s="7">
         <f t="shared" si="0"/>
-        <v>1.8907014681892331E-2</v>
+        <v>1.8887240356083069E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -5379,11 +5438,11 @@
         <v>0.08</v>
       </c>
       <c r="C46" s="27">
-        <v>-0.58284762697751802</v>
+        <v>-8.3752093802344996E-2</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>-4.6627810158201443E-4</v>
+        <v>-6.7001675041875999E-5</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -5394,11 +5453,11 @@
         <v>0.01</v>
       </c>
       <c r="C47" s="27">
-        <v>0.46816479400749</v>
+        <v>0.559179869524697</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>4.6816479400749005E-5</v>
+        <v>5.5917986952469702E-5</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -5432,7 +5491,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="30" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="5">
@@ -5442,7 +5501,7 @@
       <c r="C50" s="5"/>
       <c r="D50" s="6">
         <f>SUM(D2:D49)</f>
-        <v>1.6000922806405657</v>
+        <v>0.82457640504709806</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -5453,112 +5512,112 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
       <c r="D62" s="20"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
       <c r="D63" s="21"/>
       <c r="E63" s="21"/>
       <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
       <c r="D64" s="21"/>
       <c r="E64" s="21"/>
       <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="21"/>
       <c r="E66" s="21"/>
       <c r="F66" s="24"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="21"/>
       <c r="E67" s="21"/>
       <c r="F67" s="24"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="31"/>
       <c r="D68" s="21"/>
       <c r="E68" s="21"/>
       <c r="F68" s="24"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="21"/>
       <c r="E69" s="21"/>
       <c r="F69" s="24"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
       <c r="D70" s="21"/>
       <c r="E70" s="21"/>
       <c r="F70" s="24"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
       <c r="D71" s="21"/>
       <c r="E71" s="21"/>
       <c r="F71" s="24"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
       <c r="D72" s="21"/>
       <c r="E72" s="21"/>
       <c r="F72" s="24"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
       <c r="F73" s="24"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="31"/>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
       <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="31"/>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
       <c r="F75" s="24"/>
@@ -5632,11 +5691,11 @@
         <v>7.18</v>
       </c>
       <c r="C2" s="8">
-        <v>6.9473684210526301</v>
+        <v>3.8713910761154802</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.49882105263157883</v>
+        <v>0.27796587926509148</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5647,11 +5706,11 @@
         <v>7.24</v>
       </c>
       <c r="C3" s="8">
-        <v>-1.0989010989010899</v>
+        <v>-1.1111111111111101</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>-7.9560439560438914E-2</v>
+        <v>-8.0444444444444374E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5662,11 +5721,11 @@
         <v>6.71</v>
       </c>
       <c r="C4" s="8">
-        <v>1.4942528735632099</v>
+        <v>0.90600226500566206</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D30" si="0">B4*C4/100</f>
-        <v>0.10026436781609138</v>
+        <v>6.0792751981879924E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5677,11 +5736,11 @@
         <v>5.6</v>
       </c>
       <c r="C5" s="8">
-        <v>0</v>
+        <v>0.69033530571992097</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.8658777120315568E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5692,11 +5751,11 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>9.9510603588907003</v>
+        <v>9.9406528189910901</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.46670473083197384</v>
+        <v>0.46621661721068214</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5707,11 +5766,11 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>0.25789813023855501</v>
+        <v>4.1157556270096398</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>1.1218568665377142E-2</v>
+        <v>0.17903536977491932</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5722,11 +5781,11 @@
         <v>4.12</v>
       </c>
       <c r="C8" s="8">
-        <v>1.5228426395939001</v>
+        <v>8.5</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>6.2741116751268686E-2</v>
+        <v>0.35020000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5737,11 +5796,11 @@
         <v>3.82</v>
       </c>
       <c r="C9" s="8">
-        <v>4.8150322959483196</v>
+        <v>-0.44817927170868299</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>0.1839342337052258</v>
+        <v>-1.7120448179271691E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5752,11 +5811,11 @@
         <v>3.66</v>
       </c>
       <c r="C10" s="8">
-        <v>2.5747508305647799</v>
+        <v>-0.24291497975708501</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>9.4235880398670951E-2</v>
+        <v>-8.8906882591093112E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5767,11 +5826,11 @@
         <v>3.65</v>
       </c>
       <c r="C11" s="8">
-        <v>-0.474683544303797</v>
+        <v>-0.15898251192368801</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7325949367088592E-2</v>
+        <v>-5.8028616852146119E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5782,11 +5841,11 @@
         <v>3.64</v>
       </c>
       <c r="C12" s="8">
-        <v>-0.36063884595569201</v>
+        <v>1.4994829369183</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-1.3127253992787189E-2</v>
+        <v>5.4581178903826126E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5797,11 +5856,11 @@
         <v>3.63</v>
       </c>
       <c r="C13" s="8">
-        <v>9.9415204678362503</v>
+        <v>9.9290780141843893</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>0.36087719298245591</v>
+        <v>0.36042553191489335</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5812,11 +5871,11 @@
         <v>3.26</v>
       </c>
       <c r="C14" s="8">
-        <v>-2.0289855072463698</v>
+        <v>-2.7366863905325398</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-6.6144927536231649E-2</v>
+        <v>-8.9215976331360788E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5827,11 +5886,11 @@
         <v>3.13</v>
       </c>
       <c r="C15" s="8">
-        <v>-9.9750623441396495</v>
+        <v>9.9722991689750593</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-0.31221945137157103</v>
+        <v>0.31213296398891932</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5842,11 +5901,11 @@
         <v>3.09</v>
       </c>
       <c r="C16" s="8">
-        <v>-4.0404040404040398</v>
+        <v>2.6973684210526301</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-0.12484848484848482</v>
+        <v>8.3348684210526255E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5857,11 +5916,11 @@
         <v>2.82</v>
       </c>
       <c r="C17" s="8">
-        <v>4.6583850931677002</v>
+        <v>2.29970326409495</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>0.13136645962732912</v>
+        <v>6.4851632047477584E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5872,11 +5931,11 @@
         <v>2.62</v>
       </c>
       <c r="C18" s="8">
-        <v>6.2885326757089999</v>
+        <v>0.46403712296983701</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>0.16475955610357582</v>
+        <v>1.2157772621809731E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5887,11 +5946,11 @@
         <v>2.44</v>
       </c>
       <c r="C19" s="8">
-        <v>2.0172910662824202</v>
+        <v>3.4463276836158099</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>4.9221902017291048E-2</v>
+        <v>8.409039548022576E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5902,11 +5961,11 @@
         <v>2.4</v>
       </c>
       <c r="C20" s="8">
-        <v>2.7777777777777701</v>
+        <v>3.3783783783783701</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>6.6666666666666485E-2</v>
+        <v>8.1081081081080877E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5917,11 +5976,11 @@
         <v>2.36</v>
       </c>
       <c r="C21" s="8">
-        <v>-4.3628808864265904</v>
+        <v>0.362056480811006</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>-0.10296398891966753</v>
+        <v>8.5445329471397422E-3</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5932,11 +5991,11 @@
         <v>2.12</v>
       </c>
       <c r="C22" s="8">
-        <v>-1.4867485455720699</v>
+        <v>1.2467191601049801</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>-3.1519069166127879E-2</v>
+        <v>2.643044619422558E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5947,11 +6006,11 @@
         <v>2.06</v>
       </c>
       <c r="C23" s="8">
-        <v>4.3833580980683502</v>
+        <v>-1.49466192170818</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>9.0297176820208019E-2</v>
+        <v>-3.079003558718851E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5962,11 +6021,11 @@
         <v>1.7</v>
       </c>
       <c r="C24" s="8">
-        <v>1.25361620057859</v>
+        <v>-0.952380952380952</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>2.1311475409836033E-2</v>
+        <v>-1.6190476190476186E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5977,11 +6036,11 @@
         <v>1.59</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.92264017033356904</v>
+        <v>3.8681948424068699</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>-1.4669978708303747E-2</v>
+        <v>6.1504297994269236E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5992,11 +6051,11 @@
         <v>0.99</v>
       </c>
       <c r="C26" s="14">
-        <v>-2.41477272727272</v>
+        <v>2.62008733624454</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>-2.3906249999999928E-2</v>
+        <v>2.5938864628820949E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -6007,11 +6066,11 @@
         <v>0.95</v>
       </c>
       <c r="C27" s="8">
-        <v>6.2429057888762696</v>
+        <v>-1.7628205128205101</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>5.9307604994324553E-2</v>
+        <v>-1.6746794871794847E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -6022,11 +6081,11 @@
         <v>0.91</v>
       </c>
       <c r="C28" s="8">
-        <v>0.83148558758314794</v>
+        <v>-3.7932930181418301</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>7.5665188470066466E-3</v>
+        <v>-3.4518966465090652E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6037,11 +6096,11 @@
         <v>0.91</v>
       </c>
       <c r="C29" s="14">
-        <v>6.0096153846153797</v>
+        <v>-2.49433106575963</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>5.4687499999999958E-2</v>
+        <v>-2.2698412698412634E-2</v>
       </c>
       <c r="E29" s="4"/>
     </row>
@@ -6053,11 +6112,11 @@
         <v>0.05</v>
       </c>
       <c r="C30" s="8">
-        <v>0.84388185654008396</v>
+        <v>4.6025104602510396</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>4.2194092827004204E-4</v>
+        <v>2.3012552301255196E-3</v>
       </c>
       <c r="E30" s="17"/>
     </row>
@@ -6072,116 +6131,121 @@
       <c r="C31" s="5"/>
       <c r="D31" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D25+D26+D27+D28+D29+D30</f>
-        <v>1.6381181517264491</v>
+        <v>2.2278389278838651</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="20"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="18"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="25"/>
       <c r="E33" s="21"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="25"/>
       <c r="E34" s="22"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="25"/>
       <c r="E35" s="22"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="18"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="25"/>
       <c r="E36" s="22"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="18"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
       <c r="D37" s="25"/>
       <c r="E37" s="22"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="18"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="25"/>
       <c r="E38" s="22"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="18"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
       <c r="D39" s="25"/>
       <c r="E39" s="22"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="18"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="25"/>
       <c r="E40" s="22"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="18"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="25"/>
       <c r="E41" s="22"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="18"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
       <c r="D42" s="25"/>
       <c r="E42" s="22"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="18"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
       <c r="D43" s="25"/>
       <c r="E43" s="22"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="18"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
       <c r="D44" s="25"/>
       <c r="E44" s="22"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="18"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
       <c r="D45" s="25"/>
       <c r="E45" s="22"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="18"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
       <c r="D46" s="25"/>
       <c r="E46" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
@@ -6192,11 +6256,6 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0DE09A-44AB-47AE-8F27-599182CE94F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6566B9FD-169C-4F31-B0A0-6B705A318CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13275" yWindow="150" windowWidth="12750" windowHeight="20745" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18975" yWindow="1350" windowWidth="12270" windowHeight="19485" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="KHA" sheetId="7" r:id="rId5"/>
     <sheet name="THF" sheetId="8" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="105">
   <si>
     <t>DSTKF</t>
   </si>
@@ -322,9 +297,6 @@
   </si>
   <si>
     <t>TMPOL</t>
-  </si>
-  <si>
-    <t>METEN</t>
   </si>
   <si>
     <t>T3B</t>
@@ -552,37 +524,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <ddeLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ddeService="MTXIQ" ddeTopic="DATA">
-    <ddeItems>
-      <ddeItem name="IEYHO.GUNFY" advise="1">
-        <values>
-          <value>
-            <val>0.55865921787709405</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="ISKPL.GUNFY" advise="1">
-        <values>
-          <value>
-            <val>10</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="LIDER.GUNFY" advise="1">
-        <values>
-          <value>
-            <val>-9.9813084112149504</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="StdDocumentName" ole="1" advise="1"/>
-    </ddeItems>
-  </ddeLink>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -899,14 +840,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>32.590000000000003</v>
+        <v>31.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.1111111111111101</v>
+        <v>-1.1235955056179701</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.36211111111111083</v>
+        <v>-0.35786516853932349</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -914,14 +855,14 @@
         <v>0</v>
       </c>
       <c r="B3" s="4">
-        <v>11.57</v>
+        <v>13.91</v>
       </c>
       <c r="C3" s="3">
-        <v>0.90763481046449501</v>
+        <v>1.0582010582010499</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.10501334757074207</v>
+        <v>0.14719576719576605</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -929,14 +870,14 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>9.02</v>
+        <v>8.77</v>
       </c>
       <c r="C4" s="3">
-        <v>0.69033530571992097</v>
+        <v>0.48971596474044998</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" ref="D4:D23" si="0">B4*C4/100</f>
-        <v>6.2268244575936868E-2</v>
+        <f t="shared" ref="D4:D20" si="0">B4*C4/100</f>
+        <v>4.2948090107737459E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -944,14 +885,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>5.94</v>
+        <v>7.16</v>
       </c>
       <c r="C5" s="3">
-        <v>3.3783783783783701</v>
+        <v>0.65359477124182996</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.20067567567567518</v>
+        <v>4.6797385620915025E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -959,14 +900,14 @@
         <v>2</v>
       </c>
       <c r="B6" s="4">
-        <v>4.0199999999999996</v>
+        <v>2.91</v>
       </c>
       <c r="C6" s="3">
-        <v>0.90600226500566206</v>
+        <v>0.168350168350168</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>3.6421291053227611E-2</v>
+        <v>4.8989898989898889E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -974,14 +915,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="4">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="C7" s="3">
-        <v>8.5</v>
+        <v>3.91705069124423</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.33405000000000001</v>
+        <v>0.16490783410138207</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -989,14 +930,14 @@
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="C8" s="3">
-        <v>2.29970326409495</v>
+        <v>0.65264684554024599</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>4.9443620178041423E-2</v>
+        <v>1.3313995649021018E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1004,14 +945,14 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="C9" s="3">
-        <v>-0.29325513196480901</v>
+        <v>0.11764705882352899</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-5.4838709677419283E-3</v>
+        <v>1.8823529411764639E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1019,14 +960,14 @@
         <v>43</v>
       </c>
       <c r="B10" s="4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="C10" s="3">
-        <v>4.0084388185654003</v>
+        <v>1.82555780933062</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>6.694092827004218E-2</v>
+        <v>2.9208924949289922E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,14 +975,14 @@
         <v>83</v>
       </c>
       <c r="B11" s="4">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="C11" s="3">
-        <v>0.55865921787709405</v>
+        <v>5.07936507936508</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>7.7653631284916071E-3</v>
+        <v>8.6349206349206356E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,14 +990,14 @@
         <v>9</v>
       </c>
       <c r="B12" s="4">
-        <v>0.55000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="C12" s="3">
-        <v>-10</v>
+        <v>-9.9715099715099704</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-5.5E-2</v>
+        <v>-2.9914529914529909E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1064,14 +1005,14 @@
         <v>8</v>
       </c>
       <c r="B13" s="4">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="C13" s="3">
-        <v>1.2467191601049801</v>
+        <v>-0.97213220998055705</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>6.3582677165353986E-3</v>
+        <v>-4.8606610499027855E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1079,14 +1020,14 @@
         <v>55</v>
       </c>
       <c r="B14" s="4">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="C14" s="3">
-        <v>-1.7628205128205101</v>
+        <v>5.7096247960848201</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-6.8749999999999896E-3</v>
+        <v>1.1419249592169641E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1094,14 +1035,14 @@
         <v>44</v>
       </c>
       <c r="B15" s="4">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="C15" s="3">
-        <v>4.1157556270096398</v>
+        <v>4.0148239654107396</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>1.1112540192926028E-2</v>
+        <v>1.2044471896232218E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,14 +1050,14 @@
         <v>84</v>
       </c>
       <c r="B16" s="4">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="C16" s="3">
-        <v>4.5827633378932902</v>
+        <v>-1.50425114453891</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>5.4993160054719482E-3</v>
+        <v>-3.00850228907782E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1124,119 +1065,92 @@
         <v>27</v>
       </c>
       <c r="B17" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C17" s="3">
-        <v>0.581395348837209</v>
+        <v>-0.23121387283236899</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>2.9069767441860448E-4</v>
+        <v>-2.3121387283236899E-4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" s="4">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="C18" s="3">
-        <v>-0.48899755501222397</v>
+        <v>8.7768440709617099</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-1.955990220048896E-4</v>
+        <v>8.7768440709617094E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="B19" s="4">
-        <v>0.03</v>
+        <v>4.41</v>
       </c>
       <c r="C19" s="3">
-        <v>9.9589322381930092</v>
+        <v>0.59</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>2.9876796714579028E-3</v>
+        <v>2.6019E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="B20" s="4">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="C20" s="3">
-        <v>-0.44817927170868299</v>
+        <v>1.17</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>-1.3445378151260488E-4</v>
+        <v>1.17E-4</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="C21" s="3">
-        <v>-2.5862068965517202</v>
-      </c>
-      <c r="D21" s="7">
-        <f t="shared" si="0"/>
-        <v>-5.1724137931034408E-4</v>
+      <c r="A21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="5">
+        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20</f>
+        <v>81.869999999999976</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20</f>
+        <v>0.19999903670718147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="4">
-        <v>5.62</v>
-      </c>
-      <c r="C22" s="3">
-        <v>2.92</v>
-      </c>
-      <c r="D22" s="7">
-        <f t="shared" si="0"/>
-        <v>0.164104</v>
-      </c>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="4">
-        <v>0.01</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3.56</v>
-      </c>
-      <c r="D23" s="7">
-        <f t="shared" si="0"/>
-        <v>3.5599999999999998E-4</v>
-      </c>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="5">
-        <f>B2+B3+B4+B5+B6+B7+B8+B9+B10+B11+B12+B13+B14+B15+B16+B17+B18+B19+B20+B21</f>
-        <v>76.160000000000025</v>
-      </c>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="6">
-        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21</f>
-        <v>0.45850969545128628</v>
-      </c>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
@@ -1435,11 +1349,11 @@
         <v>15.5</v>
       </c>
       <c r="C2" s="27">
-        <v>-3.62537764350453</v>
+        <v>2.1943573667711598</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>-0.56193353474320207</v>
+        <v>0.34012539184952978</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,11 +1364,11 @@
         <v>11.91</v>
       </c>
       <c r="C3" s="27">
-        <v>9.3088857545839208</v>
+        <v>9.0322580645161299</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D26" si="0">B3*C3/100</f>
-        <v>1.108688293370945</v>
+        <v>1.0757419354838711</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1465,11 +1379,11 @@
         <v>10.17</v>
       </c>
       <c r="C4" s="27">
-        <v>-9.9893162393162296</v>
+        <v>-9.9703264094955397</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0159134615384606</v>
+        <v>-1.0139821958456965</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,11 +1394,11 @@
         <v>9.48</v>
       </c>
       <c r="C5" s="27">
-        <v>-0.38095238095237999</v>
+        <v>5.1625239005736097</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6114285714285627E-2</v>
+        <v>0.48940726577437821</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1495,11 +1409,11 @@
         <v>8</v>
       </c>
       <c r="C6" s="27">
-        <v>-10</v>
+        <v>-9.9715099715099704</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.8</v>
+        <v>-0.79772079772079763</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,11 +1424,11 @@
         <v>5.28</v>
       </c>
       <c r="C7" s="27">
-        <v>0.90763481046449501</v>
+        <v>1.0582010582010499</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>4.7923117992525341E-2</v>
+        <v>5.5873015873015436E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1525,11 +1439,11 @@
         <v>5.08</v>
       </c>
       <c r="C8" s="27">
-        <v>1.8226002430133601</v>
+        <v>2.9236276849641998</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>9.2588092345078699E-2</v>
+        <v>0.14852028639618134</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1540,11 +1454,11 @@
         <v>2.82</v>
       </c>
       <c r="C9" s="27">
-        <v>-1.9819819819819799</v>
+        <v>-1.47058823529411</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-5.589189189189183E-2</v>
+        <v>-4.1470588235293898E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,11 +1469,11 @@
         <v>2.75</v>
       </c>
       <c r="C10" s="27">
-        <v>2.29970326409495</v>
+        <v>0.65264684554024599</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>6.3241839762611121E-2</v>
+        <v>1.7947788252356763E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1570,11 +1484,11 @@
         <v>1.89</v>
       </c>
       <c r="C11" s="27">
-        <v>2.2754491017963998</v>
+        <v>0.23419203747072601</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>4.3005988023951953E-2</v>
+        <v>4.4262295081967211E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,11 +1499,11 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="C12" s="27">
-        <v>-1.3535031847133701</v>
+        <v>0.40355125100887801</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5023885350318409E-2</v>
+        <v>4.4794188861985466E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,11 +1514,11 @@
         <v>1.07</v>
       </c>
       <c r="C13" s="27">
-        <v>9.9589322381930092</v>
+        <v>8.7768440709617099</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>0.10656057494866519</v>
+        <v>9.3912231559290293E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,11 +1529,11 @@
         <v>1.01</v>
       </c>
       <c r="C14" s="27">
-        <v>3.3783783783783701</v>
+        <v>0.65359477124182996</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>3.4121621621621537E-2</v>
+        <v>6.6013071895424822E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,11 +1544,11 @@
         <v>0.66</v>
       </c>
       <c r="C15" s="27">
-        <v>-0.29325513196480901</v>
+        <v>0.11764705882352899</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-1.9354838709677398E-3</v>
+        <v>7.7647058823529134E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,11 +1559,11 @@
         <v>0.53</v>
       </c>
       <c r="C16" s="27">
-        <v>0.581395348837209</v>
+        <v>-0.23121387283236899</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>3.081395348837208E-3</v>
+        <v>-1.2254335260115559E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,11 +1574,11 @@
         <v>0.38</v>
       </c>
       <c r="C17" s="27">
-        <v>-0.11574074074074001</v>
+        <v>-1.8539976825028901</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-4.3981481481481205E-4</v>
+        <v>-7.0451911935109825E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,11 +1589,11 @@
         <v>0.13</v>
       </c>
       <c r="C18" s="27">
-        <v>-2.19780219780219</v>
+        <v>-1.68539325842696</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8571428571428472E-3</v>
+        <v>-2.1910112359550481E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,11 +1604,11 @@
         <v>0.13</v>
       </c>
       <c r="C19" s="27">
-        <v>8.5</v>
+        <v>3.91705069124423</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>1.1049999999999999E-2</v>
+        <v>5.092165898617499E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1705,11 +1619,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C20" s="27">
-        <v>-1.42630744849445</v>
+        <v>0.96463022508038498</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-9.9841521394611506E-4</v>
+        <v>6.7524115755626961E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,11 +1634,11 @@
         <v>0.04</v>
       </c>
       <c r="C21" s="27">
-        <v>0.83857442348008304</v>
+        <v>-1.8295218295218201</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>3.354297693920332E-4</v>
+        <v>-7.3180873180872812E-4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1735,11 +1649,11 @@
         <v>0.04</v>
       </c>
       <c r="C22" s="27">
-        <v>-7.2411296162201294E-2</v>
+        <v>1.3043478260869501</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8964518464880521E-5</v>
+        <v>5.2173913043478007E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1750,11 +1664,11 @@
         <v>9.73</v>
       </c>
       <c r="C23" s="27">
-        <v>7.61</v>
+        <v>-0.37</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>0.74045300000000014</v>
+        <v>-3.6001000000000005E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,11 +1679,11 @@
         <v>9.19</v>
       </c>
       <c r="C24" s="27">
-        <v>5.51</v>
+        <v>-1.5</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>0.50636899999999996</v>
+        <v>-0.13785</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1789,17 +1703,17 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="4">
         <v>0.02</v>
       </c>
       <c r="C26" s="3">
-        <v>-5.81</v>
+        <v>-0.76</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-1.1620000000000001E-3</v>
+        <v>-1.5200000000000001E-4</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1812,7 +1726,7 @@
       </c>
       <c r="D27" s="6">
         <f>SUM(D2:D26)</f>
-        <v>0.26727747267013302</v>
+        <v>0.20788846105833014</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2155,26 +2069,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2184,6 +2078,26 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2223,11 +2137,11 @@
         <v>15.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-10</v>
+        <v>-9.9715099715099704</v>
       </c>
       <c r="D2" s="29">
         <f>B2*C2/100</f>
-        <v>-1.585</v>
+        <v>-1.5804843304843303</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2238,11 +2152,11 @@
         <v>14.37</v>
       </c>
       <c r="C3" s="3">
-        <v>-3.62537764350453</v>
+        <v>2.1943573667711598</v>
       </c>
       <c r="D3" s="29">
         <f t="shared" ref="D3:D21" si="0">B3*C3/100</f>
-        <v>-0.52096676737160097</v>
+        <v>0.31532915360501568</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2253,11 +2167,11 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="C4" s="3">
-        <v>-9.9893162393162296</v>
+        <v>-9.9703264094955397</v>
       </c>
       <c r="D4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.99393696581196478</v>
+        <v>-0.99204747774480606</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2268,11 +2182,11 @@
         <v>9.31</v>
       </c>
       <c r="C5" s="3">
-        <v>-0.38095238095237999</v>
+        <v>5.1625239005736097</v>
       </c>
       <c r="D5" s="29">
         <f t="shared" si="0"/>
-        <v>-3.5466666666666577E-2</v>
+        <v>0.48063097514340308</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2283,11 +2197,11 @@
         <v>7.94</v>
       </c>
       <c r="C6" s="3">
-        <v>9.3088857545839208</v>
+        <v>9.0322580645161299</v>
       </c>
       <c r="D6" s="29">
         <f t="shared" si="0"/>
-        <v>0.73912552891396333</v>
+        <v>0.7171612903225808</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2298,11 +2212,11 @@
         <v>3.39</v>
       </c>
       <c r="C7" s="3">
-        <v>0.90763481046449501</v>
+        <v>1.0582010582010499</v>
       </c>
       <c r="D7" s="29">
         <f t="shared" si="0"/>
-        <v>3.0768820074746382E-2</v>
+        <v>3.5873015873015592E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2313,11 +2227,11 @@
         <v>5.47</v>
       </c>
       <c r="C8" s="3">
-        <v>-1.9819819819819799</v>
+        <v>-1.47058823529411</v>
       </c>
       <c r="D8" s="29">
         <f t="shared" si="0"/>
-        <v>-0.10841441441441431</v>
+        <v>-8.0441176470587822E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2328,11 +2242,11 @@
         <v>5.29</v>
       </c>
       <c r="C9" s="3">
-        <v>2.29970326409495</v>
+        <v>0.65264684554024599</v>
       </c>
       <c r="D9" s="29">
         <f t="shared" si="0"/>
-        <v>0.12165430267062285</v>
+        <v>3.4525018129079016E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2343,11 +2257,11 @@
         <v>3.04</v>
       </c>
       <c r="C10" s="3">
-        <v>1.8226002430133601</v>
+        <v>2.9236276849641998</v>
       </c>
       <c r="D10" s="29">
         <f t="shared" si="0"/>
-        <v>5.540704738760615E-2</v>
+        <v>8.8878281622911684E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2358,11 +2272,11 @@
         <v>2.08</v>
       </c>
       <c r="C11" s="3">
-        <v>9.9589322381930092</v>
+        <v>8.7768440709617099</v>
       </c>
       <c r="D11" s="29">
         <f t="shared" si="0"/>
-        <v>0.20714579055441459</v>
+        <v>0.18255835667600359</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2373,11 +2287,11 @@
         <v>1.81</v>
       </c>
       <c r="C12" s="3">
-        <v>-1.3535031847133701</v>
+        <v>0.40355125100887801</v>
       </c>
       <c r="D12" s="29">
         <f t="shared" si="0"/>
-        <v>-2.4498407643311997E-2</v>
+        <v>7.3042776432606926E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,11 +2302,11 @@
         <v>1.39</v>
       </c>
       <c r="C13" s="3">
-        <v>2.2754491017963998</v>
+        <v>0.23419203747072601</v>
       </c>
       <c r="D13" s="29">
         <f t="shared" si="0"/>
-        <v>3.1628742514969957E-2</v>
+        <v>3.2552693208430911E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2403,11 +2317,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C14" s="3">
-        <v>0.581395348837209</v>
+        <v>-0.23121387283236899</v>
       </c>
       <c r="D14" s="29">
         <f t="shared" si="0"/>
-        <v>3.3139534883720912E-3</v>
+        <v>-1.3179190751445031E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2418,11 +2332,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C15" s="3">
-        <v>-0.49504950495049499</v>
+        <v>-0.99502487562189001</v>
       </c>
       <c r="D15" s="29">
         <f t="shared" si="0"/>
-        <v>-6.9306930693069303E-4</v>
+        <v>-1.3930348258706462E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2433,11 +2347,11 @@
         <v>0.11</v>
       </c>
       <c r="C16" s="3">
-        <v>4.5827633378932902</v>
+        <v>-1.50425114453891</v>
       </c>
       <c r="D16" s="29">
         <f t="shared" si="0"/>
-        <v>5.041039671682619E-3</v>
+        <v>-1.6546762589928011E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2448,11 +2362,11 @@
         <v>8.98</v>
       </c>
       <c r="C17" s="3">
-        <v>5.51</v>
+        <v>-1.5</v>
       </c>
       <c r="D17" s="29">
         <f t="shared" si="0"/>
-        <v>0.49479799999999996</v>
+        <v>-0.13470000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2463,26 +2377,26 @@
         <v>8.66</v>
       </c>
       <c r="C18" s="3">
-        <v>7.61</v>
+        <v>-0.37</v>
       </c>
       <c r="D18" s="29">
         <f t="shared" si="0"/>
-        <v>0.65902600000000011</v>
+        <v>-3.2042000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4">
         <v>0.69</v>
       </c>
       <c r="C19" s="3">
-        <v>7.59</v>
+        <v>5.76</v>
       </c>
       <c r="D19" s="29">
         <f t="shared" si="0"/>
-        <v>5.2371000000000001E-2</v>
+        <v>3.9743999999999995E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2493,11 +2407,11 @@
         <v>0.09</v>
       </c>
       <c r="C20" s="3">
-        <v>0.62</v>
+        <v>-0.49</v>
       </c>
       <c r="D20" s="29">
         <f t="shared" si="0"/>
-        <v>5.579999999999999E-4</v>
+        <v>-4.4099999999999999E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2525,7 +2439,7 @@
       </c>
       <c r="D22" s="6">
         <f>SUM(D2:D21)</f>
-        <v>-0.86812506593851124</v>
+        <v>-0.91924897652361903</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3456,97 +3370,6 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3560,6 +3383,97 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3599,13 +3513,12 @@
       <c r="B2" s="4">
         <v>41.32</v>
       </c>
-      <c r="C2" s="8" cm="1">
-        <f t="array" ref="C2">[1]!IEYHO.GUNFY</f>
-        <v>0.55865921787709405</v>
+      <c r="C2" s="8">
+        <v>-0.77777777777777701</v>
       </c>
       <c r="D2" s="29">
         <f>B2*C2/100</f>
-        <v>0.23083798882681528</v>
+        <v>-0.32137777777777748</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3615,13 +3528,12 @@
       <c r="B3" s="4">
         <v>3.28</v>
       </c>
-      <c r="C3" s="8" cm="1">
-        <f t="array" ref="C3">[1]!ISKPL.GUNFY</f>
-        <v>10</v>
+      <c r="C3" s="8">
+        <v>9.8930481283422402</v>
       </c>
       <c r="D3" s="29">
         <f t="shared" ref="D3:D9" si="0">B3*C3/100</f>
-        <v>0.32799999999999996</v>
+        <v>0.32449197860962548</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3631,13 +3543,12 @@
       <c r="B4" s="4">
         <v>0.19</v>
       </c>
-      <c r="C4" s="8" cm="1">
-        <f t="array" ref="C4">[1]!LIDER.GUNFY</f>
-        <v>-9.9813084112149504</v>
+      <c r="C4" s="8">
+        <v>-8.0980066445182697</v>
       </c>
       <c r="D4" s="29">
         <f t="shared" si="0"/>
-        <v>-1.8964485981308406E-2</v>
+        <v>-1.5386212624584712E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3648,16 +3559,16 @@
         <v>22.96</v>
       </c>
       <c r="C5" s="4">
-        <v>-0.35</v>
+        <v>0.33</v>
       </c>
       <c r="D5" s="29">
         <f t="shared" si="0"/>
-        <v>-8.0360000000000001E-2</v>
+        <v>7.5768000000000002E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" s="4">
         <v>5.29</v>
@@ -3672,47 +3583,47 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4">
         <v>1.07</v>
       </c>
       <c r="C7" s="4">
-        <v>2.93</v>
+        <v>-9.89</v>
       </c>
       <c r="D7" s="29">
         <f t="shared" si="0"/>
-        <v>3.1351000000000004E-2</v>
+        <v>-0.10582300000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="4">
         <v>0.13</v>
       </c>
       <c r="C8" s="4">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="29">
         <f t="shared" si="0"/>
-        <v>1.4300000000000001E-4</v>
+        <v>1.3000000000000002E-4</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4">
         <v>0.03</v>
       </c>
       <c r="C9" s="4">
-        <v>-7.0000000000000007E-2</v>
+        <v>0.47</v>
       </c>
       <c r="D9" s="29">
         <f t="shared" si="0"/>
-        <v>-2.1000000000000002E-5</v>
+        <v>1.4099999999999998E-4</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -3727,7 +3638,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9</f>
-        <v>0.4973345028455069</v>
+        <v>-3.5708011792736728E-2</v>
       </c>
       <c r="E10" s="17"/>
     </row>
@@ -4627,106 +4538,6 @@
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4739,6 +4550,106 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4778,11 +4689,11 @@
         <v>8.27</v>
       </c>
       <c r="C2" s="3">
-        <v>0.90763481046449501</v>
+        <v>1.0582010582010499</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>7.5061398825413739E-2</v>
+        <v>8.7513227513226821E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4793,11 +4704,11 @@
         <v>8.11</v>
       </c>
       <c r="C3" s="3">
-        <v>-1.1111111111111101</v>
+        <v>-1.1235955056179701</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D49" si="0">B3*C3/100</f>
-        <v>-9.0111111111111017E-2</v>
+        <v>-9.1123595505617369E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4808,11 +4719,11 @@
         <v>6.92</v>
       </c>
       <c r="C4" s="3">
-        <v>0.90600226500566206</v>
+        <v>0.168350168350168</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>6.2695356738391814E-2</v>
+        <v>1.1649831649831625E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4823,11 +4734,11 @@
         <v>6.9</v>
       </c>
       <c r="C5" s="3">
-        <v>3.3783783783783701</v>
+        <v>0.65359477124182996</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>0.23310810810810753</v>
+        <v>4.5098039215686274E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4838,11 +4749,11 @@
         <v>5.76</v>
       </c>
       <c r="C6" s="3">
-        <v>-0.48899755501222397</v>
+        <v>3.8083538083538002</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>-2.8166259168704098E-2</v>
+        <v>0.21936117936117888</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4853,11 +4764,11 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="C7" s="3">
-        <v>4.0084388185654003</v>
+        <v>1.82555780933062</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.18278481012658221</v>
+        <v>8.3245436105476273E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4868,11 +4779,11 @@
         <v>4.28</v>
       </c>
       <c r="C8" s="27">
-        <v>-1.7628205128205101</v>
+        <v>5.7096247960848201</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-7.5448717948717839E-2</v>
+        <v>0.24437194127243031</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4883,11 +4794,11 @@
         <v>4.21</v>
       </c>
       <c r="C9" s="3">
-        <v>2.29970326409495</v>
+        <v>0.65264684554024599</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>9.6817507418397397E-2</v>
+        <v>2.7476432197244355E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4898,11 +4809,11 @@
         <v>4.08</v>
       </c>
       <c r="C10" s="3">
-        <v>0.69033530571992097</v>
+        <v>0.48971596474044998</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>2.8165680473372774E-2</v>
+        <v>1.998041136141036E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -4913,11 +4824,11 @@
         <v>2.88</v>
       </c>
       <c r="C11" s="3">
-        <v>4.1157556270096398</v>
+        <v>4.0148239654107396</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>0.11853376205787763</v>
+        <v>0.1156269302038293</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4928,11 +4839,11 @@
         <v>2.62</v>
       </c>
       <c r="C12" s="28">
-        <v>8.5</v>
+        <v>3.91705069124423</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>0.22270000000000001</v>
+        <v>0.10262672811059882</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -4943,26 +4854,26 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="C13" s="3">
-        <v>-0.29325513196480901</v>
+        <v>0.11764705882352899</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-7.3020527859237452E-3</v>
+        <v>2.9294117647058722E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B14" s="26">
         <v>2.4</v>
       </c>
       <c r="C14" s="3">
-        <v>-4.7619047619047601</v>
+        <v>-2.6315789473684199</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-0.11428571428571424</v>
+        <v>-6.315789473684208E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -4973,26 +4884,26 @@
         <v>1.77</v>
       </c>
       <c r="C15" s="27">
-        <v>-0.96061479346781897</v>
+        <v>0.969932104752667</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7002881844380396E-2</v>
+        <v>1.7167798254122207E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="4">
         <v>1.76</v>
       </c>
       <c r="C16" s="3">
-        <v>3.7790697674418601</v>
+        <v>-0.84033613445378097</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>6.6511627906976734E-2</v>
+        <v>-1.4789915966386544E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5003,11 +4914,11 @@
         <v>1.61</v>
       </c>
       <c r="C17" s="3">
-        <v>2.8509951586874598</v>
+        <v>-2.24895397489539</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>4.5901022054868103E-2</v>
+        <v>-3.6208158995815781E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5018,11 +4929,11 @@
         <v>1.58</v>
       </c>
       <c r="C18" s="3">
-        <v>-0.24291497975708501</v>
+        <v>-0.89285714285714202</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>-3.8380566801619431E-3</v>
+        <v>-1.4107142857142844E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5033,11 +4944,11 @@
         <v>1.54</v>
       </c>
       <c r="C19" s="3">
-        <v>0.197498354180381</v>
+        <v>-0.32851511169513797</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>3.0414746543778676E-3</v>
+        <v>-5.0591327201051249E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5048,11 +4959,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C20" s="3">
-        <v>-1.38319672131147</v>
+        <v>0.415584415584415</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>-1.521516393442617E-2</v>
+        <v>4.5714285714285648E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5063,11 +4974,11 @@
         <v>1.06</v>
       </c>
       <c r="C21" s="3">
-        <v>0.62322946175637395</v>
+        <v>0.67567567567567499</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>6.6062322946175648E-3</v>
+        <v>7.1621621621621558E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5078,11 +4989,11 @@
         <v>0.99</v>
       </c>
       <c r="C22" s="3">
-        <v>-1.65208940719144</v>
+        <v>2.3715415019762802</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6355685131195258E-2</v>
+        <v>2.3478260869565174E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5093,11 +5004,11 @@
         <v>0.98</v>
       </c>
       <c r="C23" s="27">
-        <v>-2.57334019557385</v>
+        <v>0.73956682514527206</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5218733916623728E-2</v>
+        <v>7.2477548864236666E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5108,11 +5019,11 @@
         <v>0.98</v>
       </c>
       <c r="C24" s="27">
-        <v>-1.953125</v>
+        <v>-0.46480743691899001</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>-1.9140625000000001E-2</v>
+        <v>-4.5551128818061021E-3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5123,11 +5034,11 @@
         <v>0.88</v>
       </c>
       <c r="C25" s="27">
-        <v>-0.39808917197452198</v>
+        <v>0.159872102318145</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>-3.5031847133757937E-3</v>
+        <v>1.4068745003996761E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5138,11 +5049,11 @@
         <v>0.87</v>
       </c>
       <c r="C26" s="27">
-        <v>0.62893081761006298</v>
+        <v>3.0681818181818099</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>5.471698113207548E-3</v>
+        <v>2.6693181818181748E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5153,11 +5064,11 @@
         <v>0.8</v>
       </c>
       <c r="C27" s="27">
-        <v>0.36337209302325502</v>
+        <v>-0.362056480811006</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>2.90697674418604E-3</v>
+        <v>-2.896451846488048E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5168,11 +5079,11 @@
         <v>0.75</v>
       </c>
       <c r="C28" s="27">
-        <v>0.46403712296983701</v>
+        <v>-1.3279445727482599</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>3.4802784222737774E-3</v>
+        <v>-9.9595842956119503E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5183,11 +5094,11 @@
         <v>0.59</v>
       </c>
       <c r="C29" s="27">
-        <v>9.9472990777338595</v>
+        <v>9.9460754943079692</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>5.8689064558629767E-2</v>
+        <v>5.8681845416417015E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5198,11 +5109,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C30" s="27">
-        <v>-8.9605734767025005E-2</v>
+        <v>-0.98654708520179302</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>-4.9283154121863761E-4</v>
+        <v>-5.426008968609862E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5213,11 +5124,11 @@
         <v>0.52</v>
       </c>
       <c r="C31" s="27">
-        <v>-1.42687277051129</v>
+        <v>-0.24125452352231599</v>
       </c>
       <c r="D31" s="7">
         <f t="shared" si="0"/>
-        <v>-7.419738406658708E-3</v>
+        <v>-1.2545235223160431E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5228,11 +5139,11 @@
         <v>0.5</v>
       </c>
       <c r="C32" s="27">
-        <v>-1.0687022900763301</v>
+        <v>1.0802469135802399</v>
       </c>
       <c r="D32" s="7">
         <f t="shared" si="0"/>
-        <v>-5.3435114503816508E-3</v>
+        <v>5.4012345679011996E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5243,11 +5154,11 @@
         <v>0.48</v>
       </c>
       <c r="C33" s="27">
-        <v>1.0746910263299301</v>
+        <v>1.8607123870281701</v>
       </c>
       <c r="D33" s="7">
         <f t="shared" si="0"/>
-        <v>5.1585169263836635E-3</v>
+        <v>8.9314194577352155E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5258,11 +5169,11 @@
         <v>0.47</v>
       </c>
       <c r="C34" s="27">
-        <v>-3.49650349650349</v>
+        <v>0.54347826086956497</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6433566433566402E-2</v>
+        <v>2.5543478260869551E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5273,11 +5184,11 @@
         <v>0.46</v>
       </c>
       <c r="C35" s="27">
-        <v>2.04204204204204</v>
+        <v>-3.23719835197174</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="0"/>
-        <v>9.3933933933933837E-3</v>
+        <v>-1.4891112419070006E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5288,11 +5199,11 @@
         <v>0.46</v>
       </c>
       <c r="C36" s="27">
-        <v>0.98522167487684698</v>
+        <v>0.87804878048780399</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="0"/>
-        <v>4.5320197044334968E-3</v>
+        <v>4.0390243902438984E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5303,11 +5214,11 @@
         <v>0.45</v>
       </c>
       <c r="C37" s="27">
-        <v>-3.73944511459589</v>
+        <v>-2.44360902255639</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6827503015681505E-2</v>
+        <v>-1.0996240601503756E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5318,11 +5229,11 @@
         <v>0.4</v>
       </c>
       <c r="C38" s="27">
-        <v>-6.2695924764890207E-2</v>
+        <v>-0.75282308657465402</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5078369905956086E-4</v>
+        <v>-3.0112923462986161E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5333,11 +5244,11 @@
         <v>0.39</v>
       </c>
       <c r="C39" s="27">
-        <v>-0.61538461538461497</v>
+        <v>-1.39318885448916</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="0"/>
-        <v>-2.3999999999999985E-3</v>
+        <v>-5.4334365325077235E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5348,26 +5259,26 @@
         <v>0.34</v>
       </c>
       <c r="C40" s="27">
-        <v>3.8713910761154802</v>
+        <v>-2.0846493998736499</v>
       </c>
       <c r="D40" s="7">
         <f t="shared" si="0"/>
-        <v>1.3162729658792633E-2</v>
+        <v>-7.0878079595704099E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="26">
         <v>0.3</v>
       </c>
       <c r="C41" s="27">
-        <v>5.4054054054053999</v>
+        <v>-2.5641025641025599</v>
       </c>
       <c r="D41" s="7">
         <f t="shared" si="0"/>
-        <v>1.62162162162162E-2</v>
+        <v>-7.6923076923076797E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5393,41 +5304,41 @@
         <v>0.25</v>
       </c>
       <c r="C43" s="27">
-        <v>-10</v>
+        <v>-9.9715099715099704</v>
       </c>
       <c r="D43" s="7">
         <f t="shared" si="0"/>
-        <v>-2.5000000000000001E-2</v>
+        <v>-2.4928774928774926E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="26">
         <v>0.22</v>
       </c>
       <c r="C44" s="27">
-        <v>1.11386138613861</v>
+        <v>-1.8359853121175</v>
       </c>
       <c r="D44" s="7">
         <f t="shared" si="0"/>
-        <v>2.4504950495049418E-3</v>
+        <v>-4.0391676866585007E-3</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="26">
         <v>0.19</v>
       </c>
       <c r="C45" s="27">
-        <v>9.9406528189910901</v>
+        <v>9.9865047233468296</v>
       </c>
       <c r="D45" s="7">
         <f t="shared" si="0"/>
-        <v>1.8887240356083069E-2</v>
+        <v>1.8974358974358976E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -5438,11 +5349,11 @@
         <v>0.08</v>
       </c>
       <c r="C46" s="27">
-        <v>-8.3752093802344996E-2</v>
+        <v>1.5926236378876699</v>
       </c>
       <c r="D46" s="7">
         <f t="shared" si="0"/>
-        <v>-6.7001675041875999E-5</v>
+        <v>1.2740989103101361E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -5453,16 +5364,16 @@
         <v>0.01</v>
       </c>
       <c r="C47" s="27">
-        <v>0.559179869524697</v>
+        <v>-0.46339202965708898</v>
       </c>
       <c r="D47" s="7">
         <f t="shared" si="0"/>
-        <v>5.5917986952469702E-5</v>
+        <v>-4.6339202965708901E-5</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B48" s="26">
         <v>3.34</v>
@@ -5477,7 +5388,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B49" s="26">
         <v>2.5499999999999998</v>
@@ -5501,7 +5412,7 @@
       <c r="C50" s="5"/>
       <c r="D50" s="6">
         <f>SUM(D2:D49)</f>
-        <v>0.82457640504709806</v>
+        <v>0.85286735769455646</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -5691,11 +5602,11 @@
         <v>7.18</v>
       </c>
       <c r="C2" s="8">
-        <v>3.8713910761154802</v>
+        <v>-2.0846493998736499</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>0.27796587926509148</v>
+        <v>-0.14967782691092807</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5706,11 +5617,11 @@
         <v>7.24</v>
       </c>
       <c r="C3" s="8">
-        <v>-1.1111111111111101</v>
+        <v>-1.1235955056179701</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>-8.0444444444444374E-2</v>
+        <v>-8.1348314606741037E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5721,11 +5632,11 @@
         <v>6.71</v>
       </c>
       <c r="C4" s="8">
-        <v>0.90600226500566206</v>
+        <v>0.168350168350168</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D30" si="0">B4*C4/100</f>
-        <v>6.0792751981879924E-2</v>
+        <v>1.1296296296296273E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5736,26 +5647,26 @@
         <v>5.6</v>
       </c>
       <c r="C5" s="8">
-        <v>0.69033530571992097</v>
+        <v>0.48971596474044998</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>3.8658777120315568E-2</v>
+        <v>2.7424094025465195E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4">
         <v>4.6900000000000004</v>
       </c>
       <c r="C6" s="8">
-        <v>9.9406528189910901</v>
+        <v>9.9865047233468296</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>0.46621661721068214</v>
+        <v>0.46836707152496637</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5766,11 +5677,11 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="C7" s="8">
-        <v>4.1157556270096398</v>
+        <v>4.0148239654107396</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.17903536977491932</v>
+        <v>0.17464484249536716</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5781,11 +5692,11 @@
         <v>4.12</v>
       </c>
       <c r="C8" s="8">
-        <v>8.5</v>
+        <v>3.91705069124423</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>0.35020000000000001</v>
+        <v>0.16138248847926229</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5796,11 +5707,11 @@
         <v>3.82</v>
       </c>
       <c r="C9" s="8">
-        <v>-0.44817927170868299</v>
+        <v>-0.33764772087788397</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>-1.7120448179271691E-2</v>
+        <v>-1.2898142937535167E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5811,11 +5722,11 @@
         <v>3.66</v>
       </c>
       <c r="C10" s="8">
-        <v>-0.24291497975708501</v>
+        <v>-0.89285714285714202</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>-8.8906882591093112E-3</v>
+        <v>-3.2678571428571404E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5826,11 +5737,11 @@
         <v>3.65</v>
       </c>
       <c r="C11" s="8">
-        <v>-0.15898251192368801</v>
+        <v>5.5732484076433098</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>-5.8028616852146119E-3</v>
+        <v>0.20342356687898078</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5841,11 +5752,11 @@
         <v>3.64</v>
       </c>
       <c r="C12" s="8">
-        <v>1.4994829369183</v>
+        <v>-1.0697911360162999</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>5.4581178903826126E-2</v>
+        <v>-3.8940397350993319E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5856,11 +5767,11 @@
         <v>3.63</v>
       </c>
       <c r="C13" s="8">
-        <v>9.9290780141843893</v>
+        <v>2.0161290322580601</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>0.36042553191489335</v>
+        <v>7.3185483870967585E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5871,11 +5782,11 @@
         <v>3.26</v>
       </c>
       <c r="C14" s="8">
-        <v>-2.7366863905325398</v>
+        <v>-2.12927756653992</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>-8.9215976331360788E-2</v>
+        <v>-6.9414448669201392E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5886,11 +5797,11 @@
         <v>3.13</v>
       </c>
       <c r="C15" s="8">
-        <v>9.9722991689750593</v>
+        <v>-9.9916036943744704</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>0.31213296398891932</v>
+        <v>-0.31273719563392094</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5901,11 +5812,11 @@
         <v>3.09</v>
       </c>
       <c r="C16" s="8">
-        <v>2.6973684210526301</v>
+        <v>-1.2812299807815499</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>8.3348684210526255E-2</v>
+        <v>-3.9590006406149889E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5916,11 +5827,11 @@
         <v>2.82</v>
       </c>
       <c r="C17" s="8">
-        <v>2.29970326409495</v>
+        <v>0.65264684554024599</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>6.4851632047477584E-2</v>
+        <v>1.8404641044234935E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5931,11 +5842,11 @@
         <v>2.62</v>
       </c>
       <c r="C18" s="8">
-        <v>0.46403712296983701</v>
+        <v>-1.3279445727482599</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>1.2157772621809731E-2</v>
+        <v>-3.4792147806004411E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5946,11 +5857,11 @@
         <v>2.44</v>
       </c>
       <c r="C19" s="8">
-        <v>3.4463276836158099</v>
+        <v>-2.2392135445111898</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>8.409039548022576E-2</v>
+        <v>-5.463681048607303E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5961,11 +5872,11 @@
         <v>2.4</v>
       </c>
       <c r="C20" s="8">
-        <v>3.3783783783783701</v>
+        <v>0.65359477124182996</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>8.1081081081080877E-2</v>
+        <v>1.5686274509803918E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5976,11 +5887,11 @@
         <v>2.36</v>
       </c>
       <c r="C21" s="8">
-        <v>0.362056480811006</v>
+        <v>3.5353535353535301</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="0"/>
-        <v>8.5445329471397422E-3</v>
+        <v>8.3434343434343305E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5991,11 +5902,11 @@
         <v>2.12</v>
       </c>
       <c r="C22" s="8">
-        <v>1.2467191601049801</v>
+        <v>-0.97213220998055705</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="0"/>
-        <v>2.643044619422558E-2</v>
+        <v>-2.0609202851587807E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -6006,11 +5917,11 @@
         <v>2.06</v>
       </c>
       <c r="C23" s="8">
-        <v>-1.49466192170818</v>
+        <v>4.5520231213872799</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="0"/>
-        <v>-3.079003558718851E-2</v>
+        <v>9.3771676300577964E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6021,11 +5932,11 @@
         <v>1.7</v>
       </c>
       <c r="C24" s="8">
-        <v>-0.952380952380952</v>
+        <v>0.76923076923076905</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6190476190476186E-2</v>
+        <v>1.3076923076923073E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -6036,26 +5947,26 @@
         <v>1.59</v>
       </c>
       <c r="C25" s="8">
-        <v>3.8681948424068699</v>
+        <v>4.2068965517241299</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="0"/>
-        <v>6.1504297994269236E-2</v>
+        <v>6.6889655172413673E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="4">
         <v>0.99</v>
       </c>
       <c r="C26" s="14">
-        <v>2.62008733624454</v>
+        <v>5.60283687943262</v>
       </c>
       <c r="D26" s="7">
         <f t="shared" si="0"/>
-        <v>2.5938864628820949E-2</v>
+        <v>5.5468085106382937E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -6066,57 +5977,57 @@
         <v>0.95</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.7628205128205101</v>
+        <v>5.7096247960848201</v>
       </c>
       <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v>-1.6746794871794847E-2</v>
+        <v>5.4241435562805786E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="4">
         <v>0.91</v>
       </c>
       <c r="C28" s="8">
-        <v>-3.7932930181418301</v>
+        <v>-2.7428571428571402</v>
       </c>
       <c r="D28" s="7">
         <f t="shared" si="0"/>
-        <v>-3.4518966465090652E-2</v>
+        <v>-2.4959999999999979E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" s="4">
         <v>0.91</v>
       </c>
       <c r="C29" s="14">
-        <v>-2.49433106575963</v>
+        <v>-1.86046511627906</v>
       </c>
       <c r="D29" s="7">
         <f t="shared" si="0"/>
-        <v>-2.2698412698412634E-2</v>
+        <v>-1.6930232558139448E-2</v>
       </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B30" s="4">
         <v>0.05</v>
       </c>
       <c r="C30" s="8">
-        <v>4.6025104602510396</v>
+        <v>2</v>
       </c>
       <c r="D30" s="7">
         <f t="shared" si="0"/>
-        <v>2.3012552301255196E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="E30" s="17"/>
     </row>
@@ -6131,7 +6042,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D25+D26+D27+D28+D29+D30</f>
-        <v>2.2278389278838651</v>
+        <v>0.63248358013294526</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6241,11 +6152,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
@@ -6256,6 +6162,11 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
+++ b/app/fonlar/etki-analizi/_data/fon-etki-verileri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeler\hoca-ile-borsa\app\fonlar\etki-analizi\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6566B9FD-169C-4F31-B0A0-6B705A318CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC0EDB7-5F43-4501-B114-6849E8E0245A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18975" yWindow="1350" windowWidth="12270" windowHeight="19485" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15765" yWindow="75" windowWidth="12525" windowHeight="20115" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TLY" sheetId="1" r:id="rId1"/>
@@ -843,11 +843,11 @@
         <v>31.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-1.1235955056179701</v>
+        <v>-0.45454545454545398</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>-0.35786516853932349</v>
+        <v>-0.14477272727272711</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -858,11 +858,11 @@
         <v>13.91</v>
       </c>
       <c r="C3" s="3">
-        <v>1.0582010582010499</v>
+        <v>4.7643979057591599</v>
       </c>
       <c r="D3" s="7">
         <f>B3*C3/100</f>
-        <v>0.14719576719576605</v>
+        <v>0.66272774869109907</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -873,11 +873,11 @@
         <v>8.77</v>
       </c>
       <c r="C4" s="3">
-        <v>0.48971596474044998</v>
+        <v>0.19493177387914201</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" ref="D4:D20" si="0">B4*C4/100</f>
-        <v>4.2948090107737459E-2</v>
+        <v>1.7095516569200754E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -888,11 +888,11 @@
         <v>7.16</v>
       </c>
       <c r="C5" s="3">
-        <v>0.65359477124182996</v>
+        <v>0.129870129870129</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>4.6797385620915025E-2</v>
+        <v>9.2987012987012369E-3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -903,11 +903,11 @@
         <v>2.91</v>
       </c>
       <c r="C6" s="3">
-        <v>0.168350168350168</v>
+        <v>5.6022408963585402E-2</v>
       </c>
       <c r="D6" s="7">
         <f t="shared" si="0"/>
-        <v>4.8989898989898889E-3</v>
+        <v>1.6302521008403354E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -918,11 +918,11 @@
         <v>4.21</v>
       </c>
       <c r="C7" s="3">
-        <v>3.91705069124423</v>
+        <v>0.22172949002217199</v>
       </c>
       <c r="D7" s="7">
         <f t="shared" si="0"/>
-        <v>0.16490783410138207</v>
+        <v>9.334811529933441E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -933,11 +933,11 @@
         <v>2.04</v>
       </c>
       <c r="C8" s="3">
-        <v>0.65264684554024599</v>
+        <v>0.50432276657060504</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>1.3313995649021018E-2</v>
+        <v>1.0288184438040342E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -948,11 +948,11 @@
         <v>1.6</v>
       </c>
       <c r="C9" s="3">
-        <v>0.11764705882352899</v>
+        <v>-0.11750881316098701</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" si="0"/>
-        <v>1.8823529411764639E-3</v>
+        <v>-1.8801410105757921E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -963,11 +963,11 @@
         <v>1.6</v>
       </c>
       <c r="C10" s="3">
-        <v>1.82555780933062</v>
+        <v>3.5856573705179202</v>
       </c>
       <c r="D10" s="7">
         <f t="shared" si="0"/>
-        <v>2.9208924949289922E-2</v>
+        <v>5.7370517928286728E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -978,11 +978,11 @@
         <v>1.7</v>
       </c>
       <c r="C11" s="3">
-        <v>5.07936507936508</v>
+        <v>0.45317220543806602</v>
       </c>
       <c r="D11" s="7">
         <f t="shared" si="0"/>
-        <v>8.6349206349206356E-2</v>
+        <v>7.7039274924471223E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -993,11 +993,11 @@
         <v>0.3</v>
       </c>
       <c r="C12" s="3">
-        <v>-9.9715099715099704</v>
+        <v>10</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="0"/>
-        <v>-2.9914529914529909E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1008,11 +1008,11 @@
         <v>0.5</v>
       </c>
       <c r="C13" s="3">
-        <v>-0.97213220998055705</v>
+        <v>-0.32722513089005201</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="0"/>
-        <v>-4.8606610499027855E-3</v>
+        <v>-1.63612565445026E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1023,11 +1023,11 @@
         <v>0.2</v>
       </c>
       <c r="C14" s="3">
-        <v>5.7096247960848201</v>
+        <v>-0.20576131687242799</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="0"/>
-        <v>1.1419249592169641E-2</v>
+        <v>-4.1152263374485601E-4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1038,11 +1038,11 @@
         <v>0.3</v>
       </c>
       <c r="C15" s="3">
-        <v>4.0148239654107396</v>
+        <v>-0.178147268408551</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="0"/>
-        <v>1.2044471896232218E-2</v>
+        <v>-5.3444180522565295E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1053,11 +1053,11 @@
         <v>0.2</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.50425114453891</v>
+        <v>0.26560424966799401</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="0"/>
-        <v>-3.00850228907782E-3</v>
+        <v>5.3120849933598806E-4</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1068,11 +1068,11 @@
         <v>0.1</v>
       </c>
       <c r="C17" s="3">
-        <v>-0.23121387283236899</v>
+        <v>-0.81112398609501701</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="0"/>
-        <v>-2.3121387283236899E-4</v>
+        <v>-8.1112398609501702E-4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1083,11 +1083,11 @@
         <v>0.1</v>
       </c>
       <c r="C18" s="3">
-        <v>8.7768440709617099</v>
+        <v>-9.9570815450643693</v>
       </c>
       <c r="D18" s="7">
         <f t="shared" si="0"/>
-        <v>8.7768440709617094E-3</v>
+        <v>-9.9570815450643699E-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1098,11 +1098,11 @@
         <v>4.41</v>
       </c>
       <c r="C19" s="3">
-        <v>0.59</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>2.6019E-2</v>
+        <v>1.2789E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1113,11 +1113,11 @@
         <v>0.01</v>
       </c>
       <c r="C20" s="3">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="0"/>
-        <v>1.17E-4</v>
+        <v>9.3000000000000011E-5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1131,7 +1131,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20</f>
-        <v>0.19999903670718147</v>
+        <v>0.65885970464000188</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1349,11 +1349,11 @@
         <v>15.5</v>
       </c>
       <c r="C2" s="27">
-        <v>2.1943573667711598</v>
+        <v>-7.6687116564417099</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2/100</f>
-        <v>0.34012539184952978</v>
+        <v>-1.1886503067484651</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1364,11 +1364,11 @@
         <v>11.91</v>
       </c>
       <c r="C3" s="27">
-        <v>9.0322580645161299</v>
+        <v>-2.9585798816567999</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D26" si="0">B3*C3/100</f>
-        <v>1.0757419354838711</v>
+        <v>-0.35236686390532485</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1379,11 +1379,11 @@
         <v>10.17</v>
       </c>
       <c r="C4" s="27">
-        <v>-9.9703264094955397</v>
+        <v>8.8332234673698</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-1.0139821958456965</v>
+        <v>0.89833882663150855</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1394,11 +1394,11 @@
         <v>9.48</v>
       </c>
       <c r="C5" s="27">
-        <v>5.1625239005736097</v>
+        <v>-3.63636363636363</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.48940726577437821</v>
+        <v>-0.3447272727272721</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1409,11 +1409,11 @@
         <v>8</v>
       </c>
       <c r="C6" s="27">
-        <v>-9.9715099715099704</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>-0.79772079772079763</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,11 +1424,11 @@
         <v>5.28</v>
       </c>
       <c r="C7" s="27">
-        <v>1.0582010582010499</v>
+        <v>4.7643979057591599</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5873015873015436E-2</v>
+        <v>0.25156020942408364</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1439,11 +1439,11 @@
         <v>5.08</v>
       </c>
       <c r="C8" s="27">
-        <v>2.9236276849641998</v>
+        <v>-2.1449275362318798</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.14852028639618134</v>
+        <v>-0.10896231884057948</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,11 +1454,11 @@
         <v>2.82</v>
       </c>
       <c r="C9" s="27">
-        <v>-1.47058823529411</v>
+        <v>-4.8507462686567102</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>-4.1470588235293898E-2</v>
+        <v>-0.13679104477611922</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,11 +1469,11 @@
         <v>2.75</v>
       </c>
       <c r="C10" s="27">
-        <v>0.65264684554024599</v>
+        <v>0.50432276657060504</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>1.7947788252356763E-2</v>
+        <v>1.386887608069164E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,11 +1484,11 @@
         <v>1.89</v>
       </c>
       <c r="C11" s="27">
-        <v>0.23419203747072601</v>
+        <v>4.2056074766355103</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>4.4262295081967211E-3</v>
+        <v>7.9485981308411141E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,11 +1499,11 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="C12" s="27">
-        <v>0.40355125100887801</v>
+        <v>-3.5369774919614101</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>4.4794188861985466E-3</v>
+        <v>-3.9260450160771655E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1514,11 +1514,11 @@
         <v>1.07</v>
       </c>
       <c r="C13" s="27">
-        <v>8.7768440709617099</v>
+        <v>-9.9570815450643693</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>9.3912231559290293E-2</v>
+        <v>-0.10654077253218876</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1529,11 +1529,11 @@
         <v>1.01</v>
       </c>
       <c r="C14" s="27">
-        <v>0.65359477124182996</v>
+        <v>0.129870129870129</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>6.6013071895424822E-3</v>
+        <v>1.3116883116883029E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1544,11 +1544,11 @@
         <v>0.66</v>
       </c>
       <c r="C15" s="27">
-        <v>0.11764705882352899</v>
+        <v>-0.11750881316098701</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>7.7647058823529134E-4</v>
+        <v>-7.7555816686251434E-4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1559,11 +1559,11 @@
         <v>0.53</v>
       </c>
       <c r="C16" s="27">
-        <v>-0.23121387283236899</v>
+        <v>-0.81112398609501701</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-1.2254335260115559E-3</v>
+        <v>-4.2989571263035899E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1574,11 +1574,11 @@
         <v>0.38</v>
       </c>
       <c r="C17" s="27">
-        <v>-1.8539976825028901</v>
+        <v>1.06257378984651</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>-7.0451911935109825E-3</v>
+        <v>4.0377804014167379E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1589,11 +1589,11 @@
         <v>0.13</v>
       </c>
       <c r="C18" s="27">
-        <v>-1.68539325842696</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>-2.1910112359550481E-3</v>
+        <v>7.4285714285714233E-4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1604,11 +1604,11 @@
         <v>0.13</v>
       </c>
       <c r="C19" s="27">
-        <v>3.91705069124423</v>
+        <v>0.22172949002217199</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>5.092165898617499E-3</v>
+        <v>2.8824833702882359E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,11 +1619,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C20" s="27">
-        <v>0.96463022508038498</v>
+        <v>-1.11464968152866</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>6.7524115755626961E-4</v>
+        <v>-7.8025477707006202E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,11 +1634,11 @@
         <v>0.04</v>
       </c>
       <c r="C21" s="27">
-        <v>-1.8295218295218201</v>
+        <v>3.9813638288860602</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>-7.3180873180872812E-4</v>
+        <v>1.5925455315544241E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1649,11 +1649,11 @@
         <v>0.04</v>
       </c>
       <c r="C22" s="27">
-        <v>1.3043478260869501</v>
+        <v>1.00143061516452</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>5.2173913043478007E-4</v>
+        <v>4.00572246065808E-4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,11 +1664,11 @@
         <v>9.73</v>
       </c>
       <c r="C23" s="27">
-        <v>-0.37</v>
+        <v>5.39</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6001000000000005E-2</v>
+        <v>0.524447</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,11 +1679,11 @@
         <v>9.19</v>
       </c>
       <c r="C24" s="27">
-        <v>-1.5</v>
+        <v>5.25</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-0.13785</v>
+        <v>0.48247499999999993</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,11 +1709,11 @@
         <v>0.02</v>
       </c>
       <c r="C26" s="3">
-        <v>-0.76</v>
+        <v>-0.45</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-1.5200000000000001E-4</v>
+        <v>-9.0000000000000006E-5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D27" s="6">
         <f>SUM(D2:D26)</f>
-        <v>0.20788846105833014</v>
+        <v>0.77746378565434893</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2069,6 +2069,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B78:C78"/>
     <mergeCell ref="B79:C79"/>
     <mergeCell ref="B80:C80"/>
@@ -2078,26 +2098,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2137,11 +2137,11 @@
         <v>15.85</v>
       </c>
       <c r="C2" s="3">
-        <v>-9.9715099715099704</v>
+        <v>10</v>
       </c>
       <c r="D2" s="29">
         <f>B2*C2/100</f>
-        <v>-1.5804843304843303</v>
+        <v>1.585</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,11 +2152,11 @@
         <v>14.37</v>
       </c>
       <c r="C3" s="3">
-        <v>2.1943573667711598</v>
+        <v>-7.6687116564417099</v>
       </c>
       <c r="D3" s="29">
         <f t="shared" ref="D3:D21" si="0">B3*C3/100</f>
-        <v>0.31532915360501568</v>
+        <v>-1.1019938650306735</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,11 +2167,11 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="C4" s="3">
-        <v>-9.9703264094955397</v>
+        <v>8.8332234673698</v>
       </c>
       <c r="D4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.99204747774480606</v>
+        <v>0.87890573500329505</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2182,11 +2182,11 @@
         <v>9.31</v>
       </c>
       <c r="C5" s="3">
-        <v>5.1625239005736097</v>
+        <v>-3.63636363636363</v>
       </c>
       <c r="D5" s="29">
         <f t="shared" si="0"/>
-        <v>0.48063097514340308</v>
+        <v>-0.33854545454545393</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2197,11 +2197,11 @@
         <v>7.94</v>
       </c>
       <c r="C6" s="3">
-        <v>9.0322580645161299</v>
+        <v>-2.9585798816567999</v>
       </c>
       <c r="D6" s="29">
         <f t="shared" si="0"/>
-        <v>0.7171612903225808</v>
+        <v>-0.23491124260354992</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2212,11 +2212,11 @@
         <v>3.39</v>
       </c>
       <c r="C7" s="3">
-        <v>1.0582010582010499</v>
+        <v>4.7643979057591599</v>
       </c>
       <c r="D7" s="29">
         <f t="shared" si="0"/>
-        <v>3.5873015873015592E-2</v>
+        <v>0.16151308900523553</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,11 +2227,11 @@
         <v>5.47</v>
       </c>
       <c r="C8" s="3">
-        <v>-1.47058823529411</v>
+        <v>-4.8507462686567102</v>
       </c>
       <c r="D8" s="29">
         <f t="shared" si="0"/>
-        <v>-8.0441176470587822E-2</v>
+        <v>-0.26533582089552205</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2242,11 +2242,11 @@
         <v>5.29</v>
       </c>
       <c r="C9" s="3">
-        <v>0.65264684554024599</v>
+        <v>0.50432276657060504</v>
       </c>
       <c r="D9" s="29">
         <f t="shared" si="0"/>
-        <v>3.4525018129079016E-2</v>
+        <v>2.6678674351585007E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2257,11 +2257,11 @@
         <v>3.04</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9236276849641998</v>
+        <v>-2.1449275362318798</v>
       </c>
       <c r="D10" s="29">
         <f t="shared" si="0"/>
-        <v>8.8878281622911684E-2</v>
+        <v>-6.5205797101449151E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2272,11 +2272,11 @@
         <v>2.08</v>
       </c>
       <c r="C11" s="3">
-        <v>8.7768440709617099</v>
+        <v>-9.9570815450643693</v>
       </c>
       <c r="D11" s="29">
         <f t="shared" si="0"/>
-        <v>0.18255835667600359</v>
+        <v>-0.20710729613733889</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2287,11 +2287,11 @@
         <v>1.81</v>
       </c>
       <c r="C12" s="3">
-        <v>0.40355125100887801</v>
+        <v>-3.5369774919614101</v>
       </c>
       <c r="D12" s="29">
         <f t="shared" si="0"/>
-        <v>7.3042776432606926E-3</v>
+        <v>-6.4019292604501524E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,11 +2302,11 @@
         <v>1.39</v>
       </c>
       <c r="C13" s="3">
-        <v>0.23419203747072601</v>
+        <v>4.2056074766355103</v>
       </c>
       <c r="D13" s="29">
         <f t="shared" si="0"/>
-        <v>3.2552693208430911E-3</v>
+        <v>5.8457943925233583E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2317,11 +2317,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C14" s="3">
-        <v>-0.23121387283236899</v>
+        <v>-0.81112398609501701</v>
       </c>
       <c r="D14" s="29">
         <f t="shared" si="0"/>
-        <v>-1.3179190751445031E-3</v>
+        <v>-4.6234067207415967E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2332,11 +2332,11 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="C15" s="3">
-        <v>-0.99502487562189001</v>
+        <v>4.8576214405360103</v>
       </c>
       <c r="D15" s="29">
         <f t="shared" si="0"/>
-        <v>-1.3930348258706462E-3</v>
+        <v>6.8006700167504153E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,11 +2347,11 @@
         <v>0.11</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.50425114453891</v>
+        <v>0.26560424966799401</v>
       </c>
       <c r="D16" s="29">
         <f t="shared" si="0"/>
-        <v>-1.6546762589928011E-3</v>
+        <v>2.9216467463479343E-4</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,11 +2362,11 @@
         <v>8.98</v>
       </c>
       <c r="C17" s="3">
-        <v>-1.5</v>
+        <v>5.25</v>
       </c>
       <c r="D17" s="29">
         <f t="shared" si="0"/>
-        <v>-0.13470000000000001</v>
+        <v>0.47145000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2377,11 +2377,11 @@
         <v>8.66</v>
       </c>
       <c r="C18" s="3">
-        <v>-0.37</v>
+        <v>5.39</v>
       </c>
       <c r="D18" s="29">
         <f t="shared" si="0"/>
-        <v>-3.2042000000000001E-2</v>
+        <v>0.46677399999999997</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2392,11 +2392,11 @@
         <v>0.69</v>
       </c>
       <c r="C19" s="3">
-        <v>5.76</v>
+        <v>-2.68</v>
       </c>
       <c r="D19" s="29">
         <f t="shared" si="0"/>
-        <v>3.9743999999999995E-2</v>
+        <v>-1.8491999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2407,11 +2407,11 @@
         <v>0.09</v>
       </c>
       <c r="C20" s="3">
-        <v>-0.49</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="D20" s="29">
         <f t="shared" si="0"/>
-        <v>-4.4099999999999999E-4</v>
+        <v>-5.04E-4</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,11 +2422,11 @@
         <v>0.01</v>
       </c>
       <c r="C21" s="3">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="D21" s="29">
         <f t="shared" si="0"/>
-        <v>1.3000000000000001E-5</v>
+        <v>3.8999999999999999E-5</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D22" s="6">
         <f>SUM(D2:D21)</f>
-        <v>-0.91924897652361903</v>
+        <v>1.3551731013375037</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3370,6 +3370,97 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
     <mergeCell ref="B152:C152"/>
     <mergeCell ref="B153:C153"/>
     <mergeCell ref="B154:C154"/>
@@ -3383,97 +3474,6 @@
     <mergeCell ref="B144:C144"/>
     <mergeCell ref="B145:C145"/>
     <mergeCell ref="B146:C146"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -3514,11 +3514,11 @@
         <v>41.32</v>
       </c>
       <c r="C2" s="8">
-        <v>-0.77777777777777701</v>
+        <v>1.8477043673012301</v>
       </c>
       <c r="D2" s="29">
         <f>B2*C2/100</f>
-        <v>-0.32137777777777748</v>
+        <v>0.76347144456886828</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3529,11 +3529,11 @@
         <v>3.28</v>
       </c>
       <c r="C3" s="8">
-        <v>9.8930481283422402</v>
+        <v>-1.8248175182481701</v>
       </c>
       <c r="D3" s="29">
         <f t="shared" ref="D3:D9" si="0">B3*C3/100</f>
-        <v>0.32449197860962548</v>
+        <v>-5.9854014598539972E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3544,11 +3544,11 @@
         <v>0.19</v>
       </c>
       <c r="C4" s="8">
-        <v>-8.0980066445182697</v>
+        <v>6.1906913691821002</v>
       </c>
       <c r="D4" s="29">
         <f t="shared" si="0"/>
-        <v>-1.5386212624584712E-2</v>
+        <v>1.176231360144599E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3559,11 +3559,11 @@
         <v>22.96</v>
       </c>
       <c r="C5" s="4">
-        <v>0.33</v>
+        <v>-1.05</v>
       </c>
       <c r="D5" s="29">
         <f t="shared" si="0"/>
-        <v>7.5768000000000002E-2</v>
+        <v>-0.24108000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3574,11 +3574,11 @@
         <v>5.29</v>
       </c>
       <c r="C6" s="4">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="D6" s="29">
         <f t="shared" si="0"/>
-        <v>6.3480000000000003E-3</v>
+        <v>2.0102000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3589,11 +3589,11 @@
         <v>1.07</v>
       </c>
       <c r="C7" s="4">
-        <v>-9.89</v>
+        <v>-8.0299999999999994</v>
       </c>
       <c r="D7" s="29">
         <f t="shared" si="0"/>
-        <v>-0.10582300000000001</v>
+        <v>-8.5920999999999997E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3604,11 +3604,11 @@
         <v>0.13</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1</v>
+        <v>0.32</v>
       </c>
       <c r="D8" s="29">
         <f t="shared" si="0"/>
-        <v>1.3000000000000002E-4</v>
+        <v>4.1600000000000003E-4</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3619,11 +3619,11 @@
         <v>0.03</v>
       </c>
       <c r="C9" s="4">
-        <v>0.47</v>
+        <v>0.17</v>
       </c>
       <c r="D9" s="29">
         <f t="shared" si="0"/>
-        <v>1.4099999999999998E-4</v>
+        <v>5.1000000000000006E-5</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -3638,7 +3638,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="6">
         <f>D2+D3+D4+D5+D6+D7+D8+D9</f>
-        <v>-3.5708011792736728E-2</v>
+        <v>0.40894774357177427</v>
       </c>
       <c r="E10" s="17"/>
     </row>
@@ -4538,6 +4538,106 @@
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
     <mergeCell ref="B135:C135"/>
@@ -4550,106 +4650,6 @@
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="B133:C133"/>
     <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4689,11 +4689,11 @@
         <v>8.27</v>
       </c>
       <c r="C2" s="3">
-        <v>1.0582010582010499</v>
+        <v>4.7643979057591599</v>
       </c>
       <c r="D2" s="7">
         <f>B2*C2/100</f>
-        <v>8.7513227513226821E-2</v>
+        <v>0.39401570680628256</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4704,11 +4704,11 @@
         <v>8.11</v>
       </c>
       <c r="C3" s="3">
-        <v>-1.1235955056179701</v>
+        <v>-0.45454545454545398</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" ref="D3:D49" si="0">B3*C3/100</f>
-        <v>-9.1123595505617369E-2</v>
+        <v>-3.6863636363636314E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4719,11 +4719,11 @@
         <v>6.92</v>
       </c>
       <c r="C4" s="3">
-        <v>0.168350168350168</v>
+        <v>5.6022408963585402E-2</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="0"/>
-        <v>1.1649831649831625E-2</v>
+        <v>3.8767507002801099E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4734,11 +4734,11 @@
         <v>6.9</v>
       </c>
       <c r="C5" s="3">
-        <v>0.65359477124182996</v>
+        <v>0.129870129870129</v>
       </c>
       <c r="D5" s="7">
         <f t="shared" si="0"/>
-        <v>4.50980392